--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF14"/>
+  <dimension ref="A1:BF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,2290 +710,2114 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6721666666666666</v>
+        <v>0.5418181818181819</v>
       </c>
       <c r="C2" t="n">
-        <v>100218.4308867928</v>
+        <v>100517.2856282267</v>
       </c>
       <c r="D2" t="n">
         <v>288</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>297.6484864069328</v>
+        <v>305.9804795300442</v>
       </c>
       <c r="G2" t="n">
-        <v>11812.889983149</v>
+        <v>23620.75115897785</v>
       </c>
       <c r="H2" t="n">
-        <v>11694.76108331751</v>
+        <v>23384.54364738807</v>
       </c>
       <c r="I2" t="n">
-        <v>9011.633448421931</v>
+        <v>20369.84345329015</v>
       </c>
       <c r="J2" t="n">
-        <v>11.62501101721422</v>
+        <v>23.24507320813924</v>
       </c>
       <c r="K2" t="n">
-        <v>299.6250110172142</v>
+        <v>311.2450732081392</v>
       </c>
       <c r="L2" t="n">
-        <v>299.6250110172142</v>
+        <v>311.2450732081392</v>
       </c>
       <c r="M2" t="n">
-        <v>1.113161849170437</v>
+        <v>1.268466410091626</v>
       </c>
       <c r="N2" t="n">
-        <v>111559.3338469019</v>
+        <v>127502.8004529913</v>
       </c>
       <c r="O2" t="n">
-        <v>111559.3338469019</v>
+        <v>127502.8004529913</v>
       </c>
       <c r="P2" t="n">
         <v>310.7513475433373</v>
       </c>
       <c r="Q2" t="n">
-        <v>316.9609852869465</v>
+        <v>323.048716212724</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7615773105863909</v>
+        <v>0.73824115301167</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2932490044721779</v>
+        <v>0.1982457778753087</v>
       </c>
       <c r="T2" t="n">
-        <v>1.174080662328612</v>
+        <v>1.230553318308278</v>
       </c>
       <c r="U2" t="n">
-        <v>208.3539404848529</v>
+        <v>171.3490685368248</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7269424101347626</v>
+        <v>0.5849346974729742</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9106507829657974</v>
+        <v>0.7967300817567868</v>
       </c>
       <c r="X2" t="n">
-        <v>0.293001127744622</v>
+        <v>0.3266962403031563</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6721666666666666</v>
+        <v>0.5418181818181819</v>
       </c>
       <c r="Z2" t="n">
-        <v>200.0693909465266</v>
+        <v>165.785787090824</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6843624155051158</v>
+        <v>0.5443997693216462</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8810437960869254</v>
+        <v>0.7566082495275177</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2774968987469673</v>
+        <v>0.2819423445402975</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4374475173572833</v>
+        <v>0.4717432063264572</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7732538757837157</v>
+        <v>0.7860798739157199</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2995217868300289</v>
+        <v>0.2295725970538642</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.151602100275277</v>
+        <v>1.170020681986013</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.6910439251322914</v>
+        <v>0.5573570009293095</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2759585643602346</v>
+        <v>0.277118611545255</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1226195266860898</v>
+        <v>0.1196138735180367</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4425416509539824</v>
+        <v>0.4856368358667906</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.7674155931850533</v>
+        <v>0.762160513463695</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4647653957116505</v>
+        <v>0.5230483622799569</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9811521435425956</v>
+        <v>0.8035822579389086</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6860833333333333</v>
+        <v>0.550909090909091</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.155345257978446</v>
+        <v>1.161300470204773</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9753871839595102</v>
+        <v>0.8113344619355042</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1741931144358506</v>
+        <v>0.3577182122658643</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1762149163157664</v>
+        <v>0.3586862200505089</v>
       </c>
       <c r="AT2" t="n">
-        <v>250.6849558258153</v>
+        <v>238.0353119932859</v>
       </c>
       <c r="AU2" t="n">
-        <v>204.2116657156898</v>
+        <v>168.5674278138244</v>
       </c>
       <c r="AV2" t="n">
-        <v>246.6565457577842</v>
+        <v>232.4405470654187</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9119257887245771</v>
+        <v>0.9429752332820334</v>
       </c>
       <c r="AX2" t="n">
-        <v>262.6346271526782</v>
+        <v>271.5768671852256</v>
       </c>
       <c r="AY2" t="n">
-        <v>296.7513950839878</v>
+        <v>301.7610371920241</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.8447642032310091</v>
+        <v>0.7888205654655587</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.7781921347022716</v>
+        <v>0.7195216554036982</v>
       </c>
       <c r="BB2" t="n">
-        <v>299.6250110172142</v>
+        <v>311.2450732081392</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.8990695002479203</v>
+        <v>0.9137147645675203</v>
       </c>
       <c r="BD2" t="n">
-        <v>659.8326245065829</v>
+        <v>670.5808738798845</v>
       </c>
       <c r="BE2" t="n">
-        <v>470.3635604477214</v>
+        <v>474.179045310867</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5243955240133847</v>
+        <v>0.4901957380108035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6721666666666666</v>
+        <v>0.5418181818181819</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6443333333333333</v>
+        <v>0.5236363636363637</v>
       </c>
       <c r="C3" t="n">
-        <v>246143.2575260414</v>
+        <v>259696.1733742018</v>
       </c>
       <c r="D3" t="n">
-        <v>325.1588448135019</v>
+        <v>328.5369216147293</v>
       </c>
       <c r="E3" t="n">
-        <v>0.442011222595712</v>
+        <v>0.3555048108407364</v>
       </c>
       <c r="F3" t="n">
-        <v>297.4822304909237</v>
+        <v>305.7898521926682</v>
       </c>
       <c r="G3" t="n">
-        <v>14204.40481079624</v>
+        <v>24818.60857907457</v>
       </c>
       <c r="H3" t="n">
-        <v>13920.31671458031</v>
+        <v>24322.23640749308</v>
       </c>
       <c r="I3" t="n">
-        <v>11092.2245090369</v>
+        <v>21347.1618619938</v>
       </c>
       <c r="J3" t="n">
-        <v>13.78249179661417</v>
+        <v>24.08142218563671</v>
       </c>
       <c r="K3" t="n">
-        <v>338.9413366101161</v>
+        <v>352.618343800366</v>
       </c>
       <c r="L3" t="n">
-        <v>338.9413366101161</v>
+        <v>352.618343800366</v>
       </c>
       <c r="M3" t="n">
-        <v>1.123289797933352</v>
+        <v>1.243860030596722</v>
       </c>
       <c r="N3" t="n">
-        <v>276490.2100090841</v>
+        <v>323025.6901590863</v>
       </c>
       <c r="O3" t="n">
-        <v>276490.2100090841</v>
+        <v>323025.6901590863</v>
       </c>
       <c r="P3" t="n">
-        <v>330.1904914832758</v>
+        <v>331.9012350344884</v>
       </c>
       <c r="Q3" t="n">
-        <v>337.1157518796354</v>
+        <v>343.8501573014948</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7731021668901711</v>
+        <v>0.7504610817793644</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2827423012403118</v>
+        <v>0.1983935480548724</v>
       </c>
       <c r="T3" t="n">
-        <v>1.172621754008351</v>
+        <v>1.219795944224634</v>
       </c>
       <c r="U3" t="n">
-        <v>199.9576392616492</v>
+        <v>165.6825017334821</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6569778396427248</v>
+        <v>0.5316045280079817</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8598998937581854</v>
+        <v>0.743292007914666</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1343230154919619</v>
+        <v>0.1453279602294961</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6443333333333333</v>
+        <v>0.5236363636363637</v>
       </c>
       <c r="Z3" t="n">
-        <v>191.6777171796518</v>
+        <v>160.1226862390699</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6168362177197966</v>
+        <v>0.4959119073079256</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.826021917245764</v>
+        <v>0.7045594399148103</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1270952810443449</v>
+        <v>0.1276967514859966</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7934973681907749</v>
+        <v>0.8049069210010069</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9062782802759544</v>
+        <v>0.9138281442189199</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3624287257396914</v>
+        <v>0.3076527576199941</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.058417211055684</v>
+        <v>1.039595433301365</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6523565444133773</v>
+        <v>0.5401021988561153</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1226195266860898</v>
+        <v>0.1196138735180367</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08562308417067097</v>
+        <v>0.08466626388688835</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8016736509327737</v>
+        <v>0.8186352999554748</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8396902235830628</v>
+        <v>0.8321446129991421</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4514739650918165</v>
+        <v>0.4978764413086157</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9405309585052282</v>
+        <v>0.7760287641598343</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.65825</v>
+        <v>0.5327272727272727</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.037932668457427</v>
+        <v>1.010425779831437</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9696166277691937</v>
+        <v>0.8192012206450174</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.09740170995219888</v>
+        <v>0.2343970156716023</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.08880058328649054</v>
+        <v>0.2203942126563476</v>
       </c>
       <c r="AT3" t="n">
-        <v>247.5117991946897</v>
+        <v>236.5370003654726</v>
       </c>
       <c r="AU3" t="n">
-        <v>195.8176782206505</v>
+        <v>162.902593986276</v>
       </c>
       <c r="AV3" t="n">
-        <v>237.4500487211659</v>
+        <v>222.9707754433835</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9280633530363964</v>
+        <v>0.9528994376335685</v>
       </c>
       <c r="AX3" t="n">
-        <v>301.7680077870598</v>
+        <v>313.0626478485393</v>
       </c>
       <c r="AY3" t="n">
-        <v>318.0924598461918</v>
+        <v>323.9905952703184</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.7781127516017506</v>
+        <v>0.7300736620707161</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.7043576201860351</v>
+        <v>0.6484533181349638</v>
       </c>
       <c r="BB3" t="n">
-        <v>338.9413366101161</v>
+        <v>352.618343800366</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.9173133904809776</v>
+        <v>0.9299180490332926</v>
       </c>
       <c r="BD3" t="n">
-        <v>673.2219275252803</v>
+        <v>682.4725638012188</v>
       </c>
       <c r="BE3" t="n">
-        <v>475.1118945040489</v>
+        <v>478.3649763962122</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.4997771082305378</v>
+        <v>0.4661101594919127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6443333333333333</v>
+        <v>0.5236363636363637</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6164999999999999</v>
+        <v>0.5054545454545455</v>
       </c>
       <c r="C4" t="n">
-        <v>392068.0841652899</v>
+        <v>418875.0611201768</v>
       </c>
       <c r="D4" t="n">
-        <v>362.3176896270037</v>
+        <v>369.0738432294586</v>
       </c>
       <c r="E4" t="n">
-        <v>0.484022445191424</v>
+        <v>0.4110096216814729</v>
       </c>
       <c r="F4" t="n">
-        <v>297.3159745749147</v>
+        <v>305.5992248552921</v>
       </c>
       <c r="G4" t="n">
-        <v>16396.08656269553</v>
+        <v>25975.06100615904</v>
       </c>
       <c r="H4" t="n">
-        <v>15904.20396581466</v>
+        <v>25195.80917597427</v>
       </c>
       <c r="I4" t="n">
-        <v>13044.98382643853</v>
+        <v>22237.84207213622</v>
       </c>
       <c r="J4" t="n">
-        <v>15.66178887504014</v>
+        <v>24.7919761184167</v>
       </c>
       <c r="K4" t="n">
-        <v>377.9794785020439</v>
+        <v>393.8658193478753</v>
       </c>
       <c r="L4" t="n">
-        <v>377.9794785020439</v>
+        <v>393.8658193478753</v>
       </c>
       <c r="M4" t="n">
-        <v>1.129691903074519</v>
+        <v>1.223343120893016</v>
       </c>
       <c r="N4" t="n">
-        <v>442916.140135467</v>
+        <v>512427.92453501</v>
       </c>
       <c r="O4" t="n">
-        <v>442916.140135467</v>
+        <v>512427.92453501</v>
       </c>
       <c r="P4" t="n">
-        <v>348.5471579742609</v>
+        <v>351.7818352826613</v>
       </c>
       <c r="Q4" t="n">
-        <v>356.0007291309041</v>
+        <v>363.4050209165286</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7855818631591125</v>
+        <v>0.7645027498690725</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2747365065866861</v>
+        <v>0.2003470470202877</v>
       </c>
       <c r="T4" t="n">
-        <v>1.167749955007179</v>
+        <v>1.205373060144734</v>
       </c>
       <c r="U4" t="n">
-        <v>191.5705929511034</v>
+        <v>160.0228668333166</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5975037691519378</v>
+        <v>0.4870510726294947</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8085161418424881</v>
+        <v>0.6945920846964865</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09487005204389491</v>
+        <v>0.1027470521766324</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6164999999999999</v>
+        <v>0.5054545454545455</v>
       </c>
       <c r="Z4" t="n">
-        <v>183.2952983254349</v>
+        <v>154.4665172904931</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5597238197893952</v>
+        <v>0.4551025817895442</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7721493996791461</v>
+        <v>0.6575381057160141</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.08981436860973413</v>
+        <v>0.09165317272825486</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8592301749844373</v>
+        <v>0.8644452660815081</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9355453231892149</v>
+        <v>0.9398223441098341</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3666594076777121</v>
+        <v>0.3185571585810211</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.03425081694109</v>
+        <v>1.008438520508987</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.59905244559614</v>
+        <v>0.5024269220081136</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.08562308417067097</v>
+        <v>0.08466626388688835</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0696675211969156</v>
+        <v>0.06992016398876522</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8663083189502597</v>
+        <v>0.8755181762683212</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8605635931741638</v>
+        <v>0.8521625469894534</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.4663349114295255</v>
+        <v>0.5061224383844614</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.900444024849219</v>
+        <v>0.7481662181993752</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6304166666666666</v>
+        <v>0.5145454545454546</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.011948080468751</v>
+        <v>0.9787550326063221</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9339037741484145</v>
+        <v>0.7936504313645399</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1115040556195322</v>
+        <v>0.2305888144069469</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1003470427926759</v>
+        <v>0.2147880891444466</v>
       </c>
       <c r="AT4" t="n">
-        <v>244.4740913624744</v>
+        <v>235.2254025922055</v>
       </c>
       <c r="AU4" t="n">
-        <v>187.4329456382691</v>
+        <v>157.2446920619049</v>
       </c>
       <c r="AV4" t="n">
-        <v>233.140738673485</v>
+        <v>220.5649459315814</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.940498207641538</v>
+        <v>0.9604635421084098</v>
       </c>
       <c r="AX4" t="n">
-        <v>340.7591376910201</v>
+        <v>354.4819707677298</v>
       </c>
       <c r="AY4" t="n">
-        <v>338.0185481120807</v>
+        <v>344.7576029595573</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.7232564388194795</v>
+        <v>0.6822921396741443</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.6548883740846425</v>
+        <v>0.606939731804761</v>
       </c>
       <c r="BB4" t="n">
-        <v>377.9794785020439</v>
+        <v>393.8658193478753</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.9285202029147955</v>
+        <v>0.9386040269927941</v>
       </c>
       <c r="BD4" t="n">
-        <v>681.446675955207</v>
+        <v>688.8472563381627</v>
       </c>
       <c r="BE4" t="n">
-        <v>478.0053037862455</v>
+        <v>480.5938878618682</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.4877367192932673</v>
+        <v>0.4589424699362302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6164999999999999</v>
+        <v>0.5054545454545455</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5886666666666667</v>
+        <v>0.4872727272727273</v>
       </c>
       <c r="C5" t="n">
-        <v>537992.9108045385</v>
+        <v>578053.948866152</v>
       </c>
       <c r="D5" t="n">
-        <v>399.4765344405056</v>
+        <v>409.6107648441879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5260336677871359</v>
+        <v>0.4665144325222093</v>
       </c>
       <c r="F5" t="n">
-        <v>297.1497186589057</v>
+        <v>305.4085975179161</v>
       </c>
       <c r="G5" t="n">
-        <v>18434.80345716985</v>
+        <v>27087.57621864307</v>
       </c>
       <c r="H5" t="n">
-        <v>17697.41131888305</v>
+        <v>26004.07316989735</v>
       </c>
       <c r="I5" t="n">
-        <v>14874.55351718711</v>
+        <v>23034.00604192664</v>
       </c>
       <c r="J5" t="n">
-        <v>17.40230096293005</v>
+        <v>25.51536984632288</v>
       </c>
       <c r="K5" t="n">
-        <v>416.8788354034356</v>
+        <v>435.1261346905108</v>
       </c>
       <c r="L5" t="n">
-        <v>416.8788354034356</v>
+        <v>435.1261346905108</v>
       </c>
       <c r="M5" t="n">
-        <v>1.134122701316078</v>
+        <v>1.206809448427407</v>
       </c>
       <c r="N5" t="n">
-        <v>610149.9732905431</v>
+        <v>697600.9671924456</v>
       </c>
       <c r="O5" t="n">
-        <v>610149.9732905431</v>
+        <v>697600.9671924456</v>
       </c>
       <c r="P5" t="n">
-        <v>365.9842646862041</v>
+        <v>370.5974763166315</v>
       </c>
       <c r="Q5" t="n">
-        <v>373.8709316204885</v>
+        <v>381.9656960536225</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7989716577093292</v>
+        <v>0.7802678116363377</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2688306900680616</v>
+        <v>0.2040392326156507</v>
       </c>
       <c r="T5" t="n">
-        <v>1.159595588584208</v>
+        <v>1.187126089356396</v>
       </c>
       <c r="U5" t="n">
-        <v>183.1928015532153</v>
+        <v>154.3701638363285</v>
       </c>
       <c r="V5" t="n">
-        <v>0.546067661412585</v>
+        <v>0.4492023757970994</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7583214161141775</v>
+        <v>0.6505088932225696</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07767431522539926</v>
+        <v>0.08435414167126003</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5886666666666667</v>
+        <v>0.4872727272727273</v>
       </c>
       <c r="Z5" t="n">
-        <v>174.9221343838758</v>
+        <v>148.8172802450937</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5104151246580626</v>
+        <v>0.4201555832783126</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7205750330952487</v>
+        <v>0.6150913241916492</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07362931958543495</v>
+        <v>0.07619092557027551</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8862508256135369</v>
+        <v>0.8887648128115231</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.9478885488528848</v>
+        <v>0.9505773428354967</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3619351754531361</v>
+        <v>0.3195201412459455</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.019537248096724</v>
+        <v>0.9904023854256228</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5492270447061419</v>
+        <v>0.4659020134783136</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0696675211969156</v>
+        <v>0.06992016398876522</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.06133289317746405</v>
+        <v>0.06232707720632211</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8927403889669466</v>
+        <v>0.8984400755890104</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8734301032811069</v>
+        <v>0.8654225772359172</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.4849473428323655</v>
+        <v>0.5195295618364969</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8605710404830875</v>
+        <v>0.7200617488292373</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6025833333333332</v>
+        <v>0.4963636363636364</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9981591509554445</v>
+        <v>0.9621848532952615</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8931472086948627</v>
+        <v>0.762598609920323</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.137588110472357</v>
+        <v>0.2421231044660241</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1263900394018608</v>
+        <v>0.2278037755052997</v>
       </c>
       <c r="AT5" t="n">
-        <v>241.6106246066719</v>
+        <v>234.0959734517244</v>
       </c>
       <c r="AU5" t="n">
-        <v>179.0574679685456</v>
+        <v>151.5937220407111</v>
       </c>
       <c r="AV5" t="n">
-        <v>229.8411485803474</v>
+        <v>219.4457632791645</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9503016848598984</v>
+        <v>0.9663695375963736</v>
       </c>
       <c r="AX5" t="n">
-        <v>379.6232237408057</v>
+        <v>395.8353654169748</v>
       </c>
       <c r="AY5" t="n">
-        <v>356.7739717528343</v>
+        <v>364.3125005051455</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.6772092241472559</v>
+        <v>0.6425691490880314</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.6147606811370298</v>
+        <v>0.5745169410405836</v>
       </c>
       <c r="BB5" t="n">
-        <v>416.8788354034356</v>
+        <v>435.1261346905108</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.9370115508213226</v>
+        <v>0.9449883807428952</v>
       </c>
       <c r="BD5" t="n">
-        <v>687.6785283016799</v>
+        <v>693.5327727410057</v>
       </c>
       <c r="BE5" t="n">
-        <v>480.1860166014346</v>
+        <v>482.2256097513479</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4786502326891389</v>
+        <v>0.4550686625546874</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.5886666666666667</v>
+        <v>0.4872727272727273</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5608333333333333</v>
+        <v>0.4690909090909091</v>
       </c>
       <c r="C6" t="n">
-        <v>683917.737443787</v>
+        <v>737232.836612127</v>
       </c>
       <c r="D6" t="n">
-        <v>436.6353792540075</v>
+        <v>450.1476864589173</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5680448903828479</v>
+        <v>0.5220192433629457</v>
       </c>
       <c r="F6" t="n">
-        <v>296.9834627428966</v>
+        <v>305.21797018054</v>
       </c>
       <c r="G6" t="n">
-        <v>20352.94240210453</v>
+        <v>28151.30979167007</v>
       </c>
       <c r="H6" t="n">
-        <v>19335.29528199931</v>
+        <v>26743.74430208657</v>
       </c>
       <c r="I6" t="n">
-        <v>16578.14612092935</v>
+        <v>23726.42551768566</v>
       </c>
       <c r="J6" t="n">
-        <v>18.91174323742281</v>
+        <v>26.09085637024056</v>
       </c>
       <c r="K6" t="n">
-        <v>455.5471224914303</v>
+        <v>476.2385428291578</v>
       </c>
       <c r="L6" t="n">
-        <v>455.5471224914303</v>
+        <v>476.2385428291578</v>
       </c>
       <c r="M6" t="n">
-        <v>1.136122909736611</v>
+        <v>1.191842204148483</v>
       </c>
       <c r="N6" t="n">
-        <v>777014.6098851146</v>
+        <v>878665.2089584362</v>
       </c>
       <c r="O6" t="n">
-        <v>777014.6098851146</v>
+        <v>878665.2089584362</v>
       </c>
       <c r="P6" t="n">
-        <v>382.6275508426814</v>
+        <v>388.5029205420147</v>
       </c>
       <c r="Q6" t="n">
-        <v>390.8259845140502</v>
+        <v>399.6032825323343</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8132265974161389</v>
+        <v>0.7976540887004913</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2647333246898356</v>
+        <v>0.2094035625792643</v>
       </c>
       <c r="T6" t="n">
-        <v>1.148177885393446</v>
+        <v>1.164912553358657</v>
       </c>
       <c r="U6" t="n">
-        <v>174.8242650679852</v>
+        <v>148.7243927425177</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5009818693570599</v>
+        <v>0.4166666692465374</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7102005621563435</v>
+        <v>0.6107485176519148</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06855392439818238</v>
+        <v>0.07453709576394417</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5608333333333333</v>
+        <v>0.4690909090909091</v>
       </c>
       <c r="Z6" t="n">
-        <v>166.5582253549745</v>
+        <v>143.1749751028715</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4672821483494672</v>
+        <v>0.3899769279248844</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6718668036160703</v>
+        <v>0.5769219832901934</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0651496406683529</v>
+        <v>0.06809791262021865</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.9000837344981281</v>
+        <v>0.9012321802103712</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9542727387440068</v>
+        <v>0.9560681380102208</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.354396933542136</v>
+        <v>0.3172193443427873</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.00724250187934</v>
+        <v>0.9761933687383696</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5041269572133141</v>
+        <v>0.4325269708169439</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06133289317746405</v>
+        <v>0.06232707720632211</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.05666996572855271</v>
+        <v>0.05814606862117715</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9062410936500147</v>
+        <v>0.9100178948991395</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8837496680800728</v>
+        <v>0.8768611133553561</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5047236044273561</v>
+        <v>0.5351137485676776</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.8207113081684391</v>
+        <v>0.6917854419513849</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.57475</v>
+        <v>0.4781818181818182</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.9877978302091043</v>
+        <v>0.9502852782969918</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.8501782687194871</v>
+        <v>0.7292722521339844</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1670865220406652</v>
+        <v>0.2584998363456069</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1570642331598527</v>
+        <v>0.2469211166043852</v>
       </c>
       <c r="AT6" t="n">
-        <v>238.9514462356655</v>
+        <v>233.1420590789931</v>
       </c>
       <c r="AU6" t="n">
-        <v>170.6912452114798</v>
+        <v>145.9496839226946</v>
       </c>
       <c r="AV6" t="n">
-        <v>227.1648772145853</v>
+        <v>219.0360723987227</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9581695277625843</v>
+        <v>0.9710648144564994</v>
       </c>
       <c r="AX6" t="n">
-        <v>418.3707151442493</v>
+        <v>437.122579629251</v>
       </c>
       <c r="AY6" t="n">
-        <v>374.5393180800472</v>
+        <v>382.8409603865395</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.6379876149200346</v>
+        <v>0.6089788794897985</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.5812430243015705</v>
+        <v>0.548133816646011</v>
       </c>
       <c r="BB6" t="n">
-        <v>455.5471224914303</v>
+        <v>476.2385428291578</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.9436927577834606</v>
+        <v>0.9499248865081795</v>
       </c>
       <c r="BD6" t="n">
-        <v>692.5819070988514</v>
+        <v>697.1557046212456</v>
       </c>
       <c r="BE6" t="n">
-        <v>481.8949195107216</v>
+        <v>483.483513430917</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.4713991951714924</v>
+        <v>0.4530373142289574</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.5608333333333333</v>
+        <v>0.4690909090909091</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4509090909090909</v>
       </c>
       <c r="C7" t="n">
-        <v>829842.5640830356</v>
+        <v>896411.7243581021</v>
       </c>
       <c r="D7" t="n">
-        <v>473.7942240675094</v>
+        <v>490.6846080736466</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6100561129785599</v>
+        <v>0.5775240542036821</v>
       </c>
       <c r="F7" t="n">
-        <v>296.8172068268876</v>
+        <v>305.027342843164</v>
       </c>
       <c r="G7" t="n">
-        <v>22172.89458908636</v>
+        <v>29159.11959522752</v>
       </c>
       <c r="H7" t="n">
-        <v>20842.52091374118</v>
+        <v>27409.57241951387</v>
       </c>
       <c r="I7" t="n">
-        <v>18148.35300167006</v>
+        <v>24304.70465887271</v>
       </c>
       <c r="J7" t="n">
-        <v>20.25892064992346</v>
+        <v>26.57229180011015</v>
       </c>
       <c r="K7" t="n">
-        <v>494.0531447174329</v>
+        <v>517.2568998737568</v>
       </c>
       <c r="L7" t="n">
-        <v>494.0531447174329</v>
+        <v>517.2568998737568</v>
       </c>
       <c r="M7" t="n">
-        <v>1.136489207037134</v>
+        <v>1.17839881189298</v>
       </c>
       <c r="N7" t="n">
-        <v>943107.117620391</v>
+        <v>1056330.510950525</v>
       </c>
       <c r="O7" t="n">
-        <v>943107.117620391</v>
+        <v>1056330.510950525</v>
       </c>
       <c r="P7" t="n">
-        <v>398.5764711192018</v>
+        <v>405.6187237876152</v>
       </c>
       <c r="Q7" t="n">
-        <v>407.0086232793541</v>
+        <v>416.4567666969414</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8283020164718028</v>
+        <v>0.8165580301435587</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2622273077150689</v>
+        <v>0.216376876597049</v>
       </c>
       <c r="T7" t="n">
-        <v>1.133429879937692</v>
+        <v>1.138611098567634</v>
       </c>
       <c r="U7" t="n">
-        <v>166.4649834954128</v>
+        <v>143.0855535518842</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4610470346756654</v>
+        <v>0.3884783109281678</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6645622330699885</v>
+        <v>0.5749916311581553</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06332259725282313</v>
+        <v>0.06878319613947241</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4509090909090909</v>
       </c>
       <c r="Z7" t="n">
-        <v>158.2035712387311</v>
+        <v>137.5396018638267</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4290882982604481</v>
+        <v>0.3637029493998958</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.626124728303356</v>
+        <v>0.5426193749611409</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06038932252172544</v>
+        <v>0.0635050426375063</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9077568679537927</v>
+        <v>0.9082314240413022</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9578259029504064</v>
+        <v>0.9590781341463589</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3457271323417761</v>
+        <v>0.3135637388947004</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.995375106261994</v>
+        <v>0.9631619594734614</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.4633079844547169</v>
+        <v>0.4022668063591027</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05666996572855271</v>
+        <v>0.05814606862117715</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.05408742983334248</v>
+        <v>0.05588621292034526</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.913707240162582</v>
+        <v>0.9163305816108738</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.8930639597111045</v>
+        <v>0.8878180821449588</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5250249073857695</v>
+        <v>0.5520080637298939</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.7807470850194044</v>
+        <v>0.6634092526159557</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5469166666666666</v>
+        <v>0.46</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.9784670496224878</v>
+        <v>0.9402043619099909</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.8058178551378355</v>
+        <v>0.6947310918948724</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1977199646030834</v>
+        <v>0.2767951092940352</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1895572511241584</v>
+        <v>0.268430867578589</v>
       </c>
       <c r="AT7" t="n">
-        <v>236.5196630989821</v>
+        <v>232.354705660135</v>
       </c>
       <c r="AU7" t="n">
-        <v>162.3342773670719</v>
+        <v>140.3125777078554</v>
       </c>
       <c r="AV7" t="n">
-        <v>225.0275748442967</v>
+        <v>219.1771424810326</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.964572605302796</v>
+        <v>0.9748474336563997</v>
       </c>
       <c r="AX7" t="n">
-        <v>457.0089290862142</v>
+        <v>478.3426309152907</v>
       </c>
       <c r="AY7" t="n">
-        <v>391.4525436404873</v>
+        <v>400.4850610770606</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.6042103109086024</v>
+        <v>0.5801832034264713</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.5528815901520763</v>
+        <v>0.5262902659005884</v>
       </c>
       <c r="BB7" t="n">
-        <v>494.0531447174329</v>
+        <v>517.2568998737568</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.9490536578784853</v>
+        <v>0.953836426003048</v>
       </c>
       <c r="BD7" t="n">
-        <v>696.516304582519</v>
+        <v>700.0264074646281</v>
       </c>
       <c r="BE7" t="n">
-        <v>483.2617478411866</v>
+        <v>484.4779194379139</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.4656432582333147</v>
+        <v>0.4523986206333604</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4509090909090909</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5051666666666667</v>
+        <v>0.4327272727272727</v>
       </c>
       <c r="C8" t="n">
-        <v>975767.3907222842</v>
+        <v>1055590.612104077</v>
       </c>
       <c r="D8" t="n">
-        <v>510.9530688810112</v>
+        <v>531.2215296883759</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6520673355742719</v>
+        <v>0.6330288650444186</v>
       </c>
       <c r="F8" t="n">
-        <v>296.6509509108786</v>
+        <v>304.8367155057879</v>
       </c>
       <c r="G8" t="n">
-        <v>23904.7446241814</v>
+        <v>30102.09935387745</v>
       </c>
       <c r="H8" t="n">
-        <v>22470.45994673052</v>
+        <v>28295.9733926448</v>
       </c>
       <c r="I8" t="n">
-        <v>19780.32064898294</v>
+        <v>25024.10932992311</v>
       </c>
       <c r="J8" t="n">
-        <v>21.68564320886978</v>
+        <v>27.20127688383628</v>
       </c>
       <c r="K8" t="n">
-        <v>532.638712089881</v>
+        <v>558.4228065722122</v>
       </c>
       <c r="L8" t="n">
-        <v>532.638712089881</v>
+        <v>558.4228065722122</v>
       </c>
       <c r="M8" t="n">
-        <v>1.136983004032705</v>
+        <v>1.167670985903821</v>
       </c>
       <c r="N8" t="n">
-        <v>1109430.939140577</v>
+        <v>1232582.530746385</v>
       </c>
       <c r="O8" t="n">
-        <v>1109430.939140577</v>
+        <v>1232582.530746385</v>
       </c>
       <c r="P8" t="n">
-        <v>413.9112996715638</v>
+        <v>422.0409682773847</v>
       </c>
       <c r="Q8" t="n">
-        <v>422.6035496345684</v>
+        <v>432.7114131192552</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8441539581506831</v>
+        <v>0.8368767961831134</v>
       </c>
       <c r="S8" t="n">
-        <v>0.261182566675198</v>
+        <v>0.224898407578335</v>
       </c>
       <c r="T8" t="n">
-        <v>1.115161661381325</v>
+        <v>1.108135900730397</v>
       </c>
       <c r="U8" t="n">
-        <v>158.1149568354982</v>
+        <v>137.453646264428</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4254005733095945</v>
+        <v>0.3639507017438136</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6215847667051542</v>
+        <v>0.5429472985622027</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06031668243778929</v>
+        <v>0.06531106242877992</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5051666666666667</v>
+        <v>0.4327272727272727</v>
       </c>
       <c r="Z8" t="n">
-        <v>149.8581720351455</v>
+        <v>131.9111605279591</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3948932314879272</v>
+        <v>0.3406623185119549</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5832318344483126</v>
+        <v>0.5117659305347031</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05772560230189012</v>
+        <v>0.06084099460402899</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.912022337231375</v>
+        <v>0.9122666573460285</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.9597881427391327</v>
+        <v>0.9607011256326795</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3365923757974178</v>
+        <v>0.3093473990679195</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.9830478511790475</v>
+        <v>0.9501544681563651</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.4261123821936286</v>
+        <v>0.3747337243244909</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.05408742983334248</v>
+        <v>0.05588621292034526</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.05293402055671876</v>
+        <v>0.05495409738910737</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.917816189596407</v>
+        <v>0.9197245813741172</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9019710504449079</v>
+        <v>0.8987889609078965</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5456024418520964</v>
+        <v>0.5698228788563793</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.7406496754767768</v>
+        <v>0.6350030617170878</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5190833333333333</v>
+        <v>0.4418181818181818</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9691649048738225</v>
+        <v>0.9307772743377724</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7604953920954729</v>
+        <v>0.659535285939589</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.2285152293970456</v>
+        <v>0.2957742126206846</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2225524590835746</v>
+        <v>0.2906191822167761</v>
       </c>
       <c r="AT8" t="n">
-        <v>234.325080594597</v>
+        <v>231.7233404220885</v>
       </c>
       <c r="AU8" t="n">
-        <v>153.9865644353219</v>
+        <v>134.6824033961936</v>
       </c>
       <c r="AV8" t="n">
-        <v>223.4019069946754</v>
+        <v>219.8000440090979</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.9698390587046447</v>
+        <v>0.977923314450031</v>
       </c>
       <c r="AX8" t="n">
-        <v>495.5422433658094</v>
+        <v>519.4939190200721</v>
       </c>
       <c r="AY8" t="n">
-        <v>407.6215330432826</v>
+        <v>417.3563358180036</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5748594262063079</v>
+        <v>0.5552170184931275</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5286323486583452</v>
+        <v>0.5079598950825941</v>
       </c>
       <c r="BB8" t="n">
-        <v>532.638712089881</v>
+        <v>558.4228065722122</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.9534246399919937</v>
+        <v>0.9569961241646133</v>
       </c>
       <c r="BD8" t="n">
-        <v>699.7241951836708</v>
+        <v>702.3453293388762</v>
       </c>
       <c r="BE8" t="n">
-        <v>484.3733298243048</v>
+        <v>485.2797017466578</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.4612184305764921</v>
+        <v>0.4529347574563203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.5051666666666667</v>
+        <v>0.4327272727272727</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4773333333333333</v>
+        <v>0.4145454545454546</v>
       </c>
       <c r="C9" t="n">
-        <v>1121692.217361533</v>
+        <v>1214769.499850052</v>
       </c>
       <c r="D9" t="n">
-        <v>548.1119136945131</v>
+        <v>571.7584513031052</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6940785581699838</v>
+        <v>0.688533675885155</v>
       </c>
       <c r="F9" t="n">
-        <v>296.4846949948695</v>
+        <v>304.6460881684118</v>
       </c>
       <c r="G9" t="n">
-        <v>25544.60505934912</v>
+        <v>30967.47133341038</v>
       </c>
       <c r="H9" t="n">
-        <v>24011.92875578817</v>
+        <v>29109.42305340576</v>
       </c>
       <c r="I9" t="n">
-        <v>21270.26966384472</v>
+        <v>25618.28356772528</v>
       </c>
       <c r="J9" t="n">
-        <v>23.00825389809177</v>
+        <v>27.75532778242864</v>
       </c>
       <c r="K9" t="n">
-        <v>571.1201675926048</v>
+        <v>599.5137790855338</v>
       </c>
       <c r="L9" t="n">
-        <v>571.1201675926048</v>
+        <v>599.5137790855338</v>
       </c>
       <c r="M9" t="n">
-        <v>1.136307478140873</v>
+        <v>1.15768306628538</v>
       </c>
       <c r="N9" t="n">
-        <v>1274587.254760327</v>
+        <v>1406318.079416366</v>
       </c>
       <c r="O9" t="n">
-        <v>1274587.254760327</v>
+        <v>1406318.079416366</v>
       </c>
       <c r="P9" t="n">
-        <v>428.6979410514707</v>
+        <v>437.8477003730077</v>
       </c>
       <c r="Q9" t="n">
-        <v>437.6032360412802</v>
+        <v>448.3491609531343</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8607395206772266</v>
+        <v>0.858509936700771</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2615618109547634</v>
+        <v>0.2349252547741397</v>
       </c>
       <c r="T9" t="n">
-        <v>1.093031388725449</v>
+        <v>1.07342475970176</v>
       </c>
       <c r="U9" t="n">
-        <v>149.7741850882416</v>
+        <v>131.8286708801491</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3934236537978833</v>
+        <v>0.342591946545612</v>
       </c>
       <c r="W9" t="n">
-        <v>0.581349371500232</v>
+        <v>0.5143764919393815</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05875702662084882</v>
+        <v>0.06328238777185533</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4773333333333333</v>
+        <v>0.4145454545454546</v>
       </c>
       <c r="Z9" t="n">
-        <v>141.5220277442177</v>
+        <v>126.2896510952689</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3641819504126783</v>
+        <v>0.3205101233266683</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5432533028549134</v>
+        <v>0.4842223940785187</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05648431998227224</v>
+        <v>0.05945969904276036</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9140032284406444</v>
+        <v>0.9143518950828022</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.960663221292599</v>
+        <v>0.9613697576561276</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3273085310888311</v>
+        <v>0.3049427604630049</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.9697307724154322</v>
+        <v>0.9365702058623738</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3921298359884779</v>
+        <v>0.349678887329658</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.05293402055671876</v>
+        <v>0.05495409738910737</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0528778363302702</v>
+        <v>0.05503655341563169</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.9196453933384029</v>
+        <v>0.9211208508505294</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.9107013709849128</v>
+        <v>0.9099398471784493</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5663063119244335</v>
+        <v>0.588339600104812</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.7004745353446893</v>
+        <v>0.6066439254962718</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.49125</v>
+        <v>0.4236363636363636</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.959360216120258</v>
+        <v>0.9214698304797382</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.7145455077753315</v>
+        <v>0.6240587067333256</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.2588856807755687</v>
+        <v>0.3148259049834664</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.2551852646401006</v>
+        <v>0.3125114991290482</v>
       </c>
       <c r="AT9" t="n">
-        <v>232.3591410223163</v>
+        <v>231.2323509619447</v>
       </c>
       <c r="AU9" t="n">
-        <v>145.6481064162296</v>
+        <v>129.059160987709</v>
       </c>
       <c r="AV9" t="n">
-        <v>222.2704849331848</v>
+        <v>220.8655257840357</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.9742029714387206</v>
+        <v>0.9804384596936814</v>
       </c>
       <c r="AX9" t="n">
-        <v>533.9722550021582</v>
+        <v>560.5739753124611</v>
       </c>
       <c r="AY9" t="n">
-        <v>423.1322454058821</v>
+        <v>433.5440622615748</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5491407084785749</v>
+        <v>0.5333537489954892</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.5079269681456777</v>
+        <v>0.4926194694208933</v>
       </c>
       <c r="BB9" t="n">
-        <v>571.1201675926048</v>
+        <v>599.5137790855338</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.9570016991717233</v>
+        <v>0.959554343057913</v>
       </c>
       <c r="BD9" t="n">
-        <v>702.3494208708123</v>
+        <v>704.2228218864077</v>
       </c>
       <c r="BE9" t="n">
-        <v>485.2811152496905</v>
+        <v>485.9278878378072</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.4580241801060413</v>
+        <v>0.4545232560469057</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4773333333333333</v>
+        <v>0.4145454545454546</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4495</v>
+        <v>0.3963636363636364</v>
       </c>
       <c r="C10" t="n">
-        <v>1267617.044000781</v>
+        <v>1373948.387596027</v>
       </c>
       <c r="D10" t="n">
-        <v>585.270758508015</v>
+        <v>612.2953729178346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7360897807656958</v>
+        <v>0.7440384867258915</v>
       </c>
       <c r="F10" t="n">
-        <v>296.3184390788605</v>
+        <v>304.4554608310358</v>
       </c>
       <c r="G10" t="n">
-        <v>27078.47357265277</v>
+        <v>31741.84314335285</v>
       </c>
       <c r="H10" t="n">
-        <v>25453.76515829361</v>
+        <v>29837.33255475168</v>
       </c>
       <c r="I10" t="n">
-        <v>22581.58273195648</v>
+        <v>26070.91106950254</v>
       </c>
       <c r="J10" t="n">
-        <v>24.17137344472127</v>
+        <v>28.18285836079135</v>
       </c>
       <c r="K10" t="n">
-        <v>609.4421319527362</v>
+        <v>640.4782312786259</v>
       </c>
       <c r="L10" t="n">
-        <v>609.4421319527362</v>
+        <v>640.4782312786259</v>
       </c>
       <c r="M10" t="n">
-        <v>1.134218699348376</v>
+        <v>1.147982451894708</v>
       </c>
       <c r="N10" t="n">
-        <v>1437754.954918399</v>
+        <v>1577268.638769268</v>
       </c>
       <c r="O10" t="n">
-        <v>1437754.954918399</v>
+        <v>1577268.638769268</v>
       </c>
       <c r="P10" t="n">
-        <v>442.9912926093891</v>
+        <v>453.1033420085863</v>
       </c>
       <c r="Q10" t="n">
-        <v>452.0463989943427</v>
+        <v>463.4138009897022</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8780171311961088</v>
+        <v>0.8813606724064089</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2633886195120779</v>
+        <v>0.2464124827503199</v>
       </c>
       <c r="T10" t="n">
-        <v>1.066578494102191</v>
+        <v>1.034492768819151</v>
       </c>
       <c r="U10" t="n">
-        <v>141.4426682536428</v>
+        <v>126.2106273990476</v>
       </c>
       <c r="V10" t="n">
-        <v>0.364672484772486</v>
+        <v>0.3240414676763747</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5439021716168616</v>
+        <v>0.4890852598687269</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05824363872918614</v>
+        <v>0.06225706311848021</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4495</v>
+        <v>0.3963636363636364</v>
       </c>
       <c r="Z10" t="n">
-        <v>133.1951383659478</v>
+        <v>120.675073565756</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3365294725945194</v>
+        <v>0.3029357576384711</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.5061586819210724</v>
+        <v>0.4598000335936211</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0563084564949122</v>
+        <v>0.05899845700987404</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.914283531782479</v>
+        <v>0.9150471390931563</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9607058272696086</v>
+        <v>0.9613106284381728</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3181098119961538</v>
+        <v>0.3005928186442215</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.9549232328253213</v>
+        <v>0.9219558552334576</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3609706113493102</v>
+        <v>0.3268191246392216</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0528778363302702</v>
+        <v>0.05503655341563169</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05375127981687648</v>
+        <v>0.05596828032111666</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9197344035641843</v>
+        <v>0.9209974205698894</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9193614792328587</v>
+        <v>0.9213356504222909</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5869882247301135</v>
+        <v>0.6073990115567801</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.6603219259863411</v>
+        <v>0.5783976921119252</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.4634166666666666</v>
+        <v>0.4054545454545455</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.9486043504250566</v>
+        <v>0.9119342452135049</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.6682945721436412</v>
+        <v>0.5885971914566409</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2882824244387155</v>
+        <v>0.3335365531015797</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.2866286606816801</v>
+        <v>0.3333586637768167</v>
       </c>
       <c r="AT10" t="n">
-        <v>230.5988319436543</v>
+        <v>230.866216623476</v>
       </c>
       <c r="AU10" t="n">
-        <v>137.3189033097953</v>
+        <v>123.4428504824018</v>
       </c>
       <c r="AV10" t="n">
-        <v>221.6077990150224</v>
+        <v>222.3415004644853</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9778356631416435</v>
+        <v>0.9824995212043568</v>
       </c>
       <c r="AX10" t="n">
-        <v>572.2986202630975</v>
+        <v>601.5799107274156</v>
       </c>
       <c r="AY10" t="n">
-        <v>438.0544799157025</v>
+        <v>449.1210795174309</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5264158740895194</v>
+        <v>0.5140400376476114</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4902324175306522</v>
+        <v>0.4797904162319629</v>
       </c>
       <c r="BB10" t="n">
-        <v>609.4421319527362</v>
+        <v>640.4782312786259</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.959945362800342</v>
+        <v>0.9616335260819933</v>
       </c>
       <c r="BD10" t="n">
-        <v>704.5097936753625</v>
+        <v>705.7487470693108</v>
       </c>
       <c r="BE10" t="n">
-        <v>486.0268859017463</v>
+        <v>486.454062468739</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4559579015960487</v>
+        <v>0.457065769655842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.4495</v>
+        <v>0.3963636363636364</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4216666666666666</v>
+        <v>0.3781818181818182</v>
       </c>
       <c r="C11" t="n">
-        <v>1413541.87064003</v>
+        <v>1533127.275342002</v>
       </c>
       <c r="D11" t="n">
-        <v>622.4296033215169</v>
+        <v>652.8322945325638</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7781010033614078</v>
+        <v>0.7995432975666279</v>
       </c>
       <c r="F11" t="n">
-        <v>296.1521831628515</v>
+        <v>304.2648334936598</v>
       </c>
       <c r="G11" t="n">
-        <v>28479.74565628555</v>
+        <v>32409.0250305141</v>
       </c>
       <c r="H11" t="n">
-        <v>26770.96091690842</v>
+        <v>30464.48352868325</v>
       </c>
       <c r="I11" t="n">
-        <v>23668.43764046109</v>
+        <v>26364.60592261756</v>
       </c>
       <c r="J11" t="n">
-        <v>25.23337736275803</v>
+        <v>28.53486721278025</v>
       </c>
       <c r="K11" t="n">
-        <v>647.6629806842749</v>
+        <v>681.367161745344</v>
       </c>
       <c r="L11" t="n">
-        <v>647.6629806842749</v>
+        <v>681.367161745344</v>
       </c>
       <c r="M11" t="n">
-        <v>1.131168049845624</v>
+        <v>1.138773496746965</v>
       </c>
       <c r="N11" t="n">
-        <v>1598953.401187018</v>
+        <v>1745884.708299359</v>
       </c>
       <c r="O11" t="n">
-        <v>1598953.401187018</v>
+        <v>1745884.708299359</v>
       </c>
       <c r="P11" t="n">
-        <v>456.837658248206</v>
+        <v>467.8618047637236</v>
       </c>
       <c r="Q11" t="n">
-        <v>466.0057911908793</v>
+        <v>477.9774150869619</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8959467538397662</v>
+        <v>0.9053368115468732</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2667584227797275</v>
+        <v>0.2593281579457174</v>
       </c>
       <c r="T11" t="n">
-        <v>1.03520256682173</v>
+        <v>0.9914264016941713</v>
       </c>
       <c r="U11" t="n">
-        <v>133.1204063317017</v>
+        <v>120.5995158211233</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3388453894983673</v>
+        <v>0.3080365588773158</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5093034843751886</v>
+        <v>0.4669258004553202</v>
       </c>
       <c r="X11" t="n">
-        <v>0.05856522843683203</v>
+        <v>0.06198837150524647</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4216666666666666</v>
+        <v>0.3781818181818182</v>
       </c>
       <c r="Z11" t="n">
-        <v>124.8775039003357</v>
+        <v>115.0674279394204</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3116102525718044</v>
+        <v>0.2876863923073513</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4719001526279438</v>
+        <v>0.4383203510393384</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0569991866427223</v>
+        <v>0.05924052481935393</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9131821038107241</v>
+        <v>0.9146823288855837</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.9600432583058317</v>
+        <v>0.9606422341452905</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3092356149407436</v>
+        <v>0.2964891248538185</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.9380268380238848</v>
+        <v>0.9058967864584878</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3323121833376875</v>
+        <v>0.3059017857126065</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.05375127981687648</v>
+        <v>0.05596828032111666</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.05552850503992657</v>
+        <v>0.05769869756874035</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.9183496695904866</v>
+        <v>0.919601546348912</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.9279950060727989</v>
+        <v>0.9329895228460818</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.6074593495418869</v>
+        <v>0.626861717480877</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.6203334246401707</v>
+        <v>0.5503288594011785</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.4355833333333333</v>
+        <v>0.3872727272727273</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.9363955278546708</v>
+        <v>0.9018929053532764</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6220825077956035</v>
+        <v>0.5534022061004289</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.3160621032145001</v>
+        <v>0.3515640459520979</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.3159443302282813</v>
+        <v>0.3524945803580589</v>
       </c>
       <c r="AT11" t="n">
-        <v>229.0020968160556</v>
+        <v>230.6061116032338</v>
       </c>
       <c r="AU11" t="n">
-        <v>128.9989551160187</v>
+        <v>117.8334718802719</v>
       </c>
       <c r="AV11" t="n">
-        <v>221.3704787375916</v>
+        <v>224.1950351806423</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9808639670026166</v>
+        <v>0.9841855797325036</v>
       </c>
       <c r="AX11" t="n">
-        <v>610.5187698938081</v>
+        <v>642.5081302626319</v>
       </c>
       <c r="AY11" t="n">
-        <v>452.4455144494128</v>
+        <v>464.1475800616227</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5061429266123488</v>
+        <v>0.4968379056777962</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.4750380422781412</v>
+        <v>0.4690494322620932</v>
       </c>
       <c r="BB11" t="n">
-        <v>647.6629806842749</v>
+        <v>681.367161745344</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.9623898097314252</v>
+        <v>0.963332105015768</v>
       </c>
       <c r="BD11" t="n">
-        <v>706.3037882815179</v>
+        <v>706.9953445742814</v>
       </c>
       <c r="BE11" t="n">
-        <v>486.6453125334641</v>
+        <v>486.8834963682344</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.4548908065817834</v>
+        <v>0.4604695719878776</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.4216666666666666</v>
+        <v>0.3781818181818182</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3938333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="C12" t="n">
-        <v>1559466.697279278</v>
+        <v>1692306.163087977</v>
       </c>
       <c r="D12" t="n">
-        <v>659.5884481350188</v>
+        <v>693.3692161472932</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8201122259571196</v>
+        <v>0.8550481084073642</v>
       </c>
       <c r="F12" t="n">
-        <v>295.9859272468424</v>
+        <v>304.0742061562837</v>
       </c>
       <c r="G12" t="n">
-        <v>29710.34632635923</v>
+        <v>32950.60162525447</v>
       </c>
       <c r="H12" t="n">
-        <v>27927.72554677768</v>
+        <v>30973.5655277392</v>
       </c>
       <c r="I12" t="n">
-        <v>24478.00323351468</v>
+        <v>26481.7923777957</v>
       </c>
       <c r="J12" t="n">
-        <v>26.12241929242495</v>
+        <v>28.77136958159965</v>
       </c>
       <c r="K12" t="n">
-        <v>685.7108674274438</v>
+        <v>722.1405857288928</v>
       </c>
       <c r="L12" t="n">
-        <v>685.7108674274438</v>
+        <v>722.1405857288928</v>
       </c>
       <c r="M12" t="n">
-        <v>1.126855772995949</v>
+        <v>1.129775702180906</v>
       </c>
       <c r="N12" t="n">
-        <v>1757294.05062408</v>
+        <v>1911926.383707795</v>
       </c>
       <c r="O12" t="n">
-        <v>1757294.05062408</v>
+        <v>1911926.383707795</v>
       </c>
       <c r="P12" t="n">
-        <v>470.2765214846174</v>
+        <v>482.1687445015359</v>
       </c>
       <c r="Q12" t="n">
-        <v>479.4985441567283</v>
+        <v>492.0708672487102</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9144900390830787</v>
+        <v>0.9303513496768336</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2718250038327186</v>
+        <v>0.2736499133886414</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9981953315900436</v>
+        <v>0.9444106543470056</v>
       </c>
       <c r="U12" t="n">
-        <v>124.8073993224185</v>
+        <v>114.9953361463764</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3157563807972059</v>
+        <v>0.2943844626887498</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4776524111349399</v>
+        <v>0.4477871160479379</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05961763500520601</v>
+        <v>0.06233423933419938</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3938333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>116.5691243473814</v>
+        <v>109.4667142162621</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2892419896025067</v>
+        <v>0.2745921648935793</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4405233864725204</v>
+        <v>0.4196725451948258</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05849024100115483</v>
+        <v>0.06007918984763523</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9107999498632829</v>
+        <v>0.9134172852659774</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.958693692884539</v>
+        <v>0.9593996466991872</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.300932890494228</v>
+        <v>0.2927849636055536</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9183243619053558</v>
+        <v>0.8880031547486461</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3059536774691968</v>
+        <v>0.2867458717764375</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.05552850503992657</v>
+        <v>0.05769869756874035</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.05826439951214323</v>
+        <v>0.06024311495516003</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.915525637845926</v>
+        <v>0.9170034700986963</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.9365918659838088</v>
+        <v>0.9448754981880104</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.6274993351411295</v>
+        <v>0.6466069537807679</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.5806668776409875</v>
+        <v>0.5224960521339288</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.4077499999999999</v>
+        <v>0.3690909090909091</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.9221667642386009</v>
+        <v>0.891125707843446</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5762356545407744</v>
+        <v>0.5186810748370121</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.3414998865976134</v>
+        <v>0.3686296557095172</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.3420887073645814</v>
+        <v>0.369322079911634</v>
       </c>
       <c r="AT12" t="n">
-        <v>227.5092562077241</v>
+        <v>230.4309291739589</v>
       </c>
       <c r="AU12" t="n">
-        <v>120.6882618349</v>
+        <v>112.2310251813192</v>
       </c>
       <c r="AV12" t="n">
-        <v>221.4986472018841</v>
+        <v>226.3931305889214</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9833829846643083</v>
+        <v>0.9855562980212427</v>
       </c>
       <c r="AX12" t="n">
-        <v>648.6280567771141</v>
+        <v>683.3543978280171</v>
       </c>
       <c r="AY12" t="n">
-        <v>466.3528572201165</v>
+        <v>478.6739282556907</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4878478874641927</v>
+        <v>0.4813943596503356</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.4619381015878232</v>
+        <v>0.4600823695471778</v>
       </c>
       <c r="BB12" t="n">
-        <v>685.7108674274438</v>
+        <v>722.1405857288928</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.9644355317169063</v>
+        <v>0.964720702205309</v>
       </c>
       <c r="BD12" t="n">
-        <v>707.8051562028172</v>
+        <v>708.0144445745645</v>
       </c>
       <c r="BE12" t="n">
-        <v>487.162261340926</v>
+        <v>487.2342796497917</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.4546711943412933</v>
+        <v>0.4646494305606851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.3938333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="B13" t="n">
-        <v>0.366</v>
+        <v>0.3418181818181818</v>
       </c>
       <c r="C13" t="n">
-        <v>1705391.523918527</v>
+        <v>1851485.050833953</v>
       </c>
       <c r="D13" t="n">
-        <v>696.7472929485206</v>
+        <v>733.9061377620225</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8621234485528316</v>
+        <v>0.9105529192481008</v>
       </c>
       <c r="F13" t="n">
-        <v>295.8196713308334</v>
+        <v>303.8835788189076</v>
       </c>
       <c r="G13" t="n">
-        <v>30719.03738497328</v>
+        <v>33345.94627631325</v>
       </c>
       <c r="H13" t="n">
-        <v>28875.89514187488</v>
+        <v>31345.18949973445</v>
       </c>
       <c r="I13" t="n">
-        <v>24951.50377353315</v>
+        <v>26405.21787212439</v>
       </c>
       <c r="J13" t="n">
-        <v>26.80433785417398</v>
+        <v>28.83277439735654</v>
       </c>
       <c r="K13" t="n">
-        <v>723.5516308026945</v>
+        <v>762.738912159379</v>
       </c>
       <c r="L13" t="n">
-        <v>723.5516308026945</v>
+        <v>762.738912159379</v>
       </c>
       <c r="M13" t="n">
-        <v>1.121263334583824</v>
+        <v>1.120704655559663</v>
       </c>
       <c r="N13" t="n">
-        <v>1912192.986879876</v>
+        <v>2074967.91616873</v>
       </c>
       <c r="O13" t="n">
-        <v>1912192.986879876</v>
+        <v>2074967.91616873</v>
       </c>
       <c r="P13" t="n">
-        <v>483.3418741694526</v>
+        <v>496.0632298322525</v>
       </c>
       <c r="Q13" t="n">
-        <v>492.5513798662465</v>
+        <v>505.7137107564316</v>
       </c>
       <c r="R13" t="n">
-        <v>0.933610422109947</v>
+        <v>0.9563228060522342</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2788052258022088</v>
+        <v>0.2893648447936687</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9547700581940284</v>
+        <v>0.8937479270607351</v>
       </c>
       <c r="U13" t="n">
-        <v>116.5036472257932</v>
+        <v>109.3980883748067</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2953239517243477</v>
+        <v>0.2829425165503032</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4491109583226507</v>
+        <v>0.4315857646823992</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06136696819260479</v>
+        <v>0.06321492940044968</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.366</v>
+        <v>0.3418181818181818</v>
       </c>
       <c r="Z13" t="n">
-        <v>108.269999707085</v>
+        <v>103.8729323962811</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2693209680835347</v>
+        <v>0.2635258235764881</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.4121144803622692</v>
+        <v>0.4037721457639878</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06077989459910128</v>
+        <v>0.06146486450733273</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.907129750913281</v>
+        <v>0.911323283849541</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.9566124246331672</v>
+        <v>0.9575696090057074</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2934993946135828</v>
+        <v>0.2896206528383063</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.8948912786102198</v>
+        <v>0.8678750646782986</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.2817626701603202</v>
+        <v>0.2692139766992855</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.05826439951214323</v>
+        <v>0.06024311495516003</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.05921684165741564</v>
+        <v>0.06278753234157972</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.9111611613348617</v>
+        <v>0.913169815632715</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.9451114233715572</v>
+        <v>0.9569462075289707</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.6468369132009922</v>
+        <v>0.6665234722823843</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.5414858336198617</v>
+        <v>0.4949506459215169</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.3799166666666667</v>
+        <v>0.3509090909090909</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.9052038622295482</v>
+        <v>0.8794336703204269</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5310626589094749</v>
+        <v>0.4846039415140186</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.3637180286096865</v>
+        <v>0.3844830243989099</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.3638286197007449</v>
+        <v>0.38327112316428</v>
       </c>
       <c r="AT13" t="n">
-        <v>226.0407913801597</v>
+        <v>230.3174765589782</v>
       </c>
       <c r="AU13" t="n">
-        <v>112.3868234664391</v>
+        <v>106.6355103855439</v>
       </c>
       <c r="AV13" t="n">
-        <v>221.9110278634661</v>
+        <v>228.9013479408027</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.9854639605896526</v>
+        <v>0.9866572553880303</v>
       </c>
       <c r="AX13" t="n">
-        <v>686.619346839168</v>
+        <v>724.1138155967068</v>
       </c>
       <c r="AY13" t="n">
-        <v>479.8160762158486</v>
+        <v>492.742693877419</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.4710988284570808</v>
+        <v>0.4674193639414468</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.450533765479911</v>
+        <v>0.4526302986692191</v>
       </c>
       <c r="BB13" t="n">
-        <v>723.5516308026945</v>
+        <v>762.738912159379</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.9661698876937488</v>
+        <v>0.9658543021211022</v>
       </c>
       <c r="BD13" t="n">
-        <v>709.0780106992862</v>
+        <v>708.8464005105317</v>
       </c>
       <c r="BE13" t="n">
-        <v>487.6000994539179</v>
+        <v>487.5204591513892</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.455108659969497</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1851316.350557775</v>
-      </c>
-      <c r="D14" t="n">
-        <v>733.9061377620225</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.9041346711485436</v>
-      </c>
-      <c r="F14" t="n">
-        <v>295.6534154148244</v>
-      </c>
-      <c r="G14" t="n">
-        <v>31444.23444505393</v>
-      </c>
-      <c r="H14" t="n">
-        <v>29557.58037835069</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25029.11638499706</v>
-      </c>
-      <c r="J14" t="n">
-        <v>27.18844774532111</v>
-      </c>
-      <c r="K14" t="n">
-        <v>761.0945855073436</v>
-      </c>
-      <c r="L14" t="n">
-        <v>761.0945855073436</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.11416977193039</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2062680.716071959</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2062680.716071959</v>
-      </c>
-      <c r="P14" t="n">
-        <v>496.0632298322525</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>505.1683031630274</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.95327317794347</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2879557252140741</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.9041782148066957</v>
-      </c>
-      <c r="U14" t="n">
-        <v>108.2091500418257</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.2775556733353156</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.4239089826554646</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.06383389823301641</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>108.2091500418257</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.2725530539245822</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.4167522097442211</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.05934631531060342</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.909429439730491</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.9558868129828687</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.2897096758504782</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.9012251125583335</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.2731889702002319</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.05921684165741564</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.05921684165741564</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.9096368497752779</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.9545799954631693</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.6644066348749251</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.5029302170208082</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.9004467114969256</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.5035089684840817</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.3975164944761174</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.3977161440742518</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>224.5026475751386</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>108.2091500418257</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>224.2667433906221</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.9871604746998967</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>724.4831313383258</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>492.8683332673551</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.4555022760071658</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.4439446061568256</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>761.0945855073436</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.9671521977773768</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>709.7989340988463</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>487.8479092948367</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0.4597062713967353</v>
+        <v>0.4695215219054474</v>
       </c>
     </row>
   </sheetData>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF13"/>
+  <dimension ref="A1:BF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,2111 +713,1935 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5418181818181819</v>
+        <v>0.54</v>
       </c>
       <c r="C2" t="n">
-        <v>100517.2856282267</v>
+        <v>100454.577154708</v>
       </c>
       <c r="D2" t="n">
         <v>288</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="F2" t="n">
-        <v>305.9804795300442</v>
+        <v>320.118907248064</v>
       </c>
       <c r="G2" t="n">
-        <v>23620.75115897785</v>
+        <v>25854.06962501386</v>
       </c>
       <c r="H2" t="n">
-        <v>23384.54364738807</v>
+        <v>25595.52892876372</v>
       </c>
       <c r="I2" t="n">
-        <v>20369.84345329015</v>
+        <v>22295.79183775567</v>
       </c>
       <c r="J2" t="n">
-        <v>23.24507320813924</v>
+        <v>25.44287169857228</v>
       </c>
       <c r="K2" t="n">
-        <v>311.2450732081392</v>
+        <v>313.4428716985723</v>
       </c>
       <c r="L2" t="n">
-        <v>311.2450732081392</v>
+        <v>313.4428716985723</v>
       </c>
       <c r="M2" t="n">
-        <v>1.268466410091626</v>
+        <v>1.296254706516713</v>
       </c>
       <c r="N2" t="n">
-        <v>127502.8004529913</v>
+        <v>130214.7184279365</v>
       </c>
       <c r="O2" t="n">
-        <v>127502.8004529913</v>
+        <v>130214.7184279365</v>
       </c>
       <c r="P2" t="n">
         <v>310.7513475433373</v>
       </c>
       <c r="Q2" t="n">
-        <v>323.048716212724</v>
+        <v>324.1872836502556</v>
       </c>
       <c r="R2" t="n">
-        <v>0.73824115301167</v>
+        <v>0.7697077367416805</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1982457778753087</v>
+        <v>0.2209646382902902</v>
       </c>
       <c r="T2" t="n">
-        <v>1.230553318308278</v>
+        <v>1.194971328079617</v>
       </c>
       <c r="U2" t="n">
-        <v>171.3490685368248</v>
+        <v>179.2665880589159</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5849346974729742</v>
+        <v>0.620165498278116</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7967300817567868</v>
+        <v>0.8289595144665948</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3266962403031563</v>
+        <v>0.3184019113646743</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5418181818181819</v>
+        <v>0.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>165.785787090824</v>
+        <v>172.8642099139546</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5443997693216462</v>
+        <v>0.5732319379046732</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7566082495275177</v>
+        <v>0.785474428031451</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2819423445402975</v>
+        <v>0.2704391390523389</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4717432063264572</v>
+        <v>0.5645174635893465</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7860798739157199</v>
+        <v>0.8156702574457798</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2295725970538642</v>
+        <v>0.2506450778768315</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.170020681986013</v>
+        <v>1.136231551777349</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.5573570009293095</v>
+        <v>0.5878631958982221</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.277118611545255</v>
+        <v>0.2656934067039961</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1196138735180367</v>
+        <v>0.1101726809038104</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.4856368358667906</v>
+        <v>0.5750095110198868</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.762160513463695</v>
+        <v>0.7926889970937301</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5230483622799569</v>
+        <v>0.5328342009416011</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8035822579389086</v>
+        <v>0.7955506638277184</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.550909090909091</v>
+        <v>0.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.161300470204773</v>
+        <v>1.129419771735539</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8113344619355042</v>
+        <v>0.8012494925298089</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3577182122658643</v>
+        <v>0.333869107907821</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.3586862200505089</v>
+        <v>0.3349820592475404</v>
       </c>
       <c r="AT2" t="n">
-        <v>238.0353119932859</v>
+        <v>250.9860824435535</v>
       </c>
       <c r="AU2" t="n">
-        <v>168.5674278138244</v>
+        <v>176.0653989864352</v>
       </c>
       <c r="AV2" t="n">
-        <v>232.4405470654187</v>
+        <v>245.1392516422733</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9429752332820334</v>
+        <v>0.9358991257909094</v>
       </c>
       <c r="AX2" t="n">
-        <v>271.5768671852256</v>
+        <v>269.5389482277819</v>
       </c>
       <c r="AY2" t="n">
-        <v>301.7610371920241</v>
+        <v>300.6266943249972</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.7888205654655587</v>
+        <v>0.8348762341517854</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.7195216554036982</v>
+        <v>0.7561655376548881</v>
       </c>
       <c r="BB2" t="n">
-        <v>311.2450732081392</v>
+        <v>313.4428716985723</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.9137147645675203</v>
+        <v>0.904702279943849</v>
       </c>
       <c r="BD2" t="n">
-        <v>670.5808738798845</v>
+        <v>663.9665560980862</v>
       </c>
       <c r="BE2" t="n">
-        <v>474.179045310867</v>
+        <v>471.8347022630789</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.4901957380108035</v>
+        <v>0.5195447695273417</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5418181818181819</v>
+        <v>0.54</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5236363636363637</v>
+        <v>0.52</v>
       </c>
       <c r="C3" t="n">
-        <v>259696.1733742018</v>
+        <v>275630.2684439648</v>
       </c>
       <c r="D3" t="n">
-        <v>328.5369216147293</v>
+        <v>332.5906137762022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3555048108407364</v>
+        <v>0.4792242024808975</v>
       </c>
       <c r="F3" t="n">
-        <v>305.7898521926682</v>
+        <v>319.8787703085381</v>
       </c>
       <c r="G3" t="n">
-        <v>24818.60857907457</v>
+        <v>27290.43088549179</v>
       </c>
       <c r="H3" t="n">
-        <v>24322.23640749308</v>
+        <v>26744.62226778196</v>
       </c>
       <c r="I3" t="n">
-        <v>21347.1618619938</v>
+        <v>23488.46488831931</v>
       </c>
       <c r="J3" t="n">
-        <v>24.08142218563671</v>
+        <v>26.47303378928586</v>
       </c>
       <c r="K3" t="n">
-        <v>352.618343800366</v>
+        <v>359.0636475654881</v>
       </c>
       <c r="L3" t="n">
-        <v>352.618343800366</v>
+        <v>359.0636475654881</v>
       </c>
       <c r="M3" t="n">
-        <v>1.243860030596722</v>
+        <v>1.26680303387504</v>
       </c>
       <c r="N3" t="n">
-        <v>323025.6901590863</v>
+        <v>349169.2602926063</v>
       </c>
       <c r="O3" t="n">
-        <v>323025.6901590863</v>
+        <v>349169.2602926063</v>
       </c>
       <c r="P3" t="n">
-        <v>331.9012350344884</v>
+        <v>333.9425591312983</v>
       </c>
       <c r="Q3" t="n">
-        <v>343.8501573014948</v>
+        <v>346.9784446168208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7504610817793644</v>
+        <v>0.7841096339936948</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1983935480548724</v>
+        <v>0.2219828355331729</v>
       </c>
       <c r="T3" t="n">
-        <v>1.219795944224634</v>
+        <v>1.180775445352064</v>
       </c>
       <c r="U3" t="n">
-        <v>165.6825017334821</v>
+        <v>172.7345359666106</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5316045280079817</v>
+        <v>0.5592578656405074</v>
       </c>
       <c r="W3" t="n">
-        <v>0.743292007914666</v>
+        <v>0.7716834611885978</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1453279602294961</v>
+        <v>0.1347270471899817</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5236363636363637</v>
+        <v>0.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>160.1226862390699</v>
+        <v>166.3369605604398</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4959119073079256</v>
+        <v>0.5183116372595099</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7045594399148103</v>
+        <v>0.7291365225735928</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1276967514859966</v>
+        <v>0.1169517598723287</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8049069210010069</v>
+        <v>0.8398584757481505</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9138281442189199</v>
+        <v>0.9280196282595528</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3076527576199941</v>
+        <v>0.3172873666619888</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.039595433301365</v>
+        <v>1.022933872832624</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5401021988561153</v>
+        <v>0.5615799437371655</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1196138735180367</v>
+        <v>0.1101726809038104</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08466626388688835</v>
+        <v>0.07803314741165103</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8186352999554748</v>
+        <v>0.8499652115645657</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8321446129991421</v>
+        <v>0.8560646311266238</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4978764413086157</v>
+        <v>0.5148782255130121</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7760287641598343</v>
+        <v>0.7653244056670644</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5327272727272727</v>
+        <v>0.53</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.010425779831437</v>
+        <v>0.998828794457881</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8192012206450174</v>
+        <v>0.7998694371915022</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.2343970156716023</v>
+        <v>0.2335043887908166</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.2203942126563476</v>
+        <v>0.2230644356411223</v>
       </c>
       <c r="AT3" t="n">
-        <v>236.5370003654726</v>
+        <v>249.3385841704242</v>
       </c>
       <c r="AU3" t="n">
-        <v>162.902593986276</v>
+        <v>169.5357482635252</v>
       </c>
       <c r="AV3" t="n">
-        <v>222.9707754433835</v>
+        <v>236.3641327968556</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9528994376335685</v>
+        <v>0.9478717732865374</v>
       </c>
       <c r="AX3" t="n">
-        <v>313.0626478485393</v>
+        <v>315.2532548585067</v>
       </c>
       <c r="AY3" t="n">
-        <v>323.9905952703184</v>
+        <v>325.1221560491645</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.7300736620707161</v>
+        <v>0.7669073901340627</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.6484533181349638</v>
+        <v>0.6812069639019797</v>
       </c>
       <c r="BB3" t="n">
-        <v>352.618343800366</v>
+        <v>359.0636475654881</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.9299180490332926</v>
+        <v>0.9226595120552412</v>
       </c>
       <c r="BD3" t="n">
-        <v>682.4725638012188</v>
+        <v>677.1454789618543</v>
       </c>
       <c r="BE3" t="n">
-        <v>478.3649763962122</v>
+        <v>476.4943641806373</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.4661101594919127</v>
+        <v>0.4960481184353544</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.5236363636363637</v>
+        <v>0.52</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5054545454545455</v>
+        <v>0.5</v>
       </c>
       <c r="C4" t="n">
-        <v>418875.0611201768</v>
+        <v>450805.9597332217</v>
       </c>
       <c r="D4" t="n">
-        <v>369.0738432294586</v>
+        <v>377.1812275524045</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4110096216814729</v>
+        <v>0.528448404961795</v>
       </c>
       <c r="F4" t="n">
-        <v>305.5992248552921</v>
+        <v>319.6386333690122</v>
       </c>
       <c r="G4" t="n">
-        <v>25975.06100615904</v>
+        <v>28671.32907065673</v>
       </c>
       <c r="H4" t="n">
-        <v>25195.80917597427</v>
+        <v>27811.18919853703</v>
       </c>
       <c r="I4" t="n">
-        <v>22237.84207213622</v>
+        <v>24567.82272902698</v>
       </c>
       <c r="J4" t="n">
-        <v>24.7919761184167</v>
+        <v>27.3954765882457</v>
       </c>
       <c r="K4" t="n">
-        <v>393.8658193478753</v>
+        <v>404.5767041406502</v>
       </c>
       <c r="L4" t="n">
-        <v>393.8658193478753</v>
+        <v>404.5767041406502</v>
       </c>
       <c r="M4" t="n">
-        <v>1.223343120893016</v>
+        <v>1.24315904184726</v>
       </c>
       <c r="N4" t="n">
-        <v>512427.92453501</v>
+        <v>560423.5049609866</v>
       </c>
       <c r="O4" t="n">
-        <v>512427.92453501</v>
+        <v>560423.5049609866</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7818352826613</v>
+        <v>355.6246133190464</v>
       </c>
       <c r="Q4" t="n">
-        <v>363.4050209165286</v>
+        <v>368.3131397308003</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7645027498690725</v>
+        <v>0.7997680028316541</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2003470470202877</v>
+        <v>0.2244413126796626</v>
       </c>
       <c r="T4" t="n">
-        <v>1.205373060144734</v>
+        <v>1.16333363127941</v>
       </c>
       <c r="U4" t="n">
-        <v>160.0228668333166</v>
+        <v>166.2120893518864</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4870510726294947</v>
+        <v>0.5090576493297847</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6945920846964865</v>
+        <v>0.7190919144876908</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1027470521766324</v>
+        <v>0.09483275212219863</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5054545454545455</v>
+        <v>0.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>154.4665172904931</v>
+        <v>159.8193166845061</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4551025817895442</v>
+        <v>0.4726157899444055</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6575381057160141</v>
+        <v>0.6780635604689873</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.09165317272825486</v>
+        <v>0.08378592377249121</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8644452660815081</v>
+        <v>0.8882101567499902</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.9398223441098341</v>
+        <v>0.9495815682954533</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3185571585810211</v>
+        <v>0.3245183178108368</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.008438520508987</v>
+        <v>0.9950986376569289</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5024269220081136</v>
+        <v>0.5173054747828673</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.08466626388688835</v>
+        <v>0.07803314741165103</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.06992016398876522</v>
+        <v>0.06489756193149308</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8755181762683212</v>
+        <v>0.8963315846788537</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8521625469894534</v>
+        <v>0.8746747855635537</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5061224383844614</v>
+        <v>0.5260559530844864</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7481662181993752</v>
+        <v>0.7349294688363651</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5145454545454546</v>
+        <v>0.51</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.9787550326063221</v>
+        <v>0.9711850223246584</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7936504313645399</v>
+        <v>0.7699022166059076</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.2305888144069469</v>
+        <v>0.2362555534882933</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.2147880891444466</v>
+        <v>0.2251964210510212</v>
       </c>
       <c r="AT4" t="n">
-        <v>235.2254025922055</v>
+        <v>247.879873607367</v>
       </c>
       <c r="AU4" t="n">
-        <v>157.2446920619049</v>
+        <v>163.0157030181962</v>
       </c>
       <c r="AV4" t="n">
-        <v>220.5649459315814</v>
+        <v>234.1960803815432</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9604635421084098</v>
+        <v>0.9568100516098057</v>
       </c>
       <c r="AX4" t="n">
-        <v>354.4819707677298</v>
+        <v>360.890789800666</v>
       </c>
       <c r="AY4" t="n">
-        <v>344.7576029595573</v>
+        <v>347.8601469271284</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6822921396741443</v>
+        <v>0.7125848585905825</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.606939731804761</v>
+        <v>0.6358613232010046</v>
       </c>
       <c r="BB4" t="n">
-        <v>393.8658193478753</v>
+        <v>404.5767041406502</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.9386040269927941</v>
+        <v>0.9326133962761779</v>
       </c>
       <c r="BD4" t="n">
-        <v>688.8472563381627</v>
+        <v>684.4506956861723</v>
       </c>
       <c r="BE4" t="n">
-        <v>480.5938878618682</v>
+        <v>479.0577400100885</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.4589424699362302</v>
+        <v>0.4888681693705882</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5054545454545455</v>
+        <v>0.5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4872727272727273</v>
+        <v>0.48</v>
       </c>
       <c r="C5" t="n">
-        <v>578053.948866152</v>
+        <v>625981.6510224786</v>
       </c>
       <c r="D5" t="n">
-        <v>409.6107648441879</v>
+        <v>421.7718413286067</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4665144325222093</v>
+        <v>0.5776726074426926</v>
       </c>
       <c r="F5" t="n">
-        <v>305.4085975179161</v>
+        <v>319.3984964294863</v>
       </c>
       <c r="G5" t="n">
-        <v>27087.57621864307</v>
+        <v>29992.58961708235</v>
       </c>
       <c r="H5" t="n">
-        <v>26004.07316989735</v>
+        <v>28792.88603239906</v>
       </c>
       <c r="I5" t="n">
-        <v>23034.00604192664</v>
+        <v>25521.82283354585</v>
       </c>
       <c r="J5" t="n">
-        <v>25.51536984632288</v>
+        <v>28.21137563959589</v>
       </c>
       <c r="K5" t="n">
-        <v>435.1261346905108</v>
+        <v>449.9832169682026</v>
       </c>
       <c r="L5" t="n">
-        <v>435.1261346905108</v>
+        <v>449.9832169682026</v>
       </c>
       <c r="M5" t="n">
-        <v>1.206809448427407</v>
+        <v>1.223349171219593</v>
       </c>
       <c r="N5" t="n">
-        <v>697600.9671924456</v>
+        <v>765794.1339770217</v>
       </c>
       <c r="O5" t="n">
-        <v>697600.9671924456</v>
+        <v>765794.1339770217</v>
       </c>
       <c r="P5" t="n">
-        <v>370.5974763166315</v>
+        <v>376.0586369138221</v>
       </c>
       <c r="Q5" t="n">
-        <v>381.9656960536225</v>
+        <v>388.4319408203171</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7802678116363377</v>
+        <v>0.8166105685666942</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2040392326156507</v>
+        <v>0.2282925458895157</v>
       </c>
       <c r="T5" t="n">
-        <v>1.187126089356396</v>
+        <v>1.142479748812273</v>
       </c>
       <c r="U5" t="n">
-        <v>154.3701638363285</v>
+        <v>159.6992482147431</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4492023757970994</v>
+        <v>0.4668369588793164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6505088932225696</v>
+        <v>0.671347407885214</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08435414167126003</v>
+        <v>0.07807446227001276</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4872727272727273</v>
+        <v>0.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>148.8172802450937</v>
+        <v>153.3112782861534</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4201555832783126</v>
+        <v>0.4338874584941147</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6150913241916492</v>
+        <v>0.6320011104413988</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07619092557027551</v>
+        <v>0.07002408006027119</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8887648128115231</v>
+        <v>0.9075172909297876</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.9505773428354967</v>
+        <v>0.9582543821541679</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3195201412459455</v>
+        <v>0.3234929436994191</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.9904023854256228</v>
+        <v>0.97777272952478</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.4659020134783136</v>
+        <v>0.4759608627541544</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06992016398876522</v>
+        <v>0.06489756193149308</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.06232707720632211</v>
+        <v>0.05834925579202112</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8984400755890104</v>
+        <v>0.9146053366536476</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8654225772359172</v>
+        <v>0.887432475360431</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5195295618364969</v>
+        <v>0.5413670654787774</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.7200617488292373</v>
+        <v>0.7044246691718498</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.4963636363636364</v>
+        <v>0.49</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9621848532952615</v>
+        <v>0.955884074100192</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.762598609920323</v>
+        <v>0.7356344488799286</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.2421231044660241</v>
+        <v>0.2514594049283423</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.2278037755052997</v>
+        <v>0.2421382806448514</v>
       </c>
       <c r="AT5" t="n">
-        <v>234.0959734517244</v>
+        <v>246.6033773200912</v>
       </c>
       <c r="AU5" t="n">
-        <v>151.5937220407111</v>
+        <v>156.5052632504483</v>
       </c>
       <c r="AV5" t="n">
-        <v>219.4457632791645</v>
+        <v>233.2217769598795</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9663695375963736</v>
+        <v>0.9636772089707186</v>
       </c>
       <c r="AX5" t="n">
-        <v>395.8353654169748</v>
+        <v>406.4519108739925</v>
       </c>
       <c r="AY5" t="n">
-        <v>364.3125005051455</v>
+        <v>369.1657157917697</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.6425691490880314</v>
+        <v>0.6680018397461084</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.5745169410405836</v>
+        <v>0.6004186382493311</v>
       </c>
       <c r="BB5" t="n">
-        <v>435.1261346905108</v>
+        <v>449.9832169682026</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.9449883807428952</v>
+        <v>0.9399162431404698</v>
       </c>
       <c r="BD5" t="n">
-        <v>693.5327727410057</v>
+        <v>689.8102998230123</v>
       </c>
       <c r="BE5" t="n">
-        <v>482.2256097513479</v>
+        <v>480.9297178701437</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4550686625546874</v>
+        <v>0.484939416912581</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.4872727272727273</v>
+        <v>0.48</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4690909090909091</v>
+        <v>0.46</v>
       </c>
       <c r="C6" t="n">
-        <v>737232.836612127</v>
+        <v>801157.3423117354</v>
       </c>
       <c r="D6" t="n">
-        <v>450.1476864589173</v>
+        <v>466.362455104809</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5220192433629457</v>
+        <v>0.6268968099235901</v>
       </c>
       <c r="F6" t="n">
-        <v>305.21797018054</v>
+        <v>319.1583594899603</v>
       </c>
       <c r="G6" t="n">
-        <v>28151.30979167007</v>
+        <v>31245.70817855237</v>
       </c>
       <c r="H6" t="n">
-        <v>26743.74430208657</v>
+        <v>29683.42276962475</v>
       </c>
       <c r="I6" t="n">
-        <v>23726.42551768566</v>
+        <v>26335.71886188118</v>
       </c>
       <c r="J6" t="n">
-        <v>26.09085637024056</v>
+        <v>28.88565885097099</v>
       </c>
       <c r="K6" t="n">
-        <v>476.2385428291578</v>
+        <v>495.24811395578</v>
       </c>
       <c r="L6" t="n">
-        <v>476.2385428291578</v>
+        <v>495.24811395578</v>
       </c>
       <c r="M6" t="n">
-        <v>1.191842204148483</v>
+        <v>1.205911995239969</v>
       </c>
       <c r="N6" t="n">
-        <v>878665.2089584362</v>
+        <v>966125.2491682959</v>
       </c>
       <c r="O6" t="n">
-        <v>878665.2089584362</v>
+        <v>966125.2491682959</v>
       </c>
       <c r="P6" t="n">
-        <v>388.5029205420147</v>
+        <v>395.4381509119251</v>
       </c>
       <c r="Q6" t="n">
-        <v>399.6032825323343</v>
+        <v>407.5005430786234</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7976540887004913</v>
+        <v>0.834565638608604</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2094035625792643</v>
+        <v>0.2335073972296462</v>
       </c>
       <c r="T6" t="n">
-        <v>1.164912553358657</v>
+        <v>1.118028158715437</v>
       </c>
       <c r="U6" t="n">
-        <v>148.7243927425177</v>
+        <v>153.196012555181</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4166666692465374</v>
+        <v>0.4308176355272215</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6107485176519148</v>
+        <v>0.6282464018457337</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07453709576394417</v>
+        <v>0.06934253978099918</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4690909090909091</v>
+        <v>0.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>143.1749751028715</v>
+        <v>146.8128453653817</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3899769279248844</v>
+        <v>0.4006456594081597</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5769219832901934</v>
+        <v>0.5905700759469498</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06809791262021865</v>
+        <v>0.06303653412570757</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.9012321802103712</v>
+        <v>0.9171648858505781</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9560681380102208</v>
+        <v>0.9625487351605492</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3172193443427873</v>
+        <v>0.3198880964210269</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.9761933687383696</v>
+        <v>0.9631582845564601</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.4325269708169439</v>
+        <v>0.4388269905708816</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06232707720632211</v>
+        <v>0.05834925579202112</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.05814606862117715</v>
+        <v>0.0549523337289925</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9100178948991395</v>
+        <v>0.9235800642707409</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8768611133553561</v>
+        <v>0.8985571868845765</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5351137485676776</v>
+        <v>0.5582533447833075</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.6917854419513849</v>
+        <v>0.6738815078681362</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.4781818181818182</v>
+        <v>0.47</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.9502852782969918</v>
+        <v>0.9441106337703944</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.7292722521339844</v>
+        <v>0.6997795835910243</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.2584998363456069</v>
+        <v>0.2702291259022582</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2469211166043852</v>
+        <v>0.2633787009654358</v>
       </c>
       <c r="AT6" t="n">
-        <v>233.1420590789931</v>
+        <v>245.4971017047085</v>
       </c>
       <c r="AU6" t="n">
-        <v>145.9496839226946</v>
+        <v>150.0044289602814</v>
       </c>
       <c r="AV6" t="n">
-        <v>219.0360723987227</v>
+        <v>232.9083788747501</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9710648144564994</v>
+        <v>0.9690660274864557</v>
       </c>
       <c r="AX6" t="n">
-        <v>437.122579629251</v>
+        <v>451.9360117372478</v>
       </c>
       <c r="AY6" t="n">
-        <v>382.8409603865395</v>
+        <v>389.2738685495074</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.6089788794897985</v>
+        <v>0.6306539471027618</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.548133816646011</v>
+        <v>0.5715535422729794</v>
       </c>
       <c r="BB6" t="n">
-        <v>476.2385428291578</v>
+        <v>495.24811395578</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.9499248865081795</v>
+        <v>0.9455544247192016</v>
       </c>
       <c r="BD6" t="n">
-        <v>697.1557046212456</v>
+        <v>693.9481958894603</v>
       </c>
       <c r="BE6" t="n">
-        <v>483.483513430917</v>
+        <v>482.3700136635113</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.4530373142289574</v>
+        <v>0.4828417444646982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.4690909090909091</v>
+        <v>0.46</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4509090909090909</v>
+        <v>0.44</v>
       </c>
       <c r="C7" t="n">
-        <v>896411.7243581021</v>
+        <v>976333.0336009922</v>
       </c>
       <c r="D7" t="n">
-        <v>490.6846080736466</v>
+        <v>510.9530688810112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5775240542036821</v>
+        <v>0.6761210124044876</v>
       </c>
       <c r="F7" t="n">
-        <v>305.027342843164</v>
+        <v>318.9182225504344</v>
       </c>
       <c r="G7" t="n">
-        <v>29159.11959522752</v>
+        <v>32420.44768448206</v>
       </c>
       <c r="H7" t="n">
-        <v>27409.57241951387</v>
+        <v>30475.22082341314</v>
       </c>
       <c r="I7" t="n">
-        <v>24304.70465887271</v>
+        <v>26994.58467616461</v>
       </c>
       <c r="J7" t="n">
-        <v>26.57229180011015</v>
+        <v>29.41082501447481</v>
       </c>
       <c r="K7" t="n">
-        <v>517.2568998737568</v>
+        <v>540.3638938954861</v>
       </c>
       <c r="L7" t="n">
-        <v>517.2568998737568</v>
+        <v>540.3638938954861</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17839881189298</v>
+        <v>1.190118248300226</v>
       </c>
       <c r="N7" t="n">
-        <v>1056330.510950525</v>
+        <v>1161951.759706859</v>
       </c>
       <c r="O7" t="n">
-        <v>1056330.510950525</v>
+        <v>1161951.759706859</v>
       </c>
       <c r="P7" t="n">
-        <v>405.6187237876152</v>
+        <v>413.9112996715638</v>
       </c>
       <c r="Q7" t="n">
-        <v>416.4567666969414</v>
+        <v>425.6571550240363</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8165580301435587</v>
+        <v>0.8535630098050375</v>
       </c>
       <c r="S7" t="n">
-        <v>0.216376876597049</v>
+        <v>0.2400598207374468</v>
       </c>
       <c r="T7" t="n">
-        <v>1.138611098567634</v>
+        <v>1.08980683236612</v>
       </c>
       <c r="U7" t="n">
-        <v>143.0855535518842</v>
+        <v>146.7023823731998</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3884783109281678</v>
+        <v>0.3997907517459683</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5749916311581553</v>
+        <v>0.5894825635707247</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06878319613947241</v>
+        <v>0.06438513665450284</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4509090909090909</v>
+        <v>0.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>137.5396018638267</v>
+        <v>140.3240179221911</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3637029493998958</v>
+        <v>0.3718561195545131</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5426193749611409</v>
+        <v>0.5533668722833088</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0635050426375063</v>
+        <v>0.05926604822362767</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9082314240413022</v>
+        <v>0.9223288192165986</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9590781341463589</v>
+        <v>0.9647688932887041</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3135637388947004</v>
+        <v>0.3152911401837085</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.9631619594734614</v>
+        <v>0.9490353959753448</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.4022668063591027</v>
+        <v>0.4055641036899751</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05814606862117715</v>
+        <v>0.0549523337289925</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.05588621292034526</v>
+        <v>0.05332955355952145</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.9163305816108738</v>
+        <v>0.9282015055552439</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.8878180821449588</v>
+        <v>0.9091659515468709</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5520080637298939</v>
+        <v>0.575982445993002</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.6634092526159557</v>
+        <v>0.6433682017759724</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.9402043619099909</v>
+        <v>0.9334625504972009</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6947310918948724</v>
+        <v>0.6632177780467126</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.2767951092940352</v>
+        <v>0.2900943487212285</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.268430867578589</v>
+        <v>0.2858176179286323</v>
       </c>
       <c r="AT7" t="n">
-        <v>232.354705660135</v>
+        <v>244.5473088529627</v>
       </c>
       <c r="AU7" t="n">
-        <v>140.3125777078554</v>
+        <v>143.5132001476955</v>
       </c>
       <c r="AV7" t="n">
-        <v>219.1771424810326</v>
+        <v>233.1062666242036</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.9748474336563997</v>
+        <v>0.9733612258030656</v>
       </c>
       <c r="AX7" t="n">
-        <v>478.3426309152907</v>
+        <v>497.3419054538593</v>
       </c>
       <c r="AY7" t="n">
-        <v>400.4850610770606</v>
+        <v>408.3610423371444</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5801832034264713</v>
+        <v>0.5988507313365694</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.5262902659005884</v>
+        <v>0.5476385487072112</v>
       </c>
       <c r="BB7" t="n">
-        <v>517.2568998737568</v>
+        <v>540.3638938954861</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.953836426003048</v>
+        <v>0.9500153366616433</v>
       </c>
       <c r="BD7" t="n">
-        <v>700.0264074646281</v>
+        <v>697.2220865440341</v>
       </c>
       <c r="BE7" t="n">
-        <v>484.4779194379139</v>
+        <v>483.5065311019228</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.4523986206333604</v>
+        <v>0.4821160659256225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.4509090909090909</v>
+        <v>0.44</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4327272727272727</v>
+        <v>0.42</v>
       </c>
       <c r="C8" t="n">
-        <v>1055590.612104077</v>
+        <v>1151508.724890249</v>
       </c>
       <c r="D8" t="n">
-        <v>531.2215296883759</v>
+        <v>555.5436826572135</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6330288650444186</v>
+        <v>0.7253452148853852</v>
       </c>
       <c r="F8" t="n">
-        <v>304.8367155057879</v>
+        <v>318.6780856109085</v>
       </c>
       <c r="G8" t="n">
-        <v>30102.09935387745</v>
+        <v>33500.95798424442</v>
       </c>
       <c r="H8" t="n">
-        <v>28295.9733926448</v>
+        <v>31490.90050518975</v>
       </c>
       <c r="I8" t="n">
-        <v>25024.10932992311</v>
+        <v>27775.85944975432</v>
       </c>
       <c r="J8" t="n">
-        <v>27.20127688383628</v>
+        <v>30.12850141572489</v>
       </c>
       <c r="K8" t="n">
-        <v>558.4228065722122</v>
+        <v>585.6721840729384</v>
       </c>
       <c r="L8" t="n">
-        <v>558.4228065722122</v>
+        <v>585.6721840729384</v>
       </c>
       <c r="M8" t="n">
-        <v>1.167670985903821</v>
+        <v>1.177672429496765</v>
       </c>
       <c r="N8" t="n">
-        <v>1232582.530746385</v>
+        <v>1356100.077628222</v>
       </c>
       <c r="O8" t="n">
-        <v>1232582.530746385</v>
+        <v>1356100.077628222</v>
       </c>
       <c r="P8" t="n">
-        <v>422.0409682773847</v>
+        <v>431.5944818866012</v>
       </c>
       <c r="Q8" t="n">
-        <v>432.7114131192552</v>
+        <v>443.1431860241746</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8368767961831134</v>
+        <v>0.8735346818407171</v>
       </c>
       <c r="S8" t="n">
-        <v>0.224898407578335</v>
+        <v>0.2479496514376259</v>
       </c>
       <c r="T8" t="n">
-        <v>1.108135900730397</v>
+        <v>1.057630898712612</v>
       </c>
       <c r="U8" t="n">
-        <v>137.453646264428</v>
+        <v>140.2183576687997</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3639507017438136</v>
+        <v>0.3729182987142108</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5429472985622027</v>
+        <v>0.5547603063513185</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06531106242877992</v>
+        <v>0.06155061540582864</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4327272727272727</v>
+        <v>0.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>131.9111605279591</v>
+        <v>133.8447959565816</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3406623185119549</v>
+        <v>0.3466906393102497</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5117659305347031</v>
+        <v>0.5199056342222426</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06084099460402899</v>
+        <v>0.05726073777639079</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.9122666573460285</v>
+        <v>0.9250634840182795</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.9607011256326795</v>
+        <v>0.9658277075284067</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3093473990679195</v>
+        <v>0.3104007090008153</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.9501544681563651</v>
+        <v>0.9343405782253686</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3747337243244909</v>
+        <v>0.3755686983259461</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.05588621292034526</v>
+        <v>0.05332955355952145</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.05495409738910737</v>
+        <v>0.05298305124057681</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.9197245813741172</v>
+        <v>0.9304011614670068</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.8987889609078965</v>
+        <v>0.919681194684562</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5698228788563793</v>
+        <v>0.5941952751191257</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.6350030617170878</v>
+        <v>0.6129651554172203</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.4418181818181818</v>
+        <v>0.43</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9307772743377724</v>
+        <v>0.9228658513207149</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.659535285939589</v>
+        <v>0.626434437224918</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.2957742126206846</v>
+        <v>0.3099006959034946</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2906191822167761</v>
+        <v>0.3079061410004507</v>
       </c>
       <c r="AT8" t="n">
-        <v>231.7233404220885</v>
+        <v>243.7328313351152</v>
       </c>
       <c r="AU8" t="n">
-        <v>134.6824033961936</v>
+        <v>137.0315768126907</v>
       </c>
       <c r="AV8" t="n">
-        <v>219.8000440090979</v>
+        <v>233.7385961344311</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.977923314450031</v>
+        <v>0.9768219904140164</v>
       </c>
       <c r="AX8" t="n">
-        <v>519.4939190200721</v>
+        <v>542.6672858551519</v>
       </c>
       <c r="AY8" t="n">
-        <v>417.3563358180036</v>
+        <v>426.5634078858997</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5552170184931275</v>
+        <v>0.5713871064165698</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.5079598950825941</v>
+        <v>0.5274561439870138</v>
       </c>
       <c r="BB8" t="n">
-        <v>558.4228065722122</v>
+        <v>585.6721840729384</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.9569961241646133</v>
+        <v>0.9536316693617251</v>
       </c>
       <c r="BD8" t="n">
-        <v>702.3453293388762</v>
+        <v>699.8761353088137</v>
       </c>
       <c r="BE8" t="n">
-        <v>485.2797017466578</v>
+        <v>484.4259160790691</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.4529347574563203</v>
+        <v>0.4825063820414591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.4327272727272727</v>
+        <v>0.42</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4</v>
       </c>
       <c r="C9" t="n">
-        <v>1214769.499850052</v>
+        <v>1326684.416179506</v>
       </c>
       <c r="D9" t="n">
-        <v>571.7584513031052</v>
+        <v>600.1342964334158</v>
       </c>
       <c r="E9" t="n">
-        <v>0.688533675885155</v>
+        <v>0.7745694173662827</v>
       </c>
       <c r="F9" t="n">
-        <v>304.6460881684118</v>
+        <v>318.4379486713826</v>
       </c>
       <c r="G9" t="n">
-        <v>30967.47133341038</v>
+        <v>34468.44169094269</v>
       </c>
       <c r="H9" t="n">
-        <v>29109.42305340576</v>
+        <v>32400.33518948612</v>
       </c>
       <c r="I9" t="n">
-        <v>25618.28356772528</v>
+        <v>28378.58522352498</v>
       </c>
       <c r="J9" t="n">
-        <v>27.75532778242864</v>
+        <v>30.68127718233382</v>
       </c>
       <c r="K9" t="n">
-        <v>599.5137790855338</v>
+        <v>630.8155736157496</v>
       </c>
       <c r="L9" t="n">
-        <v>599.5137790855338</v>
+        <v>630.8155736157496</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15768306628538</v>
+        <v>1.165693290113776</v>
       </c>
       <c r="N9" t="n">
-        <v>1406318.079416366</v>
+        <v>1546507.122038963</v>
       </c>
       <c r="O9" t="n">
-        <v>1406318.079416366</v>
+        <v>1546507.122038963</v>
       </c>
       <c r="P9" t="n">
-        <v>437.8477003730077</v>
+        <v>448.5811293335067</v>
       </c>
       <c r="Q9" t="n">
-        <v>448.3491609531343</v>
+        <v>459.9048399760116</v>
       </c>
       <c r="R9" t="n">
-        <v>0.858509936700771</v>
+        <v>0.8944153907215435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2349252547741397</v>
+        <v>0.2571861897291074</v>
       </c>
       <c r="T9" t="n">
-        <v>1.07342475970176</v>
+        <v>1.021346802165702</v>
       </c>
       <c r="U9" t="n">
-        <v>131.8286708801491</v>
+        <v>133.7439384419807</v>
       </c>
       <c r="V9" t="n">
-        <v>0.342591946545612</v>
+        <v>0.3496066979914778</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5143764919393815</v>
+        <v>0.5238261269870953</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06328238777185533</v>
+        <v>0.06007271762849982</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>126.2896510952689</v>
+        <v>127.375179468553</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3205101233266683</v>
+        <v>0.3247606974226095</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4842223940785187</v>
+        <v>0.4900738174158448</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05945969904276036</v>
+        <v>0.05647361884275896</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9143518950828022</v>
+        <v>0.9261346803148492</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.9613697576561276</v>
+        <v>0.966053639303701</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3049427604630049</v>
+        <v>0.3055413633176443</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.9365702058623738</v>
+        <v>0.9184878318564227</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.349678887329658</v>
+        <v>0.348515443197201</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.05495409738910737</v>
+        <v>0.05298305124057681</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.05503655341563169</v>
+        <v>0.05362363268321267</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.9211208508505294</v>
+        <v>0.9308701671145395</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.9099398471784493</v>
+        <v>0.9302345150126223</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.588339600104812</v>
+        <v>0.612692386260354</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.6066439254962718</v>
+        <v>0.5827482756531822</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.4236363636363636</v>
+        <v>0.41</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.9214698304797382</v>
+        <v>0.9118030893985957</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.6240587067333256</v>
+        <v>0.5897389048532454</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.3148259049834664</v>
+        <v>0.3290548137454135</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.3125114991290482</v>
+        <v>0.3287489270031773</v>
       </c>
       <c r="AT9" t="n">
-        <v>231.2323509619447</v>
+        <v>243.0290916684654</v>
       </c>
       <c r="AU9" t="n">
-        <v>129.059160987709</v>
+        <v>130.5595589552669</v>
       </c>
       <c r="AV9" t="n">
-        <v>220.8655257840357</v>
+        <v>234.7585290222456</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.9804384596936814</v>
+        <v>0.9796291927865826</v>
       </c>
       <c r="AX9" t="n">
-        <v>560.5739753124611</v>
+        <v>587.9090763786107</v>
       </c>
       <c r="AY9" t="n">
-        <v>433.5440622615748</v>
+        <v>443.98864096928</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5333537489954892</v>
+        <v>0.5473768228347105</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.4926194694208933</v>
+        <v>0.5104502249519497</v>
       </c>
       <c r="BB9" t="n">
-        <v>599.5137790855338</v>
+        <v>630.8155736157496</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.959554343057913</v>
+        <v>0.9565734279744174</v>
       </c>
       <c r="BD9" t="n">
-        <v>704.2228218864077</v>
+        <v>702.0351100104829</v>
       </c>
       <c r="BE9" t="n">
-        <v>485.9278878378072</v>
+        <v>485.1725181690683</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.4545232560469057</v>
+        <v>0.4838660893411097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3963636363636364</v>
+        <v>0.38</v>
       </c>
       <c r="C10" t="n">
-        <v>1373948.387596027</v>
+        <v>1501860.107468763</v>
       </c>
       <c r="D10" t="n">
-        <v>612.2953729178346</v>
+        <v>644.724910209618</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7440384867258915</v>
+        <v>0.8237936198471802</v>
       </c>
       <c r="F10" t="n">
-        <v>304.4554608310358</v>
+        <v>318.1978117318566</v>
       </c>
       <c r="G10" t="n">
-        <v>31741.84314335285</v>
+        <v>35300.51483274155</v>
       </c>
       <c r="H10" t="n">
-        <v>29837.33255475168</v>
+        <v>33182.48394277706</v>
       </c>
       <c r="I10" t="n">
-        <v>26070.91106950254</v>
+        <v>28777.79026689593</v>
       </c>
       <c r="J10" t="n">
-        <v>28.18285836079135</v>
+        <v>31.13272172570939</v>
       </c>
       <c r="K10" t="n">
-        <v>640.4782312786259</v>
+        <v>675.8576319353274</v>
       </c>
       <c r="L10" t="n">
-        <v>640.4782312786259</v>
+        <v>675.8576319353274</v>
       </c>
       <c r="M10" t="n">
-        <v>1.147982451894708</v>
+        <v>1.154409192836292</v>
       </c>
       <c r="N10" t="n">
-        <v>1577268.638769268</v>
+        <v>1733761.114416041</v>
       </c>
       <c r="O10" t="n">
-        <v>1577268.638769268</v>
+        <v>1733761.114416041</v>
       </c>
       <c r="P10" t="n">
-        <v>453.1033420085863</v>
+        <v>464.9475910178317</v>
       </c>
       <c r="Q10" t="n">
-        <v>463.4138009897022</v>
+        <v>476.0410318322521</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8813606724064089</v>
+        <v>0.9161429823179678</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2464124827503199</v>
+        <v>0.2677913753339458</v>
       </c>
       <c r="T10" t="n">
-        <v>1.034492768819151</v>
+        <v>0.9808496374641904</v>
       </c>
       <c r="U10" t="n">
-        <v>126.2106273990476</v>
+        <v>127.2791246927427</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3240414676763747</v>
+        <v>0.3294334212053244</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4890852598687269</v>
+        <v>0.4964808357735057</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06225706311848021</v>
+        <v>0.05955674254758831</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3963636363636364</v>
+        <v>0.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>120.675073565756</v>
+        <v>120.9151684581055</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3029357576384711</v>
+        <v>0.3056686337532866</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.4598000335936211</v>
+        <v>0.4636215813598494</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.05899845700987404</v>
+        <v>0.05656533856380205</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9150471390931563</v>
+        <v>0.9260099220145901</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.9613106284381728</v>
+        <v>0.9656359160614408</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3005928186442215</v>
+        <v>0.3009704212654518</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.9219558552334576</v>
+        <v>0.9009356522330469</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3268191246392216</v>
+        <v>0.3240195410532238</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05503655341563169</v>
+        <v>0.05362363268321267</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05596828032111666</v>
+        <v>0.05514217993091131</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9209974205698894</v>
+        <v>0.9300029272941222</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9213356504222909</v>
+        <v>0.9408894491897043</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6073990115567801</v>
+        <v>0.6312992193976963</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.5783976921119252</v>
+        <v>0.5527890116881644</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.4054545454545455</v>
+        <v>0.39</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.9119342452135049</v>
+        <v>0.8998343775993204</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5885971914566409</v>
+        <v>0.5533859276947037</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.3335365531015797</v>
+        <v>0.347045365911156</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.3333586637768167</v>
+        <v>0.3475497245383432</v>
       </c>
       <c r="AT10" t="n">
-        <v>230.866216623476</v>
+        <v>242.4073881249528</v>
       </c>
       <c r="AU10" t="n">
-        <v>123.4428504824018</v>
+        <v>124.0971465754241</v>
       </c>
       <c r="AV10" t="n">
-        <v>222.3415004644853</v>
+        <v>236.1187938078528</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9824995212043568</v>
+        <v>0.9819122701654925</v>
       </c>
       <c r="AX10" t="n">
-        <v>601.5799107274156</v>
+        <v>633.0633002161693</v>
       </c>
       <c r="AY10" t="n">
-        <v>449.1210795174309</v>
+        <v>460.7234794998857</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.5140400376476114</v>
+        <v>0.5261450716340429</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4797904162319629</v>
+        <v>0.496005129849934</v>
       </c>
       <c r="BB10" t="n">
-        <v>640.4782312786259</v>
+        <v>675.8576319353274</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.9616335260819933</v>
+        <v>0.9589964851937584</v>
       </c>
       <c r="BD10" t="n">
-        <v>705.7487470693108</v>
+        <v>703.8134065759058</v>
       </c>
       <c r="BE10" t="n">
-        <v>486.454062468739</v>
+        <v>485.7866149091607</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.457065769655842</v>
+        <v>0.4860545485634791</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.3963636363636364</v>
+        <v>0.38</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3781818181818182</v>
+        <v>0.36</v>
       </c>
       <c r="C11" t="n">
-        <v>1533127.275342002</v>
+        <v>1677035.79875802</v>
       </c>
       <c r="D11" t="n">
-        <v>652.8322945325638</v>
+        <v>689.3155239858202</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7995432975666279</v>
+        <v>0.8730178223280778</v>
       </c>
       <c r="F11" t="n">
-        <v>304.2648334936598</v>
+        <v>317.9576747923307</v>
       </c>
       <c r="G11" t="n">
-        <v>32409.0250305141</v>
+        <v>35971.23456066404</v>
       </c>
       <c r="H11" t="n">
-        <v>30464.48352868325</v>
+        <v>33812.9604870242</v>
       </c>
       <c r="I11" t="n">
-        <v>26364.60592261756</v>
+        <v>28947.99391188</v>
       </c>
       <c r="J11" t="n">
-        <v>28.53486721278025</v>
+        <v>31.43492666550697</v>
       </c>
       <c r="K11" t="n">
-        <v>681.367161745344</v>
+        <v>720.7504506513271</v>
       </c>
       <c r="L11" t="n">
-        <v>681.367161745344</v>
+        <v>720.7504506513271</v>
       </c>
       <c r="M11" t="n">
-        <v>1.138773496746965</v>
+        <v>1.143445700762667</v>
       </c>
       <c r="N11" t="n">
-        <v>1745884.708299359</v>
+        <v>1917599.374114942</v>
       </c>
       <c r="O11" t="n">
-        <v>1745884.708299359</v>
+        <v>1917599.374114942</v>
       </c>
       <c r="P11" t="n">
-        <v>467.8618047637236</v>
+        <v>480.7572102344857</v>
       </c>
       <c r="Q11" t="n">
-        <v>477.9774150869619</v>
+        <v>491.5970159626582</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9053368115468732</v>
+        <v>0.9386586488448447</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2593281579457174</v>
+        <v>0.2797988555831039</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9914264016941713</v>
+        <v>0.936112743118563</v>
       </c>
       <c r="U11" t="n">
-        <v>120.5995158211233</v>
+        <v>120.8239164210857</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3080365588773158</v>
+        <v>0.3120982459958888</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4669258004553202</v>
+        <v>0.4725782428204697</v>
       </c>
       <c r="X11" t="n">
-        <v>0.06198837150524647</v>
+        <v>0.05978860244442107</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3781818181818182</v>
+        <v>0.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>115.0674279394204</v>
+        <v>114.4647629252391</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2876863923073513</v>
+        <v>0.2891523993771854</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4383203510393384</v>
+        <v>0.4403965810603694</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05924052481935393</v>
+        <v>0.05737412457430583</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9146823288855837</v>
+        <v>0.9249090728107872</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.9606422341452905</v>
+        <v>0.964644948537006</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2964891248538185</v>
+        <v>0.2968892933725633</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.9058967864584878</v>
+        <v>0.8811792882853329</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3059017857126065</v>
+        <v>0.3018091674062724</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.05596828032111666</v>
+        <v>0.05514217993091131</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.05769869756874035</v>
+        <v>0.05752573087238778</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.919601546348912</v>
+        <v>0.9279438309919011</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.9329895228460818</v>
+        <v>0.9516517986909254</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.626861717480877</v>
+        <v>0.6498642089175687</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.5503288594011785</v>
+        <v>0.5231514340937399</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.3872727272727273</v>
+        <v>0.37</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.9018929053532764</v>
+        <v>0.8865900062790161</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5534022061004289</v>
+        <v>0.5175775704862552</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.3515640459520979</v>
+        <v>0.3634385721852762</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.3524945803580589</v>
+        <v>0.3636017177990777</v>
       </c>
       <c r="AT11" t="n">
-        <v>230.6061116032338</v>
+        <v>241.8352353784946</v>
       </c>
       <c r="AU11" t="n">
-        <v>117.8334718802719</v>
+        <v>117.6443396731624</v>
       </c>
       <c r="AV11" t="n">
-        <v>224.1950351806423</v>
+        <v>237.7727140876044</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9841855797325036</v>
+        <v>0.9837657808077149</v>
       </c>
       <c r="AX11" t="n">
-        <v>642.5081302626319</v>
+        <v>678.1250246767895</v>
       </c>
       <c r="AY11" t="n">
-        <v>464.1475800616227</v>
+        <v>476.838883454493</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.4968379056777962</v>
+        <v>0.5071634125692563</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.4690494322620932</v>
+        <v>0.4836740386269262</v>
       </c>
       <c r="BB11" t="n">
-        <v>681.367161745344</v>
+        <v>720.7504506513271</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.963332105015768</v>
+        <v>0.9610099040597198</v>
       </c>
       <c r="BD11" t="n">
-        <v>706.9953445742814</v>
+        <v>705.2910670395207</v>
       </c>
       <c r="BE11" t="n">
-        <v>486.8834963682344</v>
+        <v>486.2963034800401</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.4604695719878776</v>
+        <v>0.4889461679762978</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.3781818181818182</v>
+        <v>0.36</v>
       </c>
       <c r="B12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="C12" t="n">
-        <v>1692306.163087977</v>
+        <v>1852211.490047277</v>
       </c>
       <c r="D12" t="n">
-        <v>693.3692161472932</v>
+        <v>733.9061377620225</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8550481084073642</v>
+        <v>0.9222420248089752</v>
       </c>
       <c r="F12" t="n">
-        <v>304.0742061562837</v>
+        <v>317.7175378528048</v>
       </c>
       <c r="G12" t="n">
-        <v>32950.60162525447</v>
+        <v>36451.12679313811</v>
       </c>
       <c r="H12" t="n">
-        <v>30973.5655277392</v>
+        <v>34264.05918554982</v>
       </c>
       <c r="I12" t="n">
-        <v>26481.7923777957</v>
+        <v>28864.07651118118</v>
       </c>
       <c r="J12" t="n">
-        <v>28.77136958159965</v>
+        <v>31.51768753680687</v>
       </c>
       <c r="K12" t="n">
-        <v>722.1405857288928</v>
+        <v>765.4238252988293</v>
       </c>
       <c r="L12" t="n">
-        <v>722.1405857288928</v>
+        <v>765.4238252988293</v>
       </c>
       <c r="M12" t="n">
-        <v>1.129775702180906</v>
+        <v>1.132449473453603</v>
       </c>
       <c r="N12" t="n">
-        <v>1911926.383707795</v>
+        <v>2097535.926628753</v>
       </c>
       <c r="O12" t="n">
-        <v>1911926.383707795</v>
+        <v>2097535.926628753</v>
       </c>
       <c r="P12" t="n">
-        <v>482.1687445015359</v>
+        <v>496.0632298322525</v>
       </c>
       <c r="Q12" t="n">
-        <v>492.0708672487102</v>
+        <v>506.603008896214</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9303513496768336</v>
+        <v>0.96190705172687</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2736499133886414</v>
+        <v>0.2932530053009496</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9444106543470056</v>
+        <v>0.8872211306101805</v>
       </c>
       <c r="U12" t="n">
-        <v>114.9953361463764</v>
+        <v>114.3783136270097</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2943844626887498</v>
+        <v>0.2973896404921909</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4477871160479379</v>
+        <v>0.4520182502539921</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06233423933419938</v>
+        <v>0.06065325365644233</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>109.4667142162621</v>
+        <v>108.0239628699536</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2745921648935793</v>
+        <v>0.2750245887082247</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4196725451948258</v>
+        <v>0.4202912862275296</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.06007918984763523</v>
+        <v>0.05882630642640048</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9134172852659774</v>
+        <v>0.9229291937490361</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.9593996466991872</v>
+        <v>0.9630874440313256</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2927849636055536</v>
+        <v>0.2934820178822601</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.8880031547486461</v>
+        <v>0.8586988057021904</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2867458717764375</v>
+        <v>0.2816829056940597</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.05769869756874035</v>
+        <v>0.05752573087238778</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.06024311495516003</v>
+        <v>0.05990928181386426</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.9170034700986963</v>
+        <v>0.9247025736427814</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.9448754981880104</v>
+        <v>0.9624972478790979</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.6466069537807679</v>
+        <v>0.6682440327388768</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.5224960521339288</v>
+        <v>0.4938897903379407</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.3690909090909091</v>
+        <v>0.35</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.891125707843446</v>
+        <v>0.8717124787971834</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5186810748370121</v>
+        <v>0.4824750265353266</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.3686296557095172</v>
+        <v>0.3778226884592427</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.369322079911634</v>
+        <v>0.3762237791668638</v>
       </c>
       <c r="AT12" t="n">
-        <v>230.4309291739589</v>
+        <v>241.2767637356463</v>
       </c>
       <c r="AU12" t="n">
-        <v>112.2310251813192</v>
+        <v>111.2011382484817</v>
       </c>
       <c r="AV12" t="n">
-        <v>226.3931305889214</v>
+        <v>239.6715229207628</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9855562980212427</v>
+        <v>0.9852599002879876</v>
       </c>
       <c r="AX12" t="n">
-        <v>683.3543978280171</v>
+        <v>723.0882881121523</v>
       </c>
       <c r="AY12" t="n">
-        <v>478.6739282556907</v>
+        <v>492.3936463887453</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4813943596503356</v>
+        <v>0.4900078737920149</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.4600823695471778</v>
+        <v>0.473095340359227</v>
       </c>
       <c r="BB12" t="n">
-        <v>722.1405857288928</v>
+        <v>765.4238252988293</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.964720702205309</v>
+        <v>0.9626967998217312</v>
       </c>
       <c r="BD12" t="n">
-        <v>708.0144445745645</v>
+        <v>706.5290901930256</v>
       </c>
       <c r="BE12" t="n">
-        <v>487.2342796497917</v>
+        <v>486.7229231726419</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.4646494305606851</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.3418181818181818</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1851485.050833953</v>
-      </c>
-      <c r="D13" t="n">
-        <v>733.9061377620225</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.9105529192481008</v>
-      </c>
-      <c r="F13" t="n">
-        <v>303.8835788189076</v>
-      </c>
-      <c r="G13" t="n">
-        <v>33345.94627631325</v>
-      </c>
-      <c r="H13" t="n">
-        <v>31345.18949973445</v>
-      </c>
-      <c r="I13" t="n">
-        <v>26405.21787212439</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28.83277439735654</v>
-      </c>
-      <c r="K13" t="n">
-        <v>762.738912159379</v>
-      </c>
-      <c r="L13" t="n">
-        <v>762.738912159379</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.120704655559663</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2074967.91616873</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2074967.91616873</v>
-      </c>
-      <c r="P13" t="n">
-        <v>496.0632298322525</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>505.7137107564316</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.9563228060522342</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2893648447936687</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.8937479270607351</v>
-      </c>
-      <c r="U13" t="n">
-        <v>109.3980883748067</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.2829425165503032</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.4315857646823992</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.06321492940044968</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.3418181818181818</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>103.8729323962811</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.2635258235764881</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.4037721457639878</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.06146486450733273</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.911323283849541</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.9575696090057074</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.2896206528383063</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.8678750646782986</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.2692139766992855</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.06024311495516003</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.06278753234157972</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.913169815632715</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.9569462075289707</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.6665234722823843</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.4949506459215169</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.3509090909090909</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.8794336703204269</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.4846039415140186</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.3844830243989099</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.38327112316428</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>230.3174765589782</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>106.6355103855439</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>228.9013479408027</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.9866572553880303</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>724.1138155967068</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>492.742693877419</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.4674193639414468</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.4526302986692191</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>762.738912159379</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0.9658543021211022</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>708.8464005105317</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>487.5204591513892</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0.4695215219054474</v>
+        <v>0.492418810600689</v>
       </c>
     </row>
   </sheetData>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -430,11 +430,11 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
@@ -506,2614 +506,2739 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн</t>
+          <t>σ_вх_вна</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на входе в ступень</t>
+          <t>Коэффициент сохранения полного давления в ВНА</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.36</v>
-      </c>
+        <v>0.9916542660879368</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr"/>
+      <c r="L2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн_plus_1</t>
+          <t>P1_полн_вна</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Полное давление в ВНА</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.34</v>
-      </c>
+        <v>100454.577154708</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr"/>
+      <c r="M3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i</t>
+          <t>c_1u_вна</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед ступенью</t>
+          <t>Окружная скорость в ВНА</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>100454.577154708</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>275630.2684439648</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>450805.9597332217</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>625981.6510224786</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>801157.3423117354</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>976333.0336009922</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1151508.724890249</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1326684.416179506</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1501860.107468763</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1677035.79875802</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>1852211.490047277</v>
-      </c>
+        <v>0.2874142865400933</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
+      <c r="L4" s="1" t="inlineStr"/>
+      <c r="M4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i</t>
+          <t>α_1_вна_deg</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Полная температура перед ступенью</t>
+          <t>Угол входа в ВНА</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>332.5906137762022</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>377.1812275524045</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>421.7718413286067</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>466.362455104809</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>510.9530688810112</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>555.5436826572135</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>600.1342964334158</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>644.724910209618</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>689.3155239858202</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>733.9061377620225</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+        <v>90</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="inlineStr"/>
+      <c r="G5" s="1" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
+      <c r="L5" s="1" t="inlineStr"/>
+      <c r="M5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>d1_отн_i</t>
+          <t>α_2_вна_deg</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на входе в ступень</t>
+          <t>Угол выхода из ВНА</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.4792242024808975</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.528448404961795</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.5776726074426926</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.6268968099235901</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.6761210124044876</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0.7253452148853852</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.7745694173662827</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.8237936198471802</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0.8730178223280778</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.9222420248089752</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+        <v>62.83130053977735</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
+      <c r="L6" s="1" t="inlineStr"/>
+      <c r="M6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>U_k_i</t>
+          <t>c_a_i_отн</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Окружная скорость концов рабочих лопаток ступени</t>
+          <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>320.118907248064</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>319.8787703085381</v>
+        <v>0.54</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>319.6386333690122</v>
+        <v>0.52</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>319.3984964294863</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>319.1583594899603</v>
+        <v>0.48</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>318.9182225504344</v>
+        <v>0.46</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>318.6780856109085</v>
+        <v>0.44</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>318.4379486713826</v>
+        <v>0.42</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>318.1978117318566</v>
+        <v>0.4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>317.9576747923307</v>
+        <v>0.38</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>317.7175378528048</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Hт_i</t>
+          <t>c_a_i_отн_plus_1</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Теоретический напор i-й ступени</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25854.06962501386</v>
+        <v>0.54</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>27290.43088549179</v>
+        <v>0.52</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28671.32907065673</v>
+        <v>0.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>29992.58961708235</v>
+        <v>0.48</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>31245.70817855237</v>
+        <v>0.46</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>32420.44768448206</v>
+        <v>0.44</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33500.95798424442</v>
+        <v>0.42</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34468.44169094269</v>
+        <v>0.4</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>35300.51483274155</v>
+        <v>0.38</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>35971.23456066404</v>
+        <v>0.36</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>36451.12679313811</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>L_z_i</t>
+          <t>P1_полн_i</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Действительная работа сжатия i-й ступени</t>
+          <t>Полное давление перед ступенью</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25595.52892876372</v>
+        <v>100454.577154708</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>26744.62226778196</v>
+        <v>275630.2684439648</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27811.18919853703</v>
+        <v>450805.9597332217</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>28792.88603239906</v>
+        <v>625981.6510224786</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29683.42276962475</v>
+        <v>801157.3423117354</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>30475.22082341314</v>
+        <v>976333.0336009922</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31490.90050518975</v>
+        <v>1151508.724890249</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32400.33518948612</v>
+        <v>1326684.416179506</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>33182.48394277706</v>
+        <v>1501860.107468763</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>33812.9604870242</v>
+        <v>1677035.79875802</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>34264.05918554982</v>
+        <v>1852211.490047277</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>H_ад_i</t>
+          <t>T1_полн_i</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Адиабатическая работа сжатия i-й ступени</t>
+          <t>Полная температура перед ступенью</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>22295.79183775567</v>
+        <v>288</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>23488.46488831931</v>
+        <v>332.5906137762022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>24567.82272902698</v>
+        <v>377.1812275524045</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>25521.82283354585</v>
+        <v>421.7718413286067</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>26335.71886188118</v>
+        <v>466.362455104809</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>26994.58467616461</v>
+        <v>510.9530688810112</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27775.85944975432</v>
+        <v>555.5436826572135</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28378.58522352498</v>
+        <v>600.1342964334158</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>28777.79026689593</v>
+        <v>644.724910209618</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>28947.99391188</v>
+        <v>689.3155239858202</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28864.07651118118</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+        <v>733.9061377620225</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ΔT_полн_i</t>
+          <t>d1_отн_i</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Повышение полной температуры в ступени</t>
+          <t>Относительный диаметр втулки на входе в ступень</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25.44287169857228</v>
+        <v>0.43</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>26.47303378928586</v>
+        <v>0.4792242024808975</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27.3954765882457</v>
+        <v>0.528448404961795</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>28.21137563959589</v>
+        <v>0.5776726074426926</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>28.88565885097099</v>
+        <v>0.6268968099235901</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>29.41082501447481</v>
+        <v>0.6761210124044876</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.12850141572489</v>
+        <v>0.7253452148853852</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>30.68127718233382</v>
+        <v>0.7745694173662827</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>31.13272172570939</v>
+        <v>0.8237936198471802</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>31.43492666550697</v>
+        <v>0.8730178223280778</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>31.51768753680687</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+        <v>0.9222420248089752</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>T3_полн_i</t>
+          <t>U_k_i</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из ступени</t>
+          <t>Окружная скорость концов рабочих лопаток ступени</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>313.4428716985723</v>
+        <v>320.118907248064</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>359.0636475654881</v>
+        <v>320.118907248064</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>404.5767041406502</v>
+        <v>320.118907248064</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>449.9832169682026</v>
+        <v>320.118907248064</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>495.24811395578</v>
+        <v>320.118907248064</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>540.3638938954861</v>
+        <v>320.118907248064</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>585.6721840729384</v>
+        <v>320.118907248064</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>630.8155736157496</v>
+        <v>320.118907248064</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>675.8576319353274</v>
+        <v>320.118907248064</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>720.7504506513271</v>
+        <v>320.118907248064</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>765.4238252988293</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+        <v>320.118907248064</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i_plus_1</t>
+          <t>Hт_i</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на входе в следующую ступень</t>
+          <t>Теоретический напор i-й ступени</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>313.4428716985723</v>
+        <v>25854.06962501386</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>359.0636475654881</v>
+        <v>27331.42079188165</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>404.5767041406502</v>
+        <v>28757.55416446405</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>449.9832169682026</v>
+        <v>30128.04018314102</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>495.24811395578</v>
+        <v>31434.06707948137</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>540.3638938954861</v>
+        <v>32665.02456757352</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>585.6721840729384</v>
+        <v>33804.57486335634</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>630.8155736157496</v>
+        <v>34833.30366020297</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>675.8576319353274</v>
+        <v>35728.04999640283</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>720.7504506513271</v>
+        <v>36461.90625516191</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>765.4238252988293</v>
+        <v>37004.21816460253</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>π_полн_i</t>
+          <t>L_z_i</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Степень повышения полного давления в ступени</t>
+          <t>Действительная работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.296254706516713</v>
+        <v>25595.52892876372</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.26680303387504</v>
+        <v>26784.79237604402</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.24315904184726</v>
+        <v>27894.82753953012</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.223349171219593</v>
+        <v>28922.91857581538</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.205911995239969</v>
+        <v>29862.3637255073</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.190118248300226</v>
+        <v>30705.12309351911</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.177672429496765</v>
+        <v>31776.30037155496</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.165693290113776</v>
+        <v>32743.30544059079</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.154409192836292</v>
+        <v>33584.36699661866</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.143445700762667</v>
+        <v>34274.19187985219</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.132449473453603</v>
+        <v>34783.96507472637</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>P3_полн_i</t>
+          <t>H_ад_i</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Полное давление на выходе из ступени</t>
+          <t>Адиабатическая работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>130214.7184279365</v>
+        <v>22295.79183775567</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>349169.2602926063</v>
+        <v>23523.74428647369</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>560423.5049609866</v>
+        <v>24641.70708974955</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>765794.1339770217</v>
+        <v>25637.08281588775</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>966125.2491682959</v>
+        <v>26494.47881162058</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1161951.759706859</v>
+        <v>27198.22934648805</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1356100.077628222</v>
+        <v>28027.59015443303</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1546507.122038963</v>
+        <v>28678.98367444181</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1733761.114416041</v>
+        <v>29126.32674943345</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1917599.374114942</v>
+        <v>29342.86390726762</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2097535.926628753</v>
+        <v>29302.04573375754</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i_plus_1</t>
+          <t>ΔT_полн_i</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед следующей ступенью</t>
+          <t>Повышение полной температуры в ступени</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>130214.7184279365</v>
+        <v>25.44287169857228</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>349169.2602926063</v>
+        <v>26.51279597484575</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>560423.5049609866</v>
+        <v>27.47786473052178</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>765794.1339770217</v>
+        <v>28.33878200391665</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>966125.2491682959</v>
+        <v>29.05979063645292</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1161951.759706859</v>
+        <v>29.63269758024544</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1356100.077628222</v>
+        <v>30.40155395280349</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1546507.122038963</v>
+        <v>31.00605053044571</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1733761.114416041</v>
+        <v>31.50977949218357</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1917599.374114942</v>
+        <v>31.86372008674383</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2097535.926628753</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+        <v>31.9959213407726</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>a_кр_1_i</t>
+          <t>T3_полн_i</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на входе в ступень</t>
+          <t>Полная температура на выходе из ступени</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>310.7513475433373</v>
+        <v>313.4428716985723</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>333.9425591312983</v>
+        <v>359.103409751048</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>355.6246133190464</v>
+        <v>404.6590922829263</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>376.0586369138221</v>
+        <v>450.1106233325234</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>395.4381509119251</v>
+        <v>495.4222457412619</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>413.9112996715638</v>
+        <v>540.5857664612566</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>431.5944818866012</v>
+        <v>585.945236610017</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>448.5811293335067</v>
+        <v>631.1403469638615</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>464.9475910178317</v>
+        <v>676.2346897018016</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>480.7572102344857</v>
+        <v>721.179244072564</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>496.0632298322525</v>
+        <v>765.9020591027951</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>a_кр_3_i</t>
+          <t>T1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на выходе из ступени</t>
+          <t>Полная температура на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>324.1872836502556</v>
+        <v>313.4428716985723</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>346.9784446168208</v>
+        <v>359.103409751048</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>368.3131397308003</v>
+        <v>404.6590922829263</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>388.4319408203171</v>
+        <v>450.1106233325234</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>407.5005430786234</v>
+        <v>495.4222457412619</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>425.6571550240363</v>
+        <v>540.5857664612566</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>443.1431860241746</v>
+        <v>585.945236610017</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>459.9048399760116</v>
+        <v>631.1403469638615</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>476.0410318322521</v>
+        <v>676.2346897018016</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>491.5970159626582</v>
+        <v>721.179244072564</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>506.603008896214</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+        <v>765.9020591027951</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>r_ср1_отн_i</t>
+          <t>π_полн_i</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на входе в ступень</t>
+          <t>Степень повышения полного давления в ступени</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.7697077367416805</v>
+        <v>1.296254706516713</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.7841096339936948</v>
+        <v>1.267238208318879</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.7997680028316541</v>
+        <v>1.243948169558088</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.8166105685666942</v>
+        <v>1.224431804357842</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.834565638608604</v>
+        <v>1.207237883003242</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.8535630098050375</v>
+        <v>1.191643396458117</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.8735346818407171</v>
+        <v>1.179378648812314</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8944153907215435</v>
+        <v>1.167545318776542</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.9161429823179678</v>
+        <v>1.156377337391831</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.9386586488448447</v>
+        <v>1.145498252598538</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.96190705172687</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+        <v>1.134550633368947</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>c_u1_отн_i</t>
+          <t>P3_полн_i</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на входе</t>
+          <t>Полное давление на выходе из ступени</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2209646382902902</v>
+        <v>130214.7184279365</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2219828355331729</v>
+        <v>349289.2075413818</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2244413126796626</v>
+        <v>560779.2484360184</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.2282925458895157</v>
+        <v>766471.8424563546</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.2335073972296462</v>
+        <v>967187.4938849231</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.2400598207374468</v>
+        <v>1163440.812234543</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.2479496514376259</v>
+        <v>1358064.804056653</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2571861897291074</v>
+        <v>1548964.179604172</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.2677913753339458</v>
+        <v>1736716.992209737</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.2797988555831039</v>
+        <v>1921041.577022505</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.2932530053009496</v>
+        <v>2101427.71916638</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>α_1_i</t>
+          <t>P1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на входе в РК</t>
+          <t>Полное давление перед следующей ступенью</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.194971328079617</v>
+        <v>130214.7184279365</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.180775445352064</v>
+        <v>349289.2075413818</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.16333363127941</v>
+        <v>560779.2484360184</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.142479748812273</v>
+        <v>766471.8424563546</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1.118028158715437</v>
+        <v>967187.4938849231</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.08980683236612</v>
+        <v>1163440.812234543</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1.057630898712612</v>
+        <v>1358064.804056653</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.021346802165702</v>
+        <v>1548964.179604172</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.9808496374641904</v>
+        <v>1736716.992209737</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.936112743118563</v>
+        <v>1921041.577022505</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.8872211306101805</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+        <v>2101427.71916638</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>c_a1_i</t>
+          <t>a_кр_1_i</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на входе в ступень</t>
+          <t>Критическая скорость потока на входе в ступень</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>179.2665880589159</v>
+        <v>310.7513475433373</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>172.7345359666106</v>
+        <v>333.9425591312983</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>166.2120893518864</v>
+        <v>355.6246133190464</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>159.6992482147431</v>
+        <v>376.0586369138221</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>153.196012555181</v>
+        <v>395.4381509119251</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>146.7023823731998</v>
+        <v>413.9112996715638</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>140.2183576687997</v>
+        <v>431.5944818866012</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>133.7439384419807</v>
+        <v>448.5811293335067</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>127.2791246927427</v>
+        <v>464.9475910178317</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>120.8239164210857</v>
+        <v>480.7572102344857</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>114.3783136270097</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+        <v>496.0632298322525</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>λ_1_i</t>
+          <t>a_кр_3_i</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на входе в ступень</t>
+          <t>Критическая скорость потока на выходе из ступени</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.620165498278116</v>
+        <v>324.1872836502556</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.5592578656405074</v>
+        <v>346.9976560288648</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.5090576493297847</v>
+        <v>368.3506395304143</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.4668369588793164</v>
+        <v>388.486926425324</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.4308176355272215</v>
+        <v>407.5721764265136</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.3997907517459683</v>
+        <v>425.7445331351412</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.3729182987142108</v>
+        <v>443.2464752655555</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3496066979914778</v>
+        <v>460.0232149978768</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.3294334212053244</v>
+        <v>476.173803833237</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.3120982459958888</v>
+        <v>491.7432262243484</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.2973896404921909</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+        <v>506.761245970099</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>q_1_i</t>
+          <t>r_ср1_отн_i</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на входе</t>
+          <t>Относительный средний радиус на входе в ступень</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.8289595144665948</v>
+        <v>0.7697077367416805</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.7716834611885978</v>
+        <v>0.7841096339936948</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.7190919144876908</v>
+        <v>0.7997680028316541</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.671347407885214</v>
+        <v>0.8166105685666942</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.6282464018457337</v>
+        <v>0.834565638608604</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.5894825635707247</v>
+        <v>0.8535630098050375</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.5547603063513185</v>
+        <v>0.8735346818407171</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5238261269870953</v>
+        <v>0.8944153907215435</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.4964808357735057</v>
+        <v>0.9161429823179678</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.4725782428204697</v>
+        <v>0.9386586488448447</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.4520182502539921</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+        <v>0.96190705172687</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>F_1_i</t>
+          <t>c_u1_отн_i</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в ступень</t>
+          <t>Безразмерная окружная составляющая скорости на входе</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.3184019113646743</v>
+        <v>0.2209646382902902</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.1347270471899817</v>
+        <v>0.2219828355331729</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.09483275212219863</v>
+        <v>0.2244413126796626</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.07807446227001276</v>
+        <v>0.2282925458895157</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.06934253978099918</v>
+        <v>0.2335073972296462</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.06438513665450284</v>
+        <v>0.2400598207374468</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.06155061540582864</v>
+        <v>0.2479496514376259</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.06007271762849982</v>
+        <v>0.2571861897291074</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.05955674254758831</v>
+        <v>0.2677913753339458</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.05978860244442107</v>
+        <v>0.2797988555831039</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.06065325365644233</v>
+        <v>0.2932530053009496</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>c_a3_отн_i</t>
+          <t>α_1_i</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Угол абсолютной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.54</v>
+        <v>1.194971328079617</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.52</v>
+        <v>1.180775445352064</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.5</v>
+        <v>1.16333363127941</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.48</v>
+        <v>1.142479748812273</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.46</v>
+        <v>1.118028158715437</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.44</v>
+        <v>1.08980683236612</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.42</v>
+        <v>1.057630898712612</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4</v>
+        <v>1.021346802165702</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.38</v>
+        <v>0.9808496374641904</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.36</v>
+        <v>0.936112743118563</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.34</v>
+        <v>0.8872211306101805</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>c_a3_i</t>
+          <t>c_a1_i</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из ступени</t>
+          <t>Осевая скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
+        <v>179.2665880589159</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>172.8642099139546</v>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>166.3369605604398</v>
-      </c>
       <c r="E27" s="2" t="n">
-        <v>159.8193166845061</v>
+        <v>166.4618317689933</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>153.3112782861534</v>
+        <v>160.059453624032</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>146.8128453653817</v>
+        <v>153.6570754790708</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>140.3240179221911</v>
+        <v>147.2546973341095</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>133.8447959565816</v>
+        <v>140.8523191891482</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>127.375179468553</v>
+        <v>134.4499410441869</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>120.9151684581055</v>
+        <v>128.0475628992256</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>114.4647629252391</v>
+        <v>121.6451847542643</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>108.0239628699536</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+        <v>115.242806609303</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i_0</t>
+          <t>λ_1_i</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе (1-е приближение)</t>
+          <t>Приведенная скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.5732319379046732</v>
+        <v>0.620165498278116</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.5183116372595099</v>
+        <v>0.5596777074203516</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.4726157899444055</v>
+        <v>0.5098225352552679</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.4338874584941147</v>
+        <v>0.4678899206166077</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.4006456594081597</v>
+        <v>0.4321142361070043</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.3718561195545131</v>
+        <v>0.4012959107614564</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.3466906393102497</v>
+        <v>0.3746043536327617</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3247606974226095</v>
+        <v>0.3514521890201256</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.3056686337532866</v>
+        <v>0.3314223508743308</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.2891523993771854</v>
+        <v>0.3142196505478131</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.2750245887082247</v>
+        <v>0.2996373677847143</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>q_3_i</t>
+          <t>q_1_i</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на выходе</t>
+          <t>Газодинамическая функция расхода на входе</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.785474428031451</v>
+        <v>0.8289595144665948</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.7291365225735928</v>
+        <v>0.772103307484864</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.6780635604689873</v>
+        <v>0.7199280026662993</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6320011104413988</v>
+        <v>0.6725753454599247</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.5905700759469498</v>
+        <v>0.6298340862459014</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.5533668722833088</v>
+        <v>0.5913965269212992</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.5199056342222426</v>
+        <v>0.5569689672683231</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4900738174158448</v>
+        <v>0.5263015498370621</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.4636215813598494</v>
+        <v>0.4991997626465075</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.4403965810603694</v>
+        <v>0.4755227615328155</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.4202912862275296</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+        <v>0.4551762689534743</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>F_3_i_0</t>
+          <t>F_1_i</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на выходе (1-е приближение)</t>
+          <t>Кольцевая площадь на входе в ступень</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.2704391390523389</v>
+        <v>0.3184019113646743</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1169517598723287</v>
+        <v>0.1346537867192373</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.08378592377249121</v>
+        <v>0.09472261813282659</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.07002408006027119</v>
+        <v>0.07793191977794278</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.06303653412570757</v>
+        <v>0.06916774125693943</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.05926604822362767</v>
+        <v>0.06417676412225284</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.05726073777639079</v>
+        <v>0.06130653638769019</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.05647361884275896</v>
+        <v>0.05979016976611325</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.05656533856380205</v>
+        <v>0.05923236253001255</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.05737412457430583</v>
+        <v>0.05941838113658058</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.05882630642640048</v>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+        <v>0.0602324406169755</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i_0</t>
+          <t>c_a3_отн_i</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.5645174635893465</v>
+        <v>0.54</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.8398584757481505</v>
+        <v>0.52</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.8882101567499902</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9075172909297876</v>
+        <v>0.48</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.9171648858505781</v>
+        <v>0.46</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.9223288192165986</v>
+        <v>0.44</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.9250634840182795</v>
+        <v>0.42</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9261346803148492</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.9260099220145901</v>
+        <v>0.38</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.9249090728107872</v>
+        <v>0.36</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.9229291937490361</v>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>r_ср3_отн_i</t>
+          <t>c_a3_i</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из ступени</t>
+          <t>Осевая скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.8156702574457798</v>
+        <v>172.8642099139546</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.9280196282595528</v>
+        <v>166.4618317689933</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.9495815682954533</v>
+        <v>160.059453624032</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9582543821541679</v>
+        <v>153.6570754790708</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.9625487351605492</v>
+        <v>147.2546973341095</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.9647688932887041</v>
+        <v>140.8523191891482</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.9658277075284067</v>
+        <v>134.4499410441869</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.966053639303701</v>
+        <v>128.0475628992256</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.9656359160614408</v>
+        <v>121.6451847542643</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0.964644948537006</v>
+        <v>115.242806609303</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.9630874440313256</v>
+        <v>108.8404284643418</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>c_3u_отн_i</t>
+          <t>λ_3_i_0</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе</t>
+          <t>Приведенная скорость на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.2506450778768315</v>
+        <v>0.5732319379046732</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.3172873666619888</v>
+        <v>0.5186720225032211</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.3245183178108368</v>
+        <v>0.4732777332881704</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.3234929436994191</v>
+        <v>0.434804551844695</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.3198880964210269</v>
+        <v>0.401780825685309</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.3152911401837085</v>
+        <v>0.3731795027985815</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.3104007090008153</v>
+        <v>0.3481769583530256</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3055413633176443</v>
+        <v>0.3263910224267986</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.3009704212654518</v>
+        <v>0.3074283408444913</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.2968892933725633</v>
+        <v>0.2910312774461808</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.2934820178822601</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+        <v>0.2770167507220872</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>α_3_i</t>
+          <t>q_3_i</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из ступени</t>
+          <t>Газодинамическая функция расхода на выходе</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1.136231551777349</v>
+        <v>0.785474428031451</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.022933872832624</v>
+        <v>0.7295245602191729</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.9950986376569289</v>
+        <v>0.6788292727199922</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.97777272952478</v>
+        <v>0.6331199282189844</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.9631582845564601</v>
+        <v>0.592012433429689</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.9490353959753448</v>
+        <v>0.5551027310337834</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.9343405782253686</v>
+        <v>0.5219053003578865</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9184878318564227</v>
+        <v>0.4923122975229897</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.9009356522330469</v>
+        <v>0.4660777114757437</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.8811792882853329</v>
+        <v>0.4430540784339714</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.8586988057021904</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+        <v>0.4231392637489534</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i</t>
+          <t>F_3_i_0</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе из ступени</t>
+          <t>Кольцевая площадь на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.5878631958982221</v>
+        <v>0.2704391390523389</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.5615799437371655</v>
+        <v>0.1168558820337119</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.5173054747828673</v>
+        <v>0.08364683815808009</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.4759608627541544</v>
+        <v>0.06984841787590401</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.4388269905708816</v>
+        <v>0.06282493286480222</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.4055641036899751</v>
+        <v>0.05901721452783799</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.3755686983259461</v>
+        <v>0.0569720986391795</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.348515443197201</v>
+        <v>0.05614211290290116</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.3240195410532238</v>
+        <v>0.05618715162270396</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.3018091674062724</v>
+        <v>0.0569447296148979</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2816829056940597</v>
+        <v>0.0583403758612861</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>F_3_i</t>
+          <t>d3_отн_i_0</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Действительная кольцевая площадь на выходе из ступени</t>
+          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2656934067039961</v>
+        <v>0.5645174635893465</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.1101726809038104</v>
+        <v>0.8400022650479599</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.07803314741165103</v>
+        <v>0.888407385345325</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.06489756193149308</v>
+        <v>0.9077610813634108</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.05834925579202112</v>
+        <v>0.9174554577822998</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.0549523337289925</v>
+        <v>0.9226685970493689</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.05332955355952145</v>
+        <v>0.9254564392423336</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.05298305124057681</v>
+        <v>0.9265854587238349</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.05362363268321267</v>
+        <v>0.9265242284043581</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.05514217993091131</v>
+        <v>0.9254936909521634</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.05752573087238778</v>
+        <v>0.9235921753765779</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>F_1_i_plus_1</t>
+          <t>r_ср3_отн_i</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в следующую ступень</t>
+          <t>Относительный средний радиус на выходе из ступени</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.1101726809038104</v>
+        <v>0.8156702574457798</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.07803314741165103</v>
+        <v>0.9280806691608809</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.06489756193149308</v>
+        <v>0.9496667776770478</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.05834925579202112</v>
+        <v>0.9583608254517914</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0549523337289925</v>
+        <v>0.962676818250935</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.05332955355952145</v>
+        <v>0.9649201875368761</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.05298305124057681</v>
+        <v>0.9660047178719648</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.05362363268321267</v>
+        <v>0.9662594806685907</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.05514217993091131</v>
+        <v>0.9658746106784321</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.05752573087238778</v>
+        <v>0.96492158589944</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.05990928181386426</v>
+        <v>0.9634084658840707</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i</t>
+          <t>c_3u_отн_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе из ступени</t>
+          <t>Безразмерная окружная составляющая скорости на выходе</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.5750095110198868</v>
+        <v>0.2506450778768315</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.8499652115645657</v>
+        <v>0.3173302895665055</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.8963315846788537</v>
+        <v>0.3245791553312529</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.9146053366536476</v>
+        <v>0.3235695490353206</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.9235800642707409</v>
+        <v>0.3199806779954548</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.9282015055552439</v>
+        <v>0.3154006481573666</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.9304011614670068</v>
+        <v>0.31052860128867</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9308701671145395</v>
+        <v>0.3056892968707405</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.9300029272941222</v>
+        <v>0.3011403594416843</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.9279438309919011</v>
+        <v>0.297083483610454</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.9247025736427814</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+        <v>0.2937030151296718</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>r_ср2_отн_i</t>
+          <t>α_3_i</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из РК</t>
+          <t>Угол абсолютной скорости на выходе из ступени</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.7926889970937301</v>
+        <v>1.136231551777349</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.8560646311266238</v>
+        <v>1.022873725112233</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.8746747855635537</v>
+        <v>0.9950130310403578</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.887432475360431</v>
+        <v>0.9776629903942148</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.8985571868845765</v>
+        <v>0.9630226373596299</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.9091659515468709</v>
+        <v>0.9488709712900695</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.919681194684562</v>
+        <v>0.9341436681650853</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9302345150126223</v>
+        <v>0.9182543146860374</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.9408894491897043</v>
+        <v>0.9006608987433556</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0.9516517986909254</v>
+        <v>0.8808583140310137</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.9624972478790979</v>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+        <v>0.8583264551375751</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>c_u2_отн_i</t>
+          <t>λ_3_i</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
+          <t>Приведенная скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.5328342009416011</v>
+        <v>0.5878631958982221</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.5148782255130121</v>
+        <v>0.5619910399069254</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.5260559530844864</v>
+        <v>0.5180587964719923</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.5413670654787774</v>
+        <v>0.4770021662391979</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.5582533447833075</v>
+        <v>0.4401118575457637</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.575982445993002</v>
+        <v>0.4070554144280519</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.5941952751191257</v>
+        <v>0.3772337270152328</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.612692386260354</v>
+        <v>0.3503275174307923</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.6312992193976963</v>
+        <v>0.3259558369840071</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.6498642089175687</v>
+        <v>0.3038507341316832</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.6682440327388768</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+        <v>0.2838145372424479</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>β_1_i</t>
+          <t>F_3_i</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на входе в РК</t>
+          <t>Действительная кольцевая площадь на выходе из ступени</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.7955506638277184</v>
+        <v>0.2656934067039961</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.7653244056670644</v>
+        <v>0.1100827372016622</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.7349294688363651</v>
+        <v>0.07790467272957217</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.7044246691718498</v>
+        <v>0.06473560421989191</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.6738815078681362</v>
+        <v>0.05815349676559182</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.6433682017759724</v>
+        <v>0.05472056323932454</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.6129651554172203</v>
+        <v>0.0530580869132116</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5827482756531822</v>
+        <v>0.05266729020555776</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.5527890116881644</v>
+        <v>0.05325762678365734</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0.5231514340937399</v>
+        <v>0.05471842089204163</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.4938897903379407</v>
+        <v>0.05703476526596834</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>c_a2_отн_i</t>
+          <t>F_1_i_plus_1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Относительная осевая скорость на выходе из РК</t>
+          <t>Кольцевая площадь на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.55</v>
+        <v>0.1100827372016622</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.53</v>
+        <v>0.07790467272957217</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.51</v>
+        <v>0.06473560421989191</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.49</v>
+        <v>0.05815349676559182</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.47</v>
+        <v>0.05472056323932454</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.45</v>
+        <v>0.0530580869132116</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.43</v>
+        <v>0.05266729020555776</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.41</v>
+        <v>0.05325762678365734</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.39</v>
+        <v>0.05471842089204163</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.37</v>
+        <v>0.05703476526596834</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+        <v>0.05935110963989505</v>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>β_2_i</t>
+          <t>d3_отн_i</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на выходе из РК</t>
+          <t>Относительный диаметр втулки на выходе из ступени</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.129419771735539</v>
+        <v>0.5750095110198868</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.998828794457881</v>
+        <v>0.850098498375463</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.9711850223246584</v>
+        <v>0.8965121177357361</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.955884074100192</v>
+        <v>0.9148283683409023</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.9441106337703944</v>
+        <v>0.9238470180692731</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.9334625504972009</v>
+        <v>0.9285159862018535</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.9228658513207149</v>
+        <v>0.9307686231828988</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9118030893985957</v>
+        <v>0.9312973574341706</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.8998343775993204</v>
+        <v>0.9304985368642046</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.8865900062790161</v>
+        <v>0.9285188925753641</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.8717124787971834</v>
+        <v>0.9253711386650209</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>α_2_i</t>
+          <t>r_ср2_отн_i</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из РК</t>
+          <t>Относительный средний радиус на выходе из РК</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.8012494925298089</v>
+        <v>0.7926889970937301</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7998694371915022</v>
+        <v>0.8560951515772879</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.7699022166059076</v>
+        <v>0.8747173902543509</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.7356344488799286</v>
+        <v>0.8874856970092428</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.6997795835910243</v>
+        <v>0.8986212284297694</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6632177780467126</v>
+        <v>0.9092415986709568</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.626434437224918</v>
+        <v>0.9197696998563409</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5897389048532454</v>
+        <v>0.9303374356950671</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5533859276947037</v>
+        <v>0.9410087964981999</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5175775704862552</v>
+        <v>0.9517901173721424</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.4824750265353266</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
+        <v>0.9626577588054703</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>ε_рк_i</t>
+          <t>c_u2_отн_i</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки РК</t>
+          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.333869107907821</v>
+        <v>0.5328342009416011</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.2335043887908166</v>
+        <v>0.5148598697082271</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.2362555534882933</v>
+        <v>0.5260303305788944</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.2514594049283423</v>
+        <v>0.5413346002256085</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.2702291259022582</v>
+        <v>0.5582135600490079</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.2900943487212285</v>
+        <v>0.575934525379133</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.3099006959034946</v>
+        <v>0.5941380984640318</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3290548137454135</v>
+        <v>0.6126246057797422</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.347045365911156</v>
+        <v>0.6312191522793327</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.3634385721852762</v>
+        <v>0.6497697675499742</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.3778226884592427</v>
+        <v>0.668132611553355</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>ε_на_i</t>
+          <t>β_1_i</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки НА</t>
+          <t>Угол относительной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.3349820592475404</v>
+        <v>0.7955506638277184</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.2230644356411223</v>
+        <v>0.7653244056670644</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.2251964210510212</v>
+        <v>0.7349294688363651</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.2421382806448514</v>
+        <v>0.7044246691718498</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.2633787009654358</v>
+        <v>0.6738815078681362</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.2858176179286323</v>
+        <v>0.6433682017759724</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.3079061410004507</v>
+        <v>0.6129651554172203</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3287489270031773</v>
+        <v>0.5827482756531822</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.3475497245383432</v>
+        <v>0.5527890116881644</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.3636017177990777</v>
+        <v>0.5231514340937399</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.3762237791668638</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
+        <v>0.4938897903379407</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>W_1_i</t>
+          <t>c_a2_отн_i</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Относительная скорость на входе в РК</t>
+          <t>Относительная осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>250.9860824435535</v>
+        <v>0.55</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>249.3385841704242</v>
+        <v>0.53</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>247.879873607367</v>
+        <v>0.51</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>246.6033773200912</v>
+        <v>0.49</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>245.4971017047085</v>
+        <v>0.47</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>244.5473088529627</v>
+        <v>0.45</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>243.7328313351152</v>
+        <v>0.43</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>243.0290916684654</v>
+        <v>0.41</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>242.4073881249528</v>
+        <v>0.39</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>241.8352353784946</v>
+        <v>0.37</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>241.2767637356463</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>c_a2_i</t>
+          <t>β_2_i</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из РК</t>
+          <t>Угол относительной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>176.0653989864352</v>
+        <v>1.129419771735539</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>169.5357482635252</v>
+        <v>0.9987635973879024</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>163.0157030181962</v>
+        <v>0.9710938522450858</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>156.5052632504483</v>
+        <v>0.9557674093573268</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>150.0044289602814</v>
+        <v>0.9439657206155291</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>143.5132001476955</v>
+        <v>0.9332852101926502</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>137.0315768126907</v>
+        <v>0.922650500131773</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>130.5595589552669</v>
+        <v>0.9115429005379247</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>124.0971465754241</v>
+        <v>0.8995207922639271</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>117.6443396731624</v>
+        <v>0.8862123578377138</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>111.2011382484817</v>
+        <v>0.8712574492962915</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>c_2_i</t>
+          <t>α_2_i</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Абсолютная скорость на выходе из РК</t>
+          <t>Угол абсолютной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>245.1392516422733</v>
+        <v>0.8012494925298089</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>236.3641327968556</v>
+        <v>0.7998872554191435</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>234.1960803815432</v>
+        <v>0.769926558925659</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>233.2217769598795</v>
+        <v>0.7356642859878268</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>232.9083788747501</v>
+        <v>0.6998146971342664</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>233.1062666242036</v>
+        <v>0.6632581433384951</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>233.7385961344311</v>
+        <v>0.6264801416409765</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>234.7585290222456</v>
+        <v>0.5897900410662482</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>236.1187938078528</v>
+        <v>0.553442641911435</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>237.7727140876044</v>
+        <v>0.5176400627491726</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>239.6715229207628</v>
+        <v>0.4825435662280025</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>τ_1_i</t>
+          <t>ε_рк_i</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на входе в РК</t>
+          <t>Диффузность решетки РК</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.9358991257909094</v>
+        <v>0.333869107907821</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.9478717732865374</v>
+        <v>0.233439191720838</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.9568100516098057</v>
+        <v>0.2361643834087207</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.9636772089707186</v>
+        <v>0.2513427401854771</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.9690660274864557</v>
+        <v>0.2700842127473929</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.9733612258030656</v>
+        <v>0.2899170084166778</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.9768219904140164</v>
+        <v>0.3096853447145527</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9796291927865826</v>
+        <v>0.3287946248847425</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.9819122701654925</v>
+        <v>0.3467317805757627</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.9837657808077149</v>
+        <v>0.3630609237439739</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.9852599002879876</v>
+        <v>0.3773676589583507</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>T_1_i</t>
+          <t>ε_на_i</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на входе в РК</t>
+          <t>Диффузность решетки НА</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>269.5389482277819</v>
+        <v>0.3349820592475404</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>315.2532548585067</v>
+        <v>0.2229864696930896</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>360.890789800666</v>
+        <v>0.2250864721146988</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>406.4519108739925</v>
+        <v>0.2419987044063879</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>451.9360117372478</v>
+        <v>0.2632079402253635</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>497.3419054538593</v>
+        <v>0.2856128279515744</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>542.6672858551519</v>
+        <v>0.3076635265241088</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>587.9090763786107</v>
+        <v>0.3284642736197891</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>633.0633002161693</v>
+        <v>0.3472182568319206</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>678.1250246767895</v>
+        <v>0.363218251281841</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>723.0882881121523</v>
+        <v>0.3757828889095726</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>a_1_i</t>
+          <t>W_1_i</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на входе в РК</t>
+          <t>Относительная скорость на входе в РК</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>300.6266943249972</v>
+        <v>250.9860824435535</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>325.1221560491645</v>
+        <v>249.5257657218935</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>347.8601469271284</v>
+        <v>248.2523261710058</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>369.1657157917697</v>
+        <v>247.159597035917</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>389.2738685495074</v>
+        <v>246.2359565197297</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>408.3610423371444</v>
+        <v>245.4679969504885</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>426.5634078858997</v>
+        <v>244.8348071311591</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>443.98864096928</v>
+        <v>244.3119847335906</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>460.7234794998857</v>
+        <v>243.8709046208325</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>476.838883454493</v>
+        <v>243.4790458635891</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>492.3936463887453</v>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
+        <v>243.1003792657729</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>M_w1_i</t>
+          <t>c_a2_i</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Число Маха относительной скорости на входе в РК</t>
+          <t>Осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.8348762341517854</v>
+        <v>176.0653989864352</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.7669073901340627</v>
+        <v>169.663020841474</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.7125848585905825</v>
+        <v>163.2606426965127</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.6680018397461084</v>
+        <v>156.8582645515514</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.6306539471027618</v>
+        <v>150.4558864065901</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.5988507313365694</v>
+        <v>144.0535082616288</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.5713871064165698</v>
+        <v>137.6511301166676</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5473768228347105</v>
+        <v>131.2487519717063</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.5261450716340429</v>
+        <v>124.846373826745</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.5071634125692563</v>
+        <v>118.4439956817837</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.4900078737920149</v>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
+        <v>112.0416175368224</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>λ_c2_i</t>
+          <t>c_2_i</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Приведенная абсолютная скорость на выходе из РК</t>
+          <t>Абсолютная скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.7561655376548881</v>
+        <v>245.1392516422733</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.6812069639019797</v>
+        <v>236.5374798782238</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.6358613232010046</v>
+        <v>234.5420833547407</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.6004186382493311</v>
+        <v>233.7401090335192</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.5715535422729794</v>
+        <v>233.5996037477882</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.5476385487072112</v>
+        <v>233.9717925234325</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.5274561439870138</v>
+        <v>234.7805578444938</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5104502249519497</v>
+        <v>235.9797313057512</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.496005129849934</v>
+        <v>237.522538199086</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.4836740386269262</v>
+        <v>239.3626385080285</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.473095340359227</v>
+        <v>241.4514098060957</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>T2_полн_i</t>
+          <t>τ_1_i</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из РК</t>
+          <t>Температурная функция на входе в РК</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>313.4428716985723</v>
+        <v>0.9358991257909094</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>359.0636475654881</v>
+        <v>0.9477934773027832</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>404.5767041406502</v>
+        <v>0.9566801637576485</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>449.9832169682026</v>
+        <v>0.9635131703642308</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>495.24811395578</v>
+        <v>0.96887954782561</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>540.3638938954861</v>
+        <v>0.9731602653343555</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>585.6721840729384</v>
+        <v>0.9766119297065635</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>630.8155736157496</v>
+        <v>0.9794135598054936</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>675.8576319353274</v>
+        <v>0.9816932042234887</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>720.7504506513271</v>
+        <v>0.9835443352016017</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>765.4238252988293</v>
+        <v>0.985036241304508</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>τ_2_i</t>
+          <t>T_1_i</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на выходе из РК</t>
+          <t>Статическая температура на входе в РК</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.904702279943849</v>
+        <v>269.5389482277819</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.9226595120552412</v>
+        <v>315.2272143492137</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9326133962761779</v>
+        <v>360.8417985411452</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9399162431404698</v>
+        <v>406.3827240088852</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9455544247192016</v>
+        <v>451.8490446247887</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.9500153366616433</v>
+        <v>497.2392240856481</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.9536316693617251</v>
+        <v>542.550587956152</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9565734279744174</v>
+        <v>587.7796676312171</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.9589964851937584</v>
+        <v>632.9220629463809</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.9610099040597198</v>
+        <v>677.9723787827772</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.9626967998217312</v>
+        <v>722.924143411411</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
+          <t>a_1_i</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Скорость звука на входе в РК</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>300.6266943249972</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>325.1087279223543</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>347.8365349569335</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>369.1342944785532</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>389.236412303232</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>408.3188849856418</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>426.517540250923</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>443.9397735692839</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>460.6720826205138</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>476.7852122348859</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>492.337755291879</v>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>M_w1_i</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Число Маха относительной скорости на входе в РК</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0.8348762341517854</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.7675148167092202</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0.7137039995000599</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0.6695655232604704</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>0.6326128510502794</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.6011673865124316</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0.5740322121034488</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.5503268670191854</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.5293806892607494</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0.51066819946513</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>0.4937674932560322</v>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>λ_c2_i</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Приведенная абсолютная скорость на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0.7561655376548881</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.681668811787442</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0.6367359200291949</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.6016678892756752</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0.5731490451480975</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.5495591236380347</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0.5296839815902277</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.512973527448697</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.4988147946968327</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0.4867634687027165</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>0.4764598945286007</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>T2_полн_i</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>Полная температура на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>313.4428716985723</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>359.103409751048</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>404.6590922829263</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>450.1106233325234</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>495.4222457412619</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>540.5857664612566</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>585.945236610017</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>631.1403469638615</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>676.2346897018016</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>721.179244072564</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>765.9020591027951</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>τ_2_i</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Температурная функция на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0.904702279943849</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.9225546051727161</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>0.9324278946907625</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>0.9396659585024256</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>0.945250028674304</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.9496641282710325</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0.9532391466077872</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.9561430266894735</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.9585306334319261</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0.96051022092275</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>0.9621643281509658</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
           <t>T_2_i</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>Статическая температура на выходе из РК</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C62" s="2" t="n">
         <v>663.9665560980862</v>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>677.1454789618543</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>684.4506956861723</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>689.8102998230123</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>693.9481958894603</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>697.2220865440341</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>699.8761353088137</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>702.0351100104829</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>703.8134065759058</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>705.2910670395207</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>706.5290901930256</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="D62" s="2" t="n">
+        <v>677.0684871568757</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>684.3145549340713</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>689.6266143909641</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>693.7247977637994</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>696.9643325505314</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>699.5880604504874</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>701.7192358657619</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>703.4715151086099</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>704.9243465183623</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>706.1383059656665</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>a_2_i</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>Скорость звука на выходе из РК</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C63" s="2" t="n">
         <v>471.8347022630789</v>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>476.4943641806373</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>479.0577400100885</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>480.9297178701437</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>482.3700136635113</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>483.5065311019228</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>484.4259160790691</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>485.1725181690683</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>485.7866149091607</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>486.2963034800401</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>486.7229231726419</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="D63" s="2" t="n">
+        <v>476.4672745779089</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>479.0100941205666</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>480.8656816672305</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>482.2923643291504</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>483.4171497828694</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>484.3262089429483</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>485.0633564657198</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>485.6686102847464</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>486.1698606326876</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>486.5883003014848</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>M_c2_ср_i</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>Среднее число Маха на выходе из РК</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C64" s="2" t="n">
         <v>0.5195447695273417</v>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>0.4960481184353544</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0.4888681693705882</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0.484939416912581</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>0.4828417444646982</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0.4821160659256225</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0.4825063820414591</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>0.4838660893411097</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>0.4860545485634791</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0.4889461679762978</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>0.492418810600689</v>
+      <c r="D64" s="2" t="n">
+        <v>0.4964401387015861</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0.4896391250070536</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.4860819100733257</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0.4843526894163377</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.4839956394358842</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0.4847570779968879</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.4864925955758693</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.4890629807428301</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0.4923436393126648</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>0.4962129374185425</v>
       </c>
     </row>
   </sheetData>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -430,11 +430,11 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.9916542660879368</v>
+        <v>0.9916542745863748</v>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>100454.577154708</v>
+        <v>100454.5780155997</v>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
@@ -631,2614 +631,2659 @@
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн</t>
+          <t>k_i</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на входе в ступень</t>
+          <t>Показатель адиабаты по длине компрессора перед РК</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.399944336209296</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.54</v>
+        <v>1.397730417935234</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.52</v>
+        <v>1.395170974280756</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.5</v>
+        <v>1.392955452904169</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.48</v>
+        <v>1.389895378447053</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.46</v>
+        <v>1.38614429252978</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.44</v>
+        <v>1.382383207491211</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.42</v>
+        <v>1.377411819293562</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.4</v>
+        <v>1.373497531831458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.38</v>
+        <v>1.369326438894018</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.36</v>
+        <v>1.364941218981699</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн_plus_1</t>
+          <t>c_a_i_отн</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>0.36</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.34</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i</t>
+          <t>c_a_i_отн_plus_1</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед ступенью</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>100454.577154708</v>
+        <v>0.54</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>275630.2684439648</v>
+        <v>0.52</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>450805.9597332217</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>625981.6510224786</v>
+        <v>0.48</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>801157.3423117354</v>
+        <v>0.46</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>976333.0336009922</v>
+        <v>0.44</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1151508.724890249</v>
+        <v>0.42</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1326684.416179506</v>
+        <v>0.4</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1501860.107468763</v>
+        <v>0.38</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1677035.79875802</v>
+        <v>0.36</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1852211.490047277</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>P1_полн_i</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Полное давление перед ступенью</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>100454.5780155997</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>275692.1766287496</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>450929.7752418994</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>626167.3738550491</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>801404.972468199</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>976642.5710813488</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1151880.169694499</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1327117.768307649</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1502355.366920798</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1677592.965533948</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1852830.564147098</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>T1_полн_i</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Полная температура перед ступенью</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>332.5906137762022</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>377.1812275524045</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>421.7718413286067</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>466.362455104809</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>510.9530688810112</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>555.5436826572135</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>600.1342964334158</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>644.724910209618</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>689.3155239858202</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>733.9061377620225</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>d1_отн_i</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Относительный диаметр втулки на входе в ступень</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.43</v>
-      </c>
       <c r="D11" s="2" t="n">
-        <v>0.4792242024808975</v>
+        <v>327.5017025887266</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.528448404961795</v>
+        <v>367.0034051774532</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.5776726074426926</v>
+        <v>406.5051077661798</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.6268968099235901</v>
+        <v>446.0068103549064</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.6761210124044876</v>
+        <v>485.508512943633</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.7253452148853852</v>
+        <v>525.0102155323597</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7745694173662827</v>
+        <v>564.5119181210862</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.8237936198471802</v>
+        <v>604.0136207098128</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.8730178223280778</v>
+        <v>643.5153232985394</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.9222420248089752</v>
+        <v>683.0170258872661</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>d1_отн_i</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Относительный диаметр втулки на входе в ступень</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.4798027938858659</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.5296055877717317</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.5794083816575977</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.6292111755434635</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.6790139694293295</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.7288167633151953</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.7786195572010612</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.8284223510869271</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.8782251449727929</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.9280279388586589</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>U_k_i</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Окружная скорость концов рабочих лопаток ступени</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>320.118907248064</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Hт_i</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Теоретический напор i-й ступени</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="n">
-        <v>25854.06962501386</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>27331.42079188165</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28757.55416446405</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>30128.04018314102</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>31434.06707948137</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>32665.02456757352</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33804.57486335634</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34833.30366020297</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>35728.04999640283</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>36461.90625516191</v>
+        <v>320.1197013603089</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37004.21816460253</v>
+        <v>320.1197013603089</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>L_z_i</t>
+          <t>Hт_i</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Действительная работа сжатия i-й ступени</t>
+          <t>Теоретический напор i-й ступени</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>25595.52892876372</v>
+        <v>25854.19789646718</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26784.79237604402</v>
+        <v>27331.55639301205</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27894.82753953012</v>
+        <v>28757.69684116139</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>28922.91857581538</v>
+        <v>30128.18965931852</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>29862.3637255073</v>
+        <v>31434.22303533384</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>30705.12309351911</v>
+        <v>32665.1866306543</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31776.30037155496</v>
+        <v>33804.74258016107</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>32743.30544059079</v>
+        <v>34833.47648090584</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33584.36699661866</v>
+        <v>35728.22725626807</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>34274.19187985219</v>
+        <v>36462.08715595525</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34783.96507472637</v>
+        <v>37004.40175600272</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>H_ад_i</t>
+          <t>L_z_i</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Адиабатическая работа сжатия i-й ступени</t>
+          <t>Действительная работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>22295.79183775567</v>
+        <v>25595.65591750251</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>23523.74428647369</v>
+        <v>26784.92526515181</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>24641.70708974955</v>
+        <v>27894.96593592654</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>25637.08281588775</v>
+        <v>28923.06207294577</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>26494.47881162058</v>
+        <v>29862.51188356715</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>27198.22934648805</v>
+        <v>30705.27543281504</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28027.59015443303</v>
+        <v>31776.45802535141</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28678.98367444181</v>
+        <v>32743.46789205149</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>29126.32674943345</v>
+        <v>33584.53362089198</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>29342.86390726762</v>
+        <v>34274.36192659794</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>29302.04573375754</v>
+        <v>34784.13765064256</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ΔT_полн_i</t>
+          <t>H_ад_i</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Повышение полной температуры в ступени</t>
+          <t>Адиабатическая работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>25.44287169857228</v>
+        <v>22295.90245529727</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>26.51279597484575</v>
+        <v>23523.8609963345</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27.47786473052178</v>
+        <v>24641.8293462309</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>28.33878200391665</v>
+        <v>25637.21001079051</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>29.05979063645292</v>
+        <v>26494.61026037706</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>29.63269758024544</v>
+        <v>27198.36428680719</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.40155395280349</v>
+        <v>28027.72920951312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31.00605053044571</v>
+        <v>28679.12596132233</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>31.50977949218357</v>
+        <v>29126.47125574586</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>31.86372008674383</v>
+        <v>29343.0094878997</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>31.9959213407726</v>
+        <v>29302.19111187581</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>ΔT_полн_i</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Повышение полной температуры в ступени</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>25.44299792992297</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>26.51972798529882</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>27.49138860665853</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>28.38988267523888</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>29.14778438952522</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>29.76236322732219</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>30.58363382072301</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>31.21688767539521</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>31.77696465013327</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>32.16518247860331</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>32.35962250431123</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>T3_полн_i</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Полная температура на выходе из ступени</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>313.4428716985723</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>359.103409751048</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>404.6590922829263</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>450.1106233325234</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>495.4222457412619</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>540.5857664612566</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>585.945236610017</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>631.1403469638615</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>676.2346897018016</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>721.179244072564</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>765.9020591027951</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>313.442997929923</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>354.0214305740254</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>394.4947937841117</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>434.8949904414187</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>475.1545947444316</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>515.2708761709553</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>555.5938493530826</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>595.7288057964814</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>635.7905853599461</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>675.6805057771428</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>715.3766483915773</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>T1_полн_i_plus_1</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Полная температура на входе в следующую ступень</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>313.4428716985723</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>359.103409751048</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>404.6590922829263</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>450.1106233325234</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>495.4222457412619</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>540.5857664612566</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>585.945236610017</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>631.1403469638615</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>676.2346897018016</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>721.179244072564</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>765.9020591027951</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>π_полн_i</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Степень повышения полного давления в ступени</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="n">
-        <v>1.296254706516713</v>
+        <v>313.442997929923</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.267238208318879</v>
+        <v>354.0214305740254</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.243948169558088</v>
+        <v>394.4947937841117</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.224431804357842</v>
+        <v>434.8949904414187</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.207237883003242</v>
+        <v>475.1545947444316</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.191643396458117</v>
+        <v>515.2708761709553</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.179378648812314</v>
+        <v>555.5938493530826</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.167545318776542</v>
+        <v>595.7288057964814</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.156377337391831</v>
+        <v>635.7905853599461</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.145498252598538</v>
+        <v>675.6805057771428</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.134550633368947</v>
+        <v>715.3766483915773</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>P3_полн_i</t>
+          <t>π_полн_i</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Полное давление на выходе из ступени</t>
+          <t>Степень повышения полного давления в ступени</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>130214.7184279365</v>
+        <v>1.296289753371198</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>349289.2075413818</v>
+        <v>1.273077659708594</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>560779.2484360184</v>
+        <v>1.253849641297374</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>766471.8424563546</v>
+        <v>1.237281701016347</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>967187.4938849231</v>
+        <v>1.22253229938774</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1163440.812234543</v>
+        <v>1.209023758265309</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1358064.804056653</v>
+        <v>1.198579725967046</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1548964.179604172</v>
+        <v>1.188416178809493</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1736716.992209737</v>
+        <v>1.178297216252501</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1921041.577022505</v>
+        <v>1.168073869324779</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2101427.71916638</v>
+        <v>1.157625977031957</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>P3_полн_i</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Полное давление на выходе из ступени</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>130218.2401608496</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>350977.5510224969</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>565398.1369373611</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>774745.4334443138</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>979743.4637323158</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1180784.071770667</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1380620.218139306</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1577168.227042358</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1770221.14666478</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>1959552.50640327</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2144884.792095456</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>P1_полн_i_plus_1</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>Полное давление перед следующей ступенью</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>130214.7184279365</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>349289.2075413818</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>560779.2484360184</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>766471.8424563546</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>967187.4938849231</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1163440.812234543</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>1358064.804056653</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1548964.179604172</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1736716.992209737</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>1921041.577022505</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>2101427.71916638</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>a_кр_1_i</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>Критическая скорость потока на входе в ступень</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="n">
-        <v>310.7513475433373</v>
+        <v>130218.2401608496</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>333.9425591312983</v>
+        <v>350977.5510224969</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>355.6246133190464</v>
+        <v>565398.1369373611</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>376.0586369138221</v>
+        <v>774745.4334443138</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>395.4381509119251</v>
+        <v>979743.4637323158</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>413.9112996715638</v>
+        <v>1180784.071770667</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>431.5944818866012</v>
+        <v>1380620.218139306</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>448.5811293335067</v>
+        <v>1577168.227042358</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>464.9475910178317</v>
+        <v>1770221.14666478</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>480.7572102344857</v>
+        <v>1959552.50640327</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>496.0632298322525</v>
+        <v>2144884.792095456</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>a_кр_3_i</t>
+          <t>a_кр_1_i</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на выходе из ступени</t>
+          <t>Критическая скорость потока на входе в ступень</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>324.1872836502556</v>
+        <v>310.7487734256569</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>346.9976560288648</v>
+        <v>331.2658695389746</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>368.3506395304143</v>
+        <v>350.5410496913398</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>388.486926425324</v>
+        <v>368.8015096578053</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>407.5721764265136</v>
+        <v>386.12750213934</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>425.7445331351412</v>
+        <v>402.6360656708928</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>443.2464752655555</v>
+        <v>418.456840685445</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>460.0232149978768</v>
+        <v>433.5853814040989</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>476.173803833237</v>
+        <v>448.2303868459118</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>491.7432262243484</v>
+        <v>462.3585281434915</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>506.761245970099</v>
+        <v>476.0153347549245</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>r_ср1_отн_i</t>
+          <t>a_кр_3_i</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на входе в ступень</t>
+          <t>Критическая скорость потока на выходе из ступени</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.7697077367416805</v>
+        <v>324.0777372086121</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.7841096339936948</v>
+        <v>344.2854048832162</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.7997680028316541</v>
+        <v>363.3124869844129</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.8166105685666942</v>
+        <v>381.2871709710695</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.834565638608604</v>
+        <v>398.3196353879731</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.8535630098050375</v>
+        <v>414.5573247272538</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.8735346818407171</v>
+        <v>430.1468909948723</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8944153907215435</v>
+        <v>445.1457480100918</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.9161429823179678</v>
+        <v>459.5750811212067</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.9386586488448447</v>
+        <v>473.4519105373238</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.96190705172687</v>
+        <v>486.829421102413</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>r_ср1_отн_i</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Относительный средний радиус на входе в ступень</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0.7697077367416805</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.7842865295989352</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.8001506353803143</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.8172252054161926</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0.8354360249081875</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0.8547104687203072</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0.874978249583736</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.8961719742482401</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.9182275294774144</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0.9410843228060074</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.964685403461214</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>c_u1_отн_i</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Безразмерная окружная составляющая скорости на входе</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>0.2209646382902902</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>0.2219828355331729</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0.2244413126796626</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0.2282925458895157</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0.2335073972296462</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0.2400598207374468</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0.2479496514376259</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0.2571861897291074</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0.2677913753339458</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0.2797988555831039</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0.2932530053009496</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>α_1_i</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>Угол абсолютной скорости на входе в РК</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>1.194971328079617</v>
-      </c>
       <c r="D26" s="2" t="n">
-        <v>1.180775445352064</v>
+        <v>0.2221096430231778</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.16333363127941</v>
+        <v>0.2247165257606272</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1.142479748812273</v>
+        <v>0.228735252285246</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1.118028158715437</v>
+        <v>0.2341340540041859</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.08980683236612</v>
+        <v>0.2408842262649444</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1.057630898712612</v>
+        <v>0.2489829529108338</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.021346802165702</v>
+        <v>0.258436941975602</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.9808496374641904</v>
+        <v>0.2692656201432488</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.936112743118563</v>
+        <v>0.2815002132115903</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.8872211306101805</v>
+        <v>0.2951827699082133</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>c_a1_i</t>
+          <t>α_1_i</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на входе в ступень</t>
+          <t>Угол абсолютной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>179.2665880589159</v>
+        <v>1.194971328079617</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>172.8642099139546</v>
+        <v>1.180574579602314</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>166.4618317689933</v>
+        <v>1.162887574917572</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>160.059453624032</v>
+        <v>1.141747321381765</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>153.6570754790708</v>
+        <v>1.116973003860716</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>147.2546973341095</v>
+        <v>1.088399301490598</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>140.8523191891482</v>
+        <v>1.05585028991713</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>134.4499410441869</v>
+        <v>1.019183822447235</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>128.0475628992256</v>
+        <v>0.9783090134087981</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>121.6451847542643</v>
+        <v>0.9332157000484604</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>115.242806609303</v>
+        <v>0.8840072960802917</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>λ_1_i</t>
+          <t>c_a1_i</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на входе в ступень</t>
+          <t>Осевая скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.620165498278116</v>
+        <v>179.267032761773</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.5596777074203516</v>
+        <v>172.8646387345668</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.5098225352552679</v>
+        <v>166.4622447073606</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.4678899206166077</v>
+        <v>160.0598506801545</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.4321142361070043</v>
+        <v>153.6574566529483</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.4012959107614564</v>
+        <v>147.2550626257421</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.3746043536327617</v>
+        <v>140.8526685985359</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3514521890201256</v>
+        <v>134.4502745713297</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.3314223508743308</v>
+        <v>128.0478805441236</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.3142196505478131</v>
+        <v>121.6454865169174</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.2996373677847143</v>
+        <v>115.2430924897112</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>q_1_i</t>
+          <t>λ_1_i</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на входе</t>
+          <t>Приведенная скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.8289595144665948</v>
+        <v>0.6201721739235834</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.772103307484864</v>
+        <v>0.5642480089067109</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.7199280026662993</v>
+        <v>0.5173169382832808</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6725753454599247</v>
+        <v>0.4772577835273439</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.6298340862459014</v>
+        <v>0.4427623742092848</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.5913965269212992</v>
+        <v>0.412838297016845</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.5569689672683231</v>
+        <v>0.3867548721121836</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5263015498370621</v>
+        <v>0.3640913140459806</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.4991997626465075</v>
+        <v>0.3443707830466253</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.4755227615328155</v>
+        <v>0.3274240480592623</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.4551762689534743</v>
+        <v>0.3130789351689683</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>F_1_i</t>
+          <t>q_1_i</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в ступень</t>
+          <t>Газодинамическая функция расхода на входе</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.3184019113646743</v>
+        <v>0.8289672515344797</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1346537867192373</v>
+        <v>0.7767379725045614</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.09472261813282659</v>
+        <v>0.7282607559287695</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.07793191977794278</v>
+        <v>0.6837140922479602</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.06916774125693943</v>
+        <v>0.6432028517842318</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.06417676412225284</v>
+        <v>0.6065518558070965</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.06130653638769019</v>
+        <v>0.5735101964321142</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.05979016976611325</v>
+        <v>0.5440703958039792</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.05923236253001255</v>
+        <v>0.5178567173824349</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.05941838113658058</v>
+        <v>0.4949503270135798</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.0602324406169755</v>
+        <v>0.4753068980390184</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>c_a3_отн_i</t>
+          <t>F_1_i</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Кольцевая площадь на входе в ступень</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.54</v>
+        <v>0.3197918796405437</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.52</v>
+        <v>0.1333845085186511</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.09276327801446825</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.48</v>
+        <v>0.07559418092766981</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.46</v>
+        <v>0.06653889432920902</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.44</v>
+        <v>0.06128783511166349</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.42</v>
+        <v>0.05817197964158876</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4</v>
+        <v>0.0563965166615289</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.38</v>
+        <v>0.05558444893690993</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.36</v>
+        <v>0.05549855900424231</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.34</v>
+        <v>0.0560173881283241</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>c_a3_отн_i</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Коэффициент расхода на выходе из ступени</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
           <t>c_a3_i</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Осевая скорость на выходе из ступени</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>172.8642099139546</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>166.4618317689933</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>160.059453624032</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>153.6570754790708</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>147.2546973341095</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>140.8523191891482</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>134.4499410441869</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>128.0475628992256</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>121.6451847542643</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>115.242806609303</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>108.8404284643418</v>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="C33" s="2" t="n">
+        <v>172.8646387345668</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>166.4622447073606</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>160.0598506801545</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>153.6574566529483</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>147.2550626257421</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>140.8526685985359</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>134.4502745713297</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>128.0478805441236</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>121.6454865169174</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>115.2430924897112</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>108.840698462505</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>λ_3_i_0</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>Приведенная скорость на выходе (1-е приближение)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>0.5732319379046732</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0.5186720225032211</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0.4732777332881704</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0.434804551844695</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0.401780825685309</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0.3731795027985815</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0.3481769583530256</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0.3263910224267986</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0.3074283408444913</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0.2910312774461808</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>0.2770167507220872</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="C34" s="2" t="n">
+        <v>0.5734271272297068</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.5228025526613771</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.4799344415446148</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.4431642821552224</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.4113261510914091</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.3835331465108897</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0.3591420777761956</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.3377484939263771</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.3190764313863512</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0.3029231587547552</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>0.2891175076909822</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>q_3_i</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Газодинамическая функция расхода на выходе</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>0.785474428031451</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0.7295245602191729</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0.6788292727199922</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0.6331199282189844</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0.592012433429689</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0.5551027310337834</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0.5219053003578865</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0.4923122975229897</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0.4660777114757437</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0.4430540784339714</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>0.4231392637489534</v>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>F_3_i_0</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Кольцевая площадь на выходе (1-е приближение)</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="n">
-        <v>0.2704391390523389</v>
+        <v>0.785749222309033</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1168558820337119</v>
+        <v>0.7341503741161742</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.08364683815808009</v>
+        <v>0.6867841552835888</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.06984841787590401</v>
+        <v>0.6436876257254293</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.06282493286480222</v>
+        <v>0.6046548160285634</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.05901721452783799</v>
+        <v>0.5693399760999998</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.0569720986391795</v>
+        <v>0.5375004202953272</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.05614211290290116</v>
+        <v>0.5088838758809117</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.05618715162270396</v>
+        <v>0.4834497779504509</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.0569447296148979</v>
+        <v>0.461124988676336</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.0583403758612861</v>
+        <v>0.4418193991278718</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i_0</t>
+          <t>F_3_i_0</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
+          <t>Кольцевая площадь на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.5645174635893465</v>
+        <v>0.2715199844363019</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.8400022650479599</v>
+        <v>0.1152518761147269</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.888407385345325</v>
+        <v>0.08133600902592081</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.9077610813634108</v>
+        <v>0.06712407994818359</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.9174554577822998</v>
+        <v>0.05975887380926437</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.9226685970493689</v>
+        <v>0.05563589467254893</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.9254564392423336</v>
+        <v>0.05327262404049409</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9265854587238349</v>
+        <v>0.05212041592284061</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.9265242284043581</v>
+        <v>0.05184303068786426</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.9254936909521634</v>
+        <v>0.05225713605927209</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.9235921753765779</v>
+        <v>0.05327648247001738</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>r_ср3_отн_i</t>
+          <t>d3_отн_i_0</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из ступени</t>
+          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.8156702574457798</v>
+        <v>0.5621035277056677</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.9280806691608809</v>
+        <v>0.8424050296758627</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.9496667776770478</v>
+        <v>0.8916784139804044</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.9583608254517914</v>
+        <v>0.9115341308345269</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.962676818250935</v>
+        <v>0.9216559104437274</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.9649201875368761</v>
+        <v>0.9272737612921701</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.9660047178719648</v>
+        <v>0.9304785920318749</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9662594806685907</v>
+        <v>0.9320371051015103</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.9658746106784321</v>
+        <v>0.9324119160656946</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.96492158589944</v>
+        <v>0.9318523094273016</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.9634084658840707</v>
+        <v>0.9304733686128156</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>c_3u_отн_i</t>
+          <t>r_ср3_отн_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе</t>
+          <t>Относительный средний радиус на выходе из ступени</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.2506450778768315</v>
+        <v>0.8147901831335521</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.3173302895665055</v>
+        <v>0.9291062724438937</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.3245791553312529</v>
+        <v>0.9510901796604888</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.3235695490353206</v>
+        <v>0.9600155362539734</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.3199806779954548</v>
+        <v>0.9645299711897813</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.3154006481573666</v>
+        <v>0.9669647075918497</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.31052860128867</v>
+        <v>0.9682510994927808</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3056892968707405</v>
+        <v>0.9687210437647382</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.3011403594416843</v>
+        <v>0.9685643397409724</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.297083483610454</v>
+        <v>0.9678691439543144</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.2937030151296718</v>
+        <v>0.9666562531855225</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
+          <t>c_3u_отн_i</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Безразмерная окружная составляющая скорости на выходе</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0.2500657585861941</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.3180479671978335</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.3255888272795245</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0.3247559975674831</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0.3213200463991865</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0.3168860663128854</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0.3121645376277475</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.3074800309669942</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.3030876935226646</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0.2991978289183804</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>0.295999401331859</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
           <t>α_3_i</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>Угол абсолютной скорости на выходе из ступени</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1.136231551777349</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>1.022873725112233</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0.9950130310403578</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0.9776629903942148</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0.9630226373596299</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0.9488709712900695</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0.9341436681650853</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0.9182543146860374</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0.9006608987433556</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0.8808583140310137</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>0.8583264551375751</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="C40" s="2" t="n">
+        <v>1.137114566119295</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1.021868699911092</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.9935936749826273</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0.9759654442114984</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0.9610631051701353</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0.9466444624942251</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.9316299423043648</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.9154341946829463</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.8975210063638877</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.8773745270752461</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.8544714971920427</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>λ_3_i</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>Приведенная скорость на выходе из ступени</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>0.5878631958982221</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0.5619910399069254</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0.5180587964719923</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0.4770021662391979</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0.4401118575457637</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0.4070554144280519</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0.3772337270152328</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0.3503275174307923</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0.3259558369840071</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0.3038507341316832</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>0.2838145372424479</v>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>F_3_i</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Действительная кольцевая площадь на выходе из ступени</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="n">
-        <v>0.2656934067039961</v>
+        <v>0.5878226727702892</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.1100827372016622</v>
+        <v>0.5667676571629278</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.07790467272957217</v>
+        <v>0.5257290901455642</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.06473560421989191</v>
+        <v>0.4865679818699653</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.05815349676559182</v>
+        <v>0.4509518490978591</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.05472056323932454</v>
+        <v>0.418710515432304</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.0530580869132116</v>
+        <v>0.3894479028740119</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.05266729020555776</v>
+        <v>0.3628203014767546</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.05325762678365734</v>
+        <v>0.3385735337714739</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0.05471842089204163</v>
+        <v>0.3165023114321974</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.05703476526596834</v>
+        <v>0.296424541748485</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>F_1_i_plus_1</t>
+          <t>F_3_i</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в следующую ступень</t>
+          <t>Действительная кольцевая площадь на выходе из ступени</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.1100827372016622</v>
+        <v>0.2668338728927827</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.07790467272957217</v>
+        <v>0.1085711657918483</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.06473560421989191</v>
+        <v>0.07575720556651902</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.05815349676559182</v>
+        <v>0.06221589109372239</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.05472056323932454</v>
+        <v>0.0553185434035527</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.0530580869132116</v>
+        <v>0.051585216662628</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.05266729020555776</v>
+        <v>0.04960891500043527</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.05325762678365734</v>
+        <v>0.04888627787204473</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.05471842089204163</v>
+        <v>0.0491272818916562</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.05703476526596834</v>
+        <v>0.05019599282151199</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.05935110963989505</v>
+        <v>0.0520587088962016</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>F_1_i_plus_1</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Кольцевая площадь на входе в следующую ступень</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0.1085711657918483</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.07575720556651902</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.06221589109372239</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0.0553185434035527</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0.051585216662628</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0.04960891500043527</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0.04888627787204473</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.0491272818916562</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.05019599282151199</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0.0520587088962016</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>0.05392142497089122</v>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
           <t>d3_отн_i</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>Относительный диаметр втулки на выходе из ступени</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0.5750095110198868</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0.850098498375463</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0.8965121177357361</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0.9148283683409023</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0.9238470180692731</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>0.9285159862018535</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>0.9307686231828988</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0.9312973574341706</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0.9304985368642046</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0.9285188925753641</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>0.9253711386650209</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="C44" s="2" t="n">
+        <v>0.5725085895090262</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.8523361607893765</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.8995249077670068</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.9182917073011213</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0.9277047648075981</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.9327601467989414</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.9354252419824672</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.9363978434753509</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.9360735870836928</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.9346343454194882</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0.9321204984578688</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>r_ср2_отн_i</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>Относительный средний радиус на выходе из РК</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0.7926889970937301</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0.8560951515772879</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0.8747173902543509</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0.8874856970092428</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0.8986212284297694</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0.9092415986709568</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0.9197696998563409</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0.9303374356950671</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0.9410087964981999</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0.9517901173721424</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0.9626577588054703</v>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="C45" s="2" t="n">
+        <v>0.7922489599376163</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.8566964010214144</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0.8756204075204015</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.8886203708350831</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0.8999829980489844</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.9108375881560784</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0.9216146745382584</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.9324465090064892</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.9433959346091934</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0.9544767333801609</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>0.9656708283233683</v>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>c_u2_отн_i</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>0.5328342009416011</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0.5148598697082271</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0.5260303305788944</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0.5413346002256085</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0.5582135600490079</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0.575934525379133</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0.5941380984640318</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>0.6126246057797422</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>0.6312191522793327</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0.6497697675499742</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>0.668132611553355</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="C46" s="2" t="n">
+        <v>0.5331301519094394</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.5146604548210467</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.5258374113682019</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.5412084154461251</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0.5581764649226804</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.5760013884187075</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.5943180854893927</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.6129255216237373</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.6316485675547341</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.6503293830044945</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0.6688194353854364</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>β_1_i</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>Угол относительной скорости на входе в РК</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>0.7955506638277184</v>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>0.7653244056670644</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0.7349294688363651</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0.7044246691718498</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0.6738815078681362</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0.6433682017759724</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0.6129651554172203</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0.5827482756531822</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0.5527890116881644</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0.5231514340937399</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>0.4938897903379407</v>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="D47" s="2" t="n">
+        <v>0.7652798913021186</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0.7348365983521747</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.7042804852547354</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0.673683828398578</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.6431155521545162</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0.6126566915509795</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.5823837334686925</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.5523686610810169</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0.522676040644107</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>0.493360586253362</v>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>c_a2_отн_i</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>Относительная осевая скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C48" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D48" s="2" t="n">
         <v>0.53</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F48" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>0.47</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K48" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>0.35</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>β_2_i</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Угол относительной скорости на выходе из РК</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>1.129419771735539</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0.9987635973879024</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0.9710938522450858</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0.9557674093573268</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0.9439657206155291</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0.9332852101926502</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0.922650500131773</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>0.9115429005379247</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>0.8995207922639271</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0.8862123578377138</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>0.8712574492962915</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>α_2_i</t>
+          <t>β_2_i</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из РК</t>
+          <t>Угол относительной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.8012494925298089</v>
+        <v>1.130514300932322</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.7998872554191435</v>
+        <v>0.9976963533957118</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.769926558925659</v>
+        <v>0.9696309402000549</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.7356642859878268</v>
+        <v>0.9540529427009995</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.6998146971342664</v>
+        <v>0.9420162509411002</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.6632581433384951</v>
+        <v>0.9310945109634914</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.6264801416409765</v>
+        <v>0.9201942496553147</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5897900410662482</v>
+        <v>0.9087932754368921</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.553442641911435</v>
+        <v>0.8964504952448477</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.5176400627491726</v>
+        <v>0.8827721077517899</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.4825435662280025</v>
+        <v>0.867379103508124</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>ε_рк_i</t>
+          <t>α_2_i</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки РК</t>
+          <t>Угол абсолютной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.333869107907821</v>
+        <v>0.8009719927700161</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.233439191720838</v>
+        <v>0.800080869900834</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.2361643834087207</v>
+        <v>0.7701098785047441</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.2513427401854771</v>
+        <v>0.7357802744699108</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.2700842127473929</v>
+        <v>0.6998474394994911</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.2899170084166778</v>
+        <v>0.6632018232964938</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.3096853447145527</v>
+        <v>0.626336287717333</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3287946248847425</v>
+        <v>0.5895630781807731</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.3467317805757627</v>
+        <v>0.5531385944983337</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.3630609237439739</v>
+        <v>0.5172699628481386</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.3773676589583507</v>
+        <v>0.4821213583193898</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>ε_на_i</t>
+          <t>ε_рк_i</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки НА</t>
+          <t>Диффузность решетки РК</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.3349820592475404</v>
+        <v>0.3349636371046031</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.2229864696930896</v>
+        <v>0.2324164620935932</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.2250864721146988</v>
+        <v>0.2347943418478802</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.2419987044063879</v>
+        <v>0.2497724574462641</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.2632079402253635</v>
+        <v>0.2683324225425222</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.2856128279515744</v>
+        <v>0.2879789588089752</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.3076635265241088</v>
+        <v>0.3075375581043353</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3284642736197891</v>
+        <v>0.3264095419681996</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.3472182568319206</v>
+        <v>0.3440818341638308</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.363218251281841</v>
+        <v>0.3600960671076829</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.3757828889095726</v>
+        <v>0.374018517254762</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>W_1_i</t>
+          <t>ε_на_i</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Относительная скорость на входе в РК</t>
+          <t>Диффузность решетки НА</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>250.9860824435535</v>
+        <v>0.3361425733492784</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>249.5257657218935</v>
+        <v>0.2217878300102584</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>248.2523261710058</v>
+        <v>0.2234837964778832</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>247.159597035917</v>
+        <v>0.2401851697415877</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>246.2359565197297</v>
+        <v>0.2612156656706441</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>245.4679969504885</v>
+        <v>0.2834426391977313</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>244.8348071311591</v>
+        <v>0.3052936545870318</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>244.3119847335906</v>
+        <v>0.3258711165021732</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>243.8709046208325</v>
+        <v>0.344382411865554</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>243.4790458635891</v>
+        <v>0.3601045642271075</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>243.1003792657729</v>
+        <v>0.3723501388726529</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>c_a2_i</t>
+          <t>W_1_i</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из РК</t>
+          <t>Относительная скорость на входе в РК</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>176.0653989864352</v>
+        <v>250.9867050594529</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>169.663020841474</v>
+        <v>249.5379481431306</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>163.2606426965127</v>
+        <v>248.2784541017162</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>156.8582645515514</v>
+        <v>247.2021510667909</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>150.4558864065901</v>
+        <v>246.2975394635712</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>144.0535082616288</v>
+        <v>245.551354564076</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>137.6511301166676</v>
+        <v>244.9428504897047</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>131.2487519717063</v>
+        <v>244.4478081615797</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>124.846373826745</v>
+        <v>244.0378032431153</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>118.4439956817837</v>
+        <v>243.6805327507538</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>112.0416175368224</v>
+        <v>243.3402025335798</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>c_2_i</t>
+          <t>c_a2_i</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Абсолютная скорость на выходе из РК</t>
+          <t>Осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>245.1392516422733</v>
+        <v>176.0658357481699</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>236.5374798782238</v>
+        <v>169.6634417209637</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>234.5420833547407</v>
+        <v>163.2610476937575</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>233.7401090335192</v>
+        <v>156.8586536665514</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>233.5996037477882</v>
+        <v>150.4562596393452</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>233.9717925234325</v>
+        <v>144.053865612139</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>234.7805578444938</v>
+        <v>137.6514715849328</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>235.9797313057512</v>
+        <v>131.2490775577267</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>237.522538199086</v>
+        <v>124.8466835305205</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>239.3626385080285</v>
+        <v>118.4442895033143</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>241.4514098060957</v>
+        <v>112.0418954761081</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>τ_1_i</t>
+          <t>c_2_i</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на входе в РК</t>
+          <t>Абсолютная скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.9358991257909094</v>
+        <v>245.205790034887</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.9477934773027832</v>
+        <v>236.4935905104464</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.9566801637576485</v>
+        <v>234.498329779823</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.9635131703642308</v>
+        <v>233.7107427554956</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.96887954782561</v>
+        <v>233.5910995314393</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9731602653343555</v>
+        <v>233.9892395892691</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.9766119297065635</v>
+        <v>234.8278183206815</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9794135598054936</v>
+        <v>236.0603777859788</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.9816932042234887</v>
+        <v>237.6400820277972</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.9835443352016017</v>
+        <v>239.518922866217</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.985036241304508</v>
+        <v>241.6467913137315</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>T_1_i</t>
+          <t>τ_1_i</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на входе в РК</t>
+          <t>Температурная функция на входе в РК</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>269.5389482277819</v>
+        <v>0.9359051796510285</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>315.2272143492137</v>
+        <v>0.9471884974081952</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>360.8417985411452</v>
+        <v>0.9558468274253789</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>406.3827240088852</v>
+        <v>0.9625962844363063</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>451.8490446247887</v>
+        <v>0.9680176322189936</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>497.2392240856481</v>
+        <v>0.9724188180361157</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>542.550587956152</v>
+        <v>0.9759918453834303</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>587.7796676312171</v>
+        <v>0.9789558341494647</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>632.9220629463809</v>
+        <v>0.9813382851974597</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>677.9723787827772</v>
+        <v>0.9832888381701964</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>722.924143411411</v>
+        <v>0.9848744817582111</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
+          <t>T_1_i</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Статическая температура на входе в РК</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>269.5406917394962</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>310.2058455736416</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>350.7990404931795</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>391.300306340105</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>431.7424565133022</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>472.1176143031199</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>512.4056891025803</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>552.6322356915423</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>592.7416907832766</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>632.7614345909392</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>672.6860394027558</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
           <t>a_1_i</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>Скорость звука на входе в РК</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>300.6266943249972</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>325.1087279223543</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>347.8365349569335</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>369.1342944785532</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>389.236412303232</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>408.3188849856418</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>426.517540250923</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>443.9397735692839</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>460.6720826205138</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>476.7852122348859</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>492.337755291879</v>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>M_w1_i</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Число Маха относительной скорости на входе в РК</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="n">
-        <v>0.8348762341517854</v>
+        <v>300.6251763668889</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.7675148167092202</v>
+        <v>322.3999014125897</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.7137039995000599</v>
+        <v>342.7149378286148</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.6695655232604704</v>
+        <v>361.8385052109181</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.6326128510502794</v>
+        <v>379.9026907528486</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.6011673865124316</v>
+        <v>397.0446523527072</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.5740322121034488</v>
+        <v>413.4031356106535</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5503268670191854</v>
+        <v>428.9989021073237</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.5293806892607494</v>
+        <v>444.0283162357795</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.51066819946513</v>
+        <v>458.4789778163817</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.4937674932560322</v>
+        <v>472.401628579361</v>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
+          <t>M_w1_i</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Число Маха относительной скорости на входе в РК</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0.8348825207944121</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.7740013165319974</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0.7244459657194036</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.6831836510121971</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0.6483174388038324</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.6184477063449908</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0.5925036106170077</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.5698098688849922</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.5495996411038141</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0.5314977229955928</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>0.515112962809568</v>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>λ_c2_i</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>Приведенная абсолютная скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>0.7561655376548881</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>0.681668811787442</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0.6367359200291949</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0.6016678892756752</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>0.5731490451480975</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0.5495591236380347</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0.5296839815902277</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>0.512973527448697</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>0.4988147946968327</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0.4867634687027165</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>0.4764598945286007</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>T2_полн_i</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>Полная температура на выходе из РК</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="n">
-        <v>313.4428716985723</v>
+        <v>0.7566264568091747</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>359.103409751048</v>
+        <v>0.6869114611194933</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>404.6590922829263</v>
+        <v>0.6454452796990806</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>450.1106233325234</v>
+        <v>0.6129520229077641</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>495.4222457412619</v>
+        <v>0.586441337002922</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>540.5857664612566</v>
+        <v>0.5644315650271423</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>585.945236610017</v>
+        <v>0.5459247137124625</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>631.1403469638615</v>
+        <v>0.5302990735983107</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>676.2346897018016</v>
+        <v>0.5170865257707974</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>721.179244072564</v>
+        <v>0.505899157940635</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>765.9020591027951</v>
+        <v>0.4963685037081949</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>τ_2_i</t>
+          <t>T2_полн_i</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на выходе из РК</t>
+          <t>Полная температура на выходе из РК</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.904702279943849</v>
+        <v>313.442997929923</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.9225546051727161</v>
+        <v>354.0214305740254</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.9324278946907625</v>
+        <v>394.4947937841117</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.9396659585024256</v>
+        <v>434.8949904414187</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.945250028674304</v>
+        <v>475.1545947444316</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.9496641282710325</v>
+        <v>515.2708761709553</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.9532391466077872</v>
+        <v>555.5938493530826</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9561430266894735</v>
+        <v>595.7288057964814</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.9585306334319261</v>
+        <v>635.7905853599461</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.96051022092275</v>
+        <v>675.6805057771428</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.9621643281509658</v>
+        <v>715.3766483915773</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>T_2_i</t>
+          <t>τ_2_i</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на выходе из РК</t>
+          <t>Температурная функция на выходе из РК</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>663.9665560980862</v>
+        <v>0.9050376398220753</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>677.0684871568757</v>
+        <v>0.9221515369239762</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>684.3145549340713</v>
+        <v>0.9315887440071891</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>689.6266143909641</v>
+        <v>0.9387054073290569</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>693.7247977637994</v>
+        <v>0.9443452715453308</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>696.9643325505314</v>
+        <v>0.9488659986366965</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>699.5880604504874</v>
+        <v>0.9526874245639199</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>701.7192358657619</v>
+        <v>0.9557472067545164</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>703.4715151086099</v>
+        <v>0.9583215134744612</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>704.9243465183623</v>
+        <v>0.9605060583055894</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>706.1383059656665</v>
+        <v>0.9623671724133392</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>a_2_i</t>
+          <t>T_2_i</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на выходе из РК</t>
+          <t>Статическая температура на выходе из РК</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>471.8347022630789</v>
+        <v>618.1561170673046</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>476.4672745779089</v>
+        <v>629.8452001671857</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>479.0100941205666</v>
+        <v>636.2909732818439</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>480.8656816672305</v>
+        <v>641.1517754981871</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>482.2923643291504</v>
+        <v>645.0038987815944</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>483.4171497828694</v>
+        <v>648.0916323543871</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>484.3262089429483</v>
+        <v>650.7017313258477</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>485.0633564657198</v>
+        <v>652.7916146575318</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>485.6686102847464</v>
+        <v>654.54990997711</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>486.1698606326876</v>
+        <v>656.0419912905846</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>486.5883003014848</v>
+        <v>657.3131639132968</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
+          <t>a_2_i</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Скорость звука на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>455.1878653606111</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>459.3078267797998</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>461.4872296915951</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>463.0632867898798</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>464.2141998143966</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>465.0598657953267</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>465.6865011908989</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>466.1175242700996</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>466.4555110608122</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>466.6790527756584</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>466.8137721497224</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
           <t>M_c2_ср_i</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>Среднее число Маха на выходе из РК</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>0.5195447695273417</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>0.4964401387015861</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>0.4896391250070536</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0.4860819100733257</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>0.4843526894163377</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>0.4839956394358842</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>0.4847570779968879</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>0.4864925955758693</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>0.4890629807428301</v>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0.4923436393126648</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>0.4962129374185425</v>
+      <c r="C65" s="2" t="n">
+        <v>0.5386914034727813</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.514891270563577</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0.5081361188185742</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0.5047058348668969</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0.5031967992897124</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0.5031378899770466</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0.5042615959881958</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.5064396112453169</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.5094592654449651</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0.5132412124384729</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>0.5176513756244266</v>
       </c>
     </row>
   </sheetData>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -430,13 +430,14 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -447,60 +448,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Название (из комментария)</t>
+          <t>Название</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ВНА</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Ступень 1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ступень 2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ступень 3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ступень 4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ступень 5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ступень 6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ступень 7</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Ступень 8</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Ступень 9</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ступень 10</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Ступень 11</t>
         </is>
@@ -530,6 +536,7 @@
       <c r="K2" s="1" t="inlineStr"/>
       <c r="L2" s="1" t="inlineStr"/>
       <c r="M2" s="1" t="inlineStr"/>
+      <c r="N2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -555,6 +562,7 @@
       <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -580,6 +588,7 @@
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -605,6 +614,7 @@
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -630,6 +640,7 @@
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -642,37 +653,38 @@
           <t>Показатель адиабаты по длине компрессора перед РК</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
         <v>1.399944336209296</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>1.397730417935234</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>1.395170974280756</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>1.392955452904169</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>1.389895378447053</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>1.38614429252978</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>1.382383207491211</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>1.377411819293562</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>1.373497531831458</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>1.369326438894018</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>1.364941218981699</v>
       </c>
     </row>
@@ -687,37 +699,38 @@
           <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -732,37 +745,38 @@
           <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -777,37 +791,38 @@
           <t>Полное давление перед ступенью</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="1" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
         <v>100454.5780155997</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>275692.1766287496</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>450929.7752418994</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>626167.3738550491</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>801404.972468199</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>976642.5710813488</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>1151880.169694499</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
         <v>1327117.768307649</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>1502355.366920798</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>1677592.965533948</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>1852830.564147098</v>
       </c>
     </row>
@@ -822,37 +837,38 @@
           <t>Полная температура перед ступенью</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="1" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>327.5017025887266</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>367.0034051774532</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>406.5051077661798</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>446.0068103549064</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>485.508512943633</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>525.0102155323597</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
         <v>564.5119181210862</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>604.0136207098128</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>643.5153232985394</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>683.0170258872661</v>
       </c>
     </row>
@@ -867,37 +883,38 @@
           <t>Относительный диаметр втулки на входе в ступень</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="1" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>0.4798027938858659</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>0.5296055877717317</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>0.5794083816575977</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.6292111755434635</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>0.6790139694293295</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>0.7288167633151953</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>0.7786195572010612</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>0.8284223510869271</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>0.8782251449727929</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>0.9280279388586589</v>
       </c>
     </row>
@@ -912,9 +929,7 @@
           <t>Окружная скорость концов рабочих лопаток ступени</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
+      <c r="C13" s="1" t="inlineStr"/>
       <c r="D13" s="2" t="n">
         <v>320.1197013603089</v>
       </c>
@@ -945,6 +960,9 @@
       <c r="M13" s="2" t="n">
         <v>320.1197013603089</v>
       </c>
+      <c r="N13" s="2" t="n">
+        <v>320.1197013603089</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
@@ -957,37 +975,38 @@
           <t>Теоретический напор i-й ступени</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="1" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
         <v>25854.19789646718</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>27331.55639301205</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>28757.69684116139</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>30128.18965931852</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>31434.22303533384</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>32665.1866306543</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>33804.74258016107</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>34833.47648090584</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>35728.22725626807</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>36462.08715595525</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>37004.40175600272</v>
       </c>
     </row>
@@ -1002,37 +1021,38 @@
           <t>Действительная работа сжатия i-й ступени</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="1" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
         <v>25595.65591750251</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>26784.92526515181</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>27894.96593592654</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>28923.06207294577</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>29862.51188356715</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>30705.27543281504</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>31776.45802535141</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>32743.46789205149</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>33584.53362089198</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>34274.36192659794</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>34784.13765064256</v>
       </c>
     </row>
@@ -1047,37 +1067,38 @@
           <t>Адиабатическая работа сжатия i-й ступени</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
         <v>22295.90245529727</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>23523.8609963345</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>24641.8293462309</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>25637.21001079051</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>26494.61026037706</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>27198.36428680719</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>28027.72920951312</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>28679.12596132233</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>29126.47125574586</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>29343.0094878997</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>29302.19111187581</v>
       </c>
     </row>
@@ -1092,37 +1113,38 @@
           <t>Повышение полной температуры в ступени</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="1" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
         <v>25.44299792992297</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>26.51972798529882</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>27.49138860665853</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>28.38988267523888</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>29.14778438952522</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>29.76236322732219</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>30.58363382072301</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>31.21688767539521</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>31.77696465013327</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>32.16518247860331</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>32.35962250431123</v>
       </c>
     </row>
@@ -1137,37 +1159,38 @@
           <t>Полная температура на выходе из ступени</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
         <v>313.442997929923</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>354.0214305740254</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>394.4947937841117</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>434.8949904414187</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>475.1545947444316</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>515.2708761709553</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>555.5938493530826</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>595.7288057964814</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>635.7905853599461</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>675.6805057771428</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>715.3766483915773</v>
       </c>
     </row>
@@ -1182,37 +1205,38 @@
           <t>Полная температура на входе в следующую ступень</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
         <v>313.442997929923</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>354.0214305740254</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>394.4947937841117</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>434.8949904414187</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>475.1545947444316</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="I19" s="2" t="n">
         <v>515.2708761709553</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>555.5938493530826</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>595.7288057964814</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>635.7905853599461</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="M19" s="2" t="n">
         <v>675.6805057771428</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>715.3766483915773</v>
       </c>
     </row>
@@ -1227,37 +1251,38 @@
           <t>Степень повышения полного давления в ступени</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
         <v>1.296289753371198</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>1.273077659708594</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>1.253849641297374</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>1.237281701016347</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>1.22253229938774</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>1.209023758265309</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>1.198579725967046</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>1.188416178809493</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>1.178297216252501</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>1.168073869324779</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="N20" s="2" t="n">
         <v>1.157625977031957</v>
       </c>
     </row>
@@ -1272,37 +1297,38 @@
           <t>Полное давление на выходе из ступени</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="1" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
         <v>130218.2401608496</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>350977.5510224969</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>565398.1369373611</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>774745.4334443138</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>979743.4637323158</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>1180784.071770667</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>1380620.218139306</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>1577168.227042358</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>1770221.14666478</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>1959552.50640327</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>2144884.792095456</v>
       </c>
     </row>
@@ -1317,37 +1343,38 @@
           <t>Полное давление перед следующей ступенью</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="1" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
         <v>130218.2401608496</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>350977.5510224969</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="F22" s="2" t="n">
         <v>565398.1369373611</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>774745.4334443138</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>979743.4637323158</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>1180784.071770667</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>1380620.218139306</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>1577168.227042358</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>1770221.14666478</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>1959552.50640327</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>2144884.792095456</v>
       </c>
     </row>
@@ -1362,37 +1389,38 @@
           <t>Критическая скорость потока на входе в ступень</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="1" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
         <v>310.7487734256569</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="E23" s="2" t="n">
         <v>331.2658695389746</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>350.5410496913398</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>368.8015096578053</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>386.12750213934</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>402.6360656708928</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>418.456840685445</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>433.5853814040989</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>448.2303868459118</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="M23" s="2" t="n">
         <v>462.3585281434915</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="N23" s="2" t="n">
         <v>476.0153347549245</v>
       </c>
     </row>
@@ -1407,37 +1435,38 @@
           <t>Критическая скорость потока на выходе из ступени</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
         <v>324.0777372086121</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>344.2854048832162</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>363.3124869844129</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>381.2871709710695</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>398.3196353879731</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>414.5573247272538</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>430.1468909948723</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>445.1457480100918</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>459.5750811212067</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="M24" s="2" t="n">
         <v>473.4519105373238</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>486.829421102413</v>
       </c>
     </row>
@@ -1452,37 +1481,38 @@
           <t>Относительный средний радиус на входе в ступень</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="1" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
         <v>0.7697077367416805</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="E25" s="2" t="n">
         <v>0.7842865295989352</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>0.8001506353803143</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>0.8172252054161926</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>0.8354360249081875</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>0.8547104687203072</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>0.874978249583736</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>0.8961719742482401</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>0.9182275294774144</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="M25" s="2" t="n">
         <v>0.9410843228060074</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>0.964685403461214</v>
       </c>
     </row>
@@ -1497,37 +1527,38 @@
           <t>Безразмерная окружная составляющая скорости на входе</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
         <v>0.2209646382902902</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>0.2221096430231778</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>0.2247165257606272</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.228735252285246</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.2341340540041859</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>0.2408842262649444</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>0.2489829529108338</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>0.258436941975602</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>0.2692656201432488</v>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="M26" s="2" t="n">
         <v>0.2815002132115903</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>0.2951827699082133</v>
       </c>
     </row>
@@ -1542,37 +1573,38 @@
           <t>Угол абсолютной скорости на входе в РК</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="1" t="inlineStr"/>
+      <c r="D27" s="2" t="n">
         <v>1.194971328079617</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="E27" s="2" t="n">
         <v>1.180574579602314</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>1.162887574917572</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>1.141747321381765</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>1.116973003860716</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>1.088399301490598</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>1.05585028991713</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="K27" s="2" t="n">
         <v>1.019183822447235</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="L27" s="2" t="n">
         <v>0.9783090134087981</v>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="M27" s="2" t="n">
         <v>0.9332157000484604</v>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="N27" s="2" t="n">
         <v>0.8840072960802917</v>
       </c>
     </row>
@@ -1587,37 +1619,38 @@
           <t>Осевая скорость на входе в ступень</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
         <v>179.267032761773</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="E28" s="2" t="n">
         <v>172.8646387345668</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>166.4622447073606</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>160.0598506801545</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>153.6574566529483</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>147.2550626257421</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>140.8526685985359</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="K28" s="2" t="n">
         <v>134.4502745713297</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="L28" s="2" t="n">
         <v>128.0478805441236</v>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="M28" s="2" t="n">
         <v>121.6454865169174</v>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>115.2430924897112</v>
       </c>
     </row>
@@ -1632,37 +1665,38 @@
           <t>Приведенная скорость на входе в ступень</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="1" t="inlineStr"/>
+      <c r="D29" s="2" t="n">
         <v>0.6201721739235834</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="E29" s="2" t="n">
         <v>0.5642480089067109</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>0.5173169382832808</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.4772577835273439</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.4427623742092848</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>0.412838297016845</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>0.3867548721121836</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>0.3640913140459806</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>0.3443707830466253</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="M29" s="2" t="n">
         <v>0.3274240480592623</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="N29" s="2" t="n">
         <v>0.3130789351689683</v>
       </c>
     </row>
@@ -1677,37 +1711,38 @@
           <t>Газодинамическая функция расхода на входе</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="1" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
         <v>0.8289672515344797</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="E30" s="2" t="n">
         <v>0.7767379725045614</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>0.7282607559287695</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.6837140922479602</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.6432028517842318</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>0.6065518558070965</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>0.5735101964321142</v>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="K30" s="2" t="n">
         <v>0.5440703958039792</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="L30" s="2" t="n">
         <v>0.5178567173824349</v>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="M30" s="2" t="n">
         <v>0.4949503270135798</v>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="N30" s="2" t="n">
         <v>0.4753068980390184</v>
       </c>
     </row>
@@ -1722,37 +1757,38 @@
           <t>Кольцевая площадь на входе в ступень</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="1" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
         <v>0.3197918796405437</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="E31" s="2" t="n">
         <v>0.1333845085186511</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>0.09276327801446825</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.07559418092766981</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.06653889432920902</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>0.06128783511166349</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>0.05817197964158876</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>0.0563965166615289</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="L31" s="2" t="n">
         <v>0.05558444893690993</v>
       </c>
-      <c r="L31" s="2" t="n">
+      <c r="M31" s="2" t="n">
         <v>0.05549855900424231</v>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="N31" s="2" t="n">
         <v>0.0560173881283241</v>
       </c>
     </row>
@@ -1767,37 +1803,38 @@
           <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="E32" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="K32" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="L32" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="M32" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="N32" s="2" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -1812,37 +1849,38 @@
           <t>Осевая скорость на выходе из ступени</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
         <v>172.8646387345668</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="E33" s="2" t="n">
         <v>166.4622447073606</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>160.0598506801545</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>153.6574566529483</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>147.2550626257421</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>140.8526685985359</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>134.4502745713297</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="K33" s="2" t="n">
         <v>128.0478805441236</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="L33" s="2" t="n">
         <v>121.6454865169174</v>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="M33" s="2" t="n">
         <v>115.2430924897112</v>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="N33" s="2" t="n">
         <v>108.840698462505</v>
       </c>
     </row>
@@ -1857,37 +1895,38 @@
           <t>Приведенная скорость на выходе (1-е приближение)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
         <v>0.5734271272297068</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="E34" s="2" t="n">
         <v>0.5228025526613771</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>0.4799344415446148</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>0.4431642821552224</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.4113261510914091</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>0.3835331465108897</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>0.3591420777761956</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="K34" s="2" t="n">
         <v>0.3377484939263771</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>0.3190764313863512</v>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="M34" s="2" t="n">
         <v>0.3029231587547552</v>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="N34" s="2" t="n">
         <v>0.2891175076909822</v>
       </c>
     </row>
@@ -1902,37 +1941,38 @@
           <t>Газодинамическая функция расхода на выходе</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="1" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
         <v>0.785749222309033</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="E35" s="2" t="n">
         <v>0.7341503741161742</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>0.6867841552835888</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>0.6436876257254293</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.6046548160285634</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>0.5693399760999998</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>0.5375004202953272</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>0.5088838758809117</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="L35" s="2" t="n">
         <v>0.4834497779504509</v>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="M35" s="2" t="n">
         <v>0.461124988676336</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="N35" s="2" t="n">
         <v>0.4418193991278718</v>
       </c>
     </row>
@@ -1947,37 +1987,38 @@
           <t>Кольцевая площадь на выходе (1-е приближение)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="2" t="n">
         <v>0.2715199844363019</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="E36" s="2" t="n">
         <v>0.1152518761147269</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>0.08133600902592081</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>0.06712407994818359</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.05975887380926437</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>0.05563589467254893</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>0.05327262404049409</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="K36" s="2" t="n">
         <v>0.05212041592284061</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>0.05184303068786426</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>0.05225713605927209</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="N36" s="2" t="n">
         <v>0.05327648247001738</v>
       </c>
     </row>
@@ -1992,37 +2033,38 @@
           <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
         <v>0.5621035277056677</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="E37" s="2" t="n">
         <v>0.8424050296758627</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>0.8916784139804044</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>0.9115341308345269</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>0.9216559104437274</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>0.9272737612921701</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>0.9304785920318749</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="K37" s="2" t="n">
         <v>0.9320371051015103</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>0.9324119160656946</v>
       </c>
-      <c r="L37" s="2" t="n">
+      <c r="M37" s="2" t="n">
         <v>0.9318523094273016</v>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="N37" s="2" t="n">
         <v>0.9304733686128156</v>
       </c>
     </row>
@@ -2037,37 +2079,38 @@
           <t>Относительный средний радиус на выходе из ступени</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
         <v>0.8147901831335521</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="E38" s="2" t="n">
         <v>0.9291062724438937</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="F38" s="2" t="n">
         <v>0.9510901796604888</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>0.9600155362539734</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>0.9645299711897813</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>0.9669647075918497</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>0.9682510994927808</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>0.9687210437647382</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>0.9685643397409724</v>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>0.9678691439543144</v>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>0.9666562531855225</v>
       </c>
     </row>
@@ -2082,37 +2125,38 @@
           <t>Безразмерная окружная составляющая скорости на выходе</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="1" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
         <v>0.2500657585861941</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="E39" s="2" t="n">
         <v>0.3180479671978335</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="F39" s="2" t="n">
         <v>0.3255888272795245</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>0.3247559975674831</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>0.3213200463991865</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>0.3168860663128854</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>0.3121645376277475</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>0.3074800309669942</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>0.3030876935226646</v>
       </c>
-      <c r="L39" s="2" t="n">
+      <c r="M39" s="2" t="n">
         <v>0.2991978289183804</v>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="N39" s="2" t="n">
         <v>0.295999401331859</v>
       </c>
     </row>
@@ -2127,37 +2171,38 @@
           <t>Угол абсолютной скорости на выходе из ступени</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="1" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
         <v>1.137114566119295</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>1.021868699911092</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="F40" s="2" t="n">
         <v>0.9935936749826273</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>0.9759654442114984</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>0.9610631051701353</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>0.9466444624942251</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="J40" s="2" t="n">
         <v>0.9316299423043648</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>0.9154341946829463</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="L40" s="2" t="n">
         <v>0.8975210063638877</v>
       </c>
-      <c r="L40" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>0.8773745270752461</v>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>0.8544714971920427</v>
       </c>
     </row>
@@ -2172,37 +2217,38 @@
           <t>Приведенная скорость на выходе из ступени</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="1" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
         <v>0.5878226727702892</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="E41" s="2" t="n">
         <v>0.5667676571629278</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="F41" s="2" t="n">
         <v>0.5257290901455642</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>0.4865679818699653</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>0.4509518490978591</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>0.418710515432304</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>0.3894479028740119</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="K41" s="2" t="n">
         <v>0.3628203014767546</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="L41" s="2" t="n">
         <v>0.3385735337714739</v>
       </c>
-      <c r="L41" s="2" t="n">
+      <c r="M41" s="2" t="n">
         <v>0.3165023114321974</v>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>0.296424541748485</v>
       </c>
     </row>
@@ -2217,37 +2263,38 @@
           <t>Действительная кольцевая площадь на выходе из ступени</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="1" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
         <v>0.2668338728927827</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="E42" s="2" t="n">
         <v>0.1085711657918483</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="F42" s="2" t="n">
         <v>0.07575720556651902</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>0.06221589109372239</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>0.0553185434035527</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>0.051585216662628</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>0.04960891500043527</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>0.04888627787204473</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="L42" s="2" t="n">
         <v>0.0491272818916562</v>
       </c>
-      <c r="L42" s="2" t="n">
+      <c r="M42" s="2" t="n">
         <v>0.05019599282151199</v>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>0.0520587088962016</v>
       </c>
     </row>
@@ -2262,37 +2309,38 @@
           <t>Кольцевая площадь на входе в следующую ступень</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="1" t="inlineStr"/>
+      <c r="D43" s="2" t="n">
         <v>0.1085711657918483</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="E43" s="2" t="n">
         <v>0.07575720556651902</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="F43" s="2" t="n">
         <v>0.06221589109372239</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>0.0553185434035527</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>0.051585216662628</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>0.04960891500043527</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>0.04888627787204473</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="K43" s="2" t="n">
         <v>0.0491272818916562</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>0.05019599282151199</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="M43" s="2" t="n">
         <v>0.0520587088962016</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="N43" s="2" t="n">
         <v>0.05392142497089122</v>
       </c>
     </row>
@@ -2307,37 +2355,38 @@
           <t>Относительный диаметр втулки на выходе из ступени</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="1" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
         <v>0.5725085895090262</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="E44" s="2" t="n">
         <v>0.8523361607893765</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="F44" s="2" t="n">
         <v>0.8995249077670068</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>0.9182917073011213</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>0.9277047648075981</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>0.9327601467989414</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="J44" s="2" t="n">
         <v>0.9354252419824672</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="K44" s="2" t="n">
         <v>0.9363978434753509</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="L44" s="2" t="n">
         <v>0.9360735870836928</v>
       </c>
-      <c r="L44" s="2" t="n">
+      <c r="M44" s="2" t="n">
         <v>0.9346343454194882</v>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="N44" s="2" t="n">
         <v>0.9321204984578688</v>
       </c>
     </row>
@@ -2352,37 +2401,38 @@
           <t>Относительный средний радиус на выходе из РК</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="1" t="inlineStr"/>
+      <c r="D45" s="2" t="n">
         <v>0.7922489599376163</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="E45" s="2" t="n">
         <v>0.8566964010214144</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>0.8756204075204015</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.8886203708350831</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>0.8999829980489844</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>0.9108375881560784</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>0.9216146745382584</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>0.9324465090064892</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>0.9433959346091934</v>
       </c>
-      <c r="L45" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>0.9544767333801609</v>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="N45" s="2" t="n">
         <v>0.9656708283233683</v>
       </c>
     </row>
@@ -2397,37 +2447,38 @@
           <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="1" t="inlineStr"/>
+      <c r="D46" s="2" t="n">
         <v>0.5331301519094394</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="E46" s="2" t="n">
         <v>0.5146604548210467</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="F46" s="2" t="n">
         <v>0.5258374113682019</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>0.5412084154461251</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>0.5581764649226804</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>0.5760013884187075</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>0.5943180854893927</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>0.6129255216237373</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>0.6316485675547341</v>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>0.6503293830044945</v>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="N46" s="2" t="n">
         <v>0.6688194353854364</v>
       </c>
     </row>
@@ -2442,37 +2493,38 @@
           <t>Угол относительной скорости на входе в РК</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="1" t="inlineStr"/>
+      <c r="D47" s="2" t="n">
         <v>0.7955506638277184</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="E47" s="2" t="n">
         <v>0.7652798913021186</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="F47" s="2" t="n">
         <v>0.7348365983521747</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>0.7042804852547354</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>0.673683828398578</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="I47" s="2" t="n">
         <v>0.6431155521545162</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>0.6126566915509795</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>0.5823837334686925</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="L47" s="2" t="n">
         <v>0.5523686610810169</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="M47" s="2" t="n">
         <v>0.522676040644107</v>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="N47" s="2" t="n">
         <v>0.493360586253362</v>
       </c>
     </row>
@@ -2487,37 +2539,38 @@
           <t>Относительная осевая скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="1" t="inlineStr"/>
+      <c r="D48" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>0.53</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="F48" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>0.47</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="K48" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="L48" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -2532,37 +2585,38 @@
           <t>Угол относительной скорости на выходе из РК</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
         <v>1.130514300932322</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="E49" s="2" t="n">
         <v>0.9976963533957118</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="F49" s="2" t="n">
         <v>0.9696309402000549</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>0.9540529427009995</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.9420162509411002</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>0.9310945109634914</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="J49" s="2" t="n">
         <v>0.9201942496553147</v>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="K49" s="2" t="n">
         <v>0.9087932754368921</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="L49" s="2" t="n">
         <v>0.8964504952448477</v>
       </c>
-      <c r="L49" s="2" t="n">
+      <c r="M49" s="2" t="n">
         <v>0.8827721077517899</v>
       </c>
-      <c r="M49" s="2" t="n">
+      <c r="N49" s="2" t="n">
         <v>0.867379103508124</v>
       </c>
     </row>
@@ -2577,37 +2631,38 @@
           <t>Угол абсолютной скорости на выходе из РК</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="2" t="n">
         <v>0.8009719927700161</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="E50" s="2" t="n">
         <v>0.800080869900834</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="F50" s="2" t="n">
         <v>0.7701098785047441</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>0.7357802744699108</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>0.6998474394994911</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="I50" s="2" t="n">
         <v>0.6632018232964938</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="J50" s="2" t="n">
         <v>0.626336287717333</v>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="K50" s="2" t="n">
         <v>0.5895630781807731</v>
       </c>
-      <c r="K50" s="2" t="n">
+      <c r="L50" s="2" t="n">
         <v>0.5531385944983337</v>
       </c>
-      <c r="L50" s="2" t="n">
+      <c r="M50" s="2" t="n">
         <v>0.5172699628481386</v>
       </c>
-      <c r="M50" s="2" t="n">
+      <c r="N50" s="2" t="n">
         <v>0.4821213583193898</v>
       </c>
     </row>
@@ -2622,37 +2677,38 @@
           <t>Диффузность решетки РК</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="2" t="n">
         <v>0.3349636371046031</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="E51" s="2" t="n">
         <v>0.2324164620935932</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="F51" s="2" t="n">
         <v>0.2347943418478802</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>0.2497724574462641</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.2683324225425222</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>0.2879789588089752</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>0.3075375581043353</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="K51" s="2" t="n">
         <v>0.3264095419681996</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="L51" s="2" t="n">
         <v>0.3440818341638308</v>
       </c>
-      <c r="L51" s="2" t="n">
+      <c r="M51" s="2" t="n">
         <v>0.3600960671076829</v>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="N51" s="2" t="n">
         <v>0.374018517254762</v>
       </c>
     </row>
@@ -2667,37 +2723,38 @@
           <t>Диффузность решетки НА</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
         <v>0.3361425733492784</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="E52" s="2" t="n">
         <v>0.2217878300102584</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="F52" s="2" t="n">
         <v>0.2234837964778832</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>0.2401851697415877</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.2612156656706441</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>0.2834426391977313</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>0.3052936545870318</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="K52" s="2" t="n">
         <v>0.3258711165021732</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>0.344382411865554</v>
       </c>
-      <c r="L52" s="2" t="n">
+      <c r="M52" s="2" t="n">
         <v>0.3601045642271075</v>
       </c>
-      <c r="M52" s="2" t="n">
+      <c r="N52" s="2" t="n">
         <v>0.3723501388726529</v>
       </c>
     </row>
@@ -2712,37 +2769,38 @@
           <t>Относительная скорость на входе в РК</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
         <v>250.9867050594529</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="E53" s="2" t="n">
         <v>249.5379481431306</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="F53" s="2" t="n">
         <v>248.2784541017162</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>247.2021510667909</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>246.2975394635712</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>245.551354564076</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>244.9428504897047</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="K53" s="2" t="n">
         <v>244.4478081615797</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="L53" s="2" t="n">
         <v>244.0378032431153</v>
       </c>
-      <c r="L53" s="2" t="n">
+      <c r="M53" s="2" t="n">
         <v>243.6805327507538</v>
       </c>
-      <c r="M53" s="2" t="n">
+      <c r="N53" s="2" t="n">
         <v>243.3402025335798</v>
       </c>
     </row>
@@ -2757,37 +2815,38 @@
           <t>Осевая скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
         <v>176.0658357481699</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="E54" s="2" t="n">
         <v>169.6634417209637</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="F54" s="2" t="n">
         <v>163.2610476937575</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>156.8586536665514</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>150.4562596393452</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>144.053865612139</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>137.6514715849328</v>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="K54" s="2" t="n">
         <v>131.2490775577267</v>
       </c>
-      <c r="K54" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>124.8466835305205</v>
       </c>
-      <c r="L54" s="2" t="n">
+      <c r="M54" s="2" t="n">
         <v>118.4442895033143</v>
       </c>
-      <c r="M54" s="2" t="n">
+      <c r="N54" s="2" t="n">
         <v>112.0418954761081</v>
       </c>
     </row>
@@ -2802,37 +2861,38 @@
           <t>Абсолютная скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
         <v>245.205790034887</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="E55" s="2" t="n">
         <v>236.4935905104464</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="F55" s="2" t="n">
         <v>234.498329779823</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>233.7107427554956</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>233.5910995314393</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>233.9892395892691</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="J55" s="2" t="n">
         <v>234.8278183206815</v>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="K55" s="2" t="n">
         <v>236.0603777859788</v>
       </c>
-      <c r="K55" s="2" t="n">
+      <c r="L55" s="2" t="n">
         <v>237.6400820277972</v>
       </c>
-      <c r="L55" s="2" t="n">
+      <c r="M55" s="2" t="n">
         <v>239.518922866217</v>
       </c>
-      <c r="M55" s="2" t="n">
+      <c r="N55" s="2" t="n">
         <v>241.6467913137315</v>
       </c>
     </row>
@@ -2847,37 +2907,38 @@
           <t>Температурная функция на входе в РК</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
         <v>0.9359051796510285</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="E56" s="2" t="n">
         <v>0.9471884974081952</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="F56" s="2" t="n">
         <v>0.9558468274253789</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.9625962844363063</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.9680176322189936</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>0.9724188180361157</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>0.9759918453834303</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="K56" s="2" t="n">
         <v>0.9789558341494647</v>
       </c>
-      <c r="K56" s="2" t="n">
+      <c r="L56" s="2" t="n">
         <v>0.9813382851974597</v>
       </c>
-      <c r="L56" s="2" t="n">
+      <c r="M56" s="2" t="n">
         <v>0.9832888381701964</v>
       </c>
-      <c r="M56" s="2" t="n">
+      <c r="N56" s="2" t="n">
         <v>0.9848744817582111</v>
       </c>
     </row>
@@ -2892,37 +2953,38 @@
           <t>Статическая температура на входе в РК</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
         <v>269.5406917394962</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="E57" s="2" t="n">
         <v>310.2058455736416</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="F57" s="2" t="n">
         <v>350.7990404931795</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>391.300306340105</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>431.7424565133022</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>472.1176143031199</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="J57" s="2" t="n">
         <v>512.4056891025803</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="K57" s="2" t="n">
         <v>552.6322356915423</v>
       </c>
-      <c r="K57" s="2" t="n">
+      <c r="L57" s="2" t="n">
         <v>592.7416907832766</v>
       </c>
-      <c r="L57" s="2" t="n">
+      <c r="M57" s="2" t="n">
         <v>632.7614345909392</v>
       </c>
-      <c r="M57" s="2" t="n">
+      <c r="N57" s="2" t="n">
         <v>672.6860394027558</v>
       </c>
     </row>
@@ -2937,37 +2999,38 @@
           <t>Скорость звука на входе в РК</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="1" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
         <v>300.6251763668889</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="E58" s="2" t="n">
         <v>322.3999014125897</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="F58" s="2" t="n">
         <v>342.7149378286148</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>361.8385052109181</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>379.9026907528486</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="I58" s="2" t="n">
         <v>397.0446523527072</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="J58" s="2" t="n">
         <v>413.4031356106535</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="K58" s="2" t="n">
         <v>428.9989021073237</v>
       </c>
-      <c r="K58" s="2" t="n">
+      <c r="L58" s="2" t="n">
         <v>444.0283162357795</v>
       </c>
-      <c r="L58" s="2" t="n">
+      <c r="M58" s="2" t="n">
         <v>458.4789778163817</v>
       </c>
-      <c r="M58" s="2" t="n">
+      <c r="N58" s="2" t="n">
         <v>472.401628579361</v>
       </c>
     </row>
@@ -2982,37 +3045,38 @@
           <t>Число Маха относительной скорости на входе в РК</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="1" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
         <v>0.8348825207944121</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="E59" s="2" t="n">
         <v>0.7740013165319974</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="F59" s="2" t="n">
         <v>0.7244459657194036</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>0.6831836510121971</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>0.6483174388038324</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>0.6184477063449908</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="J59" s="2" t="n">
         <v>0.5925036106170077</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>0.5698098688849922</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="L59" s="2" t="n">
         <v>0.5495996411038141</v>
       </c>
-      <c r="L59" s="2" t="n">
+      <c r="M59" s="2" t="n">
         <v>0.5314977229955928</v>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="N59" s="2" t="n">
         <v>0.515112962809568</v>
       </c>
     </row>
@@ -3027,37 +3091,38 @@
           <t>Приведенная абсолютная скорость на выходе из РК</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="1" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
         <v>0.7566264568091747</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="E60" s="2" t="n">
         <v>0.6869114611194933</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="F60" s="2" t="n">
         <v>0.6454452796990806</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>0.6129520229077641</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.586441337002922</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>0.5644315650271423</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="J60" s="2" t="n">
         <v>0.5459247137124625</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="K60" s="2" t="n">
         <v>0.5302990735983107</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>0.5170865257707974</v>
       </c>
-      <c r="L60" s="2" t="n">
+      <c r="M60" s="2" t="n">
         <v>0.505899157940635</v>
       </c>
-      <c r="M60" s="2" t="n">
+      <c r="N60" s="2" t="n">
         <v>0.4963685037081949</v>
       </c>
     </row>
@@ -3072,37 +3137,38 @@
           <t>Полная температура на выходе из РК</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="1" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
         <v>313.442997929923</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="E61" s="2" t="n">
         <v>354.0214305740254</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="F61" s="2" t="n">
         <v>394.4947937841117</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>434.8949904414187</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>475.1545947444316</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>515.2708761709553</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="J61" s="2" t="n">
         <v>555.5938493530826</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="K61" s="2" t="n">
         <v>595.7288057964814</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="L61" s="2" t="n">
         <v>635.7905853599461</v>
       </c>
-      <c r="L61" s="2" t="n">
+      <c r="M61" s="2" t="n">
         <v>675.6805057771428</v>
       </c>
-      <c r="M61" s="2" t="n">
+      <c r="N61" s="2" t="n">
         <v>715.3766483915773</v>
       </c>
     </row>
@@ -3117,37 +3183,38 @@
           <t>Температурная функция на выходе из РК</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="1" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
         <v>0.9050376398220753</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="E62" s="2" t="n">
         <v>0.9221515369239762</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="F62" s="2" t="n">
         <v>0.9315887440071891</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>0.9387054073290569</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>0.9443452715453308</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>0.9488659986366965</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="J62" s="2" t="n">
         <v>0.9526874245639199</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>0.9557472067545164</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="L62" s="2" t="n">
         <v>0.9583215134744612</v>
       </c>
-      <c r="L62" s="2" t="n">
+      <c r="M62" s="2" t="n">
         <v>0.9605060583055894</v>
       </c>
-      <c r="M62" s="2" t="n">
+      <c r="N62" s="2" t="n">
         <v>0.9623671724133392</v>
       </c>
     </row>
@@ -3162,37 +3229,38 @@
           <t>Статическая температура на выходе из РК</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="1" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
         <v>618.1561170673046</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="E63" s="2" t="n">
         <v>629.8452001671857</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="F63" s="2" t="n">
         <v>636.2909732818439</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>641.1517754981871</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>645.0038987815944</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>648.0916323543871</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>650.7017313258477</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="K63" s="2" t="n">
         <v>652.7916146575318</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="L63" s="2" t="n">
         <v>654.54990997711</v>
       </c>
-      <c r="L63" s="2" t="n">
+      <c r="M63" s="2" t="n">
         <v>656.0419912905846</v>
       </c>
-      <c r="M63" s="2" t="n">
+      <c r="N63" s="2" t="n">
         <v>657.3131639132968</v>
       </c>
     </row>
@@ -3207,37 +3275,38 @@
           <t>Скорость звука на выходе из РК</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="1" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
         <v>455.1878653606111</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="E64" s="2" t="n">
         <v>459.3078267797998</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="F64" s="2" t="n">
         <v>461.4872296915951</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>463.0632867898798</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>464.2141998143966</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>465.0598657953267</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="J64" s="2" t="n">
         <v>465.6865011908989</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="K64" s="2" t="n">
         <v>466.1175242700996</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>466.4555110608122</v>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="M64" s="2" t="n">
         <v>466.6790527756584</v>
       </c>
-      <c r="M64" s="2" t="n">
+      <c r="N64" s="2" t="n">
         <v>466.8137721497224</v>
       </c>
     </row>
@@ -3252,37 +3321,38 @@
           <t>Среднее число Маха на выходе из РК</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="1" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
         <v>0.5386914034727813</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="E65" s="2" t="n">
         <v>0.514891270563577</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="F65" s="2" t="n">
         <v>0.5081361188185742</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>0.5047058348668969</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>0.5031967992897124</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>0.5031378899770466</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="J65" s="2" t="n">
         <v>0.5042615959881958</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="K65" s="2" t="n">
         <v>0.5064396112453169</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="L65" s="2" t="n">
         <v>0.5094592654449651</v>
       </c>
-      <c r="L65" s="2" t="n">
+      <c r="M65" s="2" t="n">
         <v>0.5132412124384729</v>
       </c>
-      <c r="M65" s="2" t="n">
+      <c r="N65" s="2" t="n">
         <v>0.5176513756244266</v>
       </c>
     </row>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,23 +421,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -511,6 +513,16 @@
           <t>Ступень 11</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 12</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>СА</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -524,7 +536,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.9916542745863748</v>
+        <v>0.9899417183381966</v>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
@@ -537,6 +549,8 @@
       <c r="L2" s="1" t="inlineStr"/>
       <c r="M2" s="1" t="inlineStr"/>
       <c r="N2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr"/>
+      <c r="P2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -550,7 +564,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>100454.5780155997</v>
+        <v>100281.0960676593</v>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
@@ -563,6 +577,8 @@
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr"/>
+      <c r="P3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -576,7 +592,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.2874142865400933</v>
+        <v>0.2879994046470533</v>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
@@ -589,6 +605,8 @@
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr"/>
+      <c r="P4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -615,6 +633,8 @@
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr"/>
+      <c r="P5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -628,7 +648,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.83130053977735</v>
+        <v>66.10301705129361</v>
       </c>
       <c r="D6" s="1" t="inlineStr"/>
       <c r="E6" s="1" t="inlineStr"/>
@@ -641,2720 +661,3434 @@
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+      <c r="O6" s="1" t="inlineStr"/>
+      <c r="P6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>k_i</t>
+          <t>a_кр_1_i_СА</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Показатель адиабаты по длине компрессора перед РК</t>
+          <t>СА: Критическая скорость на входе</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="2" t="n">
-        <v>1.399944336209296</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1.397730417935234</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1.395170974280756</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1.392955452904169</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.389895378447053</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>1.38614429252978</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1.382383207491211</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1.377411819293562</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>1.373497531831458</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1.369326438894018</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>1.364941218981699</v>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+      <c r="M7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr"/>
+      <c r="P7" s="2" t="n">
+        <v>477.1612274741949</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн</t>
+          <t>r_ср1_отн_i_СА</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на входе в ступень</t>
+          <t>СА: Относительный средний радиус на входе</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0.36</v>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
+      <c r="G8" s="1" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr"/>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
+      <c r="L8" s="1" t="inlineStr"/>
+      <c r="M8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr"/>
+      <c r="P8" s="2" t="n">
+        <v>0.9611322188795871</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн_plus_1</t>
+          <t>c_a2_i_СА</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>СА: Осевая скорость на входе</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr"/>
-      <c r="D9" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0.34</v>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr"/>
+      <c r="G9" s="1" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
+      <c r="L9" s="1" t="inlineStr"/>
+      <c r="M9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>109.2378718009286</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i</t>
+          <t>q_1_i_СА</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед ступенью</t>
+          <t>СА: ГДФ расхода на входе</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>100454.5780155997</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>275692.1766287496</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>450929.7752418994</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>626167.3738550491</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>801404.972468199</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>976642.5710813488</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1151880.169694499</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>1327117.768307649</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>1502355.366920798</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>1677592.965533948</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1852830.564147098</v>
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr"/>
+      <c r="G10" s="1" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
+      <c r="L10" s="1" t="inlineStr"/>
+      <c r="M10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr"/>
+      <c r="P10" s="2" t="n">
+        <v>0.4625400694372556</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i</t>
+          <t>F_1_i_СА</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Полная температура перед ступенью</t>
+          <t>СА: Кольцевая площадь на входе</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>327.5017025887266</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>367.0034051774532</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>406.5051077661798</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>446.0068103549064</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>485.508512943633</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>525.0102155323597</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>564.5119181210862</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>604.0136207098128</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>643.5153232985394</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>683.0170258872661</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" s="1" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr"/>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr"/>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
+      <c r="L11" s="1" t="inlineStr"/>
+      <c r="M11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr"/>
+      <c r="O11" s="1" t="inlineStr"/>
+      <c r="P11" s="2" t="n">
+        <v>0.05404465568956616</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>d1_отн_i</t>
+          <t>α_3_i_СА</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на входе в ступень</t>
+          <t>СА: Угол абсолютной скорости на выходе</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.4798027938858659</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.5296055877717317</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.5794083816575977</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.6292111755434635</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.6790139694293295</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.7288167633151953</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.7786195572010612</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0.8284223510869271</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0.8782251449727929</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0.9280279388586589</v>
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
+      <c r="L12" s="1" t="inlineStr"/>
+      <c r="M12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr"/>
+      <c r="O12" s="1" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
+        <v>1.570796326794897</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U_k_i</t>
+          <t>F_3_i_СА</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Окружная скорость концов рабочих лопаток ступени</t>
+          <t>СА: Действительная кольцевая площадь на выходе</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr"/>
-      <c r="D13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>320.1197013603089</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>320.1197013603089</v>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+      <c r="G13" s="1" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
+      <c r="L13" s="1" t="inlineStr"/>
+      <c r="M13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr"/>
+      <c r="P13" s="2" t="n">
+        <v>0.05404465568956616</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Hт_i</t>
+          <t>D_вт3_i_СА</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Теоретический напор i-й ступени</t>
+          <t>СА: Втулочный диаметр на выходе</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr"/>
-      <c r="D14" s="2" t="n">
-        <v>25854.19789646718</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>27331.55639301205</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>28757.69684116139</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30128.18965931852</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>31434.22303533384</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>32665.1866306543</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>33804.74258016107</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>34833.47648090584</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>35728.22725626807</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>36462.08715595525</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>37004.40175600272</v>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
+      <c r="L14" s="1" t="inlineStr"/>
+      <c r="M14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr"/>
+      <c r="O14" s="1" t="inlineStr"/>
+      <c r="P14" s="2" t="n">
+        <v>0.3554357598494053</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>L_z_i</t>
+          <t>d3_отн_i_СА</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Действительная работа сжатия i-й ступени</t>
+          <t>СА: Относительный диаметр втулки на выходе</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr"/>
-      <c r="D15" s="2" t="n">
-        <v>25595.65591750251</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>26784.92526515181</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>27894.96593592654</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>28923.06207294577</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>29862.51188356715</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>30705.27543281504</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>31776.45802535141</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>32743.46789205149</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>33584.53362089198</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>34274.36192659794</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>34784.13765064256</v>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
+      <c r="L15" s="1" t="inlineStr"/>
+      <c r="M15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr"/>
+      <c r="O15" s="1" t="inlineStr"/>
+      <c r="P15" s="2" t="n">
+        <v>0.5183547184948523</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>H_ад_i</t>
+          <t>r_ср3_отн_i_СА</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Адиабатическая работа сжатия i-й ступени</t>
+          <t>СА: Относительный средний радиус на выходе</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>22295.90245529727</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>23523.8609963345</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>24641.8293462309</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>25637.21001079051</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>26494.61026037706</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>27198.36428680719</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>28027.72920951312</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>28679.12596132233</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>29126.47125574586</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>29343.0094878997</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>29302.19111187581</v>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
+      <c r="L16" s="1" t="inlineStr"/>
+      <c r="M16" s="1" t="inlineStr"/>
+      <c r="N16" s="1" t="inlineStr"/>
+      <c r="O16" s="1" t="inlineStr"/>
+      <c r="P16" s="2" t="n">
+        <v>0.796458289612795</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ΔT_полн_i</t>
+          <t>α_2_i_СА</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Повышение полной температуры в ступени</t>
+          <t>СА: Угол абсолютной скорости на входе</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr"/>
-      <c r="D17" s="2" t="n">
-        <v>25.44299792992297</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>26.51972798529882</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>27.49138860665853</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>28.38988267523888</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>29.14778438952522</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>29.76236322732219</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>30.58363382072301</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>31.21688767539521</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>31.77696465013327</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>32.16518247860331</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>32.35962250431123</v>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
+      <c r="L17" s="1" t="inlineStr"/>
+      <c r="M17" s="1" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr"/>
+      <c r="O17" s="1" t="inlineStr"/>
+      <c r="P17" s="2" t="n">
+        <v>0.8593837811273382</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>T3_полн_i</t>
+          <t>ε_на_i_СА</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из ступени</t>
+          <t>СА: Диффузность решетки</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>313.442997929923</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>354.0214305740254</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>394.4947937841117</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>434.8949904414187</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>475.1545947444316</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>515.2708761709553</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>555.5938493530826</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>595.7288057964814</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>635.7905853599461</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>675.6805057771428</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>715.3766483915773</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
+      <c r="L18" s="1" t="inlineStr"/>
+      <c r="M18" s="1" t="inlineStr"/>
+      <c r="N18" s="1" t="inlineStr"/>
+      <c r="O18" s="1" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>0.7114125456675584</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i_plus_1</t>
+          <t>c_2_i_СА</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на входе в следующую ступень</t>
+          <t>СА: Абсолютная скорость на входе</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" s="2" t="n">
-        <v>313.442997929923</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>354.0214305740254</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>394.4947937841117</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>434.8949904414187</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>475.1545947444316</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>515.2708761709553</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>555.5938493530826</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>595.7288057964814</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>635.7905853599461</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>675.6805057771428</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>715.3766483915773</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
+      <c r="L19" s="1" t="inlineStr"/>
+      <c r="M19" s="1" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr"/>
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="2" t="n">
+        <v>144.2197636170161</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>π_полн_i</t>
+          <t>d2_отн_i_СА</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Степень повышения полного давления в ступени</t>
+          <t>СА: Относительный диаметр втулки на выходе РК</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="2" t="n">
-        <v>1.296289753371198</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1.273077659708594</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1.253849641297374</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1.237281701016347</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1.22253229938774</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1.209023758265309</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1.198579725967046</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1.188416178809493</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>1.178297216252501</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>1.168073869324779</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>1.157625977031957</v>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr"/>
+      <c r="M20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr"/>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="2" t="n">
+        <v>0.9222789955022731</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>P3_полн_i</t>
+          <t>D_вт2_i_СА</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Полное давление на выходе из ступени</t>
+          <t>СА: Втулочный диаметр на выходе РК</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="2" t="n">
-        <v>130218.2401608496</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>350977.5510224969</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>565398.1369373611</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>774745.4334443138</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>979743.4637323158</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>1180784.071770667</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1380620.218139306</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1577168.227042358</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>1770221.14666478</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1959552.50640327</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>2144884.792095456</v>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
+      <c r="L21" s="1" t="inlineStr"/>
+      <c r="M21" s="1" t="inlineStr"/>
+      <c r="N21" s="1" t="inlineStr"/>
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
+        <v>0.6324065815612947</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i_plus_1</t>
+          <t>h_на_i_СА</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед следующей ступенью</t>
+          <t>СА: Высота лопаток на входе</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="2" t="n">
-        <v>130218.2401608496</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>350977.5510224969</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>565398.1369373611</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>774745.4334443138</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>979743.4637323158</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>1180784.071770667</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>1380620.218139306</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>1577168.227042358</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>1770221.14666478</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1959552.50640327</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>2144884.792095456</v>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" s="1" t="inlineStr"/>
+      <c r="H22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr"/>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
+      <c r="L22" s="1" t="inlineStr"/>
+      <c r="M22" s="1" t="inlineStr"/>
+      <c r="N22" s="1" t="inlineStr"/>
+      <c r="O22" s="1" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>0.02664664109755077</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>a_кр_1_i</t>
+          <t>h_на_3_i_СА</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на входе в ступень</t>
+          <t>СА: Высота лопаток на выходе</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="2" t="n">
-        <v>310.7487734256569</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>331.2658695389746</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>350.5410496913398</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>368.8015096578053</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>386.12750213934</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>402.6360656708928</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>418.456840685445</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>433.5853814040989</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>448.2303868459118</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>462.3585281434915</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>476.0153347549245</v>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+      <c r="G23" s="1" t="inlineStr"/>
+      <c r="H23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr"/>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
+      <c r="L23" s="1" t="inlineStr"/>
+      <c r="M23" s="1" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr"/>
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>0.1651320519534955</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>a_кр_3_i</t>
+          <t>k_i</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на выходе из ступени</t>
+          <t>Показатель адиабаты по длине компрессора перед РК</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr"/>
       <c r="D24" s="2" t="n">
-        <v>324.0777372086121</v>
+        <v>1.399944336209296</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>344.2854048832162</v>
+        <v>1.397730417935234</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>363.3124869844129</v>
+        <v>1.394860425858321</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>381.2871709710695</v>
+        <v>1.393519592252976</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>398.3196353879731</v>
+        <v>1.390731081206798</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>414.5573247272538</v>
+        <v>1.388035570101426</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>430.1468909948723</v>
+        <v>1.384399004818129</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>445.1457480100918</v>
+        <v>1.38071062867211</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>459.5750811212067</v>
+        <v>1.37610539882691</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>473.4519105373238</v>
+        <v>1.372438981258499</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>486.829421102413</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+        <v>1.368632710893606</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>1.364566577433034</v>
+      </c>
+      <c r="P24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>r_ср1_отн_i</t>
+          <t>c_a_i_отн</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на входе в ступень</t>
+          <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>0.7697077367416805</v>
+        <v>0.65</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.7842865295989352</v>
+        <v>0.6242423636363637</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.8001506353803143</v>
+        <v>0.5984847272727273</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.8172252054161926</v>
+        <v>0.5727270909090909</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.8354360249081875</v>
+        <v>0.5469694545454545</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.8547104687203072</v>
+        <v>0.5212118181818182</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.874978249583736</v>
+        <v>0.4954541818181818</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.8961719742482401</v>
+        <v>0.4696965454545454</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.9182275294774144</v>
+        <v>0.4439389090909091</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.9410843228060074</v>
+        <v>0.4181812727272727</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.964685403461214</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+        <v>0.3924236363636364</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.366666</v>
+      </c>
+      <c r="P25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>c_u1_отн_i</t>
+          <t>c_a_i_отн_plus_1</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на входе</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>0.2209646382902902</v>
+        <v>0.6242423636363637</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.2221096430231778</v>
+        <v>0.5984847272727273</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.2247165257606272</v>
+        <v>0.5727270909090909</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.228735252285246</v>
+        <v>0.5469694545454545</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.2341340540041859</v>
+        <v>0.5212118181818182</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.2408842262649444</v>
+        <v>0.4954541818181818</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2489829529108338</v>
+        <v>0.4696965454545454</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.258436941975602</v>
+        <v>0.4439389090909091</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.2692656201432488</v>
+        <v>0.4181812727272727</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.2815002132115903</v>
+        <v>0.3924236363636364</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2951827699082133</v>
-      </c>
+        <v>0.366666</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.3409083636363636</v>
+      </c>
+      <c r="P26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>α_1_i</t>
+          <t>P1_полн_i</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на входе в РК</t>
+          <t>Полное давление перед ступенью</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>1.194971328079617</v>
+        <v>100281.0960676593</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.180574579602314</v>
+        <v>259571.363751415</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1.162887574917572</v>
+        <v>418861.6314351707</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1.141747321381765</v>
+        <v>578151.8991189264</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.116973003860716</v>
+        <v>737442.1668026821</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1.088399301490598</v>
+        <v>896732.4344864378</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.05585028991713</v>
+        <v>1056022.702170193</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.019183822447235</v>
+        <v>1215312.969853949</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.9783090134087981</v>
+        <v>1374603.237537705</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.9332157000484604</v>
+        <v>1533893.50522146</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.8840072960802917</v>
-      </c>
+        <v>1693183.772905216</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>1852474.040588972</v>
+      </c>
+      <c r="P27" s="1" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>c_a1_i</t>
+          <t>T1_полн_i</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на входе в ступень</t>
+          <t>Полная температура перед ступенью</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>179.267032761773</v>
+        <v>288</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>324.2171870844151</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>360.4343741688301</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>396.6515612532452</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>432.8687483376602</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>469.0859354220753</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>505.3031225064903</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>541.5203095909053</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>577.7374966753205</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>613.9546837597354</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>115.2430924897112</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+        <v>650.1718708441506</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>686.3890579285655</v>
+      </c>
+      <c r="P28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>λ_1_i</t>
+          <t>d1_отн_i</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на входе в ступень</t>
+          <t>Относительный диаметр втулки на входе в ступень</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>0.6201721739235834</v>
+        <v>0.433333</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.5642480089067109</v>
+        <v>0.4776322674794443</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5173169382832808</v>
+        <v>0.5219315349588886</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.4772577835273439</v>
+        <v>0.5662308024383328</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.4427623742092848</v>
+        <v>0.610530069917777</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.412838297016845</v>
+        <v>0.6548293373972213</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3867548721121836</v>
+        <v>0.6991286048766655</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.3640913140459806</v>
+        <v>0.7434278723561097</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.3443707830466253</v>
+        <v>0.787727139835554</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.3274240480592623</v>
+        <v>0.8320264073149982</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3130789351689683</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+        <v>0.8763256747944425</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.9206249422738867</v>
+      </c>
+      <c r="P29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>q_1_i</t>
+          <t>U_k_i</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на входе</t>
+          <t>Окружная скорость концов рабочих лопаток ступени</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>0.8289672515344797</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.7767379725045614</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.7282607559287695</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.6837140922479602</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.6432028517842318</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.6065518558070965</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5735101964321142</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.5440703958039792</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.5178567173824349</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.4949503270135798</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4753068980390184</v>
-      </c>
+        <v>308.7671838180617</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>308.7671838180617</v>
+      </c>
+      <c r="P30" s="1" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>F_1_i</t>
+          <t>Hт_i</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в ступень</t>
+          <t>Теоретический напор i-й ступени</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>0.3197918796405437</v>
+        <v>17213.60769857855</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.1333845085186511</v>
+        <v>19299.98554645581</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.09276327801446825</v>
+        <v>21273.14735656712</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.07559418092766981</v>
+        <v>23153.75324077504</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.06653889432920902</v>
+        <v>24953.70657307562</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.06128783511166349</v>
+        <v>26674.66540095004</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.05817197964158876</v>
+        <v>28310.68832067646</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.0563965166615289</v>
+        <v>29844.2202373475</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.05558444893690993</v>
+        <v>31248.7969253673</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.05549855900424231</v>
+        <v>32487.91774061825</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0560173881283241</v>
-      </c>
+        <v>33516.91184758506</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>34280.02437023168</v>
+      </c>
+      <c r="P31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>c_a3_отн_i</t>
+          <t>L_z_i</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Действительная работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>0.54</v>
+        <v>17041.47162159276</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.52</v>
+        <v>18913.98583552669</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.5</v>
+        <v>20634.9529358701</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.48</v>
+        <v>22227.60311114404</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.46</v>
+        <v>23706.02124442184</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.44</v>
+        <v>25074.18547689304</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.42</v>
+        <v>26612.04702143587</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.4</v>
+        <v>28053.56702310665</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0.38</v>
+        <v>29373.86910984526</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.36</v>
+        <v>30538.64267618115</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.34</v>
-      </c>
+        <v>31505.89713672996</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>32223.22290801778</v>
+      </c>
+      <c r="P32" s="1" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>c_a3_i</t>
+          <t>H_ад_i</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из ступени</t>
+          <t>Адиабатическая работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>13900.92427422371</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>15796.53525906431</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>17577.54320165069</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>19237.8112882135</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>20765.98640729716</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>22143.66564470295</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>23598.91039964076</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>24877.01110612619</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>25935.77296985775</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>115.2430924897112</v>
+        <v>26727.17433146713</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>108.840698462505</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+        <v>27200.2266041769</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>27301.45855272918</v>
+      </c>
+      <c r="P33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i_0</t>
+          <t>ΔT_полн_i</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе (1-е приближение)</t>
+          <t>Повышение полной температуры в ступени</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>0.5734271272297068</v>
+        <v>16.93983262583773</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.5228025526613771</v>
+        <v>18.72671864903633</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.4799344415446148</v>
+        <v>20.32495419588245</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.4431642821552224</v>
+        <v>21.84032769263562</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.4113261510914091</v>
+        <v>23.17430421945738</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.3835331465108897</v>
+        <v>24.38995576350158</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3591420777761956</v>
+        <v>25.71061674214281</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.3377484939263771</v>
+        <v>26.91495509619227</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.3190764313863512</v>
+        <v>27.93394414272255</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.3029231587547552</v>
+        <v>28.83533836177422</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2891175076909822</v>
-      </c>
+        <v>29.52650486669202</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>29.95465576298807</v>
+      </c>
+      <c r="P34" s="1" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>q_3_i</t>
+          <t>T3_полн_i</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на выходе</t>
+          <t>Полная температура на выходе из ступени</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>0.785749222309033</v>
+        <v>304.9398326258377</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.7341503741161742</v>
+        <v>342.9439057334514</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.6867841552835888</v>
+        <v>380.7593283647126</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.6436876257254293</v>
+        <v>418.4918889458808</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.6046548160285634</v>
+        <v>456.0430525571176</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.5693399760999998</v>
+        <v>493.4758911855769</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5375004202953272</v>
+        <v>531.0137392486331</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.5088838758809117</v>
+        <v>568.4352646870975</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.4834497779504509</v>
+        <v>605.671440818043</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.461124988676336</v>
+        <v>642.7900221215097</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4418193991278718</v>
-      </c>
+        <v>679.6983757108426</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>716.3437136915536</v>
+      </c>
+      <c r="P35" s="1" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>F_3_i_0</t>
+          <t>T1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на выходе (1-е приближение)</t>
+          <t>Полная температура на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>0.2715199844363019</v>
+        <v>304.9398326258377</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.1152518761147269</v>
+        <v>342.9439057334514</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.08133600902592081</v>
+        <v>380.7593283647126</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.06712407994818359</v>
+        <v>418.4918889458808</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.05975887380926437</v>
+        <v>456.0430525571176</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.05563589467254893</v>
+        <v>493.4758911855769</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.05327262404049409</v>
+        <v>531.0137392486331</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.05212041592284061</v>
+        <v>568.4352646870975</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.05184303068786426</v>
+        <v>605.671440818043</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.05225713605927209</v>
+        <v>642.7900221215097</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.05327648247001738</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+        <v>679.6983757108426</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>716.3437136915536</v>
+      </c>
+      <c r="P36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i_0</t>
+          <t>π_полн_i</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
+          <t>Степень повышения полного давления в ступени</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>0.5621035277056677</v>
+        <v>1.178260816228408</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.8424050296758627</v>
+        <v>1.180059686023751</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.8916784139804044</v>
+        <v>1.180261752585527</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.9115341308345269</v>
+        <v>1.179226209432988</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.9216559104437274</v>
+        <v>1.177183419270485</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.9272737612921701</v>
+        <v>1.174206307199574</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9304785920318749</v>
+        <v>1.172268279620001</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.9320371051015103</v>
+        <v>1.169319303871302</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.9324119160656946</v>
+        <v>1.165276107422811</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.9318523094273016</v>
+        <v>1.160024162710217</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.9304733686128156</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
+        <v>1.153480708406571</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>1.145567772697492</v>
+      </c>
+      <c r="P37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>r_ср3_отн_i</t>
+          <t>P3_полн_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из ступени</t>
+          <t>Полное давление на выходе из ступени</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>0.8147901831335521</v>
+        <v>118157.2861049597</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.9291062724438937</v>
+        <v>306309.7020092516</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.9510901796604888</v>
+        <v>494366.3632085076</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.9600155362539734</v>
+        <v>681771.8724744951</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.9645299711897813</v>
+        <v>868104.6914310164</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.9669647075918497</v>
+        <v>1052948.880444404</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9682510994927808</v>
+        <v>1237941.916312718</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.9687210437647382</v>
+        <v>1421088.915895385</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.9685643397409724</v>
+        <v>1601792.30988873</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.9678691439543144</v>
+        <v>1779353.529081164</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.9666562531855225</v>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+        <v>1953054.817833219</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>2122134.560657433</v>
+      </c>
+      <c r="P38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>c_3u_отн_i</t>
+          <t>P1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе</t>
+          <t>Полное давление перед следующей ступенью</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>0.2500657585861941</v>
+        <v>118157.2861049597</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.3180479671978335</v>
+        <v>306309.7020092516</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.3255888272795245</v>
+        <v>494366.3632085076</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.3247559975674831</v>
+        <v>681771.8724744951</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.3213200463991865</v>
+        <v>868104.6914310164</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.3168860663128854</v>
+        <v>1052948.880444404</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3121645376277475</v>
+        <v>1237941.916312718</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.3074800309669942</v>
+        <v>1421088.915895385</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0.3030876935226646</v>
+        <v>1601792.30988873</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.2991978289183804</v>
+        <v>1779353.529081164</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.295999401331859</v>
-      </c>
+        <v>1953054.817833219</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>2122134.560657433</v>
+      </c>
+      <c r="P39" s="1" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>α_3_i</t>
+          <t>a_кр_1_i</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из ступени</t>
+          <t>Критическая скорость потока на входе в ступень</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>1.137114566119295</v>
+        <v>310.7487734256569</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1.021868699911092</v>
+        <v>329.6005504723648</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.9935936749826273</v>
+        <v>347.3735553312965</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.9759654442114984</v>
+        <v>364.3350972913221</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.9610631051701353</v>
+        <v>380.445728537063</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.9466444624942251</v>
+        <v>395.8808441843627</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9316299423043648</v>
+        <v>410.6535144715717</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.9154341946829463</v>
+        <v>424.8775489240568</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.8975210063638877</v>
+        <v>438.5475167594254</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.8773745270752461</v>
+        <v>451.8304907351089</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.8544714971920427</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+        <v>464.6939992401076</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>477.1612274741949</v>
+      </c>
+      <c r="P40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i</t>
+          <t>a_кр_3_i</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе из ступени</t>
+          <t>Критическая скорость потока на выходе из ступени</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>0.5878226727702892</v>
+        <v>319.6516793218951</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.5667676571629278</v>
+        <v>338.840408978856</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.5257290901455642</v>
+        <v>356.9617663217595</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.4865679818699653</v>
+        <v>374.0745126267697</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.4509518490978591</v>
+        <v>390.3383336845696</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.418710515432304</v>
+        <v>405.8191370297563</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3894479028740119</v>
+        <v>420.7356256607985</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.3628203014767546</v>
+        <v>435.0026323280875</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0.3385735337714739</v>
+        <v>448.7721777926124</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.3165023114321974</v>
+        <v>462.0484732882691</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.296424541748485</v>
-      </c>
+        <v>474.8299314097559</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>487.1541509681631</v>
+      </c>
+      <c r="P41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>F_3_i</t>
+          <t>r_ср1_отн_i</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Действительная кольцевая площадь на выходе из ступени</t>
+          <t>Относительный средний радиус на входе в ступень</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>0.2668338728927827</v>
+        <v>0.7706417743961846</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.1085711657918483</v>
+        <v>0.7836238201259439</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.07575720556651902</v>
+        <v>0.7976253905137867</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.06221589109372239</v>
+        <v>0.8125937858579643</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.0553185434035527</v>
+        <v>0.8284766038560792</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.051585216662628</v>
+        <v>0.8452222965339011</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.04960891500043527</v>
+        <v>0.8627806227995598</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.04888627787204473</v>
+        <v>0.8811030023203678</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.0491272818916562</v>
+        <v>0.9001427794615425</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.05019599282151199</v>
+        <v>0.9198554077868715</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0520587088962016</v>
-      </c>
+        <v>0.9401985663422209</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.9611322188795871</v>
+      </c>
+      <c r="P42" s="1" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>F_1_i_plus_1</t>
+          <t>c_u1_отн_i</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в следующую ступень</t>
+          <t>Безразмерная окружная составляющая скорости на входе</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>0.1085711657918483</v>
+        <v>0.2681749895065709</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.07575720556651902</v>
+        <v>0.2626432704400548</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.06221589109372239</v>
+        <v>0.2589375633691295</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0553185434035527</v>
+        <v>0.2568607551455772</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.051585216662628</v>
+        <v>0.2562726928429279</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.04960891500043527</v>
+        <v>0.2570967550023658</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.04888627787204473</v>
+        <v>0.2592994625795795</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.0491272818916562</v>
+        <v>0.2629112878393494</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.05019599282151199</v>
+        <v>0.2680050628891228</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.0520587088962016</v>
+        <v>0.274698251908746</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.05392142497089122</v>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+        <v>0.2831378005426066</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0.293512661874265</v>
+      </c>
+      <c r="P43" s="1" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i</t>
+          <t>α_1_i</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе из ступени</t>
+          <t>Угол абсолютной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>0.5725085895090262</v>
+        <v>1.179495025805272</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.8523361607893765</v>
+        <v>1.172540092051643</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.8995249077670068</v>
+        <v>1.162459517319724</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.9182917073011213</v>
+        <v>1.149201179015582</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.9277047648075981</v>
+        <v>1.132638509944415</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.9327601467989414</v>
+        <v>1.112549356360051</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9354252419824672</v>
+        <v>1.088638115525776</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.9363978434753509</v>
+        <v>1.060500535986993</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.9360735870836928</v>
+        <v>1.027662092727253</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.9346343454194882</v>
+        <v>0.9895941702830344</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.9321204984578688</v>
-      </c>
+        <v>0.9457791446682415</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.8957563504782478</v>
+      </c>
+      <c r="P44" s="1" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>r_ср2_отн_i</t>
+          <t>c_a1_i</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из РК</t>
+          <t>Осевая скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>0.7922489599376163</v>
+        <v>200.6986694817401</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.8566964010214144</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.8756204075204015</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.8886203708350831</v>
+        <v>176.839330956311</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.8999829980489844</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.9108375881560784</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9216146745382584</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.9324465090064892</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.9433959346091934</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.9544767333801609</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.9656708283233683</v>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
+        <v>121.1675410636431</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>113.2144282218334</v>
+      </c>
+      <c r="P45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>c_u2_отн_i</t>
+          <t>λ_1_i</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
+          <t>Приведенная скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>0.5331301519094394</v>
+        <v>0.6986646556318482</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.5146604548210467</v>
+        <v>0.634437213999496</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.5258374113682019</v>
+        <v>0.5796257549949456</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.5412084154461251</v>
+        <v>0.5319548871089225</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.5581764649226804</v>
+        <v>0.4902260211292075</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.5760013884187075</v>
+        <v>0.4532847195365784</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5943180854893927</v>
+        <v>0.420462445486097</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.6129255216237373</v>
+        <v>0.3911735448557356</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.6316485675547341</v>
+        <v>0.3651041087545159</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.6503293830044945</v>
+        <v>0.3419134097427888</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.6688194353854364</v>
-      </c>
+        <v>0.3215314877548091</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0.3039222399597088</v>
+      </c>
+      <c r="P46" s="1" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>β_1_i</t>
+          <t>q_1_i</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на входе в РК</t>
+          <t>Газодинамическая функция расхода на входе</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.7955506638277184</v>
+        <v>0.8914385667933102</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.7652798913021186</v>
+        <v>0.8413654411462683</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.7348365983521747</v>
+        <v>0.7918473867768651</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.7042804852547354</v>
+        <v>0.743919872638364</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.673683828398578</v>
+        <v>0.6985663358146266</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.6431155521545162</v>
+        <v>0.6558877502623367</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6126566915509795</v>
+        <v>0.6161381750887489</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.5823837334686925</v>
+        <v>0.579276471718579</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.5523686610810169</v>
+        <v>0.5454653511210359</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.522676040644107</v>
+        <v>0.5145770133537996</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.493360586253362</v>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
+        <v>0.4868686813419682</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0.4625400694372556</v>
+      </c>
+      <c r="P47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>c_a2_отн_i</t>
+          <t>F_1_i</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Относительная осевая скорость на выходе из РК</t>
+          <t>Кольцевая площадь на входе в ступень</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.55</v>
+        <v>0.2997760086890333</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.53</v>
+        <v>0.1305708370620669</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.51</v>
+        <v>0.09104134603225567</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.49</v>
+        <v>0.07408168199530155</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.47</v>
+        <v>0.06510506475817548</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.45</v>
+        <v>0.05993788310461694</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.43</v>
+        <v>0.05692069005364717</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.41</v>
+        <v>0.05529623038562134</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.39</v>
+        <v>0.05466095223076663</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.37</v>
+        <v>0.054827183603715</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.35</v>
-      </c>
+        <v>0.0556775156680256</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0.05717246956874231</v>
+      </c>
+      <c r="P48" s="1" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>β_2_i</t>
+          <t>c_a3_отн_i</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на выходе из РК</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>1.130514300932322</v>
+        <v>0.6242423636363637</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.9976963533957118</v>
+        <v>0.5984847272727273</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.9696309402000549</v>
+        <v>0.5727270909090909</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.9540529427009995</v>
+        <v>0.5469694545454545</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.9420162509411002</v>
+        <v>0.5212118181818182</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.9310945109634914</v>
+        <v>0.4954541818181818</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9201942496553147</v>
+        <v>0.4696965454545454</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.9087932754368921</v>
+        <v>0.4439389090909091</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.8964504952448477</v>
+        <v>0.4181812727272727</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.8827721077517899</v>
+        <v>0.3924236363636364</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.867379103508124</v>
-      </c>
+        <v>0.366666</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0.3409083636363636</v>
+      </c>
+      <c r="P49" s="1" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>α_2_i</t>
+          <t>c_a3_i</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из РК</t>
+          <t>Осевая скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>0.8009719927700161</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.800080869900834</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.7701098785047441</v>
+        <v>176.839330956311</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.7357802744699108</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.6998474394994911</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.6632018232964938</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.626336287717333</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.5895630781807731</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.5531385944983337</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.5172699628481386</v>
+        <v>121.1675410636431</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4821213583193898</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
+        <v>113.2144282218334</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>105.2613153800237</v>
+      </c>
+      <c r="P50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>ε_рк_i</t>
+          <t>λ_3_i_0</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки РК</t>
+          <t>Приведенная скорость на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>0.3349636371046031</v>
+        <v>0.6522905517158071</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.2324164620935932</v>
+        <v>0.5916722681277904</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.2347943418478802</v>
+        <v>0.5397807353167764</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.2497724574462641</v>
+        <v>0.4948038176090149</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.2683324225425222</v>
+        <v>0.4553014664021219</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.2879789588089752</v>
+        <v>0.4203318386608639</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3075375581043353</v>
+        <v>0.3890517169050358</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.3264095419681996</v>
+        <v>0.3611164049330443</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.3440818341638308</v>
+        <v>0.336084761670369</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.3600960671076829</v>
+        <v>0.3137579271452634</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.374018517254762</v>
-      </c>
+        <v>0.2940139725025194</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0.2767758774722232</v>
+      </c>
+      <c r="P51" s="1" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>ε_на_i</t>
+          <t>q_3_i</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки НА</t>
+          <t>Газодинамическая функция расхода на выходе</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.3361425733492784</v>
+        <v>0.8561884456079026</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.2217878300102584</v>
+        <v>0.8032724183811697</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.2234837964778832</v>
+        <v>0.7520929105030987</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.2401851697415877</v>
+        <v>0.7037061981954605</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.2612156656706441</v>
+        <v>0.658283066591168</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.2834426391977313</v>
+        <v>0.615975986237888</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3052936545870318</v>
+        <v>0.5765450975889275</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.3258711165021732</v>
+        <v>0.5401796993964766</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.344382411865554</v>
+        <v>0.5066636800736265</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3601045642271075</v>
+        <v>0.4761052408825253</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3723501388726529</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
+        <v>0.4485988961632328</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0.4242301738763019</v>
+      </c>
+      <c r="P52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>W_1_i</t>
+          <t>F_3_i_0</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Относительная скорость на входе в РК</t>
+          <t>Кольцевая площадь на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>250.9867050594529</v>
+        <v>0.2725764489056055</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>249.5379481431306</v>
+        <v>0.1191948679619388</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>248.2784541017162</v>
+        <v>0.08347232382453508</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>247.2021510667909</v>
+        <v>0.06821618591968899</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>246.2975394635712</v>
+        <v>0.06024075607525418</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>245.551354564076</v>
+        <v>0.05574802600916222</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>244.9428504897047</v>
+        <v>0.05319427144827908</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>244.4478081615797</v>
+        <v>0.05195689254414564</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>244.0378032431153</v>
+        <v>0.05170696141701898</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>243.6805327507538</v>
+        <v>0.05226882371635489</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>243.3402025335798</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
+        <v>0.05356328194591679</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0.05558908454266487</v>
+      </c>
+      <c r="P53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>c_a2_i</t>
+          <t>d3_отн_i_0</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из РК</t>
+          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>176.0658357481699</v>
+        <v>0.5117365620141191</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>169.6634417209637</v>
+        <v>0.822936967915015</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>163.2610476937575</v>
+        <v>0.8797502017606259</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>156.8586536665514</v>
+        <v>0.9029249164025733</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>150.4562596393452</v>
+        <v>0.9148062839179557</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>144.053865612139</v>
+        <v>0.92143185495546</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>137.6514715849328</v>
+        <v>0.9251768071582691</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>131.2490775577267</v>
+        <v>0.9269859195970298</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>124.8466835305205</v>
+        <v>0.927350903505445</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>118.4442895033143</v>
+        <v>0.9265301929702799</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>112.0418954761081</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
+        <v>0.9246366093865259</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0.9216653786542286</v>
+      </c>
+      <c r="P54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>c_2_i</t>
+          <t>r_ср3_отн_i</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Абсолютная скорость на выходе из РК</t>
+          <t>Относительный средний радиус на выходе из ступени</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>245.205790034887</v>
+        <v>0.796458289612795</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>236.4935905104464</v>
+        <v>0.919417850854928</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>234.498329779823</v>
+        <v>0.9449485803391221</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>233.7107427554956</v>
+        <v>0.9555507493854893</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>233.5910995314393</v>
+        <v>0.9610101424640763</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>233.9892395892691</v>
+        <v>0.9640374951618152</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>234.8278183206815</v>
+        <v>0.9657068813504274</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>236.0603777859788</v>
+        <v>0.966439896320936</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>237.6400820277972</v>
+        <v>0.9664473809156909</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>239.518922866217</v>
+        <v>0.9658261258287665</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>241.6467913137315</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
+        <v>0.9645975070963569</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0.962717331134489</v>
+      </c>
+      <c r="P55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>τ_1_i</t>
+          <t>c_3u_отн_i</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на входе в РК</t>
+          <t>Безразмерная окружная составляющая скорости на выходе</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.9359051796510285</v>
+        <v>0.2835032773053563</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9471884974081952</v>
+        <v>0.34734799712873</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9558468274253789</v>
+        <v>0.352435191420564</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9625962844363063</v>
+        <v>0.3488900827391387</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.9680176322189936</v>
+        <v>0.342616711352984</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.9724188180361157</v>
+        <v>0.335264087026765</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9759918453834303</v>
+        <v>0.3275266501489218</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.9789558341494647</v>
+        <v>0.3197587688339675</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.9813382851974597</v>
+        <v>0.312237435632604</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.9832888381701964</v>
+        <v>0.3052290747281818</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.9848744817582111</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
+        <v>0.2990037584407125</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0.293858840869402</v>
+      </c>
+      <c r="P56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>T_1_i</t>
+          <t>α_3_i</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на входе в РК</t>
+          <t>Угол абсолютной скорости на выходе из ступени</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>269.5406917394962</v>
+        <v>1.144491830869796</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>310.2058455736416</v>
+        <v>1.044928945171008</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>350.7990404931795</v>
+        <v>1.019156857158087</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>391.300306340105</v>
+        <v>1.003002581888218</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>431.7424565133022</v>
+        <v>0.9892740024897305</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>472.1176143031199</v>
+        <v>0.9758932061902008</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>512.4056891025803</v>
+        <v>0.9618743582275009</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>552.6322356915423</v>
+        <v>0.9465911904311125</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>592.7416907832766</v>
+        <v>0.9294390008286465</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>632.7614345909392</v>
+        <v>0.9097361835365582</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>672.6860394027558</v>
-      </c>
+        <v>0.8866956174027838</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>0.8593837811273382</v>
+      </c>
+      <c r="P57" s="1" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>a_1_i</t>
+          <t>λ_3_i</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на входе в РК</t>
+          <t>Приведенная скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>300.6251763668889</v>
+        <v>0.6622582740779489</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>322.3999014125897</v>
+        <v>0.6305633163667279</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>342.7149378286148</v>
+        <v>0.5816846769873533</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>361.8385052109181</v>
+        <v>0.5355036259633932</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>379.9026907528486</v>
+        <v>0.4933913256469327</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>397.0446523527072</v>
+        <v>0.4551613945620491</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>413.4031356106535</v>
+        <v>0.4202279899523212</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>428.9989021073237</v>
+        <v>0.3883403401840831</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>444.0283162357795</v>
+        <v>0.3590732794875107</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>458.4789778163817</v>
+        <v>0.3322260291847228</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>472.401628579361</v>
-      </c>
+        <v>0.3076584768227875</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0.2852685760012213</v>
+      </c>
+      <c r="P58" s="1" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>M_w1_i</t>
+          <t>F_3_i</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Число Маха относительной скорости на входе в РК</t>
+          <t>Действительная кольцевая площадь на выходе из ступени</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.8348825207944121</v>
+        <v>0.270058941538246</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.7740013165319974</v>
+        <v>0.1142342616027879</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.7244459657194036</v>
+        <v>0.07907963397931937</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.6831836510121971</v>
+        <v>0.06419800582363021</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.6483174388038324</v>
+        <v>0.05647022154636605</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.6184477063449908</v>
+        <v>0.05216602093043148</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5925036106170077</v>
+        <v>0.04978674613749996</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.5698098688849922</v>
+        <v>0.04874072379054745</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.5495996411038141</v>
+        <v>0.0487300390785172</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.5314977229955928</v>
+        <v>0.04961663669729349</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.515112962809568</v>
-      </c>
+        <v>0.05136832875840946</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0.05404465568956616</v>
+      </c>
+      <c r="P59" s="1" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>λ_c2_i</t>
+          <t>F_1_i_plus_1</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Приведенная абсолютная скорость на выходе из РК</t>
+          <t>Кольцевая площадь на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.7566264568091747</v>
+        <v>0.1142342616027879</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.6869114611194933</v>
+        <v>0.07907963397931937</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.6454452796990806</v>
+        <v>0.06419800582363021</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.6129520229077641</v>
+        <v>0.05647022154636605</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.586441337002922</v>
+        <v>0.05216602093043148</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.5644315650271423</v>
+        <v>0.04978674613749996</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5459247137124625</v>
+        <v>0.04874072379054745</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.5302990735983107</v>
+        <v>0.0487300390785172</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.5170865257707974</v>
+        <v>0.04961663669729349</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.505899157940635</v>
+        <v>0.05136832875840946</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.4963685037081949</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
+        <v>0.05404465568956616</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0.05672098262072285</v>
+      </c>
+      <c r="P60" s="1" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>T2_полн_i</t>
+          <t>d3_отн_i</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из РК</t>
+          <t>Относительный диаметр втулки на выходе из ступени</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>313.442997929923</v>
+        <v>0.5183547184948523</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>354.0214305740254</v>
+        <v>0.8310585833389782</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>394.4947937841117</v>
+        <v>0.8864849908316806</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>434.8949904414187</v>
+        <v>0.9089303984917328</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>475.1545947444316</v>
+        <v>0.9203700276723751</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>515.2708761709553</v>
+        <v>0.9266804110132759</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>555.5938493530826</v>
+        <v>0.9301502896710493</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>595.7288057964814</v>
+        <v>0.9316716945371063</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>635.7905853599461</v>
+        <v>0.9316872222788061</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>675.6805057771428</v>
+        <v>0.9303978776130181</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>715.3766483915773</v>
-      </c>
+        <v>0.9278451925795664</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0.9239314473127467</v>
+      </c>
+      <c r="P61" s="1" t="inlineStr"/>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>τ_2_i</t>
+          <t>r_ср2_отн_i</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на выходе из РК</t>
+          <t>Относительный средний радиус на выходе из РК</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.9050376398220753</v>
+        <v>0.7835500320044898</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.9221515369239762</v>
+        <v>0.851520835490436</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.9315887440071891</v>
+        <v>0.8712869854264544</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.9387054073290569</v>
+        <v>0.8840722676217267</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.9443452715453308</v>
+        <v>0.8947433731600778</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9488659986366965</v>
+        <v>0.9046298958478582</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9526874245639199</v>
+        <v>0.9142437520749935</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.9557472067545164</v>
+        <v>0.9237714493206519</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.9583215134744612</v>
+        <v>0.9332950801886167</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.9605060583055894</v>
+        <v>0.9428407668078189</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9623671724133392</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
+        <v>0.9523980367192889</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0.9619247750070381</v>
+      </c>
+      <c r="P62" s="1" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>T_2_i</t>
+          <t>c_u2_отн_i</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на выходе из РК</t>
+          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>618.1561170673046</v>
+        <v>0.4941891122024217</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>629.8452001671857</v>
+        <v>0.4794395527867925</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>636.2909732818439</v>
+        <v>0.4931453076634404</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>641.1517754981871</v>
+        <v>0.5108012363827721</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>645.0038987815944</v>
+        <v>0.52982516230889</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>648.0916323543871</v>
+        <v>0.5495029770131883</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>650.7017313258477</v>
+        <v>0.5695109756896494</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>652.7916146575318</v>
+        <v>0.5896378114298403</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>654.54990997711</v>
+        <v>0.6096830608846393</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>656.0419912905846</v>
+        <v>0.6294289763436328</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>657.3131639132968</v>
-      </c>
+        <v>0.6486443337625243</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0.6670694869952146</v>
+      </c>
+      <c r="P63" s="1" t="inlineStr"/>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>a_2_i</t>
+          <t>β_1_i</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на выходе из РК</t>
+          <t>Угол относительной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>455.1878653606111</v>
+        <v>0.9127208168054688</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>459.3078267797998</v>
+        <v>0.8753224259487161</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>461.4872296915951</v>
+        <v>0.8379336182331615</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>463.0632867898798</v>
+        <v>0.8004565383967955</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>464.2141998143966</v>
+        <v>0.7628545769696604</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>465.0598657953267</v>
+        <v>0.725152515069329</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>465.6865011908989</v>
+        <v>0.6874114880709427</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>466.1175242700996</v>
+        <v>0.649738002012511</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>466.4555110608122</v>
+        <v>0.6122558340319789</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>466.6790527756584</v>
+        <v>0.5750983286599214</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>466.8137721497224</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
+        <v>0.5383883627215444</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0.5022395472596254</v>
+      </c>
+      <c r="P64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>M_c2_ср_i</t>
+          <t>c_a2_отн_i</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Среднее число Маха на выходе из РК</t>
+          <t>Относительная осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.5386914034727813</v>
+        <v>0.6371211818181819</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.514891270563577</v>
+        <v>0.6113635454545454</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.5081361188185742</v>
+        <v>0.5856059090909091</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.5047058348668969</v>
+        <v>0.5598482727272727</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.5031967992897124</v>
+        <v>0.5340906363636364</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.5031378899770466</v>
+        <v>0.5083329999999999</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5042615959881958</v>
+        <v>0.4825753636363636</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.5064396112453169</v>
+        <v>0.4568177272727272</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.5094592654449651</v>
+        <v>0.4310600909090909</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.5132412124384729</v>
+        <v>0.4053024545454545</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.5176513756244266</v>
-      </c>
+        <v>0.3795448181818182</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0.3537871818181818</v>
+      </c>
+      <c r="P65" s="1" t="inlineStr"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>β_2_i</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Угол относительной скорости на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>1.144480572081726</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1.024070802073349</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.9974306823545782</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0.9827456836395317</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.9713996514092181</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0.9610033265773484</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.9504973245841769</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.9392814156996514</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0.9268248029940885</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>0.9125624929681139</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.8958660843865471</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0.8760036110637557</v>
+      </c>
+      <c r="P66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>α_2_i</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>0.9110743488838259</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0.9057556896616156</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0.8708999706835606</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0.8311767015007679</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0.7894073633793292</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0.7464987402784139</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.7029538330969465</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.6591494440308061</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0.6154240099789121</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>0.5720897895915963</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0.5294180059149334</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0.4876398341968385</v>
+      </c>
+      <c r="P67" s="1" t="inlineStr"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>ε_рк_i</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки РК</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>0.2317597552762571</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0.1487483761246328</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0.1594970641214167</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0.1822891452427362</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.2085450744395577</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0.2358508115080195</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.2630858365132343</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.2895434136871404</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0.3145689689621096</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>0.3374641643081925</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0.3574777216650027</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>0.3737640638041303</v>
+      </c>
+      <c r="P68" s="1" t="inlineStr"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>ε_на_i</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки НА</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>0.2334174819859701</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0.139173255509392</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.1482568864745263</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0.1718258803874496</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.1998666391104014</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0.2293944659117869</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.2589205251305544</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.2874417464003064</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0.3140149908497344</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>0.3376463939449619</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0.3572776114878504</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>0.3717439469304997</v>
+      </c>
+      <c r="P69" s="1" t="inlineStr"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>W_1_i</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Относительная скорость на входе в РК</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>253.673029334167</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>251.0524551056513</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>248.6234593867609</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>246.4061801101378</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>244.4127578697729</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>242.6433534506775</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>241.0885247514319</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>239.7226419962918</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>238.5073800674136</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>237.3902297051156</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>236.3078107281634</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>235.182478936269</v>
+      </c>
+      <c r="P70" s="1" t="inlineStr"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>c_a2_i</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>196.7221130608353</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>188.7690002190255</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>180.8158873772159</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>172.8627745354061</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>164.9096616935965</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>156.9565488517867</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>149.0034360099771</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>141.0503231681674</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>133.0972103263576</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>125.144097484548</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>117.1909846427383</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>109.2378718009286</v>
+      </c>
+      <c r="P71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>c_2_i</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Абсолютная скорость на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr"/>
+      <c r="D72" s="2" t="n">
+        <v>248.9640712888368</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>239.8919674315049</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>236.3887712508276</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>234.0015262669965</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>232.28806020156</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>231.133627173989</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>230.486323255149</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>230.307036219323</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>230.5492913204617</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>231.1532097532483</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>232.0470620862769</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>233.1441836147533</v>
+      </c>
+      <c r="P72" s="1" t="inlineStr"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>τ_1_i</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>Температурная функция на входе в РК</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr"/>
+      <c r="D73" s="2" t="n">
+        <v>0.9186540511911265</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0.9332324020183315</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0.9446065070592682</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0.9534757930317376</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0.9607228514711692</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0.9666133453688397</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.9714991543237266</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.9755303734032933</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0.9789002501146955</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>0.9816476219524559</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0.983910477052632</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0.9857586792737885</v>
+      </c>
+      <c r="P73" s="1" t="inlineStr"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>T_1_i</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>Статическая температура на входе в РК</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr"/>
+      <c r="D74" s="2" t="n">
+        <v>264.5723667430444</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>302.5699842784154</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>340.4686552077119</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>378.1976619232148</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>415.8668982157129</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>453.4247253038037</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>490.9015561921937</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>528.2695098206829</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>565.5473799961093</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>602.6871552993164</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>639.7109156084705</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>676.6139712116426</v>
+      </c>
+      <c r="P74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>a_1_i</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Скорость звука на входе в РК</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr"/>
+      <c r="D75" s="2" t="n">
+        <v>297.8416439870647</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>318.4071657272538</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>337.6153780608649</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>355.7589590562439</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>372.8994757736503</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>389.2161757057316</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>404.7592266164098</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>419.6470562163746</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>433.8962292448272</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>447.6652095460076</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>460.9404875813311</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>473.7513405775682</v>
+      </c>
+      <c r="P75" s="1" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>M_w1_i</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>Число Маха относительной скорости на входе в РК</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>0.8517043685979119</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0.7884635841415134</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.7364103519654823</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0.6926211521525788</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0.6554387274551475</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0.6234153886608478</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.59563441398684</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.5712482393125335</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0.5496876072938516</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>0.5302851877765106</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.5126644699148236</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>0.4964259914273786</v>
+      </c>
+      <c r="P76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>λ_c2_i</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>Приведенная абсолютная скорость на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>0.7788605140976763</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0.7079792169843426</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.6622243432024892</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0.625547901202427</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.5950941533435727</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0.5695483679396847</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.5478174635037193</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.5294382587681008</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0.5137334770940361</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>0.5002791332870248</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.4886951026809453</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>0.4785840029309119</v>
+      </c>
+      <c r="P77" s="1" t="inlineStr"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>T2_полн_i</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>Полная температура на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>304.9398326258377</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>342.9439057334514</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>380.7593283647126</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>418.4918889458808</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>456.0430525571176</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>493.4758911855769</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>531.0137392486331</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>568.4352646870975</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>605.671440818043</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>642.7900221215097</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>679.6983757108426</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>716.3437136915536</v>
+      </c>
+      <c r="P78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>τ_2_i</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>Температурная функция на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>0.8993745518291292</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>0.9173573147344318</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0.9278992710844721</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0.9360459025983171</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0.9424557262326057</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0.9477044727256937</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.9520089627972769</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.9556315242080048</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0.9585680081018132</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>0.9610487925453612</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.9631785168028687</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0.9650201394990218</v>
+      </c>
+      <c r="P79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>T_2_i</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Статическая температура на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>617.3208513549218</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>629.6640230444452</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>636.8999065322735</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>642.4916652623527</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>646.8912980681803</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>650.4939802288768</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>653.4485351139737</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>655.9350216279715</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>657.9505920414651</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>659.6533753385959</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>661.1151947653541</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>662.3792644328264</v>
+      </c>
+      <c r="P80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>a_2_i</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>Скорость звука на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>454.8802316354819</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>459.2311063860777</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>461.7167694612662</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>463.5956285515898</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>464.9884454582512</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>466.0587672688607</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>466.8569228138085</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>467.4492898292888</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>467.8710213489689</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>468.2073318775922</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>468.4413278818004</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>468.5935986159338</v>
+      </c>
+      <c r="P81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>M_c2_ср_i</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>Среднее число Маха на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>0.5473178519842647</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0.522377435011614</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0.5119778766680868</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0.5047535219391233</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0.499556628708564</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0.4959323660585754</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.4936979875246947</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.4926888140175172</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0.4927624939363426</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>0.4936983981568251</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.4953599272198038</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>0.4975402658153717</v>
+      </c>
+      <c r="P82" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -426,20 +426,20 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.9899417183381966</v>
+        <v>0.9900580361061417</v>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>100281.0960676593</v>
+        <v>100292.8790575521</v>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.2879994046470533</v>
+        <v>0.2224545653195953</v>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>66.10301705129361</v>
+        <v>71.10711510468475</v>
       </c>
       <c r="D6" s="1" t="inlineStr"/>
       <c r="E6" s="1" t="inlineStr"/>
@@ -717,7 +717,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>0.9611322188795871</v>
+        <v>0.9595531619480527</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -745,7 +745,7 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>109.2378718009286</v>
+        <v>106.3166261739218</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -773,7 +773,7 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="2" t="n">
-        <v>0.4625400694372556</v>
+        <v>0.4537118711400231</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -801,7 +801,7 @@
       <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>0.05404465568956616</v>
+        <v>0.05555276895854432</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -857,7 +857,7 @@
       <c r="N13" s="1" t="inlineStr"/>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>0.05404465568956616</v>
+        <v>0.05555276895854432</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -885,7 +885,7 @@
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="2" t="n">
-        <v>0.3554357598494053</v>
+        <v>0.3421954010820806</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -913,7 +913,7 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>0.5183547184948523</v>
+        <v>0.5026572059935642</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -941,7 +941,7 @@
       <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="inlineStr"/>
       <c r="P16" s="2" t="n">
-        <v>0.796458289612795</v>
+        <v>0.7914114817012881</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -969,7 +969,7 @@
       <c r="N17" s="1" t="inlineStr"/>
       <c r="O17" s="1" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>0.8593837811273382</v>
+        <v>0.8521100845146086</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -997,7 +997,7 @@
       <c r="N18" s="1" t="inlineStr"/>
       <c r="O18" s="1" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>0.7114125456675584</v>
+        <v>0.718686242280288</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1025,7 +1025,7 @@
       <c r="N19" s="1" t="inlineStr"/>
       <c r="O19" s="1" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>144.2197636170161</v>
+        <v>141.2523884686373</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1053,7 +1053,7 @@
       <c r="N20" s="1" t="inlineStr"/>
       <c r="O20" s="1" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>0.9222789955022731</v>
+        <v>0.9189293312859016</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -1081,7 +1081,7 @@
       <c r="N21" s="1" t="inlineStr"/>
       <c r="O21" s="1" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>0.6324065815612947</v>
+        <v>0.6255821807307252</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -1109,7 +1109,7 @@
       <c r="N22" s="1" t="inlineStr"/>
       <c r="O22" s="1" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>0.02664664109755077</v>
+        <v>0.02759535690110904</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1137,7 +1137,7 @@
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>0.1651320519534955</v>
+        <v>0.1692887467254313</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1206,37 +1206,37 @@
         <v>0.65</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.6242423636363637</v>
+        <v>0.6236363636363637</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.5984847272727273</v>
+        <v>0.5972727272727273</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.5727270909090909</v>
+        <v>0.5709090909090909</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.5469694545454545</v>
+        <v>0.5445454545454546</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.5212118181818182</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4954541818181818</v>
+        <v>0.4918181818181818</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.4696965454545454</v>
+        <v>0.4654545454545455</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.4439389090909091</v>
+        <v>0.4390909090909091</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.4181812727272727</v>
+        <v>0.4127272727272727</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3924236363636364</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.366666</v>
+        <v>0.36</v>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
     </row>
@@ -1253,40 +1253,40 @@
       </c>
       <c r="C26" s="1" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>0.6242423636363637</v>
+        <v>0.6236363636363637</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.5984847272727273</v>
+        <v>0.5972727272727273</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.5727270909090909</v>
+        <v>0.5709090909090909</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.5469694545454545</v>
+        <v>0.5445454545454546</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.5212118181818182</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.4954541818181818</v>
+        <v>0.4918181818181818</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4696965454545454</v>
+        <v>0.4654545454545455</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.4439389090909091</v>
+        <v>0.4390909090909091</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.4181812727272727</v>
+        <v>0.4127272727272727</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.3924236363636364</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.366666</v>
+        <v>0.36</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.3409083636363636</v>
+        <v>0.3336363636363636</v>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
     </row>
@@ -1303,40 +1303,40 @@
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>100281.0960676593</v>
+        <v>100292.8790575521</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>259571.363751415</v>
+        <v>259542.8799520527</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>418861.6314351707</v>
+        <v>418792.8808465532</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>578151.8991189264</v>
+        <v>578042.8817410537</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>737442.1668026821</v>
+        <v>737292.8826355543</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>896732.4344864378</v>
+        <v>896542.8835300547</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1056022.702170193</v>
+        <v>1055792.884424555</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1215312.969853949</v>
+        <v>1215042.885319056</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1374603.237537705</v>
+        <v>1374292.886213556</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1533893.50522146</v>
+        <v>1533542.887108057</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1693183.772905216</v>
+        <v>1692792.888002557</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>1852474.040588972</v>
+        <v>1852042.888897058</v>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
     </row>
@@ -1403,40 +1403,40 @@
       </c>
       <c r="C29" s="1" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>0.433333</v>
+        <v>0.43</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.4776322674794443</v>
+        <v>0.4743022422822237</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5219315349588886</v>
+        <v>0.5186044845644475</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.5662308024383328</v>
+        <v>0.5629067268466712</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.610530069917777</v>
+        <v>0.6072089691288949</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.6548293373972213</v>
+        <v>0.6515112114111187</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6991286048766655</v>
+        <v>0.6958134536933425</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.7434278723561097</v>
+        <v>0.7401156959755661</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.787727139835554</v>
+        <v>0.7844179382577898</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.8320264073149982</v>
+        <v>0.8287201805400136</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.8763256747944425</v>
+        <v>0.8730224228222374</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.9206249422738867</v>
+        <v>0.9173246651044611</v>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
     </row>
@@ -1453,40 +1453,40 @@
       </c>
       <c r="C30" s="1" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
     </row>
@@ -1503,40 +1503,40 @@
       </c>
       <c r="C31" s="1" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>17213.60769857855</v>
+        <v>16967.12604306373</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>19299.98554645581</v>
+        <v>19070.88223528092</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>21273.14735656712</v>
+        <v>21057.52246874931</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23153.75324077504</v>
+        <v>22950.09410526995</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>24953.70657307562</v>
+        <v>24759.14168894694</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26674.66540095004</v>
+        <v>26487.00632294096</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28310.68832067646</v>
+        <v>28125.52905279903</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>29844.2202373475</v>
+        <v>29654.33031092169</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>31248.7969253673</v>
+        <v>31044.54895603916</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>32487.91774061825</v>
+        <v>32256.73667984891</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>33516.91184758506</v>
+        <v>33239.72047130691</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>34280.02437023168</v>
+        <v>33933.38931404932</v>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
     </row>
@@ -1553,40 +1553,40 @@
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>17041.47162159276</v>
+        <v>16797.45478263309</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18913.98583552669</v>
+        <v>18689.4645905753</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20634.9529358701</v>
+        <v>20425.79679468683</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>22227.60311114404</v>
+        <v>22032.09034105915</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23706.02124442184</v>
+        <v>23521.18460449959</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25074.18547689304</v>
+        <v>24897.7859435645</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26612.04702143587</v>
+        <v>26437.99730963109</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>28053.56702310665</v>
+        <v>27875.07049226639</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>29373.86910984526</v>
+        <v>29181.87601867681</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>30538.64267618115</v>
+        <v>30321.33247905798</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>31505.89713672996</v>
+        <v>31245.33724302849</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>32223.22290801778</v>
+        <v>31897.38595520635</v>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
     </row>
@@ -1603,40 +1603,40 @@
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>13900.92427422371</v>
+        <v>13701.87693398603</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15796.53525906431</v>
+        <v>15617.01385068403</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>17577.54320165069</v>
+        <v>17413.88007155858</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19237.8112882135</v>
+        <v>19087.25918979651</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>20765.98640729716</v>
+        <v>20623.27203085376</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22143.66564470295</v>
+        <v>22003.16976086839</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23598.91039964076</v>
+        <v>23450.49881419504</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>24877.01110612619</v>
+        <v>24708.63115599736</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>25935.77296985775</v>
+        <v>25732.59482627098</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>26727.17433146713</v>
+        <v>26471.29676564151</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>27200.2266041769</v>
+        <v>26869.11978064452</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>27301.45855272918</v>
+        <v>26870.38869889748</v>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
     </row>
@@ -1653,40 +1653,40 @@
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>16.93983262583773</v>
+        <v>16.6972711556989</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.72671864903633</v>
+        <v>18.50442038670822</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>20.32495419588245</v>
+        <v>20.11894020580701</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.84032769263562</v>
+        <v>21.64822137575578</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>23.17430421945738</v>
+        <v>22.99361339494931</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.38995576350158</v>
+        <v>24.21836985820667</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25.71061674214281</v>
+        <v>25.542462618911</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>26.91495509619227</v>
+        <v>26.74370321551575</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>27.93394414272255</v>
+        <v>27.75136266990286</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28.83533836177422</v>
+        <v>28.63014872286476</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>29.52650486669202</v>
+        <v>29.28231493183464</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>29.95465576298807</v>
+        <v>29.65175826002295</v>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
     </row>
@@ -1703,40 +1703,40 @@
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>304.9398326258377</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>342.9439057334514</v>
+        <v>342.7216074711233</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>380.7593283647126</v>
+        <v>380.5533143746371</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>418.4918889458808</v>
+        <v>418.299782629001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>456.0430525571176</v>
+        <v>455.8623617326095</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>493.4758911855769</v>
+        <v>493.3043052802819</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>531.0137392486331</v>
+        <v>530.8455851254013</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>568.4352646870975</v>
+        <v>568.2640128064211</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>605.671440818043</v>
+        <v>605.4888593452233</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>642.7900221215097</v>
+        <v>642.5848324826002</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>679.6983757108426</v>
+        <v>679.4541857759853</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>716.3437136915536</v>
+        <v>716.0408161885885</v>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
     </row>
@@ -1753,40 +1753,40 @@
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>304.9398326258377</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>342.9439057334514</v>
+        <v>342.7216074711233</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>380.7593283647126</v>
+        <v>380.5533143746371</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>418.4918889458808</v>
+        <v>418.299782629001</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>456.0430525571176</v>
+        <v>455.8623617326095</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>493.4758911855769</v>
+        <v>493.3043052802819</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>531.0137392486331</v>
+        <v>530.8455851254013</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>568.4352646870975</v>
+        <v>568.2640128064211</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>605.671440818043</v>
+        <v>605.4888593452233</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>642.7900221215097</v>
+        <v>642.5848324826002</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>679.6983757108426</v>
+        <v>679.4541857759853</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>716.3437136915536</v>
+        <v>716.0408161885885</v>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
     </row>
@@ -1803,40 +1803,40 @@
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>1.178260816228408</v>
+        <v>1.175559285399187</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1.180059686023751</v>
+        <v>1.177892225128341</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1.180261752585527</v>
+        <v>1.178483449737299</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.179226209432988</v>
+        <v>1.177740365938578</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.177183419270485</v>
+        <v>1.175894000936239</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.174206307199574</v>
+        <v>1.173036766366976</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.172268279620001</v>
+        <v>1.171122407075676</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.169319303871302</v>
+        <v>1.168108071555353</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1.165276107422811</v>
+        <v>1.163909173397865</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.160024162710217</v>
+        <v>1.158409204291314</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.153480708406571</v>
+        <v>1.151515127689758</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>1.145567772697492</v>
+        <v>1.143155604508661</v>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
     </row>
@@ -1853,40 +1853,40 @@
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>118157.2861049597</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>306309.7020092516</v>
+        <v>305713.5403829411</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>494366.3632085076</v>
+        <v>493540.4789454677</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>681771.8724744951</v>
+        <v>680784.4350698986</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>868104.6914310164</v>
+        <v>866978.2776241348</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1052948.880444404</v>
+        <v>1051677.76500542</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1237941.916312718</v>
+        <v>1236462.704180656</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1421088.915895385</v>
+        <v>1419301.401627094</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1601792.30988873</v>
+        <v>1599552.097199386</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1779353.529081164</v>
+        <v>1776470.195601449</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1953054.817833219</v>
+        <v>1949276.618580578</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>2122134.560657433</v>
+        <v>2117173.208233083</v>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
     </row>
@@ -1903,40 +1903,40 @@
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>118157.2861049597</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>306309.7020092516</v>
+        <v>305713.5403829411</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>494366.3632085076</v>
+        <v>493540.4789454677</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>681771.8724744951</v>
+        <v>680784.4350698986</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>868104.6914310164</v>
+        <v>866978.2776241348</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1052948.880444404</v>
+        <v>1051677.76500542</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1237941.916312718</v>
+        <v>1236462.704180656</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1421088.915895385</v>
+        <v>1419301.401627094</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1601792.30988873</v>
+        <v>1599552.097199386</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1779353.529081164</v>
+        <v>1776470.195601449</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1953054.817833219</v>
+        <v>1949276.618580578</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>2122134.560657433</v>
+        <v>2117173.208233083</v>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
     </row>
@@ -2003,40 +2003,40 @@
       </c>
       <c r="C41" s="1" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>319.6516793218951</v>
+        <v>319.5245220964998</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>338.840408978856</v>
+        <v>338.7305720009615</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>356.9617663217595</v>
+        <v>356.8651842260853</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>374.0745126267697</v>
+        <v>373.9886443846121</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>390.3383336845696</v>
+        <v>390.2609971889856</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>405.8191370297563</v>
+        <v>405.7485774550155</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>420.7356256607985</v>
+        <v>420.6690040022493</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>435.0026323280875</v>
+        <v>434.9371010045424</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>448.7721777926124</v>
+        <v>448.7045308344883</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>462.0484732882691</v>
+        <v>461.97472048923</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>474.8299314097559</v>
+        <v>474.7446295243685</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>487.1541509681631</v>
+        <v>487.0511463806778</v>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
     </row>
@@ -2053,40 +2053,40 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>0.7706417743961846</v>
+        <v>0.7697077367416805</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.7836238201259439</v>
+        <v>0.7826118504833496</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.7976253905137867</v>
+        <v>0.7965395820078109</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.8125937858579643</v>
+        <v>0.8114382241209841</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.8284766038560792</v>
+        <v>0.8272553209833634</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.8452222965339011</v>
+        <v>0.8439392331780717</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8627806227995598</v>
+        <v>0.8614395980974688</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.8811030023203678</v>
+        <v>0.8797076910626043</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.9001427794615425</v>
+        <v>0.8986966957379452</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.9198554077868715</v>
+        <v>0.9183618942536413</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.9401985663422209</v>
+        <v>0.9386607882377982</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.9611322188795871</v>
+        <v>0.9595531619480527</v>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
     </row>
@@ -2103,40 +2103,40 @@
       </c>
       <c r="C43" s="1" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>0.2681749895065709</v>
+        <v>0.2675658145409672</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.2626432704400548</v>
+        <v>0.2616490023434986</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.2589375633691295</v>
+        <v>0.2576095825081036</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.2568607551455772</v>
+        <v>0.2552316373223689</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.2562726928429279</v>
+        <v>0.2543820897171053</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.2570967550023658</v>
+        <v>0.2549786247517394</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2592994625795795</v>
+        <v>0.2570008412996226</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.2629112878393494</v>
+        <v>0.2604957112317619</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.2680050628891228</v>
+        <v>0.2655491738474892</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.274698251908746</v>
+        <v>0.2722944518517804</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2831378005426066</v>
+        <v>0.2809134165726251</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.293512661874265</v>
+        <v>0.2916156103246133</v>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
     </row>
@@ -2153,40 +2153,40 @@
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>1.179495025805272</v>
+        <v>1.180296158977294</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1.172540092051643</v>
+        <v>1.17354769367773</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1.162459517319724</v>
+        <v>1.163593381597623</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1.149201179015582</v>
+        <v>1.15038850731903</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.132638509944415</v>
+        <v>1.133775838988559</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.112549356360051</v>
+        <v>1.113517639280561</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.088638115525776</v>
+        <v>1.089269891516375</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.060500535986993</v>
+        <v>1.060567821445653</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1.027662092727253</v>
+        <v>1.026876578551888</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.9895941702830344</v>
+        <v>0.9876014776906153</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.9457791446682415</v>
+        <v>0.9421326350930992</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.8957563504782478</v>
+        <v>0.8899613152251319</v>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
     </row>
@@ -2203,40 +2203,40 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>200.6986694817401</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
     </row>
@@ -2253,40 +2253,40 @@
       </c>
       <c r="C46" s="1" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>0.6986646556318482</v>
+        <v>0.6934155588636786</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.634437213999496</v>
+        <v>0.6290007738192603</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.5796257549949456</v>
+        <v>0.574014360850995</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.5319548871089225</v>
+        <v>0.5261763607748462</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.4902260211292075</v>
+        <v>0.4842889204649947</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.4532847195365784</v>
+        <v>0.4471981639398266</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.420462445486097</v>
+        <v>0.4142409216095714</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.3911735448557356</v>
+        <v>0.3848409007715879</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.3651041087545159</v>
+        <v>0.358692486055376</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.3419134097427888</v>
+        <v>0.335469182640696</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.3215314877548091</v>
+        <v>0.3151227911923925</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0.3039222399597088</v>
+        <v>0.2976385445704193</v>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
     </row>
@@ -2303,40 +2303,40 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.8914385667933102</v>
+        <v>0.8876763917513479</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.8413654411462683</v>
+        <v>0.8367187220902095</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.7918473867768651</v>
+        <v>0.7864274238623349</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.743919872638364</v>
+        <v>0.7378118937190112</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.6985663358146266</v>
+        <v>0.6918457719220593</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.6558877502623367</v>
+        <v>0.6486182523825925</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6161381750887489</v>
+        <v>0.608383057920596</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.579276471718579</v>
+        <v>0.571105333397828</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.5454653511210359</v>
+        <v>0.5369562412061231</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.5145770133537996</v>
+        <v>0.5058253851811065</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4868686813419682</v>
+        <v>0.4780003690667221</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0.4625400694372556</v>
+        <v>0.4537118711400231</v>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
     </row>
@@ -2353,40 +2353,40 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.2997760086890333</v>
+        <v>0.3009117955899137</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.1305708370620669</v>
+        <v>0.1312547944711213</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.09104134603225567</v>
+        <v>0.09163894407812001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.07408168199530155</v>
+        <v>0.07466934589439193</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.06510506475817548</v>
+        <v>0.06571582737082768</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.05993788310461694</v>
+        <v>0.06059354891620095</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.05692069005364717</v>
+        <v>0.05763976482606604</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.05529623038562134</v>
+        <v>0.05609774057576191</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.05466095223076663</v>
+        <v>0.05556606751348679</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.054827183603715</v>
+        <v>0.05586177064312022</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0556775156680256</v>
+        <v>0.05687360435199427</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.05717246956874231</v>
+        <v>0.05857117009930012</v>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
     </row>
@@ -2403,40 +2403,40 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.6242423636363637</v>
+        <v>0.6236363636363637</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.5984847272727273</v>
+        <v>0.5972727272727273</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.5727270909090909</v>
+        <v>0.5709090909090909</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.5469694545454545</v>
+        <v>0.5445454545454546</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.5212118181818182</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.4954541818181818</v>
+        <v>0.4918181818181818</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4696965454545454</v>
+        <v>0.4654545454545455</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.4439389090909091</v>
+        <v>0.4390909090909091</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.4181812727272727</v>
+        <v>0.4127272727272727</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.3924236363636364</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.366666</v>
+        <v>0.36</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0.3409083636363636</v>
+        <v>0.3336363636363636</v>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
     </row>
@@ -2453,40 +2453,40 @@
       </c>
       <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>105.2613153800237</v>
+        <v>102.2757583376915</v>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
     </row>
@@ -2503,40 +2503,40 @@
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>0.6522905517158071</v>
+        <v>0.6470187781110718</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.5916722681277904</v>
+        <v>0.586173210716883</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.5397807353167764</v>
+        <v>0.5340840464310409</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.4948038176090149</v>
+        <v>0.4889237180942501</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.4553014664021219</v>
+        <v>0.4492521137640234</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.4203318386608639</v>
+        <v>0.4141235259565256</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3890517169050358</v>
+        <v>0.3827019947765132</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.3611164049330443</v>
+        <v>0.3546465340521764</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.336084761670369</v>
+        <v>0.3295241151493359</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.3137579271452634</v>
+        <v>0.3071447039852674</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2940139725025194</v>
+        <v>0.2874041760296047</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>0.2767758774722232</v>
+        <v>0.2702406194692441</v>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
     </row>
@@ -2553,40 +2553,40 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.8561884456079026</v>
+        <v>0.8518815630867524</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.8032724183811697</v>
+        <v>0.7980928600064215</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.7520929105030987</v>
+        <v>0.7461548093475975</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.7037061981954605</v>
+        <v>0.697097433111779</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.658283066591168</v>
+        <v>0.6510781569448195</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.615975986237888</v>
+        <v>0.6082361540873048</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5765450975889275</v>
+        <v>0.5683324138660786</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.5401796993964766</v>
+        <v>0.5315580405223252</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.5066636800736265</v>
+        <v>0.4977046335060994</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.4761052408825253</v>
+        <v>0.4668911352930197</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.4485988961632328</v>
+        <v>0.439236548039308</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.4242301738763019</v>
+        <v>0.4148482593599832</v>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
     </row>
@@ -2603,40 +2603,40 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.2725764489056055</v>
+        <v>0.2743520218633287</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.1191948679619388</v>
+        <v>0.1201125559303119</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.08347232382453508</v>
+        <v>0.08421335092644007</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.06821618591968899</v>
+        <v>0.06891030788799436</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.06024075607525418</v>
+        <v>0.06094200283320824</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.05574802600916222</v>
+        <v>0.05648887770844104</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.05319427144827908</v>
+        <v>0.05400111276892245</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.05195689254414564</v>
+        <v>0.05285615546139544</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.05170696141701898</v>
+        <v>0.05272852012561755</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.05226882371635489</v>
+        <v>0.05344840716338015</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.05356328194591679</v>
+        <v>0.05494609946622748</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>0.05558908454266487</v>
+        <v>0.05723387284064647</v>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
     </row>
@@ -2653,40 +2653,40 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.5117365620141191</v>
+        <v>0.496259530291237</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.822936967915015</v>
+        <v>0.8185445247137505</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.8797502017606259</v>
+        <v>0.8767216867967569</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.9029249164025733</v>
+        <v>0.9003793199997074</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.9148062839179557</v>
+        <v>0.9124550510696275</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.92143185495546</v>
+        <v>0.9191345262736552</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9251768071582691</v>
+        <v>0.9228450067431002</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.9269859195970298</v>
+        <v>0.9245476971002226</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.927350903505445</v>
+        <v>0.9247373120971561</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.9265301929702799</v>
+        <v>0.9236673388761331</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.9246366093865259</v>
+        <v>0.9214373268864954</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.9216653786542286</v>
+        <v>0.9180204543028089</v>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
     </row>
@@ -2703,40 +2703,40 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.796458289612795</v>
+        <v>0.7914114817012881</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.919417850854928</v>
+        <v>0.9175642260339907</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.9449485803391221</v>
+        <v>0.9436523966497012</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9555507493854893</v>
+        <v>0.9544615921341284</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9610101424640763</v>
+        <v>0.9600071988288605</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.9640374951618152</v>
+        <v>0.9630603322341956</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9657068813504274</v>
+        <v>0.9647162909970507</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.966439896320936</v>
+        <v>0.9654026903433606</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.9664473809156909</v>
+        <v>0.9653300977116198</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9658261258287665</v>
+        <v>0.9645907141301797</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9645975070963569</v>
+        <v>0.9631964275673923</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.962717331134489</v>
+        <v>0.961087937215221</v>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
     </row>
@@ -2753,40 +2753,40 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.2835032773053563</v>
+        <v>0.2803314260408126</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.34734799712873</v>
+        <v>0.3458492759403646</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.352435191420564</v>
+        <v>0.351047131535497</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.3488900827391387</v>
+        <v>0.3474108361019247</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.342616711352984</v>
+        <v>0.3409913965417674</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.335264087026765</v>
+        <v>0.333471026166709</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3275266501489218</v>
+        <v>0.325570138399774</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.3197587688339675</v>
+        <v>0.3176637807777642</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.312237435632604</v>
+        <v>0.3100444252741181</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.3052290747281818</v>
+        <v>0.3029957910776013</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2990037584407125</v>
+        <v>0.2968234119960466</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0.293858840869402</v>
+        <v>0.2918471447312225</v>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
     </row>
@@ -2803,40 +2803,40 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>1.144491830869796</v>
+        <v>1.148349100413499</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1.044928945171008</v>
+        <v>1.045925568107925</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1.019156857158087</v>
+        <v>1.019499110376512</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.003002581888218</v>
+        <v>1.002915226818822</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.9892740024897305</v>
+        <v>0.9887803620450216</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.9758932061902008</v>
+        <v>0.9749630666974607</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9618743582275009</v>
+        <v>0.9604281068418332</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.9465911904311125</v>
+        <v>0.9444996836152652</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.9294390008286465</v>
+        <v>0.9265219325482024</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.9097361835365582</v>
+        <v>0.9057489472864968</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.8866956174027838</v>
+        <v>0.8812882212871602</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.8593837811273382</v>
+        <v>0.8521100845146086</v>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
     </row>
@@ -2853,40 +2853,40 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>0.6622582740779489</v>
+        <v>0.6559785963090488</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.6305633163667279</v>
+        <v>0.6246063457694964</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.5816846769873533</v>
+        <v>0.5757065070246412</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.5355036259633932</v>
+        <v>0.5294507601125176</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.4933913256469327</v>
+        <v>0.4872531702268296</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.4551613945620491</v>
+        <v>0.4489353796842664</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4202279899523212</v>
+        <v>0.4139239072289042</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.3883403401840831</v>
+        <v>0.3819733439588067</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.3590732794875107</v>
+        <v>0.3526664394879173</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.3322260291847228</v>
+        <v>0.3258102099036672</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3076584768227875</v>
+        <v>0.3012816010392996</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.2852685760012213</v>
+        <v>0.278992643690011</v>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
     </row>
@@ -2903,40 +2903,40 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.270058941538246</v>
+        <v>0.2720258280079406</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.1142342616027879</v>
+        <v>0.1150773962795963</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.07907963397931937</v>
+        <v>0.07972938889514986</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.06419800582363021</v>
+        <v>0.06479319133468478</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.05647022154636605</v>
+        <v>0.0570642191435431</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.05216602093043148</v>
+        <v>0.05278992205645663</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.04978674613749996</v>
+        <v>0.05046595153123931</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.04874072379054745</v>
+        <v>0.04950148906418269</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.0487300390785172</v>
+        <v>0.04960352169899662</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.04961663669729349</v>
+        <v>0.05064232585954236</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.05136832875840946</v>
+        <v>0.05259907661212716</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.05404465568956616</v>
+        <v>0.05555276895854432</v>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
     </row>
@@ -2953,40 +2953,40 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.1142342616027879</v>
+        <v>0.1150773962795963</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.07907963397931937</v>
+        <v>0.07972938889514986</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.06419800582363021</v>
+        <v>0.06479319133468478</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.05647022154636605</v>
+        <v>0.0570642191435431</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.05216602093043148</v>
+        <v>0.05278992205645663</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.04978674613749996</v>
+        <v>0.05046595153123931</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.04874072379054745</v>
+        <v>0.04950148906418269</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.0487300390785172</v>
+        <v>0.04960352169899662</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.04961663669729349</v>
+        <v>0.05064232585954236</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.05136832875840946</v>
+        <v>0.05259907661212716</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.05404465568956616</v>
+        <v>0.05555276895854432</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0.05672098262072285</v>
+        <v>0.05850646130496148</v>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
     </row>
@@ -3003,40 +3003,40 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.5183547184948523</v>
+        <v>0.5026572059935642</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.8310585833389782</v>
+        <v>0.8269511580466603</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.8864849908316806</v>
+        <v>0.8837192378835317</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.9089303984917328</v>
+        <v>0.9066387713518712</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.9203700276723751</v>
+        <v>0.9182742747166943</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.9266804110132759</v>
+        <v>0.9246460982700778</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9301502896710493</v>
+        <v>0.9280921528761098</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.9316716945371063</v>
+        <v>0.9295185361489017</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.9316872222788061</v>
+        <v>0.929367739431411</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.9303978776130181</v>
+        <v>0.9278310684452963</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.9278451925795664</v>
+        <v>0.9249295736201615</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0.9239314473127467</v>
+        <v>0.9205324796666424</v>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
     </row>
@@ -3053,40 +3053,40 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.7835500320044898</v>
+        <v>0.7805596092214843</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.851520835490436</v>
+        <v>0.8500880382586702</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8712869854264544</v>
+        <v>0.8700959893287561</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8840722676217267</v>
+        <v>0.8829499081275562</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.8947433731600778</v>
+        <v>0.893631259906112</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9046298958478582</v>
+        <v>0.9034997827061337</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9142437520749935</v>
+        <v>0.9130779445472598</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.9237714493206519</v>
+        <v>0.9225551907029824</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.9332950801886167</v>
+        <v>0.9320133967247826</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.9428407668078189</v>
+        <v>0.9414763041919105</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9523980367192889</v>
+        <v>0.9509286079025953</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0.9619247750070381</v>
+        <v>0.9603205495816369</v>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
     </row>
@@ -3103,40 +3103,40 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.4941891122024217</v>
+        <v>0.4951608024475138</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.4794395527867925</v>
+        <v>0.4796111464536851</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.4931453076634404</v>
+        <v>0.4933697911469953</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.5108012363827721</v>
+        <v>0.511158425729244</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.52982516230889</v>
+        <v>0.5303221251053101</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.5495029770131883</v>
+        <v>0.5501351231747619</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5695109756896494</v>
+        <v>0.5702552370692163</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.5896378114298403</v>
+        <v>0.5904530661631379</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.6096830608846393</v>
+        <v>0.6105143851335061</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.6294289763436328</v>
+        <v>0.630205686088978</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6486443337625243</v>
+        <v>0.6492618491206571</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0.6670694869952146</v>
+        <v>0.6674038058680815</v>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
     </row>
@@ -3153,40 +3153,40 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.9127208168054688</v>
+        <v>0.9130337357818</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.8753224259487161</v>
+        <v>0.8748613108903142</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.8379336182331615</v>
+        <v>0.8367019754879613</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.8004565383967955</v>
+        <v>0.7984417849023867</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.7628545769696604</v>
+        <v>0.760052506592651</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.725152515069329</v>
+        <v>0.7215557875774173</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6874114880709427</v>
+        <v>0.6830253822830016</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.649738002012511</v>
+        <v>0.6445808950740264</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.6122558340319789</v>
+        <v>0.6063535228830391</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5750983286599214</v>
+        <v>0.5684827367765299</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5383883627215444</v>
+        <v>0.5311064742865111</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.5022395472596254</v>
+        <v>0.4943374292495647</v>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
     </row>
@@ -3203,40 +3203,40 @@
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.6371211818181819</v>
+        <v>0.6368181818181818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.6113635454545454</v>
+        <v>0.6104545454545455</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.5856059090909091</v>
+        <v>0.5840909090909091</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.5598482727272727</v>
+        <v>0.5577272727272727</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.5340906363636364</v>
+        <v>0.5313636363636364</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.5083329999999999</v>
+        <v>0.505</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4825753636363636</v>
+        <v>0.4786363636363636</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.4568177272727272</v>
+        <v>0.4522727272727273</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.4310600909090909</v>
+        <v>0.4259090909090909</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.4053024545454545</v>
+        <v>0.3995454545454545</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3795448181818182</v>
+        <v>0.3731818181818182</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>0.3537871818181818</v>
+        <v>0.3468181818181818</v>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
     </row>
@@ -3253,40 +3253,40 @@
       </c>
       <c r="C66" s="1" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>1.144480572081726</v>
+        <v>1.149470499626858</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1.024070802073349</v>
+        <v>1.025328281506466</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.9974306823545782</v>
+        <v>0.9979591178031184</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.9827456836395317</v>
+        <v>0.9828268660091499</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.9713996514092181</v>
+        <v>0.9710736479752523</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.9610033265773484</v>
+        <v>0.9602502514475583</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9504973245841769</v>
+        <v>0.9492481850610934</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.9392814156996514</v>
+        <v>0.9374216670208639</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.9268248029940885</v>
+        <v>0.924196142381593</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.9125624929681139</v>
+        <v>0.9089535843846798</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.8958660843865471</v>
+        <v>0.8909761330468265</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>0.8760036110637557</v>
+        <v>0.8694555233106508</v>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
     </row>
@@ -3303,40 +3303,40 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>0.9110743488838259</v>
+        <v>0.9098923318704959</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.9057556896616156</v>
+        <v>0.9048592082754372</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.8708999706835606</v>
+        <v>0.8693990341364447</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.8311767015007679</v>
+        <v>0.8289382873161977</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.7894073633793292</v>
+        <v>0.7863791607528087</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.7464987402784139</v>
+        <v>0.7426475977563408</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7029538330969465</v>
+        <v>0.6982710232411901</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.6591494440308061</v>
+        <v>0.6536474291487642</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.6154240099789121</v>
+        <v>0.6091291160368223</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.5720897895915963</v>
+        <v>0.5650394600392833</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5294180059149334</v>
+        <v>0.5216678776691375</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.4876398341968385</v>
+        <v>0.4792458653577785</v>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
     </row>
@@ -3353,40 +3353,40 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.2317597552762571</v>
+        <v>0.2364367638450576</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.1487483761246328</v>
+        <v>0.1504669706161518</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.1594970641214167</v>
+        <v>0.1612571423151571</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.1822891452427362</v>
+        <v>0.1843850811067632</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.2085450744395577</v>
+        <v>0.2110211413826013</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.2358508115080195</v>
+        <v>0.2386944638701409</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2630858365132343</v>
+        <v>0.2662228027780918</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.2895434136871404</v>
+        <v>0.2928407719468376</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.3145689689621096</v>
+        <v>0.3178426194985539</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.3374641643081925</v>
+        <v>0.3404708476081498</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3574777216650027</v>
+        <v>0.3598696587603154</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.3737640638041303</v>
+        <v>0.3751180940610861</v>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
     </row>
@@ -3403,40 +3403,40 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2334174819859701</v>
+        <v>0.238456768543003</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.139173255509392</v>
+        <v>0.1410663598324875</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1482568864745263</v>
+        <v>0.1501000762400676</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1718258803874496</v>
+        <v>0.1739769395026247</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1998666391104014</v>
+        <v>0.202401201292213</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2293944659117869</v>
+        <v>0.2323154689411199</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2589205251305544</v>
+        <v>0.2621570836006432</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.2874417464003064</v>
+        <v>0.290852254466501</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.3140149908497344</v>
+        <v>0.3173928165113801</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.3376463939449619</v>
+        <v>0.3407094872472135</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3572776114878504</v>
+        <v>0.3596203436180228</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3717439469304997</v>
+        <v>0.37286421915683</v>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
     </row>
@@ -3453,40 +3453,40 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>253.673029334167</v>
+        <v>251.7894146864385</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>251.0524551056513</v>
+        <v>249.1024900209453</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>248.6234593867609</v>
+        <v>246.6107242604538</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>246.4061801101378</v>
+        <v>244.3372984316917</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>244.4127578697729</v>
+        <v>242.2923887858165</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>242.6433534506775</v>
+        <v>240.4769672604629</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>241.0885247514319</v>
+        <v>238.8781441276591</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>239.7226419962918</v>
+        <v>237.4656501333595</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>238.5073800674136</v>
+        <v>236.1969574055916</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>237.3902297051156</v>
+        <v>235.0144241906794</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>236.3078107281634</v>
+        <v>233.8442343661209</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>235.182478936269</v>
+        <v>232.6016263665796</v>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
     </row>
@@ -3503,40 +3503,40 @@
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>196.7221130608353</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>188.7690002190255</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>180.8158873772159</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>172.8627745354061</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>164.9096616935965</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>156.9565488517867</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>149.0034360099771</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>141.0503231681674</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>133.0972103263576</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>125.144097484548</v>
+        <v>122.480097518843</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>117.1909846427383</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>109.2378718009286</v>
+        <v>106.3166261739218</v>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
     </row>
@@ -3553,40 +3553,40 @@
       </c>
       <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>248.9640712888368</v>
+        <v>247.28452908</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>239.8919674315049</v>
+        <v>237.9815544364363</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>236.3887712508276</v>
+        <v>234.3795941484085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>234.0015262669965</v>
+        <v>231.9142224061601</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>232.28806020156</v>
+        <v>230.133866067011</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>231.133627173989</v>
+        <v>228.9229812149858</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>230.486323255149</v>
+        <v>228.2261602651597</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>230.307036219323</v>
+        <v>227.999923292236</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>230.5492913204617</v>
+        <v>228.1937458904654</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>231.1532097532483</v>
+        <v>228.7427276681898</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>232.0470620862769</v>
+        <v>229.5649111126124</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>233.1441836147533</v>
+        <v>230.5666674764105</v>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
     </row>
@@ -3603,40 +3603,40 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>0.9186540511911265</v>
+        <v>0.9198717705829682</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.9332324020183315</v>
+        <v>0.9343717516022703</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0.9446065070592682</v>
+        <v>0.9456738513371452</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.9534757930317376</v>
+        <v>0.9544810706406721</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.9607228514711692</v>
+        <v>0.9616684573121036</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.9666133453688397</v>
+        <v>0.9675039353435879</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9714991543237266</v>
+        <v>0.9723363601852713</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.9755303734032933</v>
+        <v>0.9763162299517529</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0.9789002501146955</v>
+        <v>0.9796348119488701</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.9816476219524559</v>
+        <v>0.9823328970460875</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.983910477052632</v>
+        <v>0.9845454709023621</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>0.9857586792737885</v>
+        <v>0.9863414798135992</v>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
     </row>
@@ -3653,40 +3653,40 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>264.5723667430444</v>
+        <v>264.9230699278949</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>302.5699842784154</v>
+        <v>302.9393809956259</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>340.4686552077119</v>
+        <v>340.8533627745312</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>378.1976619232148</v>
+        <v>378.5964068562916</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>415.8668982157129</v>
+        <v>416.2762214324989</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>453.4247253038037</v>
+        <v>453.842488535186</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>490.9015561921937</v>
+        <v>491.324598928213</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>528.2695098206829</v>
+        <v>528.6950671020987</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>565.5473799961093</v>
+        <v>565.9717639113386</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>602.6871552993164</v>
+        <v>603.1078831527154</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>639.7109156084705</v>
+        <v>640.1237707477241</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>676.6139712116426</v>
+        <v>677.0139991251236</v>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
     </row>
@@ -3703,40 +3703,40 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>297.8416439870647</v>
+        <v>298.0389802067385</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>318.4071657272538</v>
+        <v>318.6014723186276</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>337.6153780608649</v>
+        <v>337.8060659838801</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>355.7589590562439</v>
+        <v>355.9464532230144</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>372.8994757736503</v>
+        <v>373.082946582965</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>389.2161757057316</v>
+        <v>389.395436741228</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>404.7592266164098</v>
+        <v>404.9335931204457</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>419.6470562163746</v>
+        <v>419.8160494160329</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>433.8962292448272</v>
+        <v>434.0589954920686</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>447.6652095460076</v>
+        <v>447.8214368375179</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>460.9404875813311</v>
+        <v>461.0892039392522</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>473.7513405775682</v>
+        <v>473.8913655885228</v>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
     </row>
@@ -3753,40 +3753,40 @@
       </c>
       <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>0.8517043685979119</v>
+        <v>0.8448204141343578</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.7884635841415134</v>
+        <v>0.7818623316712811</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.7364103519654823</v>
+        <v>0.7300363998561882</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.6926211521525788</v>
+        <v>0.6864439755454026</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.6554387274551475</v>
+        <v>0.6494330309250312</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0.6234153886608478</v>
+        <v>0.6175649341783925</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.59563441398684</v>
+        <v>0.5899193057480068</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.5712482393125335</v>
+        <v>0.5656421436571468</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0.5496876072938516</v>
+        <v>0.5441586509175513</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>0.5302851877765106</v>
+        <v>0.5247949402563977</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5126644699148236</v>
+        <v>0.5071561692798375</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>0.4964259914273786</v>
+        <v>0.4908332230905137</v>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
     </row>
@@ -3803,40 +3803,40 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.7788605140976763</v>
+        <v>0.7739140879000126</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7079792169843426</v>
+        <v>0.7025688677305478</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.6622243432024892</v>
+        <v>0.6567734946088818</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.625547901202427</v>
+        <v>0.6201103319267046</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.5950941533435727</v>
+        <v>0.5896922001548817</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.5695483679396847</v>
+        <v>0.5641990975072881</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5478174635037193</v>
+        <v>0.5425314394305585</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.5294382587681008</v>
+        <v>0.5242135535589888</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.5137334770940361</v>
+        <v>0.5085612696312135</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5002791332870248</v>
+        <v>0.4951412220693632</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4886951026809453</v>
+        <v>0.4835545192846229</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.4785840029309119</v>
+        <v>0.4733931316860104</v>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
     </row>
@@ -3853,40 +3853,40 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>304.9398326258377</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>342.9439057334514</v>
+        <v>342.7216074711233</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>380.7593283647126</v>
+        <v>380.5533143746371</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>418.4918889458808</v>
+        <v>418.299782629001</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>456.0430525571176</v>
+        <v>455.8623617326095</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>493.4758911855769</v>
+        <v>493.3043052802819</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>531.0137392486331</v>
+        <v>530.8455851254013</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>568.4352646870975</v>
+        <v>568.2640128064211</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>605.671440818043</v>
+        <v>605.4888593452233</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>642.7900221215097</v>
+        <v>642.5848324826002</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>679.6983757108426</v>
+        <v>679.4541857759853</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>716.3437136915536</v>
+        <v>716.0408161885885</v>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
     </row>
@@ -3903,40 +3903,40 @@
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>0.8993745518291292</v>
+        <v>0.9006486075029659</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.9173573147344318</v>
+        <v>0.9186155927206895</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.9278992710844721</v>
+        <v>0.9290813257877711</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.9360459025983171</v>
+        <v>0.9371529110515402</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.9424557262326057</v>
+        <v>0.9434956981360756</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0.9477044727256937</v>
+        <v>0.9486821920661557</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9520089627972769</v>
+        <v>0.9529306488556853</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.9556315242080048</v>
+        <v>0.9565028945546096</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0.9585680081018132</v>
+        <v>0.959398073182831</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0.9610487925453612</v>
+        <v>0.9618447489108495</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.9631785168028687</v>
+        <v>0.9639490928348131</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>0.9650201394990218</v>
+        <v>0.9657748293183122</v>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
     </row>
@@ -3953,40 +3953,40 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>617.3208513549218</v>
+        <v>618.1953492286352</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>629.6640230444452</v>
+        <v>630.527691286045</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>636.8999065322735</v>
+        <v>637.711255946491</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>642.4916652623527</v>
+        <v>643.2515037516795</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>646.8912980681803</v>
+        <v>647.6051234032751</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>650.4939802288768</v>
+        <v>651.1650760858951</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>653.4485351139737</v>
+        <v>654.0811703393106</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>655.9350216279715</v>
+        <v>656.5331206992845</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>657.9505920414651</v>
+        <v>658.5203396304444</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>659.6533753385959</v>
+        <v>660.1997110784556</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>661.1151947653541</v>
+        <v>661.6441097219828</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>662.3792644328264</v>
+        <v>662.8972752669174</v>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
     </row>
@@ -4003,40 +4003,40 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>454.8802316354819</v>
+        <v>455.2023097056071</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>459.2311063860777</v>
+        <v>459.5459468369926</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>461.7167694612662</v>
+        <v>462.0107673069759</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>463.5956285515898</v>
+        <v>463.8696816901759</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>464.9884454582512</v>
+        <v>465.2449251931451</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>466.0587672688607</v>
+        <v>466.2991149814897</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>466.8569228138085</v>
+        <v>467.0828615584704</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>467.4492898292888</v>
+        <v>467.662357643633</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>467.8710213489689</v>
+        <v>468.0735522884636</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>468.2073318775922</v>
+        <v>468.4011802428435</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>468.4413278818004</v>
+        <v>468.6286750273001</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>468.5935986159338</v>
+        <v>468.7767936030652</v>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
     </row>
@@ -4053,40 +4053,40 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>0.5473178519842647</v>
+        <v>0.5432409366286526</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.522377435011614</v>
+        <v>0.5178623727930555</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.5119778766680868</v>
+        <v>0.5073033157096933</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.5047535219391233</v>
+        <v>0.4999555512253943</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.499556628708564</v>
+        <v>0.4946509969377347</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0.4959323660585754</v>
+        <v>0.4909359118643687</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4936979875246947</v>
+        <v>0.4886202835695136</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.4926888140175172</v>
+        <v>0.4875310564678288</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0.4927624939363426</v>
+        <v>0.4875168545088711</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.4936983981568251</v>
+        <v>0.4883478891953212</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4953599272198038</v>
+        <v>0.4898652672059366</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>0.4975402658153717</v>
+        <v>0.4918474434373172</v>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
     </row>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -667,15 +667,17 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>a_кр_1_i_СА</t>
+          <t>delta_c_abs_ВНА</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>СА: Критическая скорость на входе</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr"/>
+          <t>Изменение скорости абсолютной в ВНА</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>9.714170190180937</v>
+      </c>
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr"/>
@@ -688,19 +690,17 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr"/>
-      <c r="P7" s="2" t="n">
-        <v>477.1612274741949</v>
-      </c>
+      <c r="P7" s="1" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>r_ср1_отн_i_СА</t>
+          <t>a_кр_1_i_СА</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>СА: Относительный средний радиус на входе</t>
+          <t>СА: Критическая скорость на входе</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr"/>
@@ -717,18 +717,18 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>0.9595531619480527</v>
+        <v>477.1612274741949</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>c_a2_i_СА</t>
+          <t>r_ср1_отн_i_СА</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>СА: Осевая скорость на входе</t>
+          <t>СА: Относительный средний радиус на входе</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr"/>
@@ -745,18 +745,18 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>106.3166261739218</v>
+        <v>0.9595531619480527</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>q_1_i_СА</t>
+          <t>c_a2_i_СА</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>СА: ГДФ расхода на входе</t>
+          <t>СА: Осевая скорость на входе</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr"/>
@@ -773,18 +773,18 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>106.3166261739218</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>F_1_i_СА</t>
+          <t>q_1_i_СА</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>СА: Кольцевая площадь на входе</t>
+          <t>СА: ГДФ расхода на входе</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr"/>
@@ -801,18 +801,18 @@
       <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>0.05555276895854432</v>
+        <v>0.4537118711400231</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>α_3_i_СА</t>
+          <t>F_1_i_СА</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>СА: Угол абсолютной скорости на выходе</t>
+          <t>СА: Кольцевая площадь на входе</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr"/>
@@ -829,18 +829,18 @@
       <c r="N12" s="1" t="inlineStr"/>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>1.570796326794897</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+        <v>0.05555276895854432</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>F_3_i_СА</t>
+          <t>α_3_i_СА</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>СА: Действительная кольцевая площадь на выходе</t>
+          <t>СА: Угол абсолютной скорости на выходе</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr"/>
@@ -857,18 +857,18 @@
       <c r="N13" s="1" t="inlineStr"/>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>0.05555276895854432</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+        <v>1.570796326794897</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>D_вт3_i_СА</t>
+          <t>F_3_i_СА</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>СА: Втулочный диаметр на выходе</t>
+          <t>СА: Действительная кольцевая площадь на выходе</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr"/>
@@ -885,18 +885,18 @@
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="2" t="n">
-        <v>0.3421954010820806</v>
+        <v>0.05555276895854432</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i_СА</t>
+          <t>D_вт3_i_СА</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>СА: Относительный диаметр втулки на выходе</t>
+          <t>СА: Втулочный диаметр на выходе</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr"/>
@@ -913,18 +913,18 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>0.5026572059935642</v>
+        <v>0.3421954010820806</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>r_ср3_отн_i_СА</t>
+          <t>d3_отн_i_СА</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>СА: Относительный средний радиус на выходе</t>
+          <t>СА: Относительный диаметр втулки на выходе</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr"/>
@@ -941,18 +941,18 @@
       <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="inlineStr"/>
       <c r="P16" s="2" t="n">
-        <v>0.7914114817012881</v>
+        <v>0.5026572059935642</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>α_2_i_СА</t>
+          <t>r_ср3_отн_i_СА</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>СА: Угол абсолютной скорости на входе</t>
+          <t>СА: Относительный средний радиус на выходе</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr"/>
@@ -969,18 +969,18 @@
       <c r="N17" s="1" t="inlineStr"/>
       <c r="O17" s="1" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>0.8521100845146086</v>
+        <v>0.7914114817012881</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>ε_на_i_СА</t>
+          <t>α_2_i_СА</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>СА: Диффузность решетки</t>
+          <t>СА: Угол абсолютной скорости на входе</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr"/>
@@ -997,18 +997,18 @@
       <c r="N18" s="1" t="inlineStr"/>
       <c r="O18" s="1" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>0.718686242280288</v>
+        <v>0.8521100845146086</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>c_2_i_СА</t>
+          <t>ε_на_i_СА</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>СА: Абсолютная скорость на входе</t>
+          <t>СА: Диффузность решетки</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr"/>
@@ -1025,18 +1025,18 @@
       <c r="N19" s="1" t="inlineStr"/>
       <c r="O19" s="1" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>141.2523884686373</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+        <v>0.718686242280288</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>d2_отн_i_СА</t>
+          <t>c_2_i_СА</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>СА: Относительный диаметр втулки на выходе РК</t>
+          <t>СА: Абсолютная скорость на входе</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr"/>
@@ -1053,18 +1053,18 @@
       <c r="N20" s="1" t="inlineStr"/>
       <c r="O20" s="1" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>0.9189293312859016</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+        <v>141.2523884686373</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>D_вт2_i_СА</t>
+          <t>d2_отн_i_СА</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>СА: Втулочный диаметр на выходе РК</t>
+          <t>СА: Относительный диаметр втулки на выходе РК</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr"/>
@@ -1081,18 +1081,18 @@
       <c r="N21" s="1" t="inlineStr"/>
       <c r="O21" s="1" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>0.6255821807307252</v>
+        <v>0.9189293312859016</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>h_на_i_СА</t>
+          <t>D_вт2_i_СА</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>СА: Высота лопаток на входе</t>
+          <t>СА: Втулочный диаметр на выходе РК</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr"/>
@@ -1109,18 +1109,18 @@
       <c r="N22" s="1" t="inlineStr"/>
       <c r="O22" s="1" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>0.02759535690110904</v>
+        <v>0.6255821807307252</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>h_на_3_i_СА</t>
+          <t>h_на_i_СА</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>СА: Высота лопаток на выходе</t>
+          <t>СА: Высота лопаток на входе</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr"/>
@@ -1137,618 +1137,596 @@
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr"/>
       <c r="P23" s="2" t="n">
+        <v>0.02759535690110904</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>h_на_3_i_СА</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>СА: Высота лопаток на выходе</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr"/>
+      <c r="H24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr"/>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
+      <c r="L24" s="1" t="inlineStr"/>
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr"/>
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
         <v>0.1692887467254313</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>k_i</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Показатель адиабаты по длине компрессора перед РК</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>1.399944336209296</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1.397730417935234</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1.394860425858321</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1.393519592252976</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1.390731081206798</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1.388035570101426</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1.384399004818129</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>1.38071062867211</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>1.37610539882691</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1.372438981258499</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1.368632710893606</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>1.364566577433034</v>
-      </c>
-      <c r="P24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>c_a_i_отн</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>0.65</v>
+        <v>1.399944336209296</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.6236363636363637</v>
+        <v>1.397730417935234</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.5972727272727273</v>
+        <v>1.394860425858321</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.5709090909090909</v>
+        <v>1.393519592252976</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.5445454545454546</v>
+        <v>1.390731081206798</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.5181818181818182</v>
+        <v>1.388035570101426</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4918181818181818</v>
+        <v>1.384399004818129</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.4654545454545455</v>
+        <v>1.38071062867211</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.4390909090909091</v>
+        <v>1.37610539882691</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.4127272727272727</v>
+        <v>1.372438981258499</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3863636363636364</v>
+        <v>1.368632710893606</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.36</v>
+        <v>1.364566577433034</v>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>c_a_i_отн_plus_1</t>
+          <t>c_a_i_отн</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Коэффициент расхода на входе в ступень</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr"/>
       <c r="D26" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>0.6236363636363637</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>0.5972727272727273</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.5709090909090909</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.5445454545454546</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>0.5181818181818182</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>0.4918181818181818</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="K26" s="2" t="n">
         <v>0.4654545454545455</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>0.4390909090909091</v>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="M26" s="2" t="n">
         <v>0.4127272727272727</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>0.3863636363636364</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="O26" s="2" t="n">
         <v>0.36</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>0.3336363636363636</v>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i</t>
+          <t>c_a_i_отн_plus_1</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед ступенью</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>100292.8790575521</v>
+        <v>0.6236363636363637</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>259542.8799520527</v>
+        <v>0.5972727272727273</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>418792.8808465532</v>
+        <v>0.5709090909090909</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>578042.8817410537</v>
+        <v>0.5445454545454546</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>737292.8826355543</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>896542.8835300547</v>
+        <v>0.4918181818181818</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1055792.884424555</v>
+        <v>0.4654545454545455</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1215042.885319056</v>
+        <v>0.4390909090909091</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1374292.886213556</v>
+        <v>0.4127272727272727</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1533542.887108057</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1692792.888002557</v>
+        <v>0.36</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>1852042.888897058</v>
+        <v>0.3336363636363636</v>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i</t>
+          <t>P1_полн_i</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Полная температура перед ступенью</t>
+          <t>Полное давление перед ступенью</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>288</v>
+        <v>100292.8790575521</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>324.2171870844151</v>
+        <v>259542.8799520527</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>360.4343741688301</v>
+        <v>418792.8808465532</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>396.6515612532452</v>
+        <v>578042.8817410537</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>432.8687483376602</v>
+        <v>737292.8826355543</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>469.0859354220753</v>
+        <v>896542.8835300547</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>505.3031225064903</v>
+        <v>1055792.884424555</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>541.5203095909053</v>
+        <v>1215042.885319056</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>577.7374966753205</v>
+        <v>1374292.886213556</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>613.9546837597354</v>
+        <v>1533542.887108057</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>650.1718708441506</v>
+        <v>1692792.888002557</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>686.3890579285655</v>
+        <v>1852042.888897058</v>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>d1_отн_i</t>
+          <t>T1_полн_i</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на входе в ступень</t>
+          <t>Полная температура перед ступенью</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>0.43</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.4743022422822237</v>
+        <v>324.2171870844151</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.5186044845644475</v>
+        <v>360.4343741688301</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.5629067268466712</v>
+        <v>396.6515612532452</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.6072089691288949</v>
+        <v>432.8687483376602</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.6515112114111187</v>
+        <v>469.0859354220753</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6958134536933425</v>
+        <v>505.3031225064903</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.7401156959755661</v>
+        <v>541.5203095909053</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.7844179382577898</v>
+        <v>577.7374966753205</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.8287201805400136</v>
+        <v>613.9546837597354</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.8730224228222374</v>
+        <v>650.1718708441506</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.9173246651044611</v>
+        <v>686.3890579285655</v>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>U_k_i</t>
+          <t>d1_отн_i</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Окружная скорость концов рабочих лопаток ступени</t>
+          <t>Относительный диаметр втулки на входе в ступень</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.4743022422822237</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.5186044845644475</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.5629067268466712</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.6072089691288949</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.6515112114111187</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.6958134536933425</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.7401156959755661</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.7844179382577898</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.8287201805400136</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.8730224228222374</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>306.5485944726447</v>
+        <v>0.9173246651044611</v>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Hт_i</t>
+          <t>U_k_i</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Теоретический напор i-й ступени</t>
+          <t>Окружная скорость концов рабочих лопаток ступени</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>16967.12604306373</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>19070.88223528092</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>21057.52246874931</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>22950.09410526995</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>24759.14168894694</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26487.00632294096</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28125.52905279903</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>29654.33031092169</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>31044.54895603916</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>32256.73667984891</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>33239.72047130691</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>33933.38931404932</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>L_z_i</t>
+          <t>Hт_i</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Действительная работа сжатия i-й ступени</t>
+          <t>Теоретический напор i-й ступени</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16797.45478263309</v>
+        <v>16967.12604306373</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18689.4645905753</v>
+        <v>19070.88223528092</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20425.79679468683</v>
+        <v>21057.52246874931</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>22032.09034105915</v>
+        <v>22950.09410526995</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23521.18460449959</v>
+        <v>24759.14168894694</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24897.7859435645</v>
+        <v>26487.00632294096</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26437.99730963109</v>
+        <v>28125.52905279903</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>27875.07049226639</v>
+        <v>29654.33031092169</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>29181.87601867681</v>
+        <v>31044.54895603916</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>30321.33247905798</v>
+        <v>32256.73667984891</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>31245.33724302849</v>
+        <v>33239.72047130691</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31897.38595520635</v>
+        <v>33933.38931404932</v>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>H_ад_i</t>
+          <t>L_z_i</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Адиабатическая работа сжатия i-й ступени</t>
+          <t>Действительная работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>13701.87693398603</v>
+        <v>16797.45478263309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15617.01385068403</v>
+        <v>18689.4645905753</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>17413.88007155858</v>
+        <v>20425.79679468683</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19087.25918979651</v>
+        <v>22032.09034105915</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>20623.27203085376</v>
+        <v>23521.18460449959</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22003.16976086839</v>
+        <v>24897.7859435645</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23450.49881419504</v>
+        <v>26437.99730963109</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>24708.63115599736</v>
+        <v>27875.07049226639</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>25732.59482627098</v>
+        <v>29181.87601867681</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>26471.29676564151</v>
+        <v>30321.33247905798</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>26869.11978064452</v>
+        <v>31245.33724302849</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>26870.38869889748</v>
+        <v>31897.38595520635</v>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>ΔT_полн_i</t>
+          <t>H_ад_i</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Повышение полной температуры в ступени</t>
+          <t>Адиабатическая работа сжатия i-й ступени</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>16.6972711556989</v>
+        <v>13701.87693398603</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>18.50442038670822</v>
+        <v>15617.01385068403</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>20.11894020580701</v>
+        <v>17413.88007155858</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.64822137575578</v>
+        <v>19087.25918979651</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>22.99361339494931</v>
+        <v>20623.27203085376</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.21836985820667</v>
+        <v>22003.16976086839</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25.542462618911</v>
+        <v>23450.49881419504</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>26.74370321551575</v>
+        <v>24708.63115599736</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>27.75136266990286</v>
+        <v>25732.59482627098</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28.63014872286476</v>
+        <v>26471.29676564151</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>29.28231493183464</v>
+        <v>26869.11978064452</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>29.65175826002295</v>
+        <v>26870.38869889748</v>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>T3_полн_i</t>
+          <t>ΔT_полн_i</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из ступени</t>
+          <t>Повышение полной температуры в ступени</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>16.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>342.7216074711233</v>
+        <v>18.50442038670822</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>380.5533143746371</v>
+        <v>20.11894020580701</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>418.299782629001</v>
+        <v>21.64822137575578</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>455.8623617326095</v>
+        <v>22.99361339494931</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>493.3043052802819</v>
+        <v>24.21836985820667</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>530.8455851254013</v>
+        <v>25.542462618911</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>568.2640128064211</v>
+        <v>26.74370321551575</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>605.4888593452233</v>
+        <v>27.75136266990286</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>642.5848324826002</v>
+        <v>28.63014872286476</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>679.4541857759853</v>
+        <v>29.28231493183464</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>716.0408161885885</v>
+        <v>29.65175826002295</v>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>T1_полн_i_plus_1</t>
+          <t>T3_полн_i</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на входе в следующую ступень</t>
+          <t>Полная температура на выходе из ступени</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr"/>
@@ -1790,115 +1768,115 @@
       </c>
       <c r="P36" s="1" t="inlineStr"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>π_полн_i</t>
+          <t>T1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Степень повышения полного давления в ступени</t>
+          <t>Полная температура на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>1.175559285399187</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1.177892225128341</v>
+        <v>342.7216074711233</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1.178483449737299</v>
+        <v>380.5533143746371</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.177740365938578</v>
+        <v>418.299782629001</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.175894000936239</v>
+        <v>455.8623617326095</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.173036766366976</v>
+        <v>493.3043052802819</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.171122407075676</v>
+        <v>530.8455851254013</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.168108071555353</v>
+        <v>568.2640128064211</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1.163909173397865</v>
+        <v>605.4888593452233</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.158409204291314</v>
+        <v>642.5848324826002</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.151515127689758</v>
+        <v>679.4541857759853</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>1.143155604508661</v>
+        <v>716.0408161885885</v>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>P3_полн_i</t>
+          <t>π_полн_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Полное давление на выходе из ступени</t>
+          <t>Степень повышения полного давления в ступени</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>117900.225235523</v>
+        <v>1.175559285399187</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>305713.5403829411</v>
+        <v>1.177892225128341</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>493540.4789454677</v>
+        <v>1.178483449737299</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>680784.4350698986</v>
+        <v>1.177740365938578</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>866978.2776241348</v>
+        <v>1.175894000936239</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1051677.76500542</v>
+        <v>1.173036766366976</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1236462.704180656</v>
+        <v>1.171122407075676</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1419301.401627094</v>
+        <v>1.168108071555353</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1599552.097199386</v>
+        <v>1.163909173397865</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1776470.195601449</v>
+        <v>1.158409204291314</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1949276.618580578</v>
+        <v>1.151515127689758</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>2117173.208233083</v>
+        <v>1.143155604508661</v>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>P1_полн_i_plus_1</t>
+          <t>P3_полн_i</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Полное давление перед следующей ступенью</t>
+          <t>Полное давление на выходе из ступени</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr"/>
@@ -1940,2155 +1918,2205 @@
       </c>
       <c r="P39" s="1" t="inlineStr"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>a_кр_1_i</t>
+          <t>P1_полн_i_plus_1</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на входе в ступень</t>
+          <t>Полное давление перед следующей ступенью</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>310.7487734256569</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>329.6005504723648</v>
+        <v>305713.5403829411</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>347.3735553312965</v>
+        <v>493540.4789454677</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>364.3350972913221</v>
+        <v>680784.4350698986</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>380.445728537063</v>
+        <v>866978.2776241348</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>395.8808441843627</v>
+        <v>1051677.76500542</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>410.6535144715717</v>
+        <v>1236462.704180656</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>424.8775489240568</v>
+        <v>1419301.401627094</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>438.5475167594254</v>
+        <v>1599552.097199386</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>451.8304907351089</v>
+        <v>1776470.195601449</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>464.6939992401076</v>
+        <v>1949276.618580578</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>477.1612274741949</v>
+        <v>2117173.208233083</v>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>a_кр_3_i</t>
+          <t>a_кр_1_i</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Критическая скорость потока на выходе из ступени</t>
+          <t>Критическая скорость потока на входе в ступень</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>319.5245220964998</v>
+        <v>310.7487734256569</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>338.7305720009615</v>
+        <v>329.6005504723648</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>356.8651842260853</v>
+        <v>347.3735553312965</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>373.9886443846121</v>
+        <v>364.3350972913221</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>390.2609971889856</v>
+        <v>380.445728537063</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>405.7485774550155</v>
+        <v>395.8808441843627</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>420.6690040022493</v>
+        <v>410.6535144715717</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>434.9371010045424</v>
+        <v>424.8775489240568</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>448.7045308344883</v>
+        <v>438.5475167594254</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>461.97472048923</v>
+        <v>451.8304907351089</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>474.7446295243685</v>
+        <v>464.6939992401076</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>487.0511463806778</v>
+        <v>477.1612274741949</v>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>r_ср1_отн_i</t>
+          <t>a_кр_3_i</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на входе в ступень</t>
+          <t>Критическая скорость потока на выходе из ступени</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>0.7697077367416805</v>
+        <v>319.5245220964998</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.7826118504833496</v>
+        <v>338.7305720009615</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.7965395820078109</v>
+        <v>356.8651842260853</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.8114382241209841</v>
+        <v>373.9886443846121</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.8272553209833634</v>
+        <v>390.2609971889856</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.8439392331780717</v>
+        <v>405.7485774550155</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8614395980974688</v>
+        <v>420.6690040022493</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.8797076910626043</v>
+        <v>434.9371010045424</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.8986966957379452</v>
+        <v>448.7045308344883</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.9183618942536413</v>
+        <v>461.97472048923</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.9386607882377982</v>
+        <v>474.7446295243685</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.9595531619480527</v>
+        <v>487.0511463806778</v>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>c_u1_отн_i</t>
+          <t>r_ср1_отн_i</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на входе</t>
+          <t>Относительный средний радиус на входе в ступень</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>0.2675658145409672</v>
+        <v>0.7697077367416805</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.2616490023434986</v>
+        <v>0.7826118504833496</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.2576095825081036</v>
+        <v>0.7965395820078109</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.2552316373223689</v>
+        <v>0.8114382241209841</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.2543820897171053</v>
+        <v>0.8272553209833634</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.2549786247517394</v>
+        <v>0.8439392331780717</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2570008412996226</v>
+        <v>0.8614395980974688</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.2604957112317619</v>
+        <v>0.8797076910626043</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.2655491738474892</v>
+        <v>0.8986966957379452</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.2722944518517804</v>
+        <v>0.9183618942536413</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2809134165726251</v>
+        <v>0.9386607882377982</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.2916156103246133</v>
+        <v>0.9595531619480527</v>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>α_1_i</t>
+          <t>c_u1_отн_i</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на входе в РК</t>
+          <t>Безразмерная окружная составляющая скорости на входе</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>1.180296158977294</v>
+        <v>0.2675658145409672</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1.17354769367773</v>
+        <v>0.2616490023434986</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1.163593381597623</v>
+        <v>0.2576095825081036</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1.15038850731903</v>
+        <v>0.2552316373223689</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.133775838988559</v>
+        <v>0.2543820897171053</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.113517639280561</v>
+        <v>0.2549786247517394</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.089269891516375</v>
+        <v>0.2570008412996226</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.060567821445653</v>
+        <v>0.2604957112317619</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1.026876578551888</v>
+        <v>0.2655491738474892</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.9876014776906153</v>
+        <v>0.2722944518517804</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.9421326350930992</v>
+        <v>0.2809134165726251</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.8899613152251319</v>
+        <v>0.2916156103246133</v>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>c_a1_i</t>
+          <t>α_1_i</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на входе в ступень</t>
+          <t>Угол абсолютной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>199.2565864072191</v>
+        <v>1.180296158977294</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>1.17354769367773</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>1.163593381597623</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>1.15038850731903</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>1.133775838988559</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>1.113517639280561</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>1.089269891516375</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>1.060567821445653</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>1.026876578551888</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>0.9876014776906153</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>0.9421326350930992</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>110.3574940101521</v>
+        <v>0.8899613152251319</v>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>λ_1_i</t>
+          <t>c_a1_i</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на входе в ступень</t>
+          <t>Осевая скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>0.6934155588636786</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.6290007738192603</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.574014360850995</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.5261763607748462</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.4842889204649947</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.4471981639398266</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4142409216095714</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.3848409007715879</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.358692486055376</v>
+        <v>134.602701027534</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.335469182640696</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.3151227911923925</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0.2976385445704193</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>q_1_i</t>
+          <t>λ_1_i</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на входе</t>
+          <t>Приведенная скорость на входе в ступень</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.8876763917513479</v>
+        <v>0.6934155588636786</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.8367187220902095</v>
+        <v>0.6290007738192603</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.7864274238623349</v>
+        <v>0.574014360850995</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.7378118937190112</v>
+        <v>0.5261763607748462</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.6918457719220593</v>
+        <v>0.4842889204649947</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.6486182523825925</v>
+        <v>0.4471981639398266</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.608383057920596</v>
+        <v>0.4142409216095714</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.571105333397828</v>
+        <v>0.3848409007715879</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.5369562412061231</v>
+        <v>0.358692486055376</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.5058253851811065</v>
+        <v>0.335469182640696</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4780003690667221</v>
+        <v>0.3151227911923925</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>0.2976385445704193</v>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>F_1_i</t>
+          <t>q_1_i</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в ступень</t>
+          <t>Газодинамическая функция расхода на входе</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.3009117955899137</v>
+        <v>0.8876763917513479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.1312547944711213</v>
+        <v>0.8367187220902095</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.09163894407812001</v>
+        <v>0.7864274238623349</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.07466934589439193</v>
+        <v>0.7378118937190112</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.06571582737082768</v>
+        <v>0.6918457719220593</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.06059354891620095</v>
+        <v>0.6486182523825925</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.05763976482606604</v>
+        <v>0.608383057920596</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.05609774057576191</v>
+        <v>0.571105333397828</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.05556606751348679</v>
+        <v>0.5369562412061231</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.05586177064312022</v>
+        <v>0.5058253851811065</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.05687360435199427</v>
+        <v>0.4780003690667221</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.05857117009930012</v>
+        <v>0.4537118711400231</v>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>c_a3_отн_i</t>
+          <t>F_1_i</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Коэффициент расхода на выходе из ступени</t>
+          <t>Кольцевая площадь на входе в ступень</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.6236363636363637</v>
+        <v>0.3009117955899137</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.5972727272727273</v>
+        <v>0.1312547944711213</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.5709090909090909</v>
+        <v>0.09163894407812001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.5445454545454546</v>
+        <v>0.07466934589439193</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.06571582737082768</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.4918181818181818</v>
+        <v>0.06059354891620095</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4654545454545455</v>
+        <v>0.05763976482606604</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.4390909090909091</v>
+        <v>0.05609774057576191</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.4127272727272727</v>
+        <v>0.05556606751348679</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.05586177064312022</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.36</v>
+        <v>0.05687360435199427</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0.3336363636363636</v>
+        <v>0.05857117009930012</v>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>c_a3_i</t>
+          <t>c_a3_отн_i</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из ступени</t>
+          <t>Коэффициент расхода на выходе из ступени</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>0.6236363636363637</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>0.5972727272727273</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>0.5709090909090909</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>0.5445454545454546</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>0.4918181818181818</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>0.4654545454545455</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>0.4390909090909091</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>0.4127272727272727</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>110.3574940101521</v>
+        <v>0.36</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>102.2757583376915</v>
+        <v>0.3336363636363636</v>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i_0</t>
+          <t>c_a3_i</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе (1-е приближение)</t>
+          <t>Осевая скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>0.6470187781110718</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.586173210716883</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.5340840464310409</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.4889237180942501</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.4492521137640234</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.4141235259565256</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3827019947765132</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.3546465340521764</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.3295241151493359</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.3071447039852674</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2874041760296047</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>0.2702406194692441</v>
+        <v>102.2757583376915</v>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52" ht="30" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>q_3_i</t>
+          <t>λ_3_i_0</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Газодинамическая функция расхода на выходе</t>
+          <t>Приведенная скорость на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.8518815630867524</v>
+        <v>0.6470187781110718</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.7980928600064215</v>
+        <v>0.586173210716883</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.7461548093475975</v>
+        <v>0.5340840464310409</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.697097433111779</v>
+        <v>0.4889237180942501</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.6510781569448195</v>
+        <v>0.4492521137640234</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.6082361540873048</v>
+        <v>0.4141235259565256</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5683324138660786</v>
+        <v>0.3827019947765132</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.5315580405223252</v>
+        <v>0.3546465340521764</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.4977046335060994</v>
+        <v>0.3295241151493359</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.4668911352930197</v>
+        <v>0.3071447039852674</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.439236548039308</v>
+        <v>0.2874041760296047</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.4148482593599832</v>
+        <v>0.2702406194692441</v>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>F_3_i_0</t>
+          <t>q_3_i</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на выходе (1-е приближение)</t>
+          <t>Газодинамическая функция расхода на выходе</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.2743520218633287</v>
+        <v>0.8518815630867524</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.1201125559303119</v>
+        <v>0.7980928600064215</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.08421335092644007</v>
+        <v>0.7461548093475975</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.06891030788799436</v>
+        <v>0.697097433111779</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.06094200283320824</v>
+        <v>0.6510781569448195</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.05648887770844104</v>
+        <v>0.6082361540873048</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.05400111276892245</v>
+        <v>0.5683324138660786</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.05285615546139544</v>
+        <v>0.5315580405223252</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.05272852012561755</v>
+        <v>0.4977046335060994</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.05344840716338015</v>
+        <v>0.4668911352930197</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.05494609946622748</v>
+        <v>0.439236548039308</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>0.05723387284064647</v>
+        <v>0.4148482593599832</v>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i_0</t>
+          <t>F_3_i_0</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
+          <t>Кольцевая площадь на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.496259530291237</v>
+        <v>0.2743520218633287</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.8185445247137505</v>
+        <v>0.1201125559303119</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.8767216867967569</v>
+        <v>0.08421335092644007</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.9003793199997074</v>
+        <v>0.06891030788799436</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.9124550510696275</v>
+        <v>0.06094200283320824</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.9191345262736552</v>
+        <v>0.05648887770844104</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9228450067431002</v>
+        <v>0.05400111276892245</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.9245476971002226</v>
+        <v>0.05285615546139544</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.9247373120971561</v>
+        <v>0.05272852012561755</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.9236673388761331</v>
+        <v>0.05344840716338015</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.9214373268864954</v>
+        <v>0.05494609946622748</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.9180204543028089</v>
+        <v>0.05723387284064647</v>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>r_ср3_отн_i</t>
+          <t>d3_отн_i_0</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из ступени</t>
+          <t>Относительный диаметр втулки на выходе (1-е приближение)</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.7914114817012881</v>
+        <v>0.496259530291237</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.9175642260339907</v>
+        <v>0.8185445247137505</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.9436523966497012</v>
+        <v>0.8767216867967569</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9544615921341284</v>
+        <v>0.9003793199997074</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9600071988288605</v>
+        <v>0.9124550510696275</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.9630603322341956</v>
+        <v>0.9191345262736552</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9647162909970507</v>
+        <v>0.9228450067431002</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.9654026903433606</v>
+        <v>0.9245476971002226</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.9653300977116198</v>
+        <v>0.9247373120971561</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9645907141301797</v>
+        <v>0.9236673388761331</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9631964275673923</v>
+        <v>0.9214373268864954</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.961087937215221</v>
+        <v>0.9180204543028089</v>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>c_3u_отн_i</t>
+          <t>r_ср3_отн_i</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе</t>
+          <t>Относительный средний радиус на выходе из ступени</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.2803314260408126</v>
+        <v>0.7914114817012881</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.3458492759403646</v>
+        <v>0.9175642260339907</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.351047131535497</v>
+        <v>0.9436523966497012</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.3474108361019247</v>
+        <v>0.9544615921341284</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.3409913965417674</v>
+        <v>0.9600071988288605</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.333471026166709</v>
+        <v>0.9630603322341956</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.325570138399774</v>
+        <v>0.9647162909970507</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.3176637807777642</v>
+        <v>0.9654026903433606</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.3100444252741181</v>
+        <v>0.9653300977116198</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.3029957910776013</v>
+        <v>0.9645907141301797</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2968234119960466</v>
+        <v>0.9631964275673923</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0.2918471447312225</v>
+        <v>0.961087937215221</v>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>α_3_i</t>
+          <t>c_3u_отн_i</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из ступени</t>
+          <t>Безразмерная окружная составляющая скорости на выходе</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>1.148349100413499</v>
+        <v>0.2803314260408126</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1.045925568107925</v>
+        <v>0.3458492759403646</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1.019499110376512</v>
+        <v>0.351047131535497</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.002915226818822</v>
+        <v>0.3474108361019247</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.9887803620450216</v>
+        <v>0.3409913965417674</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.9749630666974607</v>
+        <v>0.333471026166709</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9604281068418332</v>
+        <v>0.325570138399774</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.9444996836152652</v>
+        <v>0.3176637807777642</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.9265219325482024</v>
+        <v>0.3100444252741181</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.9057489472864968</v>
+        <v>0.3029957910776013</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.8812882212871602</v>
+        <v>0.2968234119960466</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.8521100845146086</v>
+        <v>0.2918471447312225</v>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
     </row>
-    <row r="58" ht="15" customHeight="1">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>λ_3_i</t>
+          <t>α_3_i</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Приведенная скорость на выходе из ступени</t>
+          <t>Угол абсолютной скорости на выходе из ступени</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>0.6559785963090488</v>
+        <v>1.148349100413499</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.6246063457694964</v>
+        <v>1.045925568107925</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.5757065070246412</v>
+        <v>1.019499110376512</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.5294507601125176</v>
+        <v>1.002915226818822</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.4872531702268296</v>
+        <v>0.9887803620450216</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.4489353796842664</v>
+        <v>0.9749630666974607</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4139239072289042</v>
+        <v>0.9604281068418332</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.3819733439588067</v>
+        <v>0.9444996836152652</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.3526664394879173</v>
+        <v>0.9265219325482024</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.3258102099036672</v>
+        <v>0.9057489472864968</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3012816010392996</v>
+        <v>0.8812882212871602</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.278992643690011</v>
+        <v>0.8521100845146086</v>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="15" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>F_3_i</t>
+          <t>λ_3_i</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Действительная кольцевая площадь на выходе из ступени</t>
+          <t>Приведенная скорость на выходе из ступени</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.2720258280079406</v>
+        <v>0.6559785963090488</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.1150773962795963</v>
+        <v>0.6246063457694964</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.07972938889514986</v>
+        <v>0.5757065070246412</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.06479319133468478</v>
+        <v>0.5294507601125176</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.0570642191435431</v>
+        <v>0.4872531702268296</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.05278992205645663</v>
+        <v>0.4489353796842664</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.05046595153123931</v>
+        <v>0.4139239072289042</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.04950148906418269</v>
+        <v>0.3819733439588067</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.04960352169899662</v>
+        <v>0.3526664394879173</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.05064232585954236</v>
+        <v>0.3258102099036672</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.05259907661212716</v>
+        <v>0.3012816010392996</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.05555276895854432</v>
+        <v>0.278992643690011</v>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>F_1_i_plus_1</t>
+          <t>F_3_i</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Кольцевая площадь на входе в следующую ступень</t>
+          <t>Действительная кольцевая площадь на выходе из ступени</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
+        <v>0.2720258280079406</v>
+      </c>
+      <c r="E60" s="2" t="n">
         <v>0.1150773962795963</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="F60" s="2" t="n">
         <v>0.07972938889514986</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>0.06479319133468478</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.0570642191435431</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>0.05278992205645663</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="J60" s="2" t="n">
         <v>0.05046595153123931</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="K60" s="2" t="n">
         <v>0.04950148906418269</v>
       </c>
-      <c r="K60" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>0.04960352169899662</v>
       </c>
-      <c r="L60" s="2" t="n">
+      <c r="M60" s="2" t="n">
         <v>0.05064232585954236</v>
       </c>
-      <c r="M60" s="2" t="n">
+      <c r="N60" s="2" t="n">
         <v>0.05259907661212716</v>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="O60" s="2" t="n">
         <v>0.05555276895854432</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>0.05850646130496148</v>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>d3_отн_i</t>
+          <t>F_1_i_plus_1</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Относительный диаметр втулки на выходе из ступени</t>
+          <t>Кольцевая площадь на входе в следующую ступень</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.5026572059935642</v>
+        <v>0.1150773962795963</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.8269511580466603</v>
+        <v>0.07972938889514986</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.8837192378835317</v>
+        <v>0.06479319133468478</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.9066387713518712</v>
+        <v>0.0570642191435431</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.9182742747166943</v>
+        <v>0.05278992205645663</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.9246460982700778</v>
+        <v>0.05046595153123931</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9280921528761098</v>
+        <v>0.04950148906418269</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.9295185361489017</v>
+        <v>0.04960352169899662</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.929367739431411</v>
+        <v>0.05064232585954236</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.9278310684452963</v>
+        <v>0.05259907661212716</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.9249295736201615</v>
+        <v>0.05555276895854432</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0.9205324796666424</v>
+        <v>0.05850646130496148</v>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
     </row>
-    <row r="62" ht="15" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>r_ср2_отн_i</t>
+          <t>d3_отн_i</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Относительный средний радиус на выходе из РК</t>
+          <t>Относительный диаметр втулки на выходе из ступени</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.7805596092214843</v>
+        <v>0.5026572059935642</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.8500880382586702</v>
+        <v>0.8269511580466603</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8700959893287561</v>
+        <v>0.8837192378835317</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8829499081275562</v>
+        <v>0.9066387713518712</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.893631259906112</v>
+        <v>0.9182742747166943</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9034997827061337</v>
+        <v>0.9246460982700778</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9130779445472598</v>
+        <v>0.9280921528761098</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.9225551907029824</v>
+        <v>0.9295185361489017</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.9320133967247826</v>
+        <v>0.929367739431411</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.9414763041919105</v>
+        <v>0.9278310684452963</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9509286079025953</v>
+        <v>0.9249295736201615</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0.9603205495816369</v>
+        <v>0.9205324796666424</v>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>c_u2_отн_i</t>
+          <t>r_ср2_отн_i</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
+          <t>Относительный средний радиус на выходе из РК</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.4951608024475138</v>
+        <v>0.7805596092214843</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.4796111464536851</v>
+        <v>0.8500880382586702</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.4933697911469953</v>
+        <v>0.8700959893287561</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.511158425729244</v>
+        <v>0.8829499081275562</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.5303221251053101</v>
+        <v>0.893631259906112</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.5501351231747619</v>
+        <v>0.9034997827061337</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5702552370692163</v>
+        <v>0.9130779445472598</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.5904530661631379</v>
+        <v>0.9225551907029824</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.6105143851335061</v>
+        <v>0.9320133967247826</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.630205686088978</v>
+        <v>0.9414763041919105</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6492618491206571</v>
+        <v>0.9509286079025953</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0.6674038058680815</v>
+        <v>0.9603205495816369</v>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
     </row>
-    <row r="64" ht="15" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>β_1_i</t>
+          <t>c_u2_отн_i</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на входе в РК</t>
+          <t>Безразмерная окружная составляющая скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.9130337357818</v>
+        <v>0.4951608024475138</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.8748613108903142</v>
+        <v>0.4796111464536851</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.8367019754879613</v>
+        <v>0.4933697911469953</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.7984417849023867</v>
+        <v>0.511158425729244</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.760052506592651</v>
+        <v>0.5303221251053101</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.7215557875774173</v>
+        <v>0.5501351231747619</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6830253822830016</v>
+        <v>0.5702552370692163</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.6445808950740264</v>
+        <v>0.5904530661631379</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.6063535228830391</v>
+        <v>0.6105143851335061</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5684827367765299</v>
+        <v>0.630205686088978</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5311064742865111</v>
+        <v>0.6492618491206571</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.4943374292495647</v>
+        <v>0.6674038058680815</v>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="15" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>c_a2_отн_i</t>
+          <t>β_1_i</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Относительная осевая скорость на выходе из РК</t>
+          <t>Угол относительной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.6368181818181818</v>
+        <v>0.9130337357818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.6104545454545455</v>
+        <v>0.8748613108903142</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.5840909090909091</v>
+        <v>0.8367019754879613</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.5577272727272727</v>
+        <v>0.7984417849023867</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.5313636363636364</v>
+        <v>0.760052506592651</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.505</v>
+        <v>0.7215557875774173</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4786363636363636</v>
+        <v>0.6830253822830016</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.4522727272727273</v>
+        <v>0.6445808950740264</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.4259090909090909</v>
+        <v>0.6063535228830391</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.3995454545454545</v>
+        <v>0.5684827367765299</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3731818181818182</v>
+        <v>0.5311064742865111</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>0.3468181818181818</v>
+        <v>0.4943374292495647</v>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>β_2_i</t>
+          <t>c_a2_отн_i</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Угол относительной скорости на выходе из РК</t>
+          <t>Относительная осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>1.149470499626858</v>
+        <v>0.6368181818181818</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1.025328281506466</v>
+        <v>0.6104545454545455</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.9979591178031184</v>
+        <v>0.5840909090909091</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.9828268660091499</v>
+        <v>0.5577272727272727</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.9710736479752523</v>
+        <v>0.5313636363636364</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.9602502514475583</v>
+        <v>0.505</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9492481850610934</v>
+        <v>0.4786363636363636</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.9374216670208639</v>
+        <v>0.4522727272727273</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.924196142381593</v>
+        <v>0.4259090909090909</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.9089535843846798</v>
+        <v>0.3995454545454545</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.8909761330468265</v>
+        <v>0.3731818181818182</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>0.8694555233106508</v>
+        <v>0.3468181818181818</v>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>α_2_i</t>
+          <t>β_2_i</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Угол абсолютной скорости на выходе из РК</t>
+          <t>Угол относительной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>0.9098923318704959</v>
+        <v>1.149470499626858</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.9048592082754372</v>
+        <v>1.025328281506466</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.8693990341364447</v>
+        <v>0.9979591178031184</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.8289382873161977</v>
+        <v>0.9828268660091499</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.7863791607528087</v>
+        <v>0.9710736479752523</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.7426475977563408</v>
+        <v>0.9602502514475583</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6982710232411901</v>
+        <v>0.9492481850610934</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.6536474291487642</v>
+        <v>0.9374216670208639</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.6091291160368223</v>
+        <v>0.924196142381593</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.5650394600392833</v>
+        <v>0.9089535843846798</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5216678776691375</v>
+        <v>0.8909761330468265</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.4792458653577785</v>
+        <v>0.8694555233106508</v>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>ε_рк_i</t>
+          <t>α_2_i</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки РК</t>
+          <t>Угол абсолютной скорости на выходе из РК</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.2364367638450576</v>
+        <v>0.9098923318704959</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.1504669706161518</v>
+        <v>0.9048592082754372</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.1612571423151571</v>
+        <v>0.8693990341364447</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.1843850811067632</v>
+        <v>0.8289382873161977</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.2110211413826013</v>
+        <v>0.7863791607528087</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.2386944638701409</v>
+        <v>0.7426475977563408</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2662228027780918</v>
+        <v>0.6982710232411901</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.2928407719468376</v>
+        <v>0.6536474291487642</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.3178426194985539</v>
+        <v>0.6091291160368223</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.3404708476081498</v>
+        <v>0.5650394600392833</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3598696587603154</v>
+        <v>0.5216678776691375</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.3751180940610861</v>
+        <v>0.4792458653577785</v>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>ε_на_i</t>
+          <t>ε_рк_i</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Диффузность решетки НА</t>
+          <t>Диффузность решетки РК</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.238456768543003</v>
+        <v>0.2364367638450576</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1410663598324875</v>
+        <v>0.1504669706161518</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1501000762400676</v>
+        <v>0.1612571423151571</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1739769395026247</v>
+        <v>0.1843850811067632</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.202401201292213</v>
+        <v>0.2110211413826013</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2323154689411199</v>
+        <v>0.2386944638701409</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2621570836006432</v>
+        <v>0.2662228027780918</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.290852254466501</v>
+        <v>0.2928407719468376</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.3173928165113801</v>
+        <v>0.3178426194985539</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.3407094872472135</v>
+        <v>0.3404708476081498</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3596203436180228</v>
+        <v>0.3598696587603154</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.37286421915683</v>
+        <v>0.3751180940610861</v>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>W_1_i</t>
+          <t>ε_на_i</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Относительная скорость на входе в РК</t>
+          <t>Диффузность решетки НА</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>251.7894146864385</v>
+        <v>0.238456768543003</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>249.1024900209453</v>
+        <v>0.1410663598324875</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>246.6107242604538</v>
+        <v>0.1501000762400676</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>244.3372984316917</v>
+        <v>0.1739769395026247</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>242.2923887858165</v>
+        <v>0.202401201292213</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>240.4769672604629</v>
+        <v>0.2323154689411199</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>238.8781441276591</v>
+        <v>0.2621570836006432</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>237.4656501333595</v>
+        <v>0.290852254466501</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>236.1969574055916</v>
+        <v>0.3173928165113801</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>235.0144241906794</v>
+        <v>0.3407094872472135</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>233.8442343661209</v>
+        <v>0.3596203436180228</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>232.6016263665796</v>
+        <v>0.37286421915683</v>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>c_a2_i</t>
+          <t>W_1_i</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость на выходе из РК</t>
+          <t>Относительная скорость на входе в РК</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>251.7894146864385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>249.1024900209453</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>246.6107242604538</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>244.3372984316917</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>242.2923887858165</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>240.4769672604629</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>146.7253045362249</v>
+        <v>238.8781441276591</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>138.6435688637643</v>
+        <v>237.4656501333595</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>236.1969574055916</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>235.0144241906794</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>233.8442343661209</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>106.3166261739218</v>
+        <v>232.6016263665796</v>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>c_2_i</t>
+          <t>c_a2_i</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Абсолютная скорость на выходе из РК</t>
+          <t>Осевая скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>247.28452908</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>237.9815544364363</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>234.3795941484085</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>231.9142224061601</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>230.133866067011</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>228.9229812149858</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>228.2261602651597</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>227.999923292236</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>228.1937458904654</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>228.7427276681898</v>
+        <v>122.480097518843</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>229.5649111126124</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>230.5666674764105</v>
+        <v>106.3166261739218</v>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>τ_1_i</t>
+          <t>c_2_i</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на входе в РК</t>
+          <t>Абсолютная скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>0.9198717705829682</v>
+        <v>247.28452908</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.9343717516022703</v>
+        <v>237.9815544364363</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0.9456738513371452</v>
+        <v>234.3795941484085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.9544810706406721</v>
+        <v>231.9142224061601</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.9616684573121036</v>
+        <v>230.133866067011</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.9675039353435879</v>
+        <v>228.9229812149858</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9723363601852713</v>
+        <v>228.2261602651597</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.9763162299517529</v>
+        <v>227.999923292236</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0.9796348119488701</v>
+        <v>228.1937458904654</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.9823328970460875</v>
+        <v>228.7427276681898</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.9845454709023621</v>
+        <v>229.5649111126124</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>0.9863414798135992</v>
+        <v>230.5666674764105</v>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>T_1_i</t>
+          <t>τ_1_i</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на входе в РК</t>
+          <t>Температурная функция на входе в РК</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>264.9230699278949</v>
+        <v>0.9198717705829682</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>302.9393809956259</v>
+        <v>0.9343717516022703</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>340.8533627745312</v>
+        <v>0.9456738513371452</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>378.5964068562916</v>
+        <v>0.9544810706406721</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>416.2762214324989</v>
+        <v>0.9616684573121036</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>453.842488535186</v>
+        <v>0.9675039353435879</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>491.324598928213</v>
+        <v>0.9723363601852713</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>528.6950671020987</v>
+        <v>0.9763162299517529</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>565.9717639113386</v>
+        <v>0.9796348119488701</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>603.1078831527154</v>
+        <v>0.9823328970460875</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>640.1237707477241</v>
+        <v>0.9845454709023621</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>677.0139991251236</v>
+        <v>0.9863414798135992</v>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>a_1_i</t>
+          <t>T_1_i</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на входе в РК</t>
+          <t>Статическая температура на входе в РК</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>298.0389802067385</v>
+        <v>264.9230699278949</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>318.6014723186276</v>
+        <v>302.9393809956259</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>337.8060659838801</v>
+        <v>340.8533627745312</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>355.9464532230144</v>
+        <v>378.5964068562916</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>373.082946582965</v>
+        <v>416.2762214324989</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>389.395436741228</v>
+        <v>453.842488535186</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>404.9335931204457</v>
+        <v>491.324598928213</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>419.8160494160329</v>
+        <v>528.6950671020987</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>434.0589954920686</v>
+        <v>565.9717639113386</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>447.8214368375179</v>
+        <v>603.1078831527154</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>461.0892039392522</v>
+        <v>640.1237707477241</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>473.8913655885228</v>
+        <v>677.0139991251236</v>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
     </row>
-    <row r="76" ht="30" customHeight="1">
+    <row r="76" ht="15" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>M_w1_i</t>
+          <t>a_1_i</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Число Маха относительной скорости на входе в РК</t>
+          <t>Скорость звука на входе в РК</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>0.8448204141343578</v>
+        <v>298.0389802067385</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.7818623316712811</v>
+        <v>318.6014723186276</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.7300363998561882</v>
+        <v>337.8060659838801</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.6864439755454026</v>
+        <v>355.9464532230144</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.6494330309250312</v>
+        <v>373.082946582965</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0.6175649341783925</v>
+        <v>389.395436741228</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5899193057480068</v>
+        <v>404.9335931204457</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.5656421436571468</v>
+        <v>419.8160494160329</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0.5441586509175513</v>
+        <v>434.0589954920686</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>0.5247949402563977</v>
+        <v>447.8214368375179</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5071561692798375</v>
+        <v>461.0892039392522</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>0.4908332230905137</v>
+        <v>473.8913655885228</v>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>λ_c2_i</t>
+          <t>M_w1_i</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Приведенная абсолютная скорость на выходе из РК</t>
+          <t>Число Маха относительной скорости на входе в РК</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.7739140879000126</v>
+        <v>0.8448204141343578</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7025688677305478</v>
+        <v>0.7818623316712811</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.6567734946088818</v>
+        <v>0.7300363998561882</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.6201103319267046</v>
+        <v>0.6864439755454026</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.5896922001548817</v>
+        <v>0.6494330309250312</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.5641990975072881</v>
+        <v>0.6175649341783925</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5425314394305585</v>
+        <v>0.5899193057480068</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.5242135535589888</v>
+        <v>0.5656421436571468</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.5085612696312135</v>
+        <v>0.5441586509175513</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.4951412220693632</v>
+        <v>0.5247949402563977</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4835545192846229</v>
+        <v>0.5071561692798375</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.4733931316860104</v>
+        <v>0.4908332230905137</v>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
+    <row r="78" ht="30" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>T2_полн_i</t>
+          <t>λ_c2_i</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Полная температура на выходе из РК</t>
+          <t>Приведенная абсолютная скорость на выходе из РК</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>0.7739140879000126</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>342.7216074711233</v>
+        <v>0.7025688677305478</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>380.5533143746371</v>
+        <v>0.6567734946088818</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>418.299782629001</v>
+        <v>0.6201103319267046</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>455.8623617326095</v>
+        <v>0.5896922001548817</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>493.3043052802819</v>
+        <v>0.5641990975072881</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>530.8455851254013</v>
+        <v>0.5425314394305585</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>568.2640128064211</v>
+        <v>0.5242135535589888</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>605.4888593452233</v>
+        <v>0.5085612696312135</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>642.5848324826002</v>
+        <v>0.4951412220693632</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>679.4541857759853</v>
+        <v>0.4835545192846229</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>716.0408161885885</v>
+        <v>0.4733931316860104</v>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>τ_2_i</t>
+          <t>T2_полн_i</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Температурная функция на выходе из РК</t>
+          <t>Полная температура на выходе из РК</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>0.9006486075029659</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.9186155927206895</v>
+        <v>342.7216074711233</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.9290813257877711</v>
+        <v>380.5533143746371</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.9371529110515402</v>
+        <v>418.299782629001</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.9434956981360756</v>
+        <v>455.8623617326095</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0.9486821920661557</v>
+        <v>493.3043052802819</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9529306488556853</v>
+        <v>530.8455851254013</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.9565028945546096</v>
+        <v>568.2640128064211</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0.959398073182831</v>
+        <v>605.4888593452233</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0.9618447489108495</v>
+        <v>642.5848324826002</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.9639490928348131</v>
+        <v>679.4541857759853</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>0.9657748293183122</v>
+        <v>716.0408161885885</v>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>T_2_i</t>
+          <t>τ_2_i</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>Статическая температура на выходе из РК</t>
+          <t>Температурная функция на выходе из РК</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>618.1953492286352</v>
+        <v>0.9006486075029659</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>630.527691286045</v>
+        <v>0.9186155927206895</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>637.711255946491</v>
+        <v>0.9290813257877711</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>643.2515037516795</v>
+        <v>0.9371529110515402</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>647.6051234032751</v>
+        <v>0.9434956981360756</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>651.1650760858951</v>
+        <v>0.9486821920661557</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>654.0811703393106</v>
+        <v>0.9529306488556853</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>656.5331206992845</v>
+        <v>0.9565028945546096</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>658.5203396304444</v>
+        <v>0.959398073182831</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>660.1997110784556</v>
+        <v>0.9618447489108495</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>661.6441097219828</v>
+        <v>0.9639490928348131</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>662.8972752669174</v>
+        <v>0.9657748293183122</v>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>a_2_i</t>
+          <t>T_2_i</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Скорость звука на выходе из РК</t>
+          <t>Статическая температура на выходе из РК</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>455.2023097056071</v>
+        <v>618.1953492286352</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>459.5459468369926</v>
+        <v>630.527691286045</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>462.0107673069759</v>
+        <v>637.711255946491</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>463.8696816901759</v>
+        <v>643.2515037516795</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>465.2449251931451</v>
+        <v>647.6051234032751</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>466.2991149814897</v>
+        <v>651.1650760858951</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>467.0828615584704</v>
+        <v>654.0811703393106</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>467.662357643633</v>
+        <v>656.5331206992845</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>468.0735522884636</v>
+        <v>658.5203396304444</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>468.4011802428435</v>
+        <v>660.1997110784556</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>468.6286750273001</v>
+        <v>661.6441097219828</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>468.7767936030652</v>
+        <v>662.8972752669174</v>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>M_c2_ср_i</t>
+          <t>a_2_i</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Среднее число Маха на выходе из РК</t>
+          <t>Скорость звука на выходе из РК</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
+        <v>455.2023097056071</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>459.5459468369926</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>462.0107673069759</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>463.8696816901759</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>465.2449251931451</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>466.2991149814897</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>467.0828615584704</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>467.662357643633</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>468.0735522884636</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>468.4011802428435</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>468.6286750273001</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>468.7767936030652</v>
+      </c>
+      <c r="P82" s="1" t="inlineStr"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>M_c2_ср_i</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>Среднее число Маха на выходе из РК</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
         <v>0.5432409366286526</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E83" s="2" t="n">
         <v>0.5178623727930555</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F83" s="2" t="n">
         <v>0.5073033157096933</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>0.4999555512253943</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>0.4946509969377347</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I83" s="2" t="n">
         <v>0.4909359118643687</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J83" s="2" t="n">
         <v>0.4886202835695136</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K83" s="2" t="n">
         <v>0.4875310564678288</v>
       </c>
-      <c r="L82" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>0.4875168545088711</v>
       </c>
-      <c r="M82" s="2" t="n">
+      <c r="M83" s="2" t="n">
         <v>0.4883478891953212</v>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N83" s="2" t="n">
         <v>0.4898652672059366</v>
       </c>
-      <c r="O82" s="2" t="n">
+      <c r="O83" s="2" t="n">
         <v>0.4918474434373172</v>
       </c>
-      <c r="P82" s="1" t="inlineStr"/>
+      <c r="P83" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9.714170190180937</v>
+        <v>11.34609827837883</v>
       </c>
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr"/>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -431,15 +431,19 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -519,6 +523,26 @@
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 13</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 14</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 15</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 16</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>СА</t>
         </is>
@@ -551,6 +575,10 @@
       <c r="N2" s="1" t="inlineStr"/>
       <c r="O2" s="1" t="inlineStr"/>
       <c r="P2" s="1" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="R2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -579,6 +607,10 @@
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr"/>
       <c r="P3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="R3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr"/>
+      <c r="T3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -607,6 +639,10 @@
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
+      <c r="Q4" s="1" t="inlineStr"/>
+      <c r="R4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr"/>
+      <c r="T4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -635,6 +671,10 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr"/>
       <c r="P5" s="1" t="inlineStr"/>
+      <c r="Q5" s="1" t="inlineStr"/>
+      <c r="R5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr"/>
+      <c r="T5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -663,6 +703,10 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
+      <c r="Q6" s="1" t="inlineStr"/>
+      <c r="R6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr"/>
+      <c r="T6" s="1" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -691,6 +735,10 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr"/>
       <c r="P7" s="1" t="inlineStr"/>
+      <c r="Q7" s="1" t="inlineStr"/>
+      <c r="R7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr"/>
+      <c r="T7" s="1" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -716,7 +764,11 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr"/>
-      <c r="P8" s="2" t="n">
+      <c r="P8" s="1" t="inlineStr"/>
+      <c r="Q8" s="1" t="inlineStr"/>
+      <c r="R8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr"/>
+      <c r="T8" s="2" t="n">
         <v>477.1612274741949</v>
       </c>
     </row>
@@ -744,7 +796,11 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr"/>
-      <c r="P9" s="2" t="n">
+      <c r="P9" s="1" t="inlineStr"/>
+      <c r="Q9" s="1" t="inlineStr"/>
+      <c r="R9" s="1" t="inlineStr"/>
+      <c r="S9" s="1" t="inlineStr"/>
+      <c r="T9" s="2" t="n">
         <v>0.9595531619480527</v>
       </c>
     </row>
@@ -772,8 +828,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
-        <v>106.3166261739218</v>
+      <c r="P10" s="1" t="inlineStr"/>
+      <c r="Q10" s="1" t="inlineStr"/>
+      <c r="R10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr"/>
+      <c r="T10" s="2" t="n">
+        <v>107.3941909302498</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -800,7 +860,11 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="inlineStr"/>
-      <c r="P11" s="2" t="n">
+      <c r="P11" s="1" t="inlineStr"/>
+      <c r="Q11" s="1" t="inlineStr"/>
+      <c r="R11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr"/>
+      <c r="T11" s="2" t="n">
         <v>0.4537118711400231</v>
       </c>
     </row>
@@ -828,8 +892,12 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr"/>
       <c r="O12" s="1" t="inlineStr"/>
-      <c r="P12" s="2" t="n">
-        <v>0.05555276895854432</v>
+      <c r="P12" s="1" t="inlineStr"/>
+      <c r="Q12" s="1" t="inlineStr"/>
+      <c r="R12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr"/>
+      <c r="T12" s="2" t="n">
+        <v>0.05491106614839087</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -856,7 +924,11 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
       <c r="O13" s="1" t="inlineStr"/>
-      <c r="P13" s="2" t="n">
+      <c r="P13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="R13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr"/>
+      <c r="T13" s="2" t="n">
         <v>1.570796326794897</v>
       </c>
     </row>
@@ -884,8 +956,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr"/>
-      <c r="P14" s="2" t="n">
-        <v>0.05555276895854432</v>
+      <c r="P14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="R14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr"/>
+      <c r="T14" s="2" t="n">
+        <v>0.05491106614839087</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -912,8 +988,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
-      <c r="P15" s="2" t="n">
-        <v>0.3421954010820806</v>
+      <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
+      <c r="R15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr"/>
+      <c r="T15" s="2" t="n">
+        <v>0.3452273254016311</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -940,8 +1020,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="inlineStr"/>
-      <c r="P16" s="2" t="n">
-        <v>0.5026572059935642</v>
+      <c r="P16" s="1" t="inlineStr"/>
+      <c r="Q16" s="1" t="inlineStr"/>
+      <c r="R16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr"/>
+      <c r="T16" s="2" t="n">
+        <v>0.5071108561666231</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -968,8 +1052,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
       <c r="O17" s="1" t="inlineStr"/>
-      <c r="P17" s="2" t="n">
-        <v>0.7914114817012881</v>
+      <c r="P17" s="1" t="inlineStr"/>
+      <c r="Q17" s="1" t="inlineStr"/>
+      <c r="R17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr"/>
+      <c r="T17" s="2" t="n">
+        <v>0.7928308206805679</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -996,8 +1084,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
       <c r="O18" s="1" t="inlineStr"/>
-      <c r="P18" s="2" t="n">
-        <v>0.8521100845146086</v>
+      <c r="P18" s="1" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr"/>
+      <c r="R18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="2" t="n">
+        <v>0.861508375559446</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1024,8 +1116,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
       <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="2" t="n">
-        <v>0.718686242280288</v>
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="2" t="n">
+        <v>0.7092879512354505</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1052,8 +1148,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
       <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="2" t="n">
-        <v>141.2523884686373</v>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="2" t="n">
+        <v>141.5268009329557</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1080,8 +1180,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
       <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
-        <v>0.9189293312859016</v>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="2" t="n">
+        <v>0.919408386540464</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -1108,8 +1212,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
       <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
-        <v>0.6255821807307252</v>
+      <c r="P22" s="1" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr"/>
+      <c r="R22" s="1" t="inlineStr"/>
+      <c r="S22" s="1" t="inlineStr"/>
+      <c r="T22" s="2" t="n">
+        <v>0.6259083085630148</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1136,8 +1244,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
-        <v>0.02759535690110904</v>
+      <c r="P23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr"/>
+      <c r="R23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="2" t="n">
+        <v>0.02743229298496425</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1164,8 +1276,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>0.1692887467254313</v>
+      <c r="P24" s="1" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr"/>
+      <c r="T24" s="2" t="n">
+        <v>0.1677727845656561</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1184,39 +1300,51 @@
         <v>1.399944336209296</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.397730417935234</v>
+        <v>1.398030109901669</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.394860425858321</v>
+        <v>1.397119376129521</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1.393519592252976</v>
+        <v>1.395156317152682</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.390731081206798</v>
+        <v>1.393623697897493</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1.388035570101426</v>
+        <v>1.392036202062929</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.384399004818129</v>
+        <v>1.389809783724452</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1.38071062867211</v>
+        <v>1.387086457843369</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1.37610539882691</v>
+        <v>1.384896195015433</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1.372438981258499</v>
+        <v>1.382177452656831</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.368632710893606</v>
+        <v>1.378497276781724</v>
       </c>
       <c r="O25" s="2" t="n">
+        <v>1.375867872658643</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>1.373209687129157</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>1.370399242345619</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>1.36763080914184</v>
+      </c>
+      <c r="S25" s="2" t="n">
         <v>1.364566577433034</v>
       </c>
-      <c r="P25" s="1" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
@@ -1234,39 +1362,51 @@
         <v>0.65</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.6236363636363637</v>
+        <v>0.6306666666666667</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.5972727272727273</v>
+        <v>0.6113333333333334</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.5709090909090909</v>
+        <v>0.592</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.5445454545454546</v>
+        <v>0.5726666666666667</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4918181818181818</v>
+        <v>0.534</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.4654545454545455</v>
+        <v>0.5146666666666667</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.4390909090909091</v>
+        <v>0.4953333333333333</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.4127272727272727</v>
+        <v>0.476</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.4566666666666667</v>
       </c>
       <c r="O26" s="2" t="n">
+        <v>0.4373333333333334</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.3986666666666667</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.3793333333333334</v>
+      </c>
+      <c r="S26" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="P26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -1281,42 +1421,54 @@
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>0.6236363636363637</v>
+        <v>0.6306666666666667</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.5972727272727273</v>
+        <v>0.6113333333333334</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.5709090909090909</v>
+        <v>0.592</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.5445454545454546</v>
+        <v>0.5726666666666667</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.4918181818181818</v>
+        <v>0.534</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4654545454545455</v>
+        <v>0.5146666666666667</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.4390909090909091</v>
+        <v>0.4953333333333333</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.4127272727272727</v>
+        <v>0.476</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.4566666666666667</v>
       </c>
       <c r="N27" s="2" t="n">
+        <v>0.4373333333333334</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0.3986666666666667</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0.3793333333333334</v>
+      </c>
+      <c r="R27" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>0.3336363636363636</v>
-      </c>
-      <c r="P27" s="1" t="inlineStr"/>
+      <c r="S27" s="2" t="n">
+        <v>0.3406666666666666</v>
+      </c>
+      <c r="T27" s="1" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -1334,39 +1486,51 @@
         <v>100292.8790575521</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>259542.8799520527</v>
+        <v>217076.2130468525</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>418792.8808465532</v>
+        <v>333859.5470361529</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>578042.8817410537</v>
+        <v>450642.8810254533</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>737292.8826355543</v>
+        <v>567426.2150147536</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>896542.8835300547</v>
+        <v>684209.5490040539</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1055792.884424555</v>
+        <v>800992.8829933545</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1215042.885319056</v>
+        <v>917776.2169826548</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1374292.886213556</v>
+        <v>1034559.550971955</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1533542.887108057</v>
+        <v>1151342.884961256</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1692792.888002557</v>
+        <v>1268126.218950556</v>
       </c>
       <c r="O28" s="2" t="n">
+        <v>1384909.552939856</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1501692.886929157</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>1618476.220918457</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>1735259.554907757</v>
+      </c>
+      <c r="S28" s="2" t="n">
         <v>1852042.888897058</v>
       </c>
-      <c r="P28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
@@ -1384,39 +1548,51 @@
         <v>288</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>324.2171870844151</v>
+        <v>314.5592705285711</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>360.4343741688301</v>
+        <v>341.1185410571421</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>396.6515612532452</v>
+        <v>367.6778115857131</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>432.8687483376602</v>
+        <v>394.2370821142841</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>469.0859354220753</v>
+        <v>420.7963526428552</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>505.3031225064903</v>
+        <v>447.3556231714263</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>541.5203095909053</v>
+        <v>473.9148936999973</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>577.7374966753205</v>
+        <v>500.4741642285683</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>613.9546837597354</v>
+        <v>527.0334347571393</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>650.1718708441506</v>
+        <v>553.5927052857104</v>
       </c>
       <c r="O29" s="2" t="n">
+        <v>580.1519758142814</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>606.7112463428525</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>633.2705168714235</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>659.8297873999945</v>
+      </c>
+      <c r="S29" s="2" t="n">
         <v>686.3890579285655</v>
       </c>
-      <c r="P29" s="1" t="inlineStr"/>
+      <c r="T29" s="1" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
@@ -1434,39 +1610,51 @@
         <v>0.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.4743022422822237</v>
+        <v>0.4624883110069641</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.5186044845644475</v>
+        <v>0.4949766220139281</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.5629067268466712</v>
+        <v>0.5274649330208923</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.6072089691288949</v>
+        <v>0.5599532440278563</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.6515112114111187</v>
+        <v>0.5924415550348203</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6958134536933425</v>
+        <v>0.6249298660417845</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.7401156959755661</v>
+        <v>0.6574181770487485</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.7844179382577898</v>
+        <v>0.6899064880557126</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.8287201805400136</v>
+        <v>0.7223947990626767</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.8730224228222374</v>
+        <v>0.7548831100696407</v>
       </c>
       <c r="O30" s="2" t="n">
+        <v>0.7873714210766047</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.8198597320835689</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.852348043090533</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.8848363540974971</v>
+      </c>
+      <c r="S30" s="2" t="n">
         <v>0.9173246651044611</v>
       </c>
-      <c r="P30" s="1" t="inlineStr"/>
+      <c r="T30" s="1" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
@@ -1516,7 +1704,19 @@
       <c r="O31" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
-      <c r="P31" s="1" t="inlineStr"/>
+      <c r="P31" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="T31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
@@ -1534,39 +1734,51 @@
         <v>16967.12604306373</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19070.88223528092</v>
+        <v>18522.44457042484</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>21057.52246874931</v>
+        <v>20010.85352487777</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>22950.09410526995</v>
+        <v>21443.52757416789</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>24759.14168894694</v>
+        <v>22826.43669504646</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26487.00632294096</v>
+        <v>24164.78508955374</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28125.52905279903</v>
+        <v>25460.68314778449</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>29654.33031092169</v>
+        <v>26711.24295341488</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>31044.54895603916</v>
+        <v>27912.59985073472</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>32256.73667984891</v>
+        <v>29057.20999885778</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>33239.72047130691</v>
+        <v>30135.06929757995</v>
       </c>
       <c r="O32" s="2" t="n">
+        <v>31131.51671175844</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>32030.58870804145</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>32813.11863637829</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>33455.75153274887</v>
+      </c>
+      <c r="S32" s="2" t="n">
         <v>33933.38931404932</v>
       </c>
-      <c r="P32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
@@ -1584,39 +1796,51 @@
         <v>16797.45478263309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18689.4645905753</v>
+        <v>18151.99567901635</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20425.79679468683</v>
+        <v>19410.52791913144</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>22032.09034105915</v>
+        <v>20585.78647120117</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>23521.18460449959</v>
+        <v>21685.11486029413</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24897.7859435645</v>
+        <v>22714.89798418052</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>26437.99730963109</v>
+        <v>23933.04215891742</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>27875.07049226639</v>
+        <v>25108.56837620999</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>29181.87601867681</v>
+        <v>26237.84385969064</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>30321.33247905798</v>
+        <v>27313.77739892632</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>31245.33724302849</v>
+        <v>28326.96513972515</v>
       </c>
       <c r="O33" s="2" t="n">
+        <v>29263.62570905293</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>30108.75338555896</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>30844.33151819559</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>31448.40644078394</v>
+      </c>
+      <c r="S33" s="2" t="n">
         <v>31897.38595520635</v>
       </c>
-      <c r="P33" s="1" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
@@ -1634,39 +1858,51 @@
         <v>13701.87693398603</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15617.01385068403</v>
+        <v>15076.69597297022</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>17413.88007155858</v>
+        <v>16380.32104836129</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>19087.25918979651</v>
+        <v>17612.45722779648</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20623.27203085376</v>
+        <v>18768.90312231542</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22003.16976086839</v>
+        <v>19845.7876917099</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>23450.49881419504</v>
+        <v>21061.22894992113</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>24708.63115599736</v>
+        <v>22205.82054603481</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>25732.59482627098</v>
+        <v>23267.30088055942</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>26471.29676564151</v>
+        <v>24230.49891283819</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>26869.11978064452</v>
+        <v>25078.5381918534</v>
       </c>
       <c r="O34" s="2" t="n">
+        <v>25791.39094590568</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>26348.87669288917</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>26729.44485873016</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>26910.5198447063</v>
+      </c>
+      <c r="S34" s="2" t="n">
         <v>26870.38869889748</v>
       </c>
-      <c r="P34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
@@ -1684,39 +1920,51 @@
         <v>16.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.50442038670822</v>
+        <v>17.98195958095144</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>20.11894020580701</v>
+        <v>19.19721130784214</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>21.64822137575578</v>
+        <v>20.28741714564764</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>22.99361339494931</v>
+        <v>21.31133604977339</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.21836985820667</v>
+        <v>22.2586935435603</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25.542462618911</v>
+        <v>23.35654027139916</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>26.74370321551575</v>
+        <v>24.38033301608176</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>27.75136266990286</v>
+        <v>25.37276372176333</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>28.63014872286476</v>
+        <v>26.27823905870514</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>29.28231493183464</v>
+        <v>27.06263816738749</v>
       </c>
       <c r="O35" s="2" t="n">
+        <v>27.81633101439324</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>28.47226781897626</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>29.00758532167604</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>29.41405527703473</v>
+      </c>
+      <c r="S35" s="2" t="n">
         <v>29.65175826002295</v>
       </c>
-      <c r="P35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
@@ -1734,39 +1982,51 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>342.7216074711233</v>
+        <v>332.5412301095225</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>380.5533143746371</v>
+        <v>360.3157523649842</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>418.299782629001</v>
+        <v>387.9652287313608</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>455.8623617326095</v>
+        <v>415.5484181640575</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>493.3043052802819</v>
+        <v>443.0550461864155</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>530.8455851254013</v>
+        <v>470.7121634428254</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>568.2640128064211</v>
+        <v>498.295226716079</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>605.4888593452233</v>
+        <v>525.8469279503316</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>642.5848324826002</v>
+        <v>553.3116738158444</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>679.4541857759853</v>
+        <v>580.6553434530979</v>
       </c>
       <c r="O36" s="2" t="n">
+        <v>607.9683068286746</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>635.1835141618287</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>662.2781021930996</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>689.2438426770293</v>
+      </c>
+      <c r="S36" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="P36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
@@ -1784,39 +2044,51 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>342.7216074711233</v>
+        <v>332.5412301095225</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>380.5533143746371</v>
+        <v>360.3157523649842</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>418.299782629001</v>
+        <v>387.9652287313608</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>455.8623617326095</v>
+        <v>415.5484181640575</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>493.3043052802819</v>
+        <v>443.0550461864155</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>530.8455851254013</v>
+        <v>470.7121634428254</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>568.2640128064211</v>
+        <v>498.295226716079</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>605.4888593452233</v>
+        <v>525.8469279503316</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>642.5848324826002</v>
+        <v>553.3116738158444</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>679.4541857759853</v>
+        <v>580.6553434530979</v>
       </c>
       <c r="O37" s="2" t="n">
+        <v>607.9683068286746</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>635.1835141618287</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>662.2781021930996</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>689.2438426770293</v>
+      </c>
+      <c r="S37" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="P37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
@@ -1834,39 +2106,51 @@
         <v>1.175559285399187</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.177892225128341</v>
+        <v>1.176956036090575</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1.178483449737299</v>
+        <v>1.177314556774188</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.177740365938578</v>
+        <v>1.176870346260679</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.175894000936239</v>
+        <v>1.175734201092261</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.173036766366976</v>
+        <v>1.17400542811149</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.171122407075676</v>
+        <v>1.173698204745806</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.168108071555353</v>
+        <v>1.172847504293333</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.163909173397865</v>
+        <v>1.171437473220811</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.158409204291314</v>
+        <v>1.169448963439853</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.151515127689758</v>
+        <v>1.166851812849547</v>
       </c>
       <c r="O38" s="2" t="n">
+        <v>1.163584415306085</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1.159616698752758</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>1.154911296973687</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>1.149431198653191</v>
+      </c>
+      <c r="S38" s="2" t="n">
         <v>1.143155604508661</v>
       </c>
-      <c r="P38" s="1" t="inlineStr"/>
+      <c r="T38" s="1" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
@@ -1884,39 +2168,51 @@
         <v>117900.225235523</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>305713.5403829411</v>
+        <v>255489.1592371767</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>493540.4789454677</v>
+        <v>393057.7046436996</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>680784.4350698986</v>
+        <v>530348.2434323351</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>866978.2776241348</v>
+        <v>667142.4075891768</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1051677.76500542</v>
+        <v>803265.7244964738</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1236462.704180656</v>
+        <v>940123.9087834673</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1419301.401627094</v>
+        <v>1076411.545587883</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1599552.097199386</v>
+        <v>1211921.826287044</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1776470.195601449</v>
+        <v>1346436.74338179</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1949276.618580578</v>
+        <v>1479715.377504498</v>
       </c>
       <c r="O39" s="2" t="n">
+        <v>1611459.172409335</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1741388.148081287</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>1869196.471422007</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>1994561.470172026</v>
+      </c>
+      <c r="S39" s="2" t="n">
         <v>2117173.208233083</v>
       </c>
-      <c r="P39" s="1" t="inlineStr"/>
+      <c r="T39" s="1" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
@@ -1934,39 +2230,51 @@
         <v>117900.225235523</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>305713.5403829411</v>
+        <v>255489.1592371767</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>493540.4789454677</v>
+        <v>393057.7046436996</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>680784.4350698986</v>
+        <v>530348.2434323351</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>866978.2776241348</v>
+        <v>667142.4075891768</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1051677.76500542</v>
+        <v>803265.7244964738</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1236462.704180656</v>
+        <v>940123.9087834673</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1419301.401627094</v>
+        <v>1076411.545587883</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1599552.097199386</v>
+        <v>1211921.826287044</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1776470.195601449</v>
+        <v>1346436.74338179</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1949276.618580578</v>
+        <v>1479715.377504498</v>
       </c>
       <c r="O40" s="2" t="n">
+        <v>1611459.172409335</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1741388.148081287</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>1869196.471422007</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>1994561.470172026</v>
+      </c>
+      <c r="S40" s="2" t="n">
         <v>2117173.208233083</v>
       </c>
-      <c r="P40" s="1" t="inlineStr"/>
+      <c r="T40" s="1" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
@@ -1984,39 +2292,51 @@
         <v>310.7487734256569</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>329.6005504723648</v>
+        <v>324.6688112316239</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>347.3735553312965</v>
+        <v>338.0515793090531</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>364.3350972913221</v>
+        <v>350.862209958119</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>380.445728537063</v>
+        <v>363.2301909542014</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>395.8808441843627</v>
+        <v>375.1766092304147</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>410.6535144715717</v>
+        <v>386.7059416936959</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>424.8775489240568</v>
+        <v>397.8563095118959</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>438.5475167594254</v>
+        <v>408.7173575831252</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>451.8304907351089</v>
+        <v>419.249265744434</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>464.6939992401076</v>
+        <v>429.4426618693322</v>
       </c>
       <c r="O41" s="2" t="n">
+        <v>439.4469858198541</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>449.2103721206494</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>458.739164603982</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>468.0602766896044</v>
+      </c>
+      <c r="S41" s="2" t="n">
         <v>477.1612274741949</v>
       </c>
-      <c r="P41" s="1" t="inlineStr"/>
+      <c r="T41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
@@ -2031,42 +2351,54 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.5245220964998</v>
+        <v>319.538806481394</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>338.7305720009615</v>
+        <v>333.774424617516</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>356.8651842260853</v>
+        <v>347.3317688252171</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>373.9886443846121</v>
+        <v>360.3293224315304</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>390.2609971889856</v>
+        <v>372.8297737710806</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>405.7485774550155</v>
+        <v>384.842687051213</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>420.6690040022493</v>
+        <v>396.509668398383</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>434.9371010045424</v>
+        <v>407.8266612290232</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>448.7045308344883</v>
+        <v>418.7770733157024</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>461.97472048923</v>
+        <v>429.3336446966811</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>474.7446295243685</v>
+        <v>439.6375871105478</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>487.0511463806778</v>
-      </c>
-      <c r="P42" s="1" t="inlineStr"/>
+        <v>449.6754965258203</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>459.4315267237035</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>468.9278472826187</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>478.1524868271428</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>487.1270825678299</v>
+      </c>
+      <c r="T42" s="1" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
@@ -2084,39 +2416,51 @@
         <v>0.7697077367416805</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.7826118504833496</v>
+        <v>0.7790684943630035</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.7965395820078109</v>
+        <v>0.7889872801066945</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.8114382241209841</v>
+        <v>0.7994433236842792</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.8272553209833634</v>
+        <v>0.8104158301444142</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.8439392331780717</v>
+        <v>0.8218841147424848</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8614395980974688</v>
+        <v>0.8338277212563164</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.8797076910626043</v>
+        <v>0.8462265239030562</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.8986966957379452</v>
+        <v>0.8590608134065268</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.9183618942536413</v>
+        <v>0.8723113680655563</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.9386607882377982</v>
+        <v>0.885959510888735</v>
       </c>
       <c r="O43" s="2" t="n">
+        <v>0.8999871539994868</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0.9143768315886349</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0.9291117227116072</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0.9441756652055144</v>
+      </c>
+      <c r="S43" s="2" t="n">
         <v>0.9595531619480527</v>
       </c>
-      <c r="P43" s="1" t="inlineStr"/>
+      <c r="T43" s="1" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
@@ -2134,39 +2478,51 @@
         <v>0.2675658145409672</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2616490023434986</v>
+        <v>0.2630332328337259</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2576095825081036</v>
+        <v>0.2595454831984348</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.2552316373223689</v>
+        <v>0.2570032853991994</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2543820897171053</v>
+        <v>0.2553424548291788</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.2549786247517394</v>
+        <v>0.2545035381647927</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2570008412996226</v>
+        <v>0.254446895246222</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2604957112317619</v>
+        <v>0.2551637253988659</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2655491738474892</v>
+        <v>0.2566492233119093</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2722944518517804</v>
+        <v>0.2589189552819218</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2809134165726251</v>
+        <v>0.2620001380804975</v>
       </c>
       <c r="O44" s="2" t="n">
+        <v>0.2659437917155251</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0.2708033748788066</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0.2766454189831242</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0.2835539839765567</v>
+      </c>
+      <c r="S44" s="2" t="n">
         <v>0.2916156103246133</v>
       </c>
-      <c r="P44" s="1" t="inlineStr"/>
+      <c r="T44" s="1" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
@@ -2184,39 +2540,51 @@
         <v>1.180296158977294</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.17354769367773</v>
+        <v>1.175660120614364</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.163593381597623</v>
+        <v>1.169301466996413</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1.15038850731903</v>
+        <v>1.161220352668794</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.133775838988559</v>
+        <v>1.151371190875526</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.113517639280561</v>
+        <v>1.139702029614363</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.089269891516375</v>
+        <v>1.126131101140586</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.060567821445653</v>
+        <v>1.110526848816953</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.026876578551888</v>
+        <v>1.09274669556362</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.9876014776906153</v>
+        <v>1.072611910495834</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.9421326350930992</v>
+        <v>1.049922328542544</v>
       </c>
       <c r="O45" s="2" t="n">
+        <v>1.024439898388269</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0.9959305185620582</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0.9641580860903053</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0.9288932198626439</v>
+      </c>
+      <c r="S45" s="2" t="n">
         <v>0.8899613152251319</v>
       </c>
-      <c r="P45" s="1" t="inlineStr"/>
+      <c r="T45" s="1" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
@@ -2234,39 +2602,51 @@
         <v>199.2565864072191</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="O46" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="S46" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
-      <c r="P46" s="1" t="inlineStr"/>
+      <c r="T46" s="1" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
@@ -2284,39 +2664,51 @@
         <v>0.6934155588636786</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6290007738192603</v>
+        <v>0.6451834489675361</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.574014360850995</v>
+        <v>0.6022559501154908</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5261763607748462</v>
+        <v>0.5638685802055692</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.4842889204649947</v>
+        <v>0.5291695030894039</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4471981639398266</v>
+        <v>0.4976467391118254</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4142409216095714</v>
+        <v>0.4689105164395919</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.3848409007715879</v>
+        <v>0.4426124944584192</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.358692486055376</v>
+        <v>0.4184202956554766</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.335469182640696</v>
+        <v>0.3962015376671923</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3151227911923925</v>
+        <v>0.3758216201394586</v>
       </c>
       <c r="O47" s="2" t="n">
+        <v>0.3570527093257961</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>0.339880761221536</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0.324264400412908</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0.3101765261475119</v>
+      </c>
+      <c r="S47" s="2" t="n">
         <v>0.2976385445704193</v>
       </c>
-      <c r="P47" s="1" t="inlineStr"/>
+      <c r="T47" s="1" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
@@ -2334,39 +2726,51 @@
         <v>0.8876763917513479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8367187220902095</v>
+        <v>0.8503589546990444</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.7864274238623349</v>
+        <v>0.8129909497908511</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7378118937190112</v>
+        <v>0.7764600076873178</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.6918457719220593</v>
+        <v>0.7409792133386249</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.6486182523825925</v>
+        <v>0.7068253360544405</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.608383057920596</v>
+        <v>0.6741948941545413</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.571105333397828</v>
+        <v>0.643142168620027</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.5369562412061231</v>
+        <v>0.6135779019910447</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5058253851811065</v>
+        <v>0.5856601694094432</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.4780003690667221</v>
+        <v>0.5594616026793855</v>
       </c>
       <c r="O48" s="2" t="n">
+        <v>0.5347809281701855</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0.5117909068001266</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0.4905645083415359</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0.4711609998268694</v>
+      </c>
+      <c r="S48" s="2" t="n">
         <v>0.4537118711400231</v>
       </c>
-      <c r="P48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
@@ -2384,39 +2788,51 @@
         <v>0.3009117955899137</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.1312547944711213</v>
+        <v>0.1519633006435085</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.09163894407812001</v>
+        <v>0.1079113763941087</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.07466934589439193</v>
+        <v>0.08720732714641261</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.06571582737082768</v>
+        <v>0.07547728055219156</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.06059354891620095</v>
+        <v>0.06815267638391176</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.05763976482606604</v>
+        <v>0.06333153040060037</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.05609774057576191</v>
+        <v>0.06009085172263932</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.05556606751348679</v>
+        <v>0.05794046605351349</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.05586177064312022</v>
+        <v>0.05657548897759065</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.05687360435199427</v>
+        <v>0.05581207055463994</v>
       </c>
       <c r="O49" s="2" t="n">
+        <v>0.05556200340151933</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>0.05574366225286662</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0.05631517545884135</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0.05725981928560088</v>
+      </c>
+      <c r="S49" s="2" t="n">
         <v>0.05857117009930012</v>
       </c>
-      <c r="P49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
@@ -2431,42 +2847,54 @@
       </c>
       <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>0.6236363636363637</v>
+        <v>0.6306666666666667</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5972727272727273</v>
+        <v>0.6113333333333334</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.5709090909090909</v>
+        <v>0.592</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.5445454545454546</v>
+        <v>0.5726666666666667</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.4918181818181818</v>
+        <v>0.534</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4654545454545455</v>
+        <v>0.5146666666666667</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.4390909090909091</v>
+        <v>0.4953333333333333</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.4127272727272727</v>
+        <v>0.476</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.4566666666666667</v>
       </c>
       <c r="N50" s="2" t="n">
+        <v>0.4373333333333334</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0.3986666666666667</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0.3793333333333334</v>
+      </c>
+      <c r="R50" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="O50" s="2" t="n">
-        <v>0.3336363636363636</v>
-      </c>
-      <c r="P50" s="1" t="inlineStr"/>
+      <c r="S50" s="2" t="n">
+        <v>0.3406666666666666</v>
+      </c>
+      <c r="T50" s="1" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
@@ -2481,42 +2909,54 @@
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="N51" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="R51" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
-      <c r="O51" s="2" t="n">
-        <v>102.2757583376915</v>
-      </c>
-      <c r="P51" s="1" t="inlineStr"/>
+      <c r="S51" s="2" t="n">
+        <v>104.4308878503476</v>
+      </c>
+      <c r="T51" s="1" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
@@ -2531,42 +2971,54 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6470187781110718</v>
+        <v>0.6542834231611319</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.586173210716883</v>
+        <v>0.6083435839546485</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.5340840464310409</v>
+        <v>0.5676271902575042</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.4889237180942501</v>
+        <v>0.5311229686801958</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.4492521137640234</v>
+        <v>0.498139622561141</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4141235259565256</v>
+        <v>0.4681964345049069</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3827019947765132</v>
+        <v>0.4407596410267861</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.3546465340521764</v>
+        <v>0.4155715601725339</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.3295241151493359</v>
+        <v>0.3924301121422687</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3071447039852674</v>
+        <v>0.371181142194238</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2874041760296047</v>
+        <v>0.3515648108563043</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.2702406194692441</v>
-      </c>
-      <c r="P52" s="1" t="inlineStr"/>
+        <v>0.3335057311090038</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0.3169488695787482</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0.3018353833969528</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0.2881547528997792</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0.2758920486866353</v>
+      </c>
+      <c r="T52" s="1" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
@@ -2581,42 +3033,54 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.8518815630867524</v>
+        <v>0.857792072117288</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.7980928600064215</v>
+        <v>0.8185252274697533</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.7461548093475975</v>
+        <v>0.7801718219804457</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.697097433111779</v>
+        <v>0.7430401602428608</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.6510781569448195</v>
+        <v>0.7073740915602904</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.6082361540873048</v>
+        <v>0.6733637173071654</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5683324138660786</v>
+        <v>0.6409035082100051</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.5315580405223252</v>
+        <v>0.610025403696271</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.4977046335060994</v>
+        <v>0.5808285652718341</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.4668911352930197</v>
+        <v>0.5533778161398634</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.439236548039308</v>
+        <v>0.5274414228456362</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>0.4148482593599832</v>
-      </c>
-      <c r="P53" s="1" t="inlineStr"/>
+        <v>0.5031171631548509</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0.4804625280747954</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0.4594949713057526</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0.4403021559506097</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0.4229272680516111</v>
+      </c>
+      <c r="T53" s="1" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
@@ -2631,42 +3095,54 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2743520218633287</v>
+        <v>0.2724616335565606</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1201125559303119</v>
+        <v>0.1379177624098988</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.08421335092644007</v>
+        <v>0.09816555592580541</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.06891030788799436</v>
+        <v>0.07954151364221926</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.06094200283320824</v>
+        <v>0.06903924748959318</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.05648887770844104</v>
+        <v>0.06252706844095968</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.05400111276892245</v>
+        <v>0.05822474737954209</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.05285615546139544</v>
+        <v>0.05538843076547833</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.05272852012561755</v>
+        <v>0.0535578893703248</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.05344840716338015</v>
+        <v>0.05246103075803894</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.05494609946622748</v>
+        <v>0.05196040341182012</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.05723387284064647</v>
-      </c>
-      <c r="P54" s="1" t="inlineStr"/>
+        <v>0.05195847081933057</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0.05239292757930168</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0.05323751027373903</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0.05448237155483682</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0.05614055729666342</v>
+      </c>
+      <c r="T54" s="1" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
@@ -2681,42 +3157,54 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.496259530291237</v>
+        <v>0.5014648337358059</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.8185445247137505</v>
+        <v>0.7880983118324816</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.8767216867967569</v>
+        <v>0.8545818074176159</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9003793199997074</v>
+        <v>0.8840112219416179</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9124550510696275</v>
+        <v>0.9001825839829652</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.9191345262736552</v>
+        <v>0.9100656977821977</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9228450067431002</v>
+        <v>0.9165365938680218</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.9245476971002226</v>
+        <v>0.9207776778035037</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.9247373120971561</v>
+        <v>0.923504506091347</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9236673388761331</v>
+        <v>0.9251345681110075</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9214373268864954</v>
+        <v>0.9258776058992364</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.9180204543028089</v>
-      </c>
-      <c r="P55" s="1" t="inlineStr"/>
+        <v>0.9258804731233909</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0.925235682823888</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0.9239809247449741</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0.9221283780829891</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0.9196549445310657</v>
+      </c>
+      <c r="T55" s="1" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
@@ -2731,42 +3219,54 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7914114817012881</v>
+        <v>0.7928308206805679</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9175642260339907</v>
+        <v>0.9040007107409713</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9436523966497012</v>
+        <v>0.9334492683903225</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9544615921341284</v>
+        <v>0.9468052533979796</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.9600071988288605</v>
+        <v>0.9542146537324381</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.9630603322341956</v>
+        <v>0.9587578860438596</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9647162909970507</v>
+        <v>0.9617271470303008</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.9654026903433606</v>
+        <v>0.9636562672173354</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.9653300977116198</v>
+        <v>0.9648679757288272</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.9645907141301797</v>
+        <v>0.9655488057857011</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.9631964275673923</v>
+        <v>0.9657893502438822</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0.961087937215221</v>
-      </c>
-      <c r="P56" s="1" t="inlineStr"/>
+        <v>0.965648737702872</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0.965158885640413</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0.9643233907451992</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0.9631302347305716</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0.9615464092563861</v>
+      </c>
+      <c r="T56" s="1" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
@@ -2781,42 +3281,54 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2803314260408126</v>
+        <v>0.2813905009471096</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.3458492759403646</v>
+        <v>0.3406864454900046</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.351047131535497</v>
+        <v>0.3505989984212221</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.3474108361019247</v>
+        <v>0.3510039443043173</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.3409913965417674</v>
+        <v>0.3480432983113403</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.333471026166709</v>
+        <v>0.3435662483967508</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.325570138399774</v>
+        <v>0.3383531120609656</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.3176637807777642</v>
+        <v>0.3327431785133318</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.3100444252741181</v>
+        <v>0.3269564786201302</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.3029957910776013</v>
+        <v>0.3211507631297974</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2968234119960466</v>
+        <v>0.3154373206322919</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.2918471447312225</v>
-      </c>
-      <c r="P57" s="1" t="inlineStr"/>
+        <v>0.3099364446129152</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0.3047605865011777</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0.3000239632844169</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0.2958573094930009</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0.2923912427959964</v>
+      </c>
+      <c r="T57" s="1" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
@@ -2831,42 +3343,54 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.148349100413499</v>
+        <v>1.151124118776815</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1.045925568107925</v>
+        <v>1.062377799270185</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1.019499110376512</v>
+        <v>1.036111103650193</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.002915226818822</v>
+        <v>1.020924488333052</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.9887803620450216</v>
+        <v>1.00933013835935</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.9749630666974607</v>
+        <v>0.9990872116840966</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9604281068418332</v>
+        <v>0.9892213184073614</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.9444996836152652</v>
+        <v>0.9792785544438508</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.9265219325482024</v>
+        <v>0.9689278286328695</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.9057489472864968</v>
+        <v>0.9578925859460624</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.8812882212871602</v>
+        <v>0.9459345018896737</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.8521100845146086</v>
-      </c>
-      <c r="P58" s="1" t="inlineStr"/>
+        <v>0.9327737435617988</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0.9181114109748046</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0.9016138797803057</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0.8828878938189587</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0.861508375559446</v>
+      </c>
+      <c r="T58" s="1" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
@@ -2881,42 +3405,54 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6559785963090488</v>
+        <v>0.6625199647544942</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6246063457694964</v>
+        <v>0.6427672737493952</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.5757065070246412</v>
+        <v>0.6072415102197469</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5294507601125176</v>
+        <v>0.5714268310718572</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.4872531702268296</v>
+        <v>0.5374786818095514</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.4489353796842664</v>
+        <v>0.5057932110432251</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4139239072289042</v>
+        <v>0.47618307218868</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.3819733439588067</v>
+        <v>0.4485318823583244</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.3526664394879173</v>
+        <v>0.4227163777367752</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.3258102099036672</v>
+        <v>0.398621249447761</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3012816010392996</v>
+        <v>0.3759868888716454</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.278992643690011</v>
-      </c>
-      <c r="P59" s="1" t="inlineStr"/>
+        <v>0.3547415725698023</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0.3348255417836918</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0.3161665993594145</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0.2987406862253892</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0.2825170054424779</v>
+      </c>
+      <c r="T59" s="1" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
@@ -2931,42 +3467,54 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2720258280079406</v>
+        <v>0.2703888904097833</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.1150773962795963</v>
+        <v>0.1330636745304504</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.07972938889514986</v>
+        <v>0.09367204543933282</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.06479319133468478</v>
+        <v>0.07539032965061968</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.0570642191435431</v>
+        <v>0.06513631074733642</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.05278992205645663</v>
+        <v>0.0588093073356333</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.05046595153123931</v>
+        <v>0.05465801146599711</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.04950148906418269</v>
+        <v>0.05195404749581219</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.04960352169899662</v>
+        <v>0.05025287775359496</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.05064232585954236</v>
+        <v>0.04929609311682435</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.05259907661212716</v>
+        <v>0.04895788964246673</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0.05555276895854432</v>
-      </c>
-      <c r="P60" s="1" t="inlineStr"/>
+        <v>0.0491555999156828</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0.04984413858227942</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0.05101770853810567</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0.05269190168912224</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0.05491106614839087</v>
+      </c>
+      <c r="T60" s="1" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
@@ -2981,42 +3529,54 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.1150773962795963</v>
+        <v>0.1330636745304504</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.07972938889514986</v>
+        <v>0.09367204543933282</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.06479319133468478</v>
+        <v>0.07539032965061968</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0570642191435431</v>
+        <v>0.06513631074733642</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.05278992205645663</v>
+        <v>0.0588093073356333</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.05046595153123931</v>
+        <v>0.05465801146599711</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.04950148906418269</v>
+        <v>0.05195404749581219</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.04960352169899662</v>
+        <v>0.05025287775359496</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.05064232585954236</v>
+        <v>0.04929609311682435</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.05259907661212716</v>
+        <v>0.04895788964246673</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.05555276895854432</v>
+        <v>0.0491555999156828</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0.05850646130496148</v>
-      </c>
-      <c r="P61" s="1" t="inlineStr"/>
+        <v>0.04984413858227942</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>0.05101770853810567</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0.05269190168912224</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0.05491106614839087</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0.0571302306076595</v>
+      </c>
+      <c r="T61" s="1" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
@@ -3031,42 +3591,54 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5026572059935642</v>
+        <v>0.5071108561666231</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.8269511580466603</v>
+        <v>0.7965140112015372</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8837192378835317</v>
+        <v>0.8617743749479074</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.9066387713518712</v>
+        <v>0.8904383054002251</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.9182742747166943</v>
+        <v>0.9061187619707659</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9246460982700778</v>
+        <v>0.9156600723535896</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9280921528761098</v>
+        <v>0.9218666989701296</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.9295185361489017</v>
+        <v>0.9258870356012644</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.929367739431411</v>
+        <v>0.9284074650572826</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.9278310684452963</v>
+        <v>0.9298220220603441</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9249295736201615</v>
+        <v>0.9303215240383296</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0.9205324796666424</v>
-      </c>
-      <c r="P62" s="1" t="inlineStr"/>
+        <v>0.9300295528929712</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0.9290120284804108</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0.9272751500372671</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0.924791705252773</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0.9214895519254134</v>
+      </c>
+      <c r="T62" s="1" t="inlineStr"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
@@ -3081,42 +3653,54 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.7805596092214843</v>
+        <v>0.7812692787111242</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.8500880382586702</v>
+        <v>0.8415346025519874</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.8700959893287561</v>
+        <v>0.8612182742485085</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.8829499081275562</v>
+        <v>0.8731242885411294</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.893631259906112</v>
+        <v>0.8823152419384261</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.9034997827061337</v>
+        <v>0.8903210003931722</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.9130779445472598</v>
+        <v>0.8977774341433087</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.9225551907029824</v>
+        <v>0.9049413955601958</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.9320133967247826</v>
+        <v>0.911964394567677</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.9414763041919105</v>
+        <v>0.9189300869256287</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.9509286079025953</v>
+        <v>0.9258744305663087</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0.9603205495816369</v>
-      </c>
-      <c r="P63" s="1" t="inlineStr"/>
+        <v>0.9328179458511794</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0.9397678586145239</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0.9467175567284032</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0.9536529499680431</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0.9605497856022194</v>
+      </c>
+      <c r="T63" s="1" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
@@ -3131,42 +3715,54 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4951608024475138</v>
+        <v>0.4947110208887889</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.4796111464536851</v>
+        <v>0.4777305805592196</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.4933697911469953</v>
+        <v>0.4850371337997327</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.511158425729244</v>
+        <v>0.4966647621618928</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.5303221251053101</v>
+        <v>0.5098407336349193</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5501351231747619</v>
+        <v>0.5237673633405326</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5702552370692163</v>
+        <v>0.5381108674808632</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.5904530661631379</v>
+        <v>0.5527131589300166</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.6105143851335061</v>
+        <v>0.5674653458784754</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.630205686088978</v>
+        <v>0.5822740841432794</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6492618491206571</v>
+        <v>0.5970601655016087</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.6674038058680815</v>
-      </c>
-      <c r="P64" s="1" t="inlineStr"/>
+        <v>0.6117280265373947</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0.6261851294940463</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0.6403325756029661</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0.654056504878885</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0.6672445293840594</v>
+      </c>
+      <c r="T64" s="1" t="inlineStr"/>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
@@ -3184,39 +3780,51 @@
         <v>0.9130337357818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8748613108903142</v>
+        <v>0.8850333252548149</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8367019754879613</v>
+        <v>0.8570611050841739</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.7984417849023867</v>
+        <v>0.8290571204324678</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.760052506592651</v>
+        <v>0.8009973827639962</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7215557875774173</v>
+        <v>0.7728646278053329</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6830253822830016</v>
+        <v>0.7446612304027046</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.6445808950740264</v>
+        <v>0.7164166267770026</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6063535228830391</v>
+        <v>0.6881619377878848</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.5684827367765299</v>
+        <v>0.6599421408215783</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.5311064742865111</v>
+        <v>0.6318065171944226</v>
       </c>
       <c r="O65" s="2" t="n">
+        <v>0.6038156496800842</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0.5760225971805022</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0.5484793863228254</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0.521237818635248</v>
+      </c>
+      <c r="S65" s="2" t="n">
         <v>0.4943374292495647</v>
       </c>
-      <c r="P65" s="1" t="inlineStr"/>
+      <c r="T65" s="1" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
@@ -3231,42 +3839,54 @@
       </c>
       <c r="C66" s="1" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>0.6368181818181818</v>
+        <v>0.6403333333333334</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.6104545454545455</v>
+        <v>0.621</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.5840909090909091</v>
+        <v>0.6016666666666667</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.5577272727272727</v>
+        <v>0.5823333333333334</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.5313636363636364</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I66" s="2" t="n">
+        <v>0.5436666666666667</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.5243333333333333</v>
+      </c>
+      <c r="K66" s="2" t="n">
         <v>0.505</v>
       </c>
-      <c r="J66" s="2" t="n">
-        <v>0.4786363636363636</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>0.4522727272727273</v>
-      </c>
       <c r="L66" s="2" t="n">
-        <v>0.4259090909090909</v>
+        <v>0.4856666666666667</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.3995454545454545</v>
+        <v>0.4663333333333333</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3731818181818182</v>
+        <v>0.447</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>0.3468181818181818</v>
-      </c>
-      <c r="P66" s="1" t="inlineStr"/>
+        <v>0.4276666666666667</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0.4083333333333333</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0.3696666666666667</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0.3503333333333333</v>
+      </c>
+      <c r="T66" s="1" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
@@ -3281,42 +3901,54 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.149470499626858</v>
+        <v>1.150011517879318</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.025328281506466</v>
+        <v>1.040856798279222</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.9979591178031184</v>
+        <v>1.012030332275313</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9828268660091499</v>
+        <v>0.9969084778913009</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.9710736479752523</v>
+        <v>0.9863173959023402</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.9602502514475583</v>
+        <v>0.9775792957002311</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9492481850610934</v>
+        <v>0.9695621110230351</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.9374216670208639</v>
+        <v>0.9617625261085604</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.924196142381593</v>
+        <v>0.9538345017902922</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9089535843846798</v>
+        <v>0.9455090296099077</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.8909761330468265</v>
+        <v>0.9365735498767322</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.8694555233106508</v>
-      </c>
-      <c r="P67" s="1" t="inlineStr"/>
+        <v>0.9267867253069327</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>0.9159009995558133</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0.9036486123004409</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0.889715679701415</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0.8737700314689053</v>
+      </c>
+      <c r="T67" s="1" t="inlineStr"/>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
@@ -3331,42 +3963,54 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9098923318704959</v>
+        <v>0.9129976966874244</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.9048592082754372</v>
+        <v>0.9150619818429163</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.8693990341364447</v>
+        <v>0.8923130416932181</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8289382873161977</v>
+        <v>0.8646283651232153</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.7863791607528087</v>
+        <v>0.834907678720365</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.7426475977563408</v>
+        <v>0.8040381898895175</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6982710232411901</v>
+        <v>0.7724311182350889</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.6536474291487642</v>
+        <v>0.740318990147195</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.6091291160368223</v>
+        <v>0.7078819770274036</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.5650394600392833</v>
+        <v>0.675279039199588</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.5216678776691375</v>
+        <v>0.6426482553515347</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.4792458653577785</v>
-      </c>
-      <c r="P68" s="1" t="inlineStr"/>
+        <v>0.6101300308937273</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>0.5778478490882533</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0.5459136371160284</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0.5144310989034653</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0.4834821947991647</v>
+      </c>
+      <c r="T68" s="1" t="inlineStr"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
@@ -3381,42 +4025,54 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2364367638450576</v>
+        <v>0.2369777820975177</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1504669706161518</v>
+        <v>0.1558234730244067</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1612571423151571</v>
+        <v>0.1549692271911389</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1843850811067632</v>
+        <v>0.1678513574588331</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.2110211413826013</v>
+        <v>0.185320013138344</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2386944638701409</v>
+        <v>0.2047146678948981</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2662228027780918</v>
+        <v>0.2249008806203305</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.2928407719468376</v>
+        <v>0.2453458993315578</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.3178426194985539</v>
+        <v>0.2656725640024074</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.3404708476081498</v>
+        <v>0.2855668887883294</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3598696587603154</v>
+        <v>0.3047670326823096</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3751180940610861</v>
-      </c>
-      <c r="P69" s="1" t="inlineStr"/>
+        <v>0.3229710756268486</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>0.3398784023753111</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0.3551692259776155</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0.368477861066167</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0.3794326022193406</v>
+      </c>
+      <c r="T69" s="1" t="inlineStr"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
@@ -3431,42 +4087,54 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.238456768543003</v>
+        <v>0.2381264220893905</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1410663598324875</v>
+        <v>0.1473158174272687</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.1501000762400676</v>
+        <v>0.1437980619569752</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.1739769395026247</v>
+        <v>0.1562961232098367</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.202401201292213</v>
+        <v>0.1744224596389855</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.2323154689411199</v>
+        <v>0.1950490217945792</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2621570836006432</v>
+        <v>0.2167902001722725</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.290852254466501</v>
+        <v>0.2389595642966558</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.3173928165113801</v>
+        <v>0.2610458516054659</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.3407094872472135</v>
+        <v>0.2826135467464744</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3596203436180228</v>
+        <v>0.303286246538139</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.37286421915683</v>
-      </c>
-      <c r="P70" s="1" t="inlineStr"/>
+        <v>0.3226437126680715</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>0.3402635618865514</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0.3557002426642774</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0.3684567949154934</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0.3780261807602814</v>
+      </c>
+      <c r="T70" s="1" t="inlineStr"/>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
@@ -3484,39 +4152,51 @@
         <v>251.7894146864385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.1024900209453</v>
+        <v>249.8009621686911</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>246.6107242604538</v>
+        <v>247.9136892966872</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>244.3372984316917</v>
+        <v>246.1387065941966</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>242.2923887858165</v>
+        <v>244.4815971910143</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>240.4769672604629</v>
+        <v>242.9479317023808</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>238.8781441276591</v>
+        <v>241.539700983277</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>237.4656501333595</v>
+        <v>240.2521702422908</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>236.1969574055916</v>
+        <v>239.0793762629544</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>235.0144241906794</v>
+        <v>238.0101114191572</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>233.8442343661209</v>
+        <v>237.0296181915506</v>
       </c>
       <c r="O71" s="2" t="n">
+        <v>236.116342046438</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>235.2469960755472</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>234.3939168165112</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>233.5237985627082</v>
+      </c>
+      <c r="S71" s="2" t="n">
         <v>232.6016263665796</v>
       </c>
-      <c r="P71" s="1" t="inlineStr"/>
+      <c r="T71" s="1" t="inlineStr"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
@@ -3531,42 +4211,54 @@
       </c>
       <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>196.2932833273169</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>190.3666771675124</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>184.4400710077079</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>178.5134648479034</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>172.5868586880989</v>
       </c>
       <c r="I72" s="2" t="n">
+        <v>166.6602525282945</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>160.73364636849</v>
+      </c>
+      <c r="K72" s="2" t="n">
         <v>154.8070402086856</v>
       </c>
-      <c r="J72" s="2" t="n">
-        <v>146.7253045362249</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>138.6435688637643</v>
-      </c>
       <c r="L72" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>148.8804340488811</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>142.9538278890766</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>137.0272217292722</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>106.3166261739218</v>
-      </c>
-      <c r="P72" s="1" t="inlineStr"/>
+        <v>131.1006155694677</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>125.1740094096633</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>119.2474032498588</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>113.3207970900543</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>107.3941909302498</v>
+      </c>
+      <c r="T72" s="1" t="inlineStr"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
@@ -3581,42 +4273,54 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>247.28452908</v>
+        <v>248.0517603648712</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>237.9815544364363</v>
+        <v>240.1798960230389</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>234.3795941484085</v>
+        <v>236.9094723022859</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>231.9142224061601</v>
+        <v>234.6224489396598</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>230.133866067011</v>
+        <v>232.837041863052</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>228.9229812149858</v>
+        <v>231.4199672453222</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>228.2261602651597</v>
+        <v>230.3175196216195</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>227.999923292236</v>
+        <v>229.5057972508388</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>228.1937458904654</v>
+        <v>228.967182502565</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>228.7427276681898</v>
+        <v>228.68399545452</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>229.5649111126124</v>
+        <v>228.6387798288928</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>230.5666674764105</v>
-      </c>
-      <c r="P73" s="1" t="inlineStr"/>
+        <v>228.8072540849443</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>229.1630518688698</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>229.6756518894332</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>230.3082587879495</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>231.0222911287899</v>
+      </c>
+      <c r="T73" s="1" t="inlineStr"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
@@ -3634,39 +4338,51 @@
         <v>0.9198717705829682</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.9343717516022703</v>
+        <v>0.930908005417769</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.9456738513371452</v>
+        <v>0.9399111885257418</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9544810706406721</v>
+        <v>0.9475445209109083</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.9616684573121036</v>
+        <v>0.9539515543452253</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.9675039353435879</v>
+        <v>0.9594117104066201</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9723363601852713</v>
+        <v>0.9641351229571883</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.9763162299517529</v>
+        <v>0.9682321979656086</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.9796348119488701</v>
+        <v>0.9717447196250987</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.9823328970460875</v>
+        <v>0.9748160838275998</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9845454709023621</v>
+        <v>0.9775237620338982</v>
       </c>
       <c r="O74" s="2" t="n">
+        <v>0.9798313148293836</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>0.9818335545120593</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0.9835696379292527</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0.985061197937973</v>
+      </c>
+      <c r="S74" s="2" t="n">
         <v>0.9863414798135992</v>
       </c>
-      <c r="P74" s="1" t="inlineStr"/>
+      <c r="T74" s="1" t="inlineStr"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
@@ -3684,39 +4400,51 @@
         <v>264.9230699278949</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>302.9393809956259</v>
+        <v>292.8257431134205</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>340.8533627745312</v>
+        <v>320.6211333531855</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>378.5964068562916</v>
+        <v>348.3910958285558</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>416.2762214324989</v>
+        <v>376.0830772634475</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>453.842488535186</v>
+        <v>403.716948421949</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>491.324598928213</v>
+        <v>431.3112687519726</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>528.6950671020987</v>
+        <v>458.8596591757861</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>565.9717639113386</v>
+        <v>486.3331263978957</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>603.1078831527154</v>
+        <v>513.7606689161634</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>640.1237707477241</v>
+        <v>541.1500239054108</v>
       </c>
       <c r="O75" s="2" t="n">
+        <v>568.451073262972</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>595.6894595592446</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>622.8656529904968</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>649.9727208113966</v>
+      </c>
+      <c r="S75" s="2" t="n">
         <v>677.0139991251236</v>
       </c>
-      <c r="P75" s="1" t="inlineStr"/>
+      <c r="T75" s="1" t="inlineStr"/>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
@@ -3734,39 +4462,51 @@
         <v>298.0389802067385</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>318.6014723186276</v>
+        <v>313.2520727793622</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>337.8060659838801</v>
+        <v>327.7376828837337</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>355.9464532230144</v>
+        <v>341.5359363918575</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>373.082946582965</v>
+        <v>354.7685386161718</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>389.395436741228</v>
+        <v>367.4838532828871</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>404.9335931204457</v>
+        <v>379.7080435764382</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>419.8160494160329</v>
+        <v>391.4857966451933</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>434.0589954920686</v>
+        <v>402.9017712038968</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>447.8214368375179</v>
+        <v>413.9364337923426</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>461.0892039392522</v>
+        <v>424.589106731691</v>
       </c>
       <c r="O76" s="2" t="n">
+        <v>434.9928791022549</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>445.1113929581084</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>454.9549308573855</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>464.550991329953</v>
+      </c>
+      <c r="S76" s="2" t="n">
         <v>473.8913655885228</v>
       </c>
-      <c r="P76" s="1" t="inlineStr"/>
+      <c r="T76" s="1" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
@@ -3784,39 +4524,51 @@
         <v>0.8448204141343578</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7818623316712811</v>
+        <v>0.7974439241608384</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7300363998561882</v>
+        <v>0.7564393789426883</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.6864439755454026</v>
+        <v>0.7206817215035083</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6494330309250312</v>
+        <v>0.6891298708297292</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.6175649341783925</v>
+        <v>0.6611118543904044</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5899193057480068</v>
+        <v>0.6361195267506974</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.5656421436571468</v>
+        <v>0.6136931973039962</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.5441586509175513</v>
+        <v>0.5933937087160716</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5247949402563977</v>
+        <v>0.5749919359322656</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5071561692798375</v>
+        <v>0.5582564753394292</v>
       </c>
       <c r="O77" s="2" t="n">
+        <v>0.5428050742663618</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>0.5285126370550741</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0.515202497915088</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0.5026871170679411</v>
+      </c>
+      <c r="S77" s="2" t="n">
         <v>0.4908332230905137</v>
       </c>
-      <c r="P77" s="1" t="inlineStr"/>
+      <c r="T77" s="1" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
@@ -3831,42 +4583,54 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7739140879000126</v>
+        <v>0.7762805497595007</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7025688677305478</v>
+        <v>0.7195874767764773</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.6567734946088818</v>
+        <v>0.6820840866459945</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6201103319267046</v>
+        <v>0.6511333780898241</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.5896922001548817</v>
+        <v>0.6245130036369227</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.5641990975072881</v>
+        <v>0.6013365331651109</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5425314394305585</v>
+        <v>0.5808623041953515</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.5242135535589888</v>
+        <v>0.5627532946453329</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5085612696312135</v>
+        <v>0.5467519525118658</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.4951412220693632</v>
+        <v>0.5326486714454499</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.4835545192846229</v>
+        <v>0.5200619476864727</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0.4733931316860104</v>
-      </c>
-      <c r="P78" s="1" t="inlineStr"/>
+        <v>0.5088274897180355</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>0.4987969665535941</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0.4897888944330698</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0.4816627856862081</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>0.4742546645343235</v>
+      </c>
+      <c r="T78" s="1" t="inlineStr"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
@@ -3884,39 +4648,51 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>342.7216074711233</v>
+        <v>332.5412301095225</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>380.5533143746371</v>
+        <v>360.3157523649842</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>418.299782629001</v>
+        <v>387.9652287313608</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>455.8623617326095</v>
+        <v>415.5484181640575</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>493.3043052802819</v>
+        <v>443.0550461864155</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>530.8455851254013</v>
+        <v>470.7121634428254</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>568.2640128064211</v>
+        <v>498.295226716079</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>605.4888593452233</v>
+        <v>525.8469279503316</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>642.5848324826002</v>
+        <v>553.3116738158444</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>679.4541857759853</v>
+        <v>580.6553434530979</v>
       </c>
       <c r="O79" s="2" t="n">
+        <v>607.9683068286746</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>635.1835141618287</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>662.2781021930996</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>689.2438426770293</v>
+      </c>
+      <c r="S79" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="P79" s="1" t="inlineStr"/>
+      <c r="T79" s="1" t="inlineStr"/>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
@@ -3931,42 +4707,54 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.9006486075029659</v>
+        <v>0.899977269938159</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9186155927206895</v>
+        <v>0.9142175178994719</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.9290813257877711</v>
+        <v>0.9232442532169893</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.9371529110515402</v>
+        <v>0.9302787318018001</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.9434956981360756</v>
+        <v>0.9360793185234136</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.9486821920661557</v>
+        <v>0.9410173094649702</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9529306488556853</v>
+        <v>0.9452875433583487</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.9565028945546096</v>
+        <v>0.9488894882232354</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.959398073182831</v>
+        <v>0.9520408323758175</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0.9618447489108495</v>
+        <v>0.9548516589638915</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9639490928348131</v>
+        <v>0.9572118925929692</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>0.9657748293183122</v>
-      </c>
-      <c r="P80" s="1" t="inlineStr"/>
+        <v>0.9592846729101582</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0.9611226909214362</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0.9627508999351054</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0.9642306135656683</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>0.9655692914167171</v>
+      </c>
+      <c r="T80" s="1" t="inlineStr"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
@@ -3981,42 +4769,54 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>618.1953492286352</v>
+        <v>617.7345504699753</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>630.527691286045</v>
+        <v>627.50890085281</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>637.711255946491</v>
+        <v>633.7047532035713</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>643.2515037516795</v>
+        <v>638.5331423324183</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>647.6051234032751</v>
+        <v>642.5146015876995</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>651.1650760858951</v>
+        <v>645.9039845381343</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>654.0811703393106</v>
+        <v>648.835026357345</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>656.5331206992845</v>
+        <v>651.3073618998652</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>658.5203396304444</v>
+        <v>653.4704100439648</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>660.1997110784556</v>
+        <v>655.3997306577534</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>661.6441097219828</v>
+        <v>657.0197691949074</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>662.8972752669174</v>
-      </c>
-      <c r="P81" s="1" t="inlineStr"/>
+        <v>658.4425029241156</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>659.7040983753325</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>660.8216832263357</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>661.8373424712217</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>662.756196300273</v>
+      </c>
+      <c r="T81" s="1" t="inlineStr"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
@@ -4031,42 +4831,54 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>455.2023097056071</v>
+        <v>455.0427848274916</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>459.5459468369926</v>
+        <v>458.53212630562</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>462.0107673069759</v>
+        <v>460.6914080781864</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>463.8696816901759</v>
+        <v>462.3222412482408</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>465.2449251931451</v>
+        <v>463.6529326277467</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>466.2991149814897</v>
+        <v>464.7411309225139</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>467.0828615584704</v>
+        <v>465.6208778462529</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>467.662357643633</v>
+        <v>466.3341273542305</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>468.0735522884636</v>
+        <v>466.9342937553715</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>468.4011802428435</v>
+        <v>467.3958738720804</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>468.6286750273001</v>
+        <v>467.7481611448815</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>468.7767936030652</v>
-      </c>
-      <c r="P82" s="1" t="inlineStr"/>
+        <v>468.0650064081697</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>468.3166901067456</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>468.51200318471</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>468.660793575957</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>468.7633708704671</v>
+      </c>
+      <c r="T82" s="1" t="inlineStr"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
@@ -4081,42 +4893,54 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.5432409366286526</v>
+        <v>0.545117445294531</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5178623727930555</v>
+        <v>0.5238016754859934</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.5073033157096933</v>
+        <v>0.5142476463595752</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.4999555512253943</v>
+        <v>0.5074868306274732</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.4946509969377347</v>
+        <v>0.5021795948608611</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4909359118643687</v>
+        <v>0.4979545640515015</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4886202835695136</v>
+        <v>0.4946460319540695</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.4875310564678288</v>
+        <v>0.4921488344697206</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.4875168545088711</v>
+        <v>0.490362746032361</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.4883478891953212</v>
+        <v>0.4892726021734364</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4898652672059366</v>
+        <v>0.4888074370389106</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>0.4918474434373172</v>
-      </c>
-      <c r="P83" s="1" t="inlineStr"/>
+        <v>0.4888364884201919</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>0.4893335144998476</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0.4902236235746643</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0.4914178056812916</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>0.4928334965673503</v>
+      </c>
+      <c r="T83" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -433,17 +433,16 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -538,11 +537,6 @@
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Ступень 16</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>СА</t>
         </is>
@@ -578,7 +572,6 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr"/>
-      <c r="T2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -610,7 +603,6 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
-      <c r="T3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -642,7 +634,6 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr"/>
-      <c r="T4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -674,7 +665,6 @@
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr"/>
-      <c r="T5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -706,7 +696,6 @@
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
-      <c r="T6" s="1" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -738,7 +727,6 @@
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr"/>
-      <c r="T7" s="1" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -767,8 +755,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
-      <c r="T8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>477.1612274741949</v>
       </c>
     </row>
@@ -799,8 +786,7 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
-      <c r="S9" s="1" t="inlineStr"/>
-      <c r="T9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>0.9595531619480527</v>
       </c>
     </row>
@@ -831,9 +817,8 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
-      <c r="T10" s="2" t="n">
-        <v>107.3941909302498</v>
+      <c r="S10" s="2" t="n">
+        <v>107.1825264245426</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -863,8 +848,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
-      <c r="T11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>0.4537118711400231</v>
       </c>
     </row>
@@ -895,9 +879,8 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
-      <c r="T12" s="2" t="n">
-        <v>0.05491106614839087</v>
+      <c r="S12" s="2" t="n">
+        <v>0.05503600366715333</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -927,8 +910,7 @@
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
-      <c r="T13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>1.570796326794897</v>
       </c>
     </row>
@@ -959,9 +941,8 @@
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
-      <c r="T14" s="2" t="n">
-        <v>0.05491106614839087</v>
+      <c r="S14" s="2" t="n">
+        <v>0.05503600366715333</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -991,9 +972,8 @@
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
-      <c r="T15" s="2" t="n">
-        <v>0.3452273254016311</v>
+      <c r="S15" s="2" t="n">
+        <v>0.3446443080405253</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1023,9 +1003,8 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
-      <c r="T16" s="2" t="n">
-        <v>0.5071108561666231</v>
+      <c r="S16" s="2" t="n">
+        <v>0.5062544510926434</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1055,9 +1034,8 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
-      <c r="T17" s="2" t="n">
-        <v>0.7928308206805679</v>
+      <c r="S17" s="2" t="n">
+        <v>0.7925571175792675</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1087,9 +1065,8 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
-      <c r="T18" s="2" t="n">
-        <v>0.861508375559446</v>
+      <c r="S18" s="2" t="n">
+        <v>0.8596778720441994</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1119,9 +1096,8 @@
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
-      <c r="T19" s="2" t="n">
-        <v>0.7092879512354505</v>
+      <c r="S19" s="2" t="n">
+        <v>0.7111184547506971</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1151,9 +1127,8 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="2" t="n">
-        <v>141.5268009329557</v>
+      <c r="S20" s="2" t="n">
+        <v>141.4703657841591</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1183,9 +1158,8 @@
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr"/>
       <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="2" t="n">
-        <v>0.919408386540464</v>
+      <c r="S21" s="2" t="n">
+        <v>0.9193151445039431</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -1215,9 +1189,8 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr"/>
       <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="2" t="n">
-        <v>0.6259083085630148</v>
+      <c r="S22" s="2" t="n">
+        <v>0.6258448319119204</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1247,9 +1220,8 @@
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr"/>
       <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="2" t="n">
-        <v>0.02743229298496425</v>
+      <c r="S23" s="2" t="n">
+        <v>0.02746403131051145</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1279,9 +1251,8 @@
       <c r="P24" s="1" t="inlineStr"/>
       <c r="Q24" s="1" t="inlineStr"/>
       <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="2" t="n">
-        <v>0.1677727845656561</v>
+      <c r="S24" s="2" t="n">
+        <v>0.168064293246209</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1300,51 +1271,48 @@
         <v>1.399944336209296</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.398030109901669</v>
+        <v>1.397925561088529</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.397119376129521</v>
+        <v>1.395818006608158</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1.395156317152682</v>
+        <v>1.39503266988259</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.393623697897493</v>
+        <v>1.393257398883002</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1.392036202062929</v>
+        <v>1.390896057070977</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.389809783724452</v>
+        <v>1.388904920518764</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1.387086457843369</v>
+        <v>1.386004386389407</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1.384896195015433</v>
+        <v>1.383337910643934</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1.382177452656831</v>
+        <v>1.380449879843793</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.378497276781724</v>
+        <v>1.376615395737872</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1.375867872658643</v>
+        <v>1.373817483070391</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>1.373209687129157</v>
+        <v>1.370798140159712</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1.370399242345619</v>
+        <v>1.367827181223123</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>1.36763080914184</v>
-      </c>
-      <c r="S25" s="2" t="n">
         <v>1.364566577433034</v>
       </c>
-      <c r="T25" s="1" t="inlineStr"/>
+      <c r="S25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
@@ -1362,51 +1330,48 @@
         <v>0.65</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.6306666666666667</v>
+        <v>0.6292857142857143</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.6113333333333334</v>
+        <v>0.6085714285714285</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.592</v>
+        <v>0.5878571428571429</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.5726666666666667</v>
+        <v>0.5671428571428572</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5464285714285715</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.534</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.5146666666666667</v>
+        <v>0.505</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.4953333333333333</v>
+        <v>0.4842857142857143</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.476</v>
+        <v>0.4635714285714286</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.4373333333333334</v>
+        <v>0.4221428571428572</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.418</v>
+        <v>0.4014285714285714</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.3986666666666667</v>
+        <v>0.3807142857142857</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.3793333333333334</v>
-      </c>
-      <c r="S26" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="T26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -1421,54 +1386,51 @@
       </c>
       <c r="C27" s="1" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>0.6306666666666667</v>
+        <v>0.6292857142857143</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.6113333333333334</v>
+        <v>0.6085714285714285</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.592</v>
+        <v>0.5878571428571429</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.5726666666666667</v>
+        <v>0.5671428571428572</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5464285714285715</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.534</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5146666666666667</v>
+        <v>0.505</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.4953333333333333</v>
+        <v>0.4842857142857143</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.476</v>
+        <v>0.4635714285714286</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4373333333333334</v>
+        <v>0.4221428571428572</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.418</v>
+        <v>0.4014285714285714</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>0.3986666666666667</v>
+        <v>0.3807142857142857</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>0.3793333333333334</v>
+        <v>0.36</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S27" s="2" t="n">
-        <v>0.3406666666666666</v>
-      </c>
-      <c r="T27" s="1" t="inlineStr"/>
+        <v>0.3392857142857142</v>
+      </c>
+      <c r="S27" s="1" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -1486,51 +1448,48 @@
         <v>100292.8790575521</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>217076.2130468525</v>
+        <v>225417.879760374</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>333859.5470361529</v>
+        <v>350542.8804631958</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>450642.8810254533</v>
+        <v>475667.8811660177</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>567426.2150147536</v>
+        <v>600792.8818688395</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>684209.5490040539</v>
+        <v>725917.8825716614</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>800992.8829933545</v>
+        <v>851042.8832744833</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>917776.2169826548</v>
+        <v>976167.8839773049</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1034559.550971955</v>
+        <v>1101292.884680127</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1151342.884961256</v>
+        <v>1226417.885382949</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1268126.218950556</v>
+        <v>1351542.886085771</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>1384909.552939856</v>
+        <v>1476667.886788592</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1501692.886929157</v>
+        <v>1601792.887491414</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>1618476.220918457</v>
+        <v>1726917.888194236</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>1735259.554907757</v>
-      </c>
-      <c r="S28" s="2" t="n">
         <v>1852042.888897058</v>
       </c>
-      <c r="T28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
@@ -1548,51 +1507,48 @@
         <v>288</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>314.5592705285711</v>
+        <v>316.4563612806118</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>341.1185410571421</v>
+        <v>344.9127225612236</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>367.6778115857131</v>
+        <v>373.3690838418355</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>394.2370821142841</v>
+        <v>401.8254451224473</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>420.7963526428552</v>
+        <v>430.2818064030591</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>447.3556231714263</v>
+        <v>458.738167683671</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>473.9148936999973</v>
+        <v>487.1945289642828</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>500.4741642285683</v>
+        <v>515.6508902448945</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>527.0334347571393</v>
+        <v>544.1072515255064</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>553.5927052857104</v>
+        <v>572.5636128061183</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>580.1519758142814</v>
+        <v>601.01997408673</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>606.7112463428525</v>
+        <v>629.4763353673419</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>633.2705168714235</v>
+        <v>657.9326966479537</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>659.8297873999945</v>
-      </c>
-      <c r="S29" s="2" t="n">
         <v>686.3890579285655</v>
       </c>
-      <c r="T29" s="1" t="inlineStr"/>
+      <c r="S29" s="1" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
@@ -1610,51 +1566,48 @@
         <v>0.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.4624883110069641</v>
+        <v>0.4648089046503187</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.4949766220139281</v>
+        <v>0.4996178093006373</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.5274649330208923</v>
+        <v>0.534426713950956</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.5599532440278563</v>
+        <v>0.5692356186012746</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.5924415550348203</v>
+        <v>0.6040445232515932</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6249298660417845</v>
+        <v>0.6388534279019119</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.6574181770487485</v>
+        <v>0.6736623325522305</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.6899064880557126</v>
+        <v>0.7084712372025492</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.7223947990626767</v>
+        <v>0.7432801418528678</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7548831100696407</v>
+        <v>0.7780890465031864</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0.7873714210766047</v>
+        <v>0.812897951153505</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.8198597320835689</v>
+        <v>0.8477068558038238</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.852348043090533</v>
+        <v>0.8825157604541425</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.8848363540974971</v>
-      </c>
-      <c r="S30" s="2" t="n">
         <v>0.9173246651044611</v>
       </c>
-      <c r="T30" s="1" t="inlineStr"/>
+      <c r="S30" s="1" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
@@ -1713,10 +1666,7 @@
       <c r="R31" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
-      <c r="S31" s="2" t="n">
-        <v>306.5485944726447</v>
-      </c>
-      <c r="T31" s="1" t="inlineStr"/>
+      <c r="S31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
@@ -1734,51 +1684,48 @@
         <v>16967.12604306373</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18522.44457042484</v>
+        <v>18630.78159248007</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20010.85352487777</v>
+        <v>20218.5607708968</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21443.52757416789</v>
+        <v>21743.63912220311</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>22826.43669504646</v>
+        <v>23213.0501078087</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24164.78508955374</v>
+        <v>24632.76848581418</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>25460.68314778449</v>
+        <v>26002.0239099061</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>26711.24295341488</v>
+        <v>27318.78381964874</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>27912.59985073472</v>
+        <v>28574.47174295057</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29057.20999885778</v>
+        <v>29758.48274205851</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>30135.06929757995</v>
+        <v>30856.11876136259</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31131.51671175844</v>
+        <v>31847.15753258983</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>32030.58870804145</v>
+        <v>32709.42570822144</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>32813.11863637829</v>
+        <v>33415.02270248366</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>33455.75153274887</v>
-      </c>
-      <c r="S32" s="2" t="n">
         <v>33933.38931404932</v>
       </c>
-      <c r="T32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
@@ -1796,51 +1743,48 @@
         <v>16797.45478263309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18151.99567901635</v>
+        <v>18258.16596063047</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>19410.52791913144</v>
+        <v>19612.0039477699</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20585.78647120117</v>
+        <v>20873.89355731498</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>21685.11486029413</v>
+        <v>22052.39760241826</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22714.89798418052</v>
+        <v>23154.80237666533</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23933.04215891742</v>
+        <v>24441.90247531174</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>25108.56837620999</v>
+        <v>25679.65679046981</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>26237.84385969064</v>
+        <v>26860.00343837353</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27313.77739892632</v>
+        <v>27972.97377753499</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>28326.96513972515</v>
+        <v>29004.75163568083</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>29263.62570905293</v>
+        <v>29936.32808063443</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>30108.75338555896</v>
+        <v>30746.86016572815</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>30844.33151819559</v>
+        <v>31410.12134033464</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>31448.40644078394</v>
-      </c>
-      <c r="S33" s="2" t="n">
         <v>31897.38595520635</v>
       </c>
-      <c r="T33" s="1" t="inlineStr"/>
+      <c r="S33" s="1" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
@@ -1858,51 +1802,48 @@
         <v>13701.87693398603</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15076.69597297022</v>
+        <v>15183.18715242576</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16380.32104836129</v>
+        <v>16585.02366398544</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>17612.45722779648</v>
+        <v>17906.52312846286</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>18768.90312231542</v>
+        <v>19142.33211474175</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19845.7876917099</v>
+        <v>20287.40656738138</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21061.22894992113</v>
+        <v>21560.80915145568</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22205.82054603481</v>
+        <v>22748.12080720581</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23267.30088055942</v>
+        <v>23831.00891765521</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24230.49891283819</v>
+        <v>24789.99333265435</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>25078.5381918534</v>
+        <v>25602.7462639698</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>25791.39094590568</v>
+        <v>26243.62718943152</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>26348.87669288917</v>
+        <v>26686.81663025726</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>26729.44485873016</v>
+        <v>26904.66888708492</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>26910.5198447063</v>
-      </c>
-      <c r="S34" s="2" t="n">
         <v>26870.38869889748</v>
       </c>
-      <c r="T34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
@@ -1920,51 +1861,48 @@
         <v>16.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>17.98195958095144</v>
+        <v>18.08373681547279</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19.19721130784214</v>
+        <v>19.35093521240871</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.28741714564764</v>
+        <v>20.56673424835787</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.31133604977339</v>
+        <v>21.65781275498967</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.2586935435603</v>
+        <v>22.64232024894013</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23.35654027139916</v>
+        <v>23.81327704394781</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>24.38033301608176</v>
+        <v>24.88456689222609</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>25.37276372176333</v>
+        <v>25.89839154897781</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.27823905870514</v>
+        <v>26.82431759468589</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>27.06263816738749</v>
+        <v>27.61009078020989</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>27.81633101439324</v>
+        <v>28.34277284468556</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>28.47226781897626</v>
+        <v>28.93863549455284</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>29.00758532167604</v>
+        <v>29.38971940023348</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>29.41405527703473</v>
-      </c>
-      <c r="S35" s="2" t="n">
         <v>29.65175826002295</v>
       </c>
-      <c r="T35" s="1" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
@@ -1982,51 +1920,48 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>332.5412301095225</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>360.3157523649842</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>387.9652287313608</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>415.5484181640575</v>
+        <v>423.4832578774369</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>443.0550461864155</v>
+        <v>452.9241266519992</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>470.7121634428254</v>
+        <v>482.5514447276188</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>498.295226716079</v>
+        <v>512.0790958565088</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>525.8469279503316</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>553.3116738158444</v>
+        <v>570.9315691201923</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>580.6553434530979</v>
+        <v>600.1737035863282</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>607.9683068286746</v>
+        <v>629.3627469314156</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>635.1835141618287</v>
+        <v>658.4149708618947</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>662.2781021930996</v>
+        <v>687.3224160481872</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>689.2438426770293</v>
-      </c>
-      <c r="S36" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="T36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
@@ -2044,51 +1979,48 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>332.5412301095225</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>360.3157523649842</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>387.9652287313608</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>415.5484181640575</v>
+        <v>423.4832578774369</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>443.0550461864155</v>
+        <v>452.9241266519992</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>470.7121634428254</v>
+        <v>482.5514447276188</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>498.295226716079</v>
+        <v>512.0790958565088</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>525.8469279503316</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>553.3116738158444</v>
+        <v>570.9315691201923</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>580.6553434530979</v>
+        <v>600.1737035863282</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>607.9683068286746</v>
+        <v>629.3627469314156</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>635.1835141618287</v>
+        <v>658.4149708618947</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>662.2781021930996</v>
+        <v>687.3224160481872</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>689.2438426770293</v>
-      </c>
-      <c r="S37" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="T37" s="1" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
@@ -2106,51 +2038,48 @@
         <v>1.175559285399187</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.176956036090575</v>
+        <v>1.177149157361195</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1.177314556774188</v>
+        <v>1.177580116958397</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.176870346260679</v>
+        <v>1.177095915781244</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.175734201092261</v>
+        <v>1.175855347567406</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.17400542811149</v>
+        <v>1.173962116210552</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.173698204745806</v>
+        <v>1.173396175963183</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.172847504293333</v>
+        <v>1.172215437821457</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.171437473220811</v>
+        <v>1.170376301404517</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.169448963439853</v>
+        <v>1.167847518639031</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.166851812849547</v>
+        <v>1.164588351389238</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1.163584415306085</v>
+        <v>1.160528026232</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>1.159616698752758</v>
+        <v>1.155630506097777</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>1.154911296973687</v>
+        <v>1.149848870725617</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>1.149431198653191</v>
-      </c>
-      <c r="S38" s="2" t="n">
         <v>1.143155604508661</v>
       </c>
-      <c r="T38" s="1" t="inlineStr"/>
+      <c r="S38" s="1" t="inlineStr"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
@@ -2168,51 +2097,48 @@
         <v>117900.225235523</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>255489.1592371767</v>
+        <v>265350.4672140714</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>393057.7046436996</v>
+        <v>412792.3261747835</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>530348.2434323351</v>
+        <v>559906.7201888376</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>667142.4075891768</v>
+        <v>706445.5229259076</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>803265.7244964738</v>
+        <v>852200.0936189106</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>940123.9087834673</v>
+        <v>998610.46481496</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1076411.545587883</v>
+        <v>1144279.063503702</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1211921.826287044</v>
+        <v>1288927.093135038</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1346436.74338179</v>
+        <v>1432269.084259004</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1479715.377504498</v>
+        <v>1573991.10153848</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>1611459.172409335</v>
+        <v>1713714.468054943</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1741388.148081287</v>
+        <v>1851080.725235523</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1869196.471422007</v>
+        <v>1985694.583576011</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>1994561.470172026</v>
-      </c>
-      <c r="S39" s="2" t="n">
         <v>2117173.208233083</v>
       </c>
-      <c r="T39" s="1" t="inlineStr"/>
+      <c r="S39" s="1" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
@@ -2230,51 +2156,48 @@
         <v>117900.225235523</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>255489.1592371767</v>
+        <v>265350.4672140714</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>393057.7046436996</v>
+        <v>412792.3261747835</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>530348.2434323351</v>
+        <v>559906.7201888376</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>667142.4075891768</v>
+        <v>706445.5229259076</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>803265.7244964738</v>
+        <v>852200.0936189106</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>940123.9087834673</v>
+        <v>998610.46481496</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1076411.545587883</v>
+        <v>1144279.063503702</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1211921.826287044</v>
+        <v>1288927.093135038</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1346436.74338179</v>
+        <v>1432269.084259004</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1479715.377504498</v>
+        <v>1573991.10153848</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1611459.172409335</v>
+        <v>1713714.468054943</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1741388.148081287</v>
+        <v>1851080.725235523</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1869196.471422007</v>
+        <v>1985694.583576011</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>1994561.470172026</v>
-      </c>
-      <c r="S40" s="2" t="n">
         <v>2117173.208233083</v>
       </c>
-      <c r="T40" s="1" t="inlineStr"/>
+      <c r="S40" s="1" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
@@ -2292,51 +2215,48 @@
         <v>310.7487734256569</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>324.6688112316239</v>
+        <v>325.6412920534009</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>338.0515793090531</v>
+        <v>339.860328445252</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>350.862209958119</v>
+        <v>353.5607325376019</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>363.2301909542014</v>
+        <v>366.6891593767065</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>375.1766092304147</v>
+        <v>379.3166107530025</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>386.7059416936959</v>
+        <v>391.5413584539659</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>397.8563095118959</v>
+        <v>403.32604206627</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>408.7173575831252</v>
+        <v>414.7702463409155</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>419.249265744434</v>
+        <v>425.8743045830093</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>429.4426618693322</v>
+        <v>436.6134499325574</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>439.4469858198541</v>
+        <v>447.1401723128121</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>449.2103721206494</v>
+        <v>457.3909295893897</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>458.739164603982</v>
+        <v>467.4010982997746</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>468.0602766896044</v>
-      </c>
-      <c r="S41" s="2" t="n">
         <v>477.1612274741949</v>
       </c>
-      <c r="T41" s="1" t="inlineStr"/>
+      <c r="S41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
@@ -2351,54 +2271,51 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.538806481394</v>
+        <v>319.5338237912142</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>333.774424617516</v>
+        <v>334.7109771300942</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>347.3317688252171</v>
+        <v>349.222944744292</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>360.3293224315304</v>
+        <v>363.0714408965355</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>372.8297737710806</v>
+        <v>376.3080358645553</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>384.842687051213</v>
+        <v>389.0522517673508</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>396.509668398383</v>
+        <v>401.3995426568525</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>407.8266612290232</v>
+        <v>413.3312413404398</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>418.7770733157024</v>
+        <v>424.8720601328997</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>429.3336446966811</v>
+        <v>435.9907411935118</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>439.6375871105478</v>
+        <v>446.8252619518367</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>449.6754965258203</v>
+        <v>457.3496598375589</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>459.4315267237035</v>
+        <v>467.5723728126169</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>468.9278472826187</v>
+        <v>477.4855413613454</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>478.1524868271428</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>487.1270825678299</v>
-      </c>
-      <c r="T42" s="1" t="inlineStr"/>
+        <v>487.112205135101</v>
+      </c>
+      <c r="S42" s="1" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
@@ -2416,51 +2333,48 @@
         <v>0.7697077367416805</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.7790684943630035</v>
+        <v>0.779758718400195</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.7889872801066945</v>
+        <v>0.7904485926897359</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.7994433236842792</v>
+        <v>0.8017518046703783</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.8104158301444142</v>
+        <v>0.8136427930868606</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.8218841147424848</v>
+        <v>0.826096176625411</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8338277212563164</v>
+        <v>0.8390869151470612</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.8462265239030562</v>
+        <v>0.8525904463163166</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.8590608134065268</v>
+        <v>0.8665827986820737</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.8723113680655563</v>
+        <v>0.8810406827362796</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.885959510888735</v>
+        <v>0.8959415617907894</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.8999871539994868</v>
+        <v>0.9112637046951794</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.9143768315886349</v>
+        <v>0.9269862224911449</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>0.9291117227116072</v>
+        <v>0.9430890910857662</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>0.9441756652055144</v>
-      </c>
-      <c r="S43" s="2" t="n">
         <v>0.9595531619480527</v>
       </c>
-      <c r="T43" s="1" t="inlineStr"/>
+      <c r="S43" s="1" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
@@ -2478,51 +2392,48 @@
         <v>0.2675658145409672</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2630332328337259</v>
+        <v>0.2627510762416364</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2595454831984348</v>
+        <v>0.2591274840795844</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.2570032853991994</v>
+        <v>0.256576799401226</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2553424548291788</v>
+        <v>0.2550220951838035</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.2545035381647927</v>
+        <v>0.254393016919423</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.254446895246222</v>
+        <v>0.2546621015587227</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2551637253988659</v>
+        <v>0.2558078397057248</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2566492233119093</v>
+        <v>0.2578470068353897</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2589189552819218</v>
+        <v>0.2608045797416076</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2620001380804975</v>
+        <v>0.2647254322067381</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.2659437917155251</v>
+        <v>0.2696810959896801</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.2708033748788066</v>
+        <v>0.2757469847403645</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.2766454189831242</v>
+        <v>0.2830232632486962</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>0.2835539839765567</v>
-      </c>
-      <c r="S44" s="2" t="n">
         <v>0.2916156103246133</v>
       </c>
-      <c r="T44" s="1" t="inlineStr"/>
+      <c r="S44" s="1" t="inlineStr"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
@@ -2540,51 +2451,48 @@
         <v>1.180296158977294</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.175660120614364</v>
+        <v>1.175262487903347</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.169301466996413</v>
+        <v>1.168251369555617</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1.161220352668794</v>
+        <v>1.15925817796077</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.151371190875526</v>
+        <v>1.148224245120433</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.139702029614363</v>
+        <v>1.135081723832521</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.126131101140586</v>
+        <v>1.119697021419855</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.110526848816953</v>
+        <v>1.101922316939652</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.09274669556362</v>
+        <v>1.081544540058967</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.072611910495834</v>
+        <v>1.058332062101629</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.049922328542544</v>
+        <v>1.032020278583349</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>1.024439898388269</v>
+        <v>1.0023075858643</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.9959305185620582</v>
+        <v>0.9689068762009189</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.9641580860903053</v>
+        <v>0.9315321714560333</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.9288932198626439</v>
-      </c>
-      <c r="S45" s="2" t="n">
         <v>0.8899613152251319</v>
       </c>
-      <c r="T45" s="1" t="inlineStr"/>
+      <c r="S45" s="1" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
@@ -2602,51 +2510,48 @@
         <v>199.2565864072191</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>116.2841001699566</v>
-      </c>
-      <c r="S46" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
-      <c r="T46" s="1" t="inlineStr"/>
+      <c r="S46" s="1" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
@@ -2664,51 +2569,48 @@
         <v>0.6934155588636786</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6451834489675361</v>
+        <v>0.6419546944869913</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.6022559501154908</v>
+        <v>0.5966106211168183</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5638685802055692</v>
+        <v>0.5561238216798053</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.5291695030894039</v>
+        <v>0.5198537807125588</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4976467391118254</v>
+        <v>0.4871134947236217</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4689105164395919</v>
+        <v>0.4573452836046674</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.4426124944584192</v>
+        <v>0.4302607947475137</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4184202956554766</v>
+        <v>0.4054971202086974</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.3962015376671923</v>
+        <v>0.382866877454614</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3758216201394586</v>
+        <v>0.3622495702925325</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0.3570527093257961</v>
+        <v>0.3434267211217917</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>0.339880761221536</v>
+        <v>0.3264013915200195</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0.324264400412908</v>
+        <v>0.3111320861419942</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0.3101765261475119</v>
-      </c>
-      <c r="S47" s="2" t="n">
         <v>0.2976385445704193</v>
       </c>
-      <c r="T47" s="1" t="inlineStr"/>
+      <c r="S47" s="1" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
@@ -2726,51 +2628,48 @@
         <v>0.8876763917513479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8503589546990444</v>
+        <v>0.8476827557110529</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.8129909497908511</v>
+        <v>0.807838102390409</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7764600076873178</v>
+        <v>0.7687303178641441</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.7409792133386249</v>
+        <v>0.7310690251477328</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.7068253360544405</v>
+        <v>0.6950438015492818</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6741948941545413</v>
+        <v>0.6606666216532919</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.643142168620027</v>
+        <v>0.6281613417983278</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.6135779019910447</v>
+        <v>0.5974295303378844</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5856601694094432</v>
+        <v>0.5685574328276755</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5594616026793855</v>
+        <v>0.5416626339362809</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.5347809281701855</v>
+        <v>0.5165679427658935</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.5117909068001266</v>
+        <v>0.4934870266617923</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>0.4905645083415359</v>
+        <v>0.4724845076896956</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>0.4711609998268694</v>
-      </c>
-      <c r="S48" s="2" t="n">
         <v>0.4537118711400231</v>
       </c>
-      <c r="T48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
@@ -2788,51 +2687,48 @@
         <v>0.3009117955899137</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.1519633006435085</v>
+        <v>0.1472682986886746</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.1079113763941087</v>
+        <v>0.1040512028785386</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.08720732714641261</v>
+        <v>0.08416531485429166</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.07547728055219156</v>
+        <v>0.07304667532585596</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.06815267638391176</v>
+        <v>0.06619932070733821</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.06333153040060037</v>
+        <v>0.0617872384426807</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.06009085172263932</v>
+        <v>0.05890202559086238</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.05794046605351349</v>
+        <v>0.05707687219159215</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.05657548897759065</v>
+        <v>0.05602993268923052</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.05581207055463994</v>
+        <v>0.05558691697384634</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0.05556200340151933</v>
+        <v>0.0556712005930268</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.05574366225286662</v>
+        <v>0.05621043688048771</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>0.05631517545884135</v>
+        <v>0.05718010096659844</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>0.05725981928560088</v>
-      </c>
-      <c r="S49" s="2" t="n">
         <v>0.05857117009930012</v>
       </c>
-      <c r="T49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
@@ -2847,54 +2743,51 @@
       </c>
       <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>0.6306666666666667</v>
+        <v>0.6292857142857143</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.6113333333333334</v>
+        <v>0.6085714285714285</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.592</v>
+        <v>0.5878571428571429</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.5726666666666667</v>
+        <v>0.5671428571428572</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5464285714285715</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.534</v>
+        <v>0.5257142857142857</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5146666666666667</v>
+        <v>0.505</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.4953333333333333</v>
+        <v>0.4842857142857143</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.476</v>
+        <v>0.4635714285714286</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4373333333333334</v>
+        <v>0.4221428571428572</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>0.418</v>
+        <v>0.4014285714285714</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>0.3986666666666667</v>
+        <v>0.3807142857142857</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>0.3793333333333334</v>
+        <v>0.36</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S50" s="2" t="n">
-        <v>0.3406666666666666</v>
-      </c>
-      <c r="T50" s="1" t="inlineStr"/>
+        <v>0.3392857142857142</v>
+      </c>
+      <c r="S50" s="1" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
@@ -2909,54 +2802,51 @@
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>116.2841001699566</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>110.3574940101521</v>
-      </c>
-      <c r="S51" s="2" t="n">
-        <v>104.4308878503476</v>
-      </c>
-      <c r="T51" s="1" t="inlineStr"/>
+        <v>104.007558838933</v>
+      </c>
+      <c r="S51" s="1" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
@@ -2971,54 +2861,51 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6542834231611319</v>
+        <v>0.6528609381672205</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.6083435839546485</v>
+        <v>0.6040008906918644</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.5676271902575042</v>
+        <v>0.5608528404519376</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.5311229686801958</v>
+        <v>0.5224733005942056</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.498139622561141</v>
+        <v>0.4880639358485558</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4681964345049069</v>
+        <v>0.4569203160469202</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4407596410267861</v>
+        <v>0.4285352724020985</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.4155715601725339</v>
+        <v>0.4026243969644493</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.3924301121422687</v>
+        <v>0.3789240751115422</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.371181142194238</v>
+        <v>0.3572719824747077</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3515648108563043</v>
+        <v>0.3374139715597593</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.3335057311090038</v>
+        <v>0.3192848027412507</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3169488695787482</v>
+        <v>0.3028179399616254</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>0.3018353833969528</v>
+        <v>0.2879901483751846</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>0.2881547528997792</v>
-      </c>
-      <c r="S52" s="2" t="n">
-        <v>0.2758920486866353</v>
-      </c>
-      <c r="T52" s="1" t="inlineStr"/>
+        <v>0.2747820638038408</v>
+      </c>
+      <c r="S52" s="1" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
@@ -3033,54 +2920,51 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.857792072117288</v>
+        <v>0.8566449408652137</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.8185252274697533</v>
+        <v>0.8146305802312926</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.7801718219804457</v>
+        <v>0.7734667621979159</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.7430401602428608</v>
+        <v>0.7338759548743808</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.7073740915602904</v>
+        <v>0.6961191242501733</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.6733637173071654</v>
+        <v>0.6601638683567802</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6409035082100051</v>
+        <v>0.6260427988521639</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.610025403696271</v>
+        <v>0.5937907596548805</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.5808285652718341</v>
+        <v>0.5634296976475788</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.5533778161398634</v>
+        <v>0.5350423151502405</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5274414228456362</v>
+        <v>0.5084161145598954</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>0.5031171631548509</v>
+        <v>0.4836795065578707</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>0.4804625280747954</v>
+        <v>0.4608658406019039</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>0.4594949713057526</v>
+        <v>0.4400685175575864</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>0.4403021559506097</v>
-      </c>
-      <c r="S53" s="2" t="n">
-        <v>0.4229272680516111</v>
-      </c>
-      <c r="T53" s="1" t="inlineStr"/>
+        <v>0.4213432296968064</v>
+      </c>
+      <c r="S53" s="1" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
@@ -3095,54 +2979,51 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2724616335565606</v>
+        <v>0.2728264862976837</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1379177624098988</v>
+        <v>0.1338497572918128</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.09816555592580541</v>
+        <v>0.09484023765812551</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.07954151364221926</v>
+        <v>0.07693362720631663</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.06903924748959318</v>
+        <v>0.0669762425432088</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.06252706844095968</v>
+        <v>0.06091105339602894</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.05822474737954209</v>
+        <v>0.05699304098048162</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.05538843076547833</v>
+        <v>0.05449766392638357</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.0535578893703248</v>
+        <v>0.05299351220560669</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.05246103075803894</v>
+        <v>0.05222397695379562</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.05196040341182012</v>
+        <v>0.05206385535377919</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.05195847081933057</v>
+        <v>0.05242649001453024</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>0.05239292757930168</v>
+        <v>0.05326713372110947</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>0.05323751027373903</v>
+        <v>0.05457087868506504</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>0.05448237155483682</v>
-      </c>
-      <c r="S54" s="2" t="n">
-        <v>0.05614055729666342</v>
-      </c>
-      <c r="T54" s="1" t="inlineStr"/>
+        <v>0.05635161751966029</v>
+      </c>
+      <c r="S54" s="1" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
@@ -3157,54 +3038,51 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5014648337358059</v>
+        <v>0.5004644049712301</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.7880983118324816</v>
+        <v>0.7951571965663656</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.8545818074176159</v>
+        <v>0.8599102873979747</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.8840112219416179</v>
+        <v>0.8880543221133667</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.9001825839829652</v>
+        <v>0.9033251749764167</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.9100656977821977</v>
+        <v>0.9125016424738571</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9165365938680218</v>
+        <v>0.9183807441133749</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.9207776778035037</v>
+        <v>0.9221055975212045</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.923504506091347</v>
+        <v>0.9243435965300111</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9251345681110075</v>
+        <v>0.9254864808911322</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9258776058992364</v>
+        <v>0.9257241100343748</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.9258804731233909</v>
+        <v>0.9251858531094985</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>0.925235682823888</v>
+        <v>0.9239368836048013</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>0.9239809247449741</v>
+        <v>0.921996524014703</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>0.9221283780829891</v>
-      </c>
-      <c r="S55" s="2" t="n">
-        <v>0.9196549445310657</v>
-      </c>
-      <c r="T55" s="1" t="inlineStr"/>
+        <v>0.9193396390285498</v>
+      </c>
+      <c r="S55" s="1" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
@@ -3219,54 +3097,51 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7928308206805679</v>
+        <v>0.7925571175792675</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9040007107409713</v>
+        <v>0.9071180477959627</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9334492683903225</v>
+        <v>0.9358895185677403</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9468052533979796</v>
+        <v>0.948685461697101</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.9542146537324381</v>
+        <v>0.9556884738180345</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.9587578860438596</v>
+        <v>0.9599063667841907</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9617271470303008</v>
+        <v>0.9625977918536026</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.9636562672173354</v>
+        <v>0.964278961015491</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.9648679757288272</v>
+        <v>0.9652498884133429</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.9655488057857011</v>
+        <v>0.965683442559767</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.9657893502438822</v>
+        <v>0.965658328898274</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0.965648737702872</v>
+        <v>0.9652218941086499</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>0.965158885640413</v>
+        <v>0.9643884025523056</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>0.9643233907451992</v>
+        <v>0.9631461936180357</v>
       </c>
       <c r="R56" s="2" t="n">
-        <v>0.9631302347305716</v>
-      </c>
-      <c r="S56" s="2" t="n">
-        <v>0.9615464092563861</v>
-      </c>
-      <c r="T56" s="1" t="inlineStr"/>
+        <v>0.9614571633309685</v>
+      </c>
+      <c r="S56" s="1" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
@@ -3281,54 +3156,51 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2813905009471096</v>
+        <v>0.2811863433358084</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.3406864454900046</v>
+        <v>0.3419728067953003</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.3505989984212221</v>
+        <v>0.3509410655936228</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.3510039443043173</v>
+        <v>0.3505057511486546</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.3480432983113403</v>
+        <v>0.3468279629635574</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.3435662483967508</v>
+        <v>0.3417081181479366</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3383531120609656</v>
+        <v>0.3359234221056464</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.3327431785133318</v>
+        <v>0.3297983277471504</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.3269564786201302</v>
+        <v>0.3235650470477323</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.3211507631297974</v>
+        <v>0.31739063742177</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3154373206322919</v>
+        <v>0.3114061941828092</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.3099364446129152</v>
+        <v>0.3057573784837125</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>0.3047605865011777</v>
+        <v>0.3005825024172691</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>0.3000239632844169</v>
+        <v>0.2960388638501384</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>0.2958573094930009</v>
-      </c>
-      <c r="S57" s="2" t="n">
-        <v>0.2923912427959964</v>
-      </c>
-      <c r="T57" s="1" t="inlineStr"/>
+        <v>0.2922862607409257</v>
+      </c>
+      <c r="S57" s="1" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
@@ -3343,54 +3215,51 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.151124118776815</v>
+        <v>1.150578245989658</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1.062377799270185</v>
+        <v>1.058842137058633</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1.036111103650193</v>
+        <v>1.03259772936633</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.020924488333052</v>
+        <v>1.017231933919797</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.00933013835935</v>
+        <v>1.005239401872601</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.9990872116840966</v>
+        <v>0.9944293535476197</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9892213184073614</v>
+        <v>0.9838133341616834</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.9792785544438508</v>
+        <v>0.9729365229403433</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.9689278286328695</v>
+        <v>0.9614252343707766</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.9578925859460624</v>
+        <v>0.9489575905895593</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9459345018896737</v>
+        <v>0.9352269846819268</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.9327737435617988</v>
+        <v>0.9198661432115165</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>0.9181114109748046</v>
+        <v>0.9024768235733482</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>0.9016138797803057</v>
+        <v>0.8825869545836461</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>0.8828878938189587</v>
-      </c>
-      <c r="S58" s="2" t="n">
-        <v>0.861508375559446</v>
-      </c>
-      <c r="T58" s="1" t="inlineStr"/>
+        <v>0.8596778720441994</v>
+      </c>
+      <c r="S58" s="1" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
@@ -3405,54 +3274,51 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6625199647544942</v>
+        <v>0.6612407210601744</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6427672737493952</v>
+        <v>0.6393366808686474</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.6072415102197469</v>
+        <v>0.6009807379947486</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5714268310718572</v>
+        <v>0.5629187482016862</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.5374786818095514</v>
+        <v>0.5272267598629743</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.5057932110432251</v>
+        <v>0.4940432659250179</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.47618307218868</v>
+        <v>0.4632008778470891</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.4485318823583244</v>
+        <v>0.434547983835321</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.4227163777367752</v>
+        <v>0.4078868049211564</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.398621249447761</v>
+        <v>0.3830869581536965</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3759868888716454</v>
+        <v>0.3598891790707875</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.3547415725698023</v>
+        <v>0.3382266797622753</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>0.3348255417836918</v>
+        <v>0.3180205486364964</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0.3161665993594145</v>
+        <v>0.2992319827470267</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0.2987406862253892</v>
-      </c>
-      <c r="S59" s="2" t="n">
-        <v>0.2825170054424779</v>
-      </c>
-      <c r="T59" s="1" t="inlineStr"/>
+        <v>0.2818236131273244</v>
+      </c>
+      <c r="S59" s="1" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
@@ -3467,54 +3333,51 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2703888904097833</v>
+        <v>0.2707047831582408</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.1330636745304504</v>
+        <v>0.1289535490674906</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.09367204543933282</v>
+        <v>0.09035121456081503</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.07539032965061968</v>
+        <v>0.07279583956722309</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.06513631074733642</v>
+        <v>0.0630871303195517</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.0588093073356333</v>
+        <v>0.0572051495289134</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.05465801146599711</v>
+        <v>0.05343833731776829</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.05195404749581219</v>
+        <v>0.05108008787467855</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.05025287775359496</v>
+        <v>0.04971625102356635</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04929609311682435</v>
+        <v>0.04910680533129995</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.04895788964246673</v>
+        <v>0.04914211499311783</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0.0491555999156828</v>
+        <v>0.04975559312298664</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>0.04984413858227942</v>
+        <v>0.0509264267870588</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>0.05101770853810567</v>
+        <v>0.05266952243484315</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>0.05269190168912224</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>0.05491106614839087</v>
-      </c>
-      <c r="T60" s="1" t="inlineStr"/>
+        <v>0.05503600366715333</v>
+      </c>
+      <c r="S60" s="1" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
@@ -3529,54 +3392,51 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.1330636745304504</v>
+        <v>0.1289535490674906</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.09367204543933282</v>
+        <v>0.09035121456081503</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.07539032965061968</v>
+        <v>0.07279583956722309</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.06513631074733642</v>
+        <v>0.0630871303195517</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.0588093073356333</v>
+        <v>0.0572051495289134</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.05465801146599711</v>
+        <v>0.05343833731776829</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.05195404749581219</v>
+        <v>0.05108008787467855</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.05025287775359496</v>
+        <v>0.04971625102356635</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.04929609311682435</v>
+        <v>0.04910680533129995</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.04895788964246673</v>
+        <v>0.04914211499311783</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0491555999156828</v>
+        <v>0.04975559312298664</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>0.04984413858227942</v>
+        <v>0.0509264267870588</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>0.05101770853810567</v>
+        <v>0.05266952243484315</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>0.05269190168912224</v>
+        <v>0.05503600366715333</v>
       </c>
       <c r="R61" s="2" t="n">
-        <v>0.05491106614839087</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>0.0571302306076595</v>
-      </c>
-      <c r="T61" s="1" t="inlineStr"/>
+        <v>0.05740248489946351</v>
+      </c>
+      <c r="S61" s="1" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
@@ -3591,54 +3451,51 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5071108561666231</v>
+        <v>0.5062544510926434</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.7965140112015372</v>
+        <v>0.8035709709007146</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8617743749479074</v>
+        <v>0.8670515451401452</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8904383054002251</v>
+        <v>0.8944317807808952</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.9061187619707659</v>
+        <v>0.9092199502745679</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.9156600723535896</v>
+        <v>0.9180634324411635</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9218666989701296</v>
+        <v>0.9236823143066361</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.9258870356012644</v>
+        <v>0.9271827378215309</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.9284074650572826</v>
+        <v>0.9292011053393887</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.9298220220603441</v>
+        <v>0.9301016194309984</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9303215240383296</v>
+        <v>0.9300494698354567</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0.9300295528929712</v>
+        <v>0.9291429436493502</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>0.9290120284804108</v>
+        <v>0.9274103632992117</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>0.9272751500372671</v>
+        <v>0.9248249459015589</v>
       </c>
       <c r="R62" s="2" t="n">
-        <v>0.924791705252773</v>
-      </c>
-      <c r="S62" s="2" t="n">
-        <v>0.9214895519254134</v>
-      </c>
-      <c r="T62" s="1" t="inlineStr"/>
+        <v>0.9213032909096034</v>
+      </c>
+      <c r="S62" s="1" t="inlineStr"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
@@ -3653,54 +3510,51 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.7812692787111242</v>
+        <v>0.781132427160474</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.8415346025519874</v>
+        <v>0.8434383830980788</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.8612182742485085</v>
+        <v>0.8631690556287381</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.8731242885411294</v>
+        <v>0.8752186331837397</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.8823152419384261</v>
+        <v>0.8846656334524475</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.8903210003931722</v>
+        <v>0.8930012717048008</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8977774341433087</v>
+        <v>0.9008423535003319</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.9049413955601958</v>
+        <v>0.9084347036659038</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.911964394567677</v>
+        <v>0.9159163435477082</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.9189300869256287</v>
+        <v>0.9233620626480232</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.9258744305663087</v>
+        <v>0.9307999453445317</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0.9328179458511794</v>
+        <v>0.9382427994019147</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>0.9397678586145239</v>
+        <v>0.9456873125217253</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>0.9467175567284032</v>
+        <v>0.953117642351901</v>
       </c>
       <c r="R63" s="2" t="n">
-        <v>0.9536529499680431</v>
-      </c>
-      <c r="S63" s="2" t="n">
-        <v>0.9605497856022194</v>
-      </c>
-      <c r="T63" s="1" t="inlineStr"/>
+        <v>0.9605051626395107</v>
+      </c>
+      <c r="S63" s="1" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
@@ -3715,54 +3569,51 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4947110208887889</v>
+        <v>0.4947976924542986</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.4777305805592196</v>
+        <v>0.4779735242447286</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.4850371337997327</v>
+        <v>0.4865582469952273</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.4966647621618928</v>
+        <v>0.4994124070984718</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.5098407336349193</v>
+        <v>0.5137734390610369</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5237673633405326</v>
+        <v>0.5288702372127254</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5381108674808632</v>
+        <v>0.5443607442121166</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.5527131589300166</v>
+        <v>0.5600965560548041</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.5674653458784754</v>
+        <v>0.5759477597191387</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5822740841432794</v>
+        <v>0.5918081993459784</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5970601655016087</v>
+        <v>0.6075771359846209</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.6117280265373947</v>
+        <v>0.6231339534389799</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.6261851294940463</v>
+        <v>0.6383608968284006</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>0.6403325756029661</v>
+        <v>0.6531207208541026</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>0.654056504878885</v>
-      </c>
-      <c r="S64" s="2" t="n">
-        <v>0.6672445293840594</v>
-      </c>
-      <c r="T64" s="1" t="inlineStr"/>
+        <v>0.6672755281010996</v>
+      </c>
+      <c r="S64" s="1" t="inlineStr"/>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
@@ -3780,51 +3631,48 @@
         <v>0.9130337357818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8850333252548149</v>
+        <v>0.8830355266498334</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8570611050841739</v>
+        <v>0.8530645253444216</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.8290571204324678</v>
+        <v>0.8230510799514991</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.8009973827639962</v>
+        <v>0.7929681334991677</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7728646278053329</v>
+        <v>0.7627977092904863</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7446612304027046</v>
+        <v>0.7325616461288711</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.7164166267770026</v>
+        <v>0.7022863254977531</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6881619377878848</v>
+        <v>0.6720276223556498</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6599421408215783</v>
+        <v>0.6418422361217935</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6318065171944226</v>
+        <v>0.611794636858556</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>0.6038156496800842</v>
+        <v>0.5819584578441279</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>0.5760225971805022</v>
+        <v>0.552396365214525</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0.5484793863228254</v>
+        <v>0.5231726932408487</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.521237818635248</v>
-      </c>
-      <c r="S65" s="2" t="n">
         <v>0.4943374292495647</v>
       </c>
-      <c r="T65" s="1" t="inlineStr"/>
+      <c r="S65" s="1" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
@@ -3839,54 +3687,51 @@
       </c>
       <c r="C66" s="1" t="inlineStr"/>
       <c r="D66" s="2" t="n">
-        <v>0.6403333333333334</v>
+        <v>0.6396428571428572</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.621</v>
+        <v>0.6189285714285715</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.6016666666666667</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.5823333333333334</v>
+        <v>0.5775</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5567857142857143</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0.5436666666666667</v>
+        <v>0.5360714285714285</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5243333333333333</v>
+        <v>0.5153571428571428</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.505</v>
+        <v>0.4946428571428572</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.4856666666666667</v>
+        <v>0.4739285714285715</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.4663333333333333</v>
+        <v>0.4532142857142857</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.447</v>
+        <v>0.4325</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>0.4276666666666667</v>
+        <v>0.4117857142857143</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.3910714285714286</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>0.389</v>
+        <v>0.3703571428571428</v>
       </c>
       <c r="R66" s="2" t="n">
-        <v>0.3696666666666667</v>
-      </c>
-      <c r="S66" s="2" t="n">
-        <v>0.3503333333333333</v>
-      </c>
-      <c r="T66" s="1" t="inlineStr"/>
+        <v>0.3496428571428571</v>
+      </c>
+      <c r="S66" s="1" t="inlineStr"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
@@ -3901,54 +3746,51 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.150011517879318</v>
+        <v>1.149900190948778</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.040856798279222</v>
+        <v>1.037406335378524</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1.012030332275313</v>
+        <v>1.008925798296564</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9969084778913009</v>
+        <v>0.9938963560643232</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.9863173959023402</v>
+        <v>0.9831646987246834</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.9775792957002311</v>
+        <v>0.9741269377820952</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9695621110230351</v>
+        <v>0.9656506714457721</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.9617625261085604</v>
+        <v>0.9572427390595025</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.9538345017902922</v>
+        <v>0.9485264056880329</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9455090296099077</v>
+        <v>0.9392010422085477</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.9365735498767322</v>
+        <v>0.9290023750862315</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.9267867253069327</v>
+        <v>0.9176220242343975</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>0.9159009995558133</v>
+        <v>0.9047385458666748</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>0.9036486123004409</v>
+        <v>0.8899750486647011</v>
       </c>
       <c r="R67" s="2" t="n">
-        <v>0.889715679701415</v>
-      </c>
-      <c r="S67" s="2" t="n">
-        <v>0.8737700314689053</v>
-      </c>
-      <c r="T67" s="1" t="inlineStr"/>
+        <v>0.8729257643027138</v>
+      </c>
+      <c r="S67" s="1" t="inlineStr"/>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
@@ -3963,54 +3805,51 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9129976966874244</v>
+        <v>0.9123908734224122</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.9150619818429163</v>
+        <v>0.9132006195531562</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.8923130416932181</v>
+        <v>0.887967323159673</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8646283651232153</v>
+        <v>0.8577821070040713</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.834907678720365</v>
+        <v>0.8255539583207618</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.8040381898895175</v>
+        <v>0.792160112745544</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7724311182350889</v>
+        <v>0.7580358219315676</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.740318990147195</v>
+        <v>0.72342089195214</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.7078819770274036</v>
+        <v>0.6885297165190225</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.675279039199588</v>
+        <v>0.6535447189435526</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6426482553515347</v>
+        <v>0.6186306556226798</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.6101300308937273</v>
+        <v>0.5839510578580409</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.5778478490882533</v>
+        <v>0.5496458774495508</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>0.5459136371160284</v>
+        <v>0.5158449565439994</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>0.5144310989034653</v>
-      </c>
-      <c r="S68" s="2" t="n">
-        <v>0.4834821947991647</v>
-      </c>
-      <c r="T68" s="1" t="inlineStr"/>
+        <v>0.4826515564353129</v>
+      </c>
+      <c r="S68" s="1" t="inlineStr"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
@@ -4025,54 +3864,51 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2369777820975177</v>
+        <v>0.236866455166978</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1558234730244067</v>
+        <v>0.1543708087286905</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1549692271911389</v>
+        <v>0.1558612729521429</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1678513574588331</v>
+        <v>0.1708452761128242</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.185320013138344</v>
+        <v>0.1901965652255156</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2047146678948981</v>
+        <v>0.211329228491609</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2249008806203305</v>
+        <v>0.233089025316901</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.2453458993315578</v>
+        <v>0.2549564135617495</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.2656725640024074</v>
+        <v>0.2764987833323831</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.2855668887883294</v>
+        <v>0.2973588060867542</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3047670326823096</v>
+        <v>0.3172077382276756</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3229710756268486</v>
+        <v>0.3356635663902696</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.3398784023753111</v>
+        <v>0.3523421806521498</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.3551692259776155</v>
+        <v>0.3668023554238524</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.368477861066167</v>
-      </c>
-      <c r="S69" s="2" t="n">
-        <v>0.3794326022193406</v>
-      </c>
-      <c r="T69" s="1" t="inlineStr"/>
+        <v>0.3785883350531491</v>
+      </c>
+      <c r="S69" s="1" t="inlineStr"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
@@ -4087,54 +3923,51 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.2381264220893905</v>
+        <v>0.2381873725672461</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1473158174272687</v>
+        <v>0.1456415175054772</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.1437980619569752</v>
+        <v>0.1446304062066568</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.1562961232098367</v>
+        <v>0.1594498269157253</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.1744224596389855</v>
+        <v>0.1796854435518387</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.1950490217945792</v>
+        <v>0.2022692408020758</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2167902001722725</v>
+        <v>0.2257775122301158</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.2389595642966558</v>
+        <v>0.2495156309882033</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.2610458516054659</v>
+        <v>0.2728955178517541</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.2826135467464744</v>
+        <v>0.2954128716460067</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.303286246538139</v>
+        <v>0.316596329059247</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.3226437126680715</v>
+        <v>0.3359150853534756</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.3402635618865514</v>
+        <v>0.3528309461237974</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0.3557002426642774</v>
+        <v>0.3667419980396467</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0.3684567949154934</v>
-      </c>
-      <c r="S70" s="2" t="n">
-        <v>0.3780261807602814</v>
-      </c>
-      <c r="T70" s="1" t="inlineStr"/>
+        <v>0.3770263156088866</v>
+      </c>
+      <c r="S70" s="1" t="inlineStr"/>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
@@ -4152,51 +3985,48 @@
         <v>251.7894146864385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.8009621686911</v>
+        <v>249.6625952542775</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>247.9136892966872</v>
+        <v>247.6528107706313</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>246.1387065941966</v>
+        <v>245.7731838000793</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>244.4815971910143</v>
+        <v>244.0304158041251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>242.9479317023808</v>
+        <v>242.4310417988148</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>241.539700983277</v>
+        <v>240.972909827971</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>240.2521702422908</v>
+        <v>239.6524840515102</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>239.0793762629544</v>
+        <v>238.4569611637397</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>238.0101114191572</v>
+        <v>237.3706330162411</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>237.0296181915506</v>
+        <v>236.3718770966746</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>236.116342046438</v>
+        <v>235.4310839272837</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>235.2469960755472</v>
+        <v>234.5161748631908</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>234.3939168165112</v>
+        <v>233.5872660970408</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>233.5237985627082</v>
-      </c>
-      <c r="S71" s="2" t="n">
         <v>232.6016263665796</v>
       </c>
-      <c r="T71" s="1" t="inlineStr"/>
+      <c r="S71" s="1" t="inlineStr"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
@@ -4211,54 +4041,51 @@
       </c>
       <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="2" t="n">
-        <v>196.2932833273169</v>
+        <v>196.0816188216095</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>190.3666771675124</v>
+        <v>189.7316836503905</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>184.4400710077079</v>
+        <v>183.3817484791714</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>178.5134648479034</v>
+        <v>177.0318133079523</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>172.5868586880989</v>
+        <v>170.6818781367333</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>166.6602525282945</v>
+        <v>164.3319429655142</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>160.73364636849</v>
+        <v>157.9820077942951</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>151.6320726230761</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>148.8804340488811</v>
+        <v>145.282137451857</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>142.9538278890766</v>
+        <v>138.9322022806379</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>137.0272217292722</v>
+        <v>132.5822671094188</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>131.1006155694677</v>
+        <v>126.2323319381998</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>125.1740094096633</v>
+        <v>119.8823967669807</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>119.2474032498588</v>
+        <v>113.5324615957616</v>
       </c>
       <c r="R72" s="2" t="n">
-        <v>113.3207970900543</v>
-      </c>
-      <c r="S72" s="2" t="n">
-        <v>107.3941909302498</v>
-      </c>
-      <c r="T72" s="1" t="inlineStr"/>
+        <v>107.1825264245426</v>
+      </c>
+      <c r="S72" s="1" t="inlineStr"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
@@ -4273,54 +4100,51 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>248.0517603648712</v>
+        <v>247.9005511003574</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>240.1798960230389</v>
+        <v>239.722425110993</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>236.9094723022859</v>
+        <v>236.3804261005702</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>234.6224489396598</v>
+        <v>234.0471923727898</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>232.837041863052</v>
+        <v>232.2443952114634</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>231.4199672453222</v>
+        <v>230.8447911323391</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>230.3175196216195</v>
+        <v>229.7932112410973</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>229.5057972508388</v>
+        <v>229.0678517566361</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>228.967182502565</v>
+        <v>228.6458226289366</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>228.68399545452</v>
+        <v>228.5052237669685</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>228.6387798288928</v>
+        <v>228.6215960141323</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>228.8072540849443</v>
+        <v>228.9619226465695</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>229.1630518688698</v>
+        <v>229.4903727663425</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>229.6756518894332</v>
+        <v>230.1629008037089</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>230.3082587879495</v>
-      </c>
-      <c r="S73" s="2" t="n">
-        <v>231.0222911287899</v>
-      </c>
-      <c r="T73" s="1" t="inlineStr"/>
+        <v>230.932388801264</v>
+      </c>
+      <c r="S73" s="1" t="inlineStr"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
@@ -4338,51 +4162,48 @@
         <v>0.9198717705829682</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.930908005417769</v>
+        <v>0.9316127880691234</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.9399111885257418</v>
+        <v>0.9411937231993717</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9475445209109083</v>
+        <v>0.9489889140291673</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.9539515543452253</v>
+        <v>0.9555931563290563</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.9594117104066201</v>
+        <v>0.961206325603477</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9641351229571883</v>
+        <v>0.9659487560133837</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.9682321979656086</v>
+        <v>0.9700508464641263</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.9717447196250987</v>
+        <v>0.9735532872138978</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.9748160838275998</v>
+        <v>0.9765720654514889</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9775237620338982</v>
+        <v>0.9792051916840198</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>0.9798313148293836</v>
+        <v>0.9814270687200961</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.9818335545120593</v>
+        <v>0.9833372387193101</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>0.9835696379292527</v>
+        <v>0.9849622306534793</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0.985061197937973</v>
-      </c>
-      <c r="S74" s="2" t="n">
         <v>0.9863414798135992</v>
       </c>
-      <c r="T74" s="1" t="inlineStr"/>
+      <c r="S74" s="1" t="inlineStr"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
@@ -4400,51 +4221,48 @@
         <v>264.9230699278949</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>292.8257431134205</v>
+        <v>294.8147930348406</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>320.6211333531855</v>
+        <v>324.62968952623</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>348.3910958285558</v>
+        <v>354.3231214071286</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>376.0830772634475</v>
+        <v>383.9816453978873</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>403.716948421949</v>
+        <v>413.5895941067111</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>431.3112687519726</v>
+        <v>443.117562409901</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>458.8596591757861</v>
+        <v>472.6034652144938</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>486.3331263978957</v>
+        <v>502.0136192526899</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>513.7606689161634</v>
+        <v>531.3599424493966</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>541.1500239054108</v>
+        <v>560.65726222911</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>568.451073262972</v>
+        <v>589.8572714101675</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>595.6894595592446</v>
+        <v>618.9875214592724</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>622.8656529904968</v>
+        <v>648.0388565102273</v>
       </c>
       <c r="R75" s="2" t="n">
-        <v>649.9727208113966</v>
-      </c>
-      <c r="S75" s="2" t="n">
         <v>677.0139991251236</v>
       </c>
-      <c r="T75" s="1" t="inlineStr"/>
+      <c r="S75" s="1" t="inlineStr"/>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
@@ -4462,51 +4280,48 @@
         <v>298.0389802067385</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>313.2520727793622</v>
+        <v>314.3092699735009</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>327.7376828837337</v>
+        <v>329.7159706916777</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>341.5359363918575</v>
+        <v>344.4249425018446</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>354.7685386161718</v>
+        <v>358.4549534872339</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>367.4838532828871</v>
+        <v>371.8862930918287</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>379.7080435764382</v>
+        <v>384.8173876481858</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>391.4857966451933</v>
+        <v>397.2404946796239</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>402.9017712038968</v>
+        <v>409.2488411885599</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>413.9364337923426</v>
+        <v>420.8560609516754</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>424.589106731691</v>
+        <v>432.0499545452333</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>434.9928791022549</v>
+        <v>442.9683589780464</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>445.1113929581084</v>
+        <v>453.5642238185459</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>454.9549308573855</v>
+        <v>463.8734511232522</v>
       </c>
       <c r="R76" s="2" t="n">
-        <v>464.550991329953</v>
-      </c>
-      <c r="S76" s="2" t="n">
         <v>473.8913655885228</v>
       </c>
-      <c r="T76" s="1" t="inlineStr"/>
+      <c r="S76" s="1" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
@@ -4524,51 +4339,48 @@
         <v>0.8448204141343578</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7974439241608384</v>
+        <v>0.7943214505742267</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7564393789426883</v>
+        <v>0.7511095390711756</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7206817215035083</v>
+        <v>0.7135754513445642</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6891298708297292</v>
+        <v>0.6807840523057973</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.6611118543904044</v>
+        <v>0.651895609766268</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6361195267506974</v>
+        <v>0.6262006800178096</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.6136931973039962</v>
+        <v>0.6032931870271456</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.5933937087160716</v>
+        <v>0.582669850624871</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5749919359322656</v>
+        <v>0.5640185684375758</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5582564753394292</v>
+        <v>0.5470938594252941</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.5428050742663618</v>
+        <v>0.5314851030679409</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>0.5285126370550741</v>
+        <v>0.5170517482371183</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>0.515202497915088</v>
+        <v>0.5035581698659797</v>
       </c>
       <c r="R77" s="2" t="n">
-        <v>0.5026871170679411</v>
-      </c>
-      <c r="S77" s="2" t="n">
         <v>0.4908332230905137</v>
       </c>
-      <c r="T77" s="1" t="inlineStr"/>
+      <c r="S77" s="1" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
@@ -4583,54 +4395,51 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7762805497595007</v>
+        <v>0.7758194364498247</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7195874767764773</v>
+        <v>0.7162072399490459</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.6820840866459945</v>
+        <v>0.6768754162864432</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6511333780898241</v>
+        <v>0.6446312378490995</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.6245130036369227</v>
+        <v>0.6171656544030198</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.6013365331651109</v>
+        <v>0.5933516387160817</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5808623041953515</v>
+        <v>0.5724800026430085</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.5627532946453329</v>
+        <v>0.5541992204938717</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5467519525118658</v>
+        <v>0.5381521735211686</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.5326486714454499</v>
+        <v>0.5241056797248543</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5200619476864727</v>
+        <v>0.5116577227873375</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0.5088274897180355</v>
+        <v>0.5006277313683627</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>0.4987969665535941</v>
+        <v>0.4908125161156869</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0.4897888944330698</v>
+        <v>0.4820311420268309</v>
       </c>
       <c r="R78" s="2" t="n">
-        <v>0.4816627856862081</v>
-      </c>
-      <c r="S78" s="2" t="n">
-        <v>0.4742546645343235</v>
-      </c>
-      <c r="T78" s="1" t="inlineStr"/>
+        <v>0.474084587425221</v>
+      </c>
+      <c r="S78" s="1" t="inlineStr"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
@@ -4648,51 +4457,48 @@
         <v>304.6972711556989</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>332.5412301095225</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>360.3157523649842</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>387.9652287313608</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>415.5484181640575</v>
+        <v>423.4832578774369</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>443.0550461864155</v>
+        <v>452.9241266519992</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>470.7121634428254</v>
+        <v>482.5514447276188</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>498.295226716079</v>
+        <v>512.0790958565088</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>525.8469279503316</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>553.3116738158444</v>
+        <v>570.9315691201923</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>580.6553434530979</v>
+        <v>600.1737035863282</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>607.9683068286746</v>
+        <v>629.3627469314156</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>635.1835141618287</v>
+        <v>658.4149708618947</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>662.2781021930996</v>
+        <v>687.3224160481872</v>
       </c>
       <c r="R79" s="2" t="n">
-        <v>689.2438426770293</v>
-      </c>
-      <c r="S79" s="2" t="n">
         <v>716.0408161885885</v>
       </c>
-      <c r="T79" s="1" t="inlineStr"/>
+      <c r="S79" s="1" t="inlineStr"/>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
@@ -4707,54 +4513,51 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.899977269938159</v>
+        <v>0.9001179490256411</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9142175178994719</v>
+        <v>0.9152540141204015</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.9232442532169893</v>
+        <v>0.9244318040653919</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.9302787318018001</v>
+        <v>0.9317173785273669</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.9360793185234136</v>
+        <v>0.937726382807626</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.9410173094649702</v>
+        <v>0.9426849249698401</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9452875433583487</v>
+        <v>0.946979765540149</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.9488894882232354</v>
+        <v>0.9505998836898391</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.9520408323758175</v>
+        <v>0.9537141112961338</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0.9548516589638915</v>
+        <v>0.9564711798415051</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9572118925929692</v>
+        <v>0.9587739854529909</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>0.9592846729101582</v>
+        <v>0.9608011997304212</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>0.9611226909214362</v>
+        <v>0.9625781653535936</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>0.9627508999351054</v>
+        <v>0.9641758826673019</v>
       </c>
       <c r="R80" s="2" t="n">
-        <v>0.9642306135656683</v>
-      </c>
-      <c r="S80" s="2" t="n">
-        <v>0.9655692914167171</v>
-      </c>
-      <c r="T80" s="1" t="inlineStr"/>
+        <v>0.9656098120502704</v>
+      </c>
+      <c r="S80" s="1" t="inlineStr"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
@@ -4769,54 +4572,51 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>617.7345504699753</v>
+        <v>617.8311110563023</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>627.50890085281</v>
+        <v>628.2203405174404</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>633.7047532035713</v>
+        <v>634.5198751116486</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>638.5331423324183</v>
+        <v>639.5206137030721</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>642.5146015876995</v>
+        <v>643.6451284900878</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>645.9039845381343</v>
+        <v>647.0486175735091</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>648.835026357345</v>
+        <v>649.9965491465167</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>651.3073618998652</v>
+        <v>652.4813586328726</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>653.4704100439648</v>
+        <v>654.6189303857324</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>655.3997306577534</v>
+        <v>656.5113520672343</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>657.0197691949074</v>
+        <v>658.0919726414946</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>658.4425029241156</v>
+        <v>659.4834303395994</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>659.7040983753325</v>
+        <v>660.7031200996602</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>660.8216832263357</v>
+        <v>661.7997757814525</v>
       </c>
       <c r="R81" s="2" t="n">
-        <v>661.8373424712217</v>
-      </c>
-      <c r="S81" s="2" t="n">
-        <v>662.756196300273</v>
-      </c>
-      <c r="T81" s="1" t="inlineStr"/>
+        <v>662.7840092197644</v>
+      </c>
+      <c r="S81" s="1" t="inlineStr"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
@@ -4831,54 +4631,51 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>455.0427848274916</v>
+        <v>455.0748040551998</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>458.53212630562</v>
+        <v>458.7438421848687</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>460.6914080781864</v>
+        <v>460.9384929530079</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>462.3222412482408</v>
+        <v>462.6626102681121</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>463.6529326277467</v>
+        <v>464.0082012350092</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>464.7411309225139</v>
+        <v>465.0811967823042</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>465.6208778462529</v>
+        <v>465.9676196840014</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>466.3341273542305</v>
+        <v>466.6609994820503</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>466.9342937553715</v>
+        <v>467.2279376337091</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>467.3958738720804</v>
+        <v>467.6634924923767</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>467.7481611448815</v>
+        <v>467.9889608220808</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>468.0650064081697</v>
+        <v>468.2745682991455</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>468.3166901067456</v>
+        <v>468.4914645249083</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>468.51200318471</v>
+        <v>468.6546100479192</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>468.660793575957</v>
-      </c>
-      <c r="S82" s="2" t="n">
-        <v>468.7633708704671</v>
-      </c>
-      <c r="T82" s="1" t="inlineStr"/>
+        <v>468.7660613130769</v>
+      </c>
+      <c r="S82" s="1" t="inlineStr"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
@@ -4893,54 +4690,51 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.545117445294531</v>
+        <v>0.5447468172074134</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5238016754859934</v>
+        <v>0.5225627094398959</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.5142476463595752</v>
+        <v>0.5128242264736803</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.5074868306274732</v>
+        <v>0.5058701247484856</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.5021795948608611</v>
+        <v>0.500517867126743</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4979545640515015</v>
+        <v>0.4963537393673502</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4946460319540695</v>
+        <v>0.4931527461005401</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.4921488344697206</v>
+        <v>0.4908656433918407</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.490362746032361</v>
+        <v>0.4893667613005351</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.4892726021734364</v>
+        <v>0.4886103521768771</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4888074370389106</v>
+        <v>0.4885192069755876</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>0.4888364884201919</v>
+        <v>0.4889480192746724</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>0.4893335144998476</v>
+        <v>0.4898496347186731</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>0.4902236235746643</v>
+        <v>0.4911141294015546</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>0.4914178056812916</v>
-      </c>
-      <c r="S83" s="2" t="n">
-        <v>0.4928334965673503</v>
-      </c>
-      <c r="T83" s="1" t="inlineStr"/>
+        <v>0.4926388829310537</v>
+      </c>
+      <c r="S83" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -431,7 +431,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -439,8 +439,8 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
@@ -849,7 +849,7 @@
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>0.4537118711400233</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -880,7 +880,7 @@
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -942,7 +942,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -973,7 +973,7 @@
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="2" t="n">
-        <v>0.3446443080405253</v>
+        <v>0.3446443080405244</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1004,7 +1004,7 @@
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="2" t="n">
-        <v>0.5062544510926434</v>
+        <v>0.5062544510926422</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1035,7 +1035,7 @@
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="2" t="n">
-        <v>0.7925571175792675</v>
+        <v>0.7925571175792671</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1066,7 +1066,7 @@
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="2" t="n">
-        <v>0.8596778720441994</v>
+        <v>0.8596778720441987</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1097,7 +1097,7 @@
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="2" t="n">
-        <v>0.7111184547506971</v>
+        <v>0.7111184547506979</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1128,7 +1128,7 @@
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="2" t="n">
-        <v>141.4703657841591</v>
+        <v>141.4703657841592</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1252,7 +1252,7 @@
       <c r="Q24" s="1" t="inlineStr"/>
       <c r="R24" s="1" t="inlineStr"/>
       <c r="S24" s="2" t="n">
-        <v>0.168064293246209</v>
+        <v>0.1680642932462094</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1681,49 +1681,49 @@
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16967.12604306373</v>
+        <v>16967.12604306353</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18630.78159248007</v>
+        <v>18630.78159247993</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20218.5607708968</v>
+        <v>20218.56077089675</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21743.63912220311</v>
+        <v>21743.63912220303</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23213.0501078087</v>
+        <v>23213.05010780867</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24632.76848581418</v>
+        <v>24632.76848581409</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26002.0239099061</v>
+        <v>26002.02390990612</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>27318.78381964874</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>28574.47174295057</v>
+        <v>28574.47174295066</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29758.48274205851</v>
+        <v>29758.48274205857</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>30856.11876136259</v>
+        <v>30856.11876136265</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31847.15753258983</v>
+        <v>31847.15753258981</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>32709.42570822144</v>
+        <v>32709.42570822141</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>33415.02270248366</v>
+        <v>33415.02270248363</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>33933.38931404932</v>
+        <v>33933.38931404923</v>
       </c>
       <c r="S32" s="1" t="inlineStr"/>
     </row>
@@ -1740,49 +1740,49 @@
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>16797.45478263309</v>
+        <v>16797.4547826329</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18258.16596063047</v>
+        <v>18258.16596063033</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>19612.0039477699</v>
+        <v>19612.00394776985</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20873.89355731498</v>
+        <v>20873.89355731491</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>22052.39760241826</v>
+        <v>22052.39760241824</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23154.80237666533</v>
+        <v>23154.80237666525</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24441.90247531174</v>
+        <v>24441.90247531175</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>25679.65679046981</v>
+        <v>25679.65679046982</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>26860.00343837353</v>
+        <v>26860.00343837362</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27972.97377753499</v>
+        <v>27972.97377753505</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>29004.75163568083</v>
+        <v>29004.75163568088</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>29936.32808063443</v>
+        <v>29936.32808063442</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>30746.86016572815</v>
+        <v>30746.86016572812</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>31410.12134033464</v>
+        <v>31410.12134033461</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>31897.38595520635</v>
+        <v>31897.38595520627</v>
       </c>
       <c r="S33" s="1" t="inlineStr"/>
     </row>
@@ -1799,49 +1799,49 @@
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>13701.87693398603</v>
+        <v>13701.87693398587</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15183.18715242576</v>
+        <v>15183.18715242563</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16585.02366398544</v>
+        <v>16585.02366398539</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>17906.52312846286</v>
+        <v>17906.5231284628</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19142.33211474175</v>
+        <v>19142.33211474172</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20287.40656738138</v>
+        <v>20287.4065673813</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>21560.80915145568</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22748.12080720581</v>
+        <v>22748.1208072058</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23831.00891765521</v>
+        <v>23831.00891765527</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24789.99333265435</v>
+        <v>24789.99333265438</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>25602.7462639698</v>
+        <v>25602.74626396982</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>26243.62718943152</v>
+        <v>26243.62718943147</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>26686.81663025726</v>
+        <v>26686.8166302572</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>26904.66888708492</v>
+        <v>26904.66888708486</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>26870.38869889748</v>
+        <v>26870.38869889738</v>
       </c>
       <c r="S34" s="1" t="inlineStr"/>
     </row>
@@ -1858,49 +1858,49 @@
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>16.6972711556989</v>
+        <v>16.69727115569871</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.08373681547279</v>
+        <v>18.08373681547265</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19.35093521240871</v>
+        <v>19.35093521240866</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.56673424835787</v>
+        <v>20.5667342483578</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.65781275498967</v>
+        <v>21.65781275498965</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.64232024894013</v>
+        <v>22.64232024894005</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23.81327704394781</v>
+        <v>23.81327704394782</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>24.88456689222609</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>25.89839154897781</v>
+        <v>25.8983915489779</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.82431759468589</v>
+        <v>26.82431759468595</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>27.61009078020989</v>
+        <v>27.61009078020994</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>28.34277284468556</v>
+        <v>28.34277284468554</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>28.93863549455284</v>
+        <v>28.93863549455281</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>29.38971940023348</v>
+        <v>29.38971940023345</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>29.65175826002295</v>
+        <v>29.65175826002287</v>
       </c>
       <c r="S35" s="1" t="inlineStr"/>
     </row>
@@ -1917,16 +1917,16 @@
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>423.4832578774369</v>
@@ -1941,7 +1941,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>570.9315691201923</v>
@@ -1976,16 +1976,16 @@
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>423.4832578774369</v>
@@ -2000,7 +2000,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>570.9315691201923</v>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>1.175559285399187</v>
+        <v>1.175559285399185</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.177149157361195</v>
+        <v>1.177149157361193</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>1.177580116958397</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.177095915781244</v>
+        <v>1.177095915781243</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.175855347567406</v>
+        <v>1.175855347567405</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.173962116210552</v>
+        <v>1.173962116210551</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.173396175963183</v>
@@ -2059,10 +2059,10 @@
         <v>1.172215437821457</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.170376301404517</v>
+        <v>1.170376301404518</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.167847518639031</v>
+        <v>1.167847518639032</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>1.164588351389238</v>
@@ -2074,7 +2074,7 @@
         <v>1.155630506097777</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>1.149848870725617</v>
+        <v>1.149848870725616</v>
       </c>
       <c r="R38" s="2" t="n">
         <v>1.143155604508661</v>
@@ -2094,22 +2094,22 @@
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>117900.225235523</v>
+        <v>117900.2252355229</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>265350.4672140714</v>
+        <v>265350.467214071</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>559906.7201888376</v>
+        <v>559906.720188837</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>706445.5229259076</v>
+        <v>706445.5229259072</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>852200.0936189106</v>
+        <v>852200.0936189099</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>998610.46481496</v>
@@ -2118,10 +2118,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1288927.093135038</v>
+        <v>1288927.093135039</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1432269.084259004</v>
+        <v>1432269.084259005</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2130,10 +2130,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1851080.725235523</v>
+        <v>1851080.725235522</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1985694.583576011</v>
+        <v>1985694.583576009</v>
       </c>
       <c r="R39" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2153,22 +2153,22 @@
       </c>
       <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>117900.225235523</v>
+        <v>117900.2252355229</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>265350.4672140714</v>
+        <v>265350.467214071</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>559906.7201888376</v>
+        <v>559906.720188837</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>706445.5229259076</v>
+        <v>706445.5229259072</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>852200.0936189106</v>
+        <v>852200.0936189099</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>998610.46481496</v>
@@ -2177,10 +2177,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1288927.093135038</v>
+        <v>1288927.093135039</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1432269.084259004</v>
+        <v>1432269.084259005</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2189,10 +2189,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1851080.725235523</v>
+        <v>1851080.725235522</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1985694.583576011</v>
+        <v>1985694.583576009</v>
       </c>
       <c r="R40" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2271,10 +2271,10 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.5338237912142</v>
+        <v>319.5338237912141</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>334.7109771300942</v>
+        <v>334.7109771300941</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>349.222944744292</v>
@@ -2295,7 +2295,7 @@
         <v>413.3312413404398</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>424.8720601328997</v>
+        <v>424.8720601328998</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>435.9907411935118</v>
@@ -2389,49 +2389,49 @@
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>0.2675658145409672</v>
+        <v>0.2675658145409686</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2627510762416364</v>
+        <v>0.2627510762416373</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2591274840795844</v>
+        <v>0.2591274840795847</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.256576799401226</v>
+        <v>0.2565767994012265</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2550220951838035</v>
+        <v>0.2550220951838037</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.254393016919423</v>
+        <v>0.2543930169194235</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.2546621015587227</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2558078397057248</v>
+        <v>0.2558078397057247</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2578470068353897</v>
+        <v>0.2578470068353892</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2608045797416076</v>
+        <v>0.2608045797416072</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2647254322067381</v>
+        <v>0.2647254322067377</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.2696810959896801</v>
+        <v>0.2696810959896802</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.2757469847403645</v>
+        <v>0.2757469847403647</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.2830232632486962</v>
+        <v>0.2830232632486964</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>0.2916156103246133</v>
+        <v>0.2916156103246137</v>
       </c>
       <c r="S44" s="1" t="inlineStr"/>
     </row>
@@ -2448,13 +2448,13 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1.180296158977294</v>
+        <v>1.180296158977292</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.175262487903347</v>
+        <v>1.175262487903346</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.168251369555617</v>
+        <v>1.168251369555616</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>1.15925817796077</v>
@@ -2463,7 +2463,7 @@
         <v>1.148224245120433</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.135081723832521</v>
+        <v>1.13508172383252</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.119697021419855</v>
@@ -2472,10 +2472,10 @@
         <v>1.101922316939652</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.081544540058967</v>
+        <v>1.081544540058968</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.058332062101629</v>
+        <v>1.05833206210163</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>1.032020278583349</v>
@@ -2484,13 +2484,13 @@
         <v>1.0023075858643</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.9689068762009189</v>
+        <v>0.9689068762009185</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.9315321714560333</v>
+        <v>0.9315321714560331</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.8899613152251319</v>
+        <v>0.8899613152251311</v>
       </c>
       <c r="S45" s="1" t="inlineStr"/>
     </row>
@@ -2566,22 +2566,22 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.6934155588636786</v>
+        <v>0.6934155588636791</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6419546944869913</v>
+        <v>0.6419546944869916</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.5966106211168183</v>
+        <v>0.5966106211168185</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5561238216798053</v>
+        <v>0.5561238216798055</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0.5198537807125588</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4871134947236217</v>
+        <v>0.4871134947236219</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4573452836046674</v>
@@ -2590,13 +2590,13 @@
         <v>0.4302607947475137</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4054971202086974</v>
+        <v>0.4054971202086972</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.382866877454614</v>
+        <v>0.3828668774546138</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3622495702925325</v>
+        <v>0.3622495702925324</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0.3434267211217917</v>
@@ -2605,10 +2605,10 @@
         <v>0.3264013915200195</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0.3111320861419942</v>
+        <v>0.3111320861419943</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0.2976385445704193</v>
+        <v>0.2976385445704194</v>
       </c>
       <c r="S47" s="1" t="inlineStr"/>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.8876763917513479</v>
+        <v>0.8876763917513484</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8476827557110529</v>
+        <v>0.8476827557110533</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.807838102390409</v>
+        <v>0.8078381023904093</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7687303178641441</v>
+        <v>0.7687303178641439</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.7310690251477328</v>
+        <v>0.7310690251477326</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.6950438015492818</v>
+        <v>0.695043801549282</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.6606666216532919</v>
@@ -2649,25 +2649,25 @@
         <v>0.6281613417983278</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.5974295303378844</v>
+        <v>0.5974295303378842</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5685574328276755</v>
+        <v>0.5685574328276751</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5416626339362809</v>
+        <v>0.5416626339362808</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>0.5165679427658935</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.4934870266617923</v>
+        <v>0.4934870266617922</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>0.4724845076896956</v>
+        <v>0.4724845076896957</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>0.4537118711400232</v>
       </c>
       <c r="S48" s="1" t="inlineStr"/>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.3009117955899137</v>
+        <v>0.3009117955899138</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0.1472682986886746</v>
@@ -2693,10 +2693,10 @@
         <v>0.1040512028785386</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.08416531485429166</v>
+        <v>0.08416531485429168</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.07304667532585596</v>
+        <v>0.07304667532585597</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>0.06619932070733821</v>
@@ -2708,7 +2708,7 @@
         <v>0.05890202559086238</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.05707687219159215</v>
+        <v>0.05707687219159214</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>0.05602993268923052</v>
@@ -2720,13 +2720,13 @@
         <v>0.0556712005930268</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.05621043688048771</v>
+        <v>0.05621043688048773</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>0.05718010096659844</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>0.05857117009930012</v>
+        <v>0.05857117009930016</v>
       </c>
       <c r="S49" s="1" t="inlineStr"/>
     </row>
@@ -2861,22 +2861,22 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6528609381672205</v>
+        <v>0.652860938167221</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.6040008906918644</v>
+        <v>0.6040008906918648</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.5608528404519376</v>
+        <v>0.5608528404519377</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.5224733005942056</v>
+        <v>0.5224733005942057</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0.4880639358485558</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4569203160469202</v>
+        <v>0.4569203160469203</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.4285352724020985</v>
@@ -2885,25 +2885,25 @@
         <v>0.4026243969644493</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.3789240751115422</v>
+        <v>0.378924075111542</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3572719824747077</v>
+        <v>0.3572719824747075</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3374139715597593</v>
+        <v>0.3374139715597592</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0.3192848027412507</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3028179399616254</v>
+        <v>0.3028179399616255</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>0.2879901483751846</v>
+        <v>0.2879901483751847</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>0.2747820638038408</v>
+        <v>0.2747820638038409</v>
       </c>
       <c r="S52" s="1" t="inlineStr"/>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.8566449408652137</v>
+        <v>0.856644940865214</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.8146305802312926</v>
+        <v>0.814630580231293</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.7734667621979159</v>
+        <v>0.773466762197916</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.7338759548743808</v>
+        <v>0.733875954874381</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0.6961191242501733</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.6601638683567802</v>
+        <v>0.6601638683567803</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6260427988521639</v>
@@ -2944,25 +2944,25 @@
         <v>0.5937907596548805</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.5634296976475788</v>
+        <v>0.5634296976475786</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.5350423151502405</v>
+        <v>0.5350423151502401</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5084161145598954</v>
+        <v>0.5084161145598953</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>0.4836795065578707</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>0.4608658406019039</v>
+        <v>0.460865840601904</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>0.4400685175575864</v>
+        <v>0.4400685175575865</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>0.4213432296968064</v>
+        <v>0.4213432296968065</v>
       </c>
       <c r="S53" s="1" t="inlineStr"/>
     </row>
@@ -2979,22 +2979,22 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2728264862976837</v>
+        <v>0.2728264862976842</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1338497572918128</v>
+        <v>0.1338497572918129</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0.09484023765812551</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.07693362720631663</v>
+        <v>0.07693362720631673</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.0669762425432088</v>
+        <v>0.06697624254320884</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.06091105339602894</v>
+        <v>0.06091105339602899</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.05699304098048162</v>
@@ -3003,10 +3003,10 @@
         <v>0.05449766392638357</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.05299351220560669</v>
+        <v>0.05299351220560665</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.05222397695379562</v>
+        <v>0.05222397695379559</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0.05206385535377919</v>
@@ -3018,10 +3018,10 @@
         <v>0.05326713372110947</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>0.05457087868506504</v>
+        <v>0.05457087868506506</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>0.05635161751966029</v>
+        <v>0.05635161751966031</v>
       </c>
       <c r="S54" s="1" t="inlineStr"/>
     </row>
@@ -3038,16 +3038,16 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5004644049712301</v>
+        <v>0.5004644049712288</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.7951571965663656</v>
+        <v>0.7951571965663653</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>0.8599102873979747</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.8880543221133667</v>
+        <v>0.8880543221133665</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0.9033251749764167</v>
@@ -3065,7 +3065,7 @@
         <v>0.9243435965300111</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9254864808911322</v>
+        <v>0.9254864808911323</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>0.9257241100343748</v>
@@ -3080,7 +3080,7 @@
         <v>0.921996524014703</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>0.9193396390285498</v>
+        <v>0.9193396390285495</v>
       </c>
       <c r="S55" s="1" t="inlineStr"/>
     </row>
@@ -3097,13 +3097,13 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7925571175792675</v>
+        <v>0.7925571175792671</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9071180477959627</v>
+        <v>0.9071180477959626</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9358895185677403</v>
+        <v>0.9358895185677402</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0.948685461697101</v>
@@ -3156,49 +3156,49 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2811863433358084</v>
+        <v>0.2811863433358094</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.3419728067953003</v>
+        <v>0.341972806795301</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.3509410655936228</v>
+        <v>0.350941065593623</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.3505057511486546</v>
+        <v>0.350505751148655</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.3468279629635574</v>
+        <v>0.3468279629635576</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.3417081181479366</v>
+        <v>0.3417081181479371</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3359234221056464</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.3297983277471504</v>
+        <v>0.3297983277471503</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.3235650470477323</v>
+        <v>0.3235650470477318</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.31739063742177</v>
+        <v>0.3173906374217697</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3114061941828092</v>
+        <v>0.3114061941828089</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.3057573784837125</v>
+        <v>0.3057573784837126</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>0.3005825024172691</v>
+        <v>0.3005825024172694</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>0.2960388638501384</v>
+        <v>0.2960388638501387</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>0.2922862607409257</v>
+        <v>0.2922862607409261</v>
       </c>
       <c r="S57" s="1" t="inlineStr"/>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.150578245989658</v>
+        <v>1.150578245989657</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1.058842137058633</v>
@@ -3224,13 +3224,13 @@
         <v>1.03259772936633</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.017231933919797</v>
+        <v>1.017231933919796</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.005239401872601</v>
+        <v>1.0052394018726</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.9944293535476197</v>
+        <v>0.9944293535476192</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.9838133341616834</v>
@@ -3239,25 +3239,25 @@
         <v>0.9729365229403433</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.9614252343707766</v>
+        <v>0.9614252343707773</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.9489575905895593</v>
+        <v>0.9489575905895599</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9352269846819268</v>
+        <v>0.9352269846819273</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.9198661432115165</v>
+        <v>0.9198661432115164</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>0.9024768235733482</v>
+        <v>0.9024768235733479</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>0.8825869545836461</v>
+        <v>0.8825869545836458</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>0.8596778720441994</v>
+        <v>0.8596778720441987</v>
       </c>
       <c r="S58" s="1" t="inlineStr"/>
     </row>
@@ -3274,22 +3274,22 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6612407210601744</v>
+        <v>0.6612407210601751</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6393366808686474</v>
+        <v>0.6393366808686478</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.6009807379947486</v>
+        <v>0.6009807379947487</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5629187482016862</v>
+        <v>0.5629187482016864</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.5272267598629743</v>
+        <v>0.5272267598629744</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.4940432659250179</v>
+        <v>0.4940432659250182</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4632008778470891</v>
@@ -3298,13 +3298,13 @@
         <v>0.434547983835321</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.4078868049211564</v>
+        <v>0.4078868049211561</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.3830869581536965</v>
+        <v>0.3830869581536963</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3598891790707875</v>
+        <v>0.3598891790707873</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>0.3382266797622753</v>
@@ -3313,10 +3313,10 @@
         <v>0.3180205486364964</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0.2992319827470267</v>
+        <v>0.2992319827470268</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0.2818236131273244</v>
+        <v>0.2818236131273246</v>
       </c>
       <c r="S59" s="1" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2707047831582408</v>
+        <v>0.2707047831582413</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.1289535490674906</v>
+        <v>0.1289535490674907</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.09035121456081503</v>
+        <v>0.09035121456081506</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.07279583956722309</v>
+        <v>0.07279583956722319</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.0630871303195517</v>
+        <v>0.06308713031955175</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.0572051495289134</v>
+        <v>0.05720514952891342</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3357,13 +3357,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.04971625102356635</v>
+        <v>0.04971625102356633</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04910680533129995</v>
+        <v>0.04910680533129991</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.04914211499311783</v>
+        <v>0.04914211499311785</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3372,10 +3372,10 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>0.05266952243484315</v>
+        <v>0.05266952243484317</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
       <c r="S60" s="1" t="inlineStr"/>
     </row>
@@ -3392,19 +3392,19 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.1289535490674906</v>
+        <v>0.1289535490674907</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.09035121456081503</v>
+        <v>0.09035121456081506</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.07279583956722309</v>
+        <v>0.07279583956722319</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0630871303195517</v>
+        <v>0.06308713031955175</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.0572051495289134</v>
+        <v>0.05720514952891342</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3413,13 +3413,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.04971625102356635</v>
+        <v>0.04971625102356633</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.04910680533129995</v>
+        <v>0.04910680533129991</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.04914211499311783</v>
+        <v>0.04914211499311785</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3428,13 +3428,13 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>0.05266952243484315</v>
+        <v>0.05266952243484317</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
       <c r="R61" s="2" t="n">
-        <v>0.05740248489946351</v>
+        <v>0.05740248489946354</v>
       </c>
       <c r="S61" s="1" t="inlineStr"/>
     </row>
@@ -3451,16 +3451,16 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5062544510926434</v>
+        <v>0.5062544510926422</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.8035709709007146</v>
+        <v>0.8035709709007143</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8670515451401452</v>
+        <v>0.8670515451401449</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8944317807808952</v>
+        <v>0.8944317807808951</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>0.9092199502745679</v>
@@ -3510,13 +3510,13 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.781132427160474</v>
+        <v>0.7811324271604738</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.8434383830980788</v>
+        <v>0.8434383830980787</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.8631690556287381</v>
+        <v>0.863169055628738</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0.8752186331837397</v>
@@ -3569,49 +3569,49 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4947976924542986</v>
+        <v>0.4947976924542974</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.4779735242447286</v>
+        <v>0.4779735242447278</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.4865582469952273</v>
+        <v>0.486558246995227</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.4994124070984718</v>
+        <v>0.4994124070984713</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>0.5137734390610369</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5288702372127254</v>
+        <v>0.5288702372127249</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5443607442121166</v>
+        <v>0.5443607442121167</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0.5600965560548041</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.5759477597191387</v>
+        <v>0.5759477597191393</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5918081993459784</v>
+        <v>0.5918081993459788</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6075771359846209</v>
+        <v>0.6075771359846212</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.6231339534389799</v>
+        <v>0.6231339534389797</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.6383608968284006</v>
+        <v>0.6383608968284005</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>0.6531207208541026</v>
+        <v>0.6531207208541023</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>0.6672755281010996</v>
+        <v>0.6672755281010991</v>
       </c>
       <c r="S64" s="1" t="inlineStr"/>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.9130337357818</v>
+        <v>0.9130337357818012</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8830355266498334</v>
+        <v>0.8830355266498343</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8530645253444216</v>
+        <v>0.8530645253444218</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.8230510799514991</v>
+        <v>0.8230510799514995</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.7929681334991677</v>
+        <v>0.7929681334991679</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7627977092904863</v>
+        <v>0.7627977092904867</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7325616461288711</v>
@@ -3652,25 +3652,25 @@
         <v>0.7022863254977531</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6720276223556498</v>
+        <v>0.6720276223556494</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6418422361217935</v>
+        <v>0.6418422361217931</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.611794636858556</v>
+        <v>0.6117946368585556</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>0.5819584578441279</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>0.552396365214525</v>
+        <v>0.5523963652145252</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0.5231726932408487</v>
+        <v>0.5231726932408488</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.4943374292495647</v>
+        <v>0.494337429249565</v>
       </c>
       <c r="S65" s="1" t="inlineStr"/>
     </row>
@@ -3746,49 +3746,49 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.149900190948778</v>
+        <v>1.149900190948777</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.037406335378524</v>
+        <v>1.037406335378523</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1.008925798296564</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9938963560643232</v>
+        <v>0.9938963560643226</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0.9831646987246834</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.9741269377820952</v>
+        <v>0.9741269377820945</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9656506714457721</v>
+        <v>0.9656506714457722</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0.9572427390595025</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.9485264056880329</v>
+        <v>0.9485264056880337</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9392010422085477</v>
+        <v>0.9392010422085484</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.9290023750862315</v>
+        <v>0.9290023750862318</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.9176220242343975</v>
+        <v>0.9176220242343971</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>0.9047385458666748</v>
+        <v>0.9047385458666746</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>0.8899750486647011</v>
+        <v>0.8899750486647007</v>
       </c>
       <c r="R67" s="2" t="n">
-        <v>0.8729257643027138</v>
+        <v>0.872925764302713</v>
       </c>
       <c r="S67" s="1" t="inlineStr"/>
     </row>
@@ -3805,22 +3805,22 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9123908734224122</v>
+        <v>0.9123908734224133</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.9132006195531562</v>
+        <v>0.9132006195531571</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.887967323159673</v>
+        <v>0.8879673231596732</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8577821070040713</v>
+        <v>0.8577821070040718</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>0.8255539583207618</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.792160112745544</v>
+        <v>0.7921601127455445</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7580358219315676</v>
@@ -3829,25 +3829,25 @@
         <v>0.72342089195214</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.6885297165190225</v>
+        <v>0.6885297165190221</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.6535447189435526</v>
+        <v>0.6535447189435523</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6186306556226798</v>
+        <v>0.6186306556226797</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.5839510578580409</v>
+        <v>0.583951057858041</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.5496458774495508</v>
+        <v>0.549645877449551</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>0.5158449565439994</v>
+        <v>0.5158449565439995</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>0.4826515564353129</v>
+        <v>0.4826515564353131</v>
       </c>
       <c r="S68" s="1" t="inlineStr"/>
     </row>
@@ -3864,49 +3864,49 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.236866455166978</v>
+        <v>0.2368664551669755</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1543708087286905</v>
+        <v>0.1543708087286889</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1558612729521429</v>
+        <v>0.1558612729521425</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1708452761128242</v>
+        <v>0.1708452761128231</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1901965652255156</v>
+        <v>0.1901965652255154</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.211329228491609</v>
+        <v>0.2113292284916077</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.233089025316901</v>
+        <v>0.2330890253169011</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0.2549564135617495</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.2764987833323831</v>
+        <v>0.2764987833323843</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.2973588060867542</v>
+        <v>0.2973588060867552</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3172077382276756</v>
+        <v>0.3172077382276762</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3356635663902696</v>
+        <v>0.3356635663902692</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.3523421806521498</v>
+        <v>0.3523421806521494</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.3668023554238524</v>
+        <v>0.3668023554238519</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.3785883350531491</v>
+        <v>0.3785883350531479</v>
       </c>
       <c r="S69" s="1" t="inlineStr"/>
     </row>
@@ -3923,22 +3923,22 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.2381873725672461</v>
+        <v>0.2381873725672434</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1456415175054772</v>
+        <v>0.1456415175054754</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.1446304062066568</v>
+        <v>0.1446304062066563</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.1594498269157253</v>
+        <v>0.1594498269157244</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.1796854435518387</v>
+        <v>0.1796854435518385</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.2022692408020758</v>
+        <v>0.2022692408020746</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.2257775122301158</v>
@@ -3947,25 +3947,25 @@
         <v>0.2495156309882033</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.2728955178517541</v>
+        <v>0.2728955178517553</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.2954128716460067</v>
+        <v>0.2954128716460076</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.316596329059247</v>
+        <v>0.3165963290592476</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.3359150853534756</v>
+        <v>0.3359150853534754</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.3528309461237974</v>
+        <v>0.352830946123797</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0.3667419980396467</v>
+        <v>0.3667419980396462</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0.3770263156088866</v>
+        <v>0.3770263156088856</v>
       </c>
       <c r="S70" s="1" t="inlineStr"/>
     </row>
@@ -3982,22 +3982,22 @@
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>251.7894146864385</v>
+        <v>251.7894146864383</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.6625952542775</v>
+        <v>249.6625952542773</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>247.6528107706313</v>
+        <v>247.6528107706312</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>245.7731838000793</v>
+        <v>245.7731838000792</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>244.0304158041251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>242.4310417988148</v>
+        <v>242.4310417988147</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>240.972909827971</v>
@@ -4006,25 +4006,25 @@
         <v>239.6524840515102</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>238.4569611637397</v>
+        <v>238.4569611637399</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>237.3706330162411</v>
+        <v>237.3706330162412</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>236.3718770966746</v>
+        <v>236.3718770966747</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>235.4310839272837</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>234.5161748631908</v>
+        <v>234.5161748631907</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>233.5872660970408</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>232.6016263665796</v>
+        <v>232.6016263665795</v>
       </c>
       <c r="S71" s="1" t="inlineStr"/>
     </row>
@@ -4100,22 +4100,22 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>247.9005511003574</v>
+        <v>247.9005511003572</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>239.722425110993</v>
+        <v>239.7224251109928</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>236.3804261005702</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>234.0471923727898</v>
+        <v>234.0471923727897</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>232.2443952114634</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>230.8447911323391</v>
+        <v>230.844791132339</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>229.7932112410973</v>
@@ -4124,10 +4124,10 @@
         <v>229.0678517566361</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>228.6458226289366</v>
+        <v>228.6458226289367</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>228.5052237669685</v>
+        <v>228.5052237669686</v>
       </c>
       <c r="N73" s="2" t="n">
         <v>228.6215960141323</v>
@@ -4142,7 +4142,7 @@
         <v>230.1629008037089</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>230.932388801264</v>
+        <v>230.9323888012639</v>
       </c>
       <c r="S73" s="1" t="inlineStr"/>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>0.9198717705829682</v>
+        <v>0.9198717705829681</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>0.9316127880691234</v>
@@ -4168,7 +4168,7 @@
         <v>0.9411937231993717</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9489889140291673</v>
+        <v>0.9489889140291672</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0.9555931563290563</v>
@@ -4183,25 +4183,25 @@
         <v>0.9700508464641263</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.9735532872138978</v>
+        <v>0.9735532872138979</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>0.9765720654514889</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9792051916840198</v>
+        <v>0.9792051916840199</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>0.9814270687200961</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.9833372387193101</v>
+        <v>0.98333723871931</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>0.9849622306534793</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0.9863414798135992</v>
+        <v>0.9863414798135991</v>
       </c>
       <c r="S74" s="1" t="inlineStr"/>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>264.9230699278949</v>
+        <v>264.9230699278948</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>294.8147930348406</v>
@@ -4254,13 +4254,13 @@
         <v>589.8572714101675</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>618.9875214592724</v>
+        <v>618.9875214592723</v>
       </c>
       <c r="Q75" s="2" t="n">
         <v>648.0388565102273</v>
       </c>
       <c r="R75" s="2" t="n">
-        <v>677.0139991251236</v>
+        <v>677.0139991251235</v>
       </c>
       <c r="S75" s="1" t="inlineStr"/>
     </row>
@@ -4336,22 +4336,22 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.8448204141343578</v>
+        <v>0.8448204141343573</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7943214505742267</v>
+        <v>0.7943214505742261</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7511095390711756</v>
+        <v>0.7511095390711755</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7135754513445642</v>
+        <v>0.7135754513445639</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6807840523057973</v>
+        <v>0.6807840523057971</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.651895609766268</v>
+        <v>0.6518956097662678</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6262006800178096</v>
@@ -4360,25 +4360,25 @@
         <v>0.6032931870271456</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.582669850624871</v>
+        <v>0.5826698506248713</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5640185684375758</v>
+        <v>0.5640185684375761</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5470938594252941</v>
+        <v>0.5470938594252943</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.5314851030679409</v>
+        <v>0.5314851030679412</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>0.5170517482371183</v>
+        <v>0.5170517482371181</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>0.5035581698659797</v>
+        <v>0.5035581698659796</v>
       </c>
       <c r="R77" s="2" t="n">
-        <v>0.4908332230905137</v>
+        <v>0.4908332230905135</v>
       </c>
       <c r="S77" s="1" t="inlineStr"/>
     </row>
@@ -4395,22 +4395,22 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7758194364498247</v>
+        <v>0.7758194364498243</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7162072399490459</v>
+        <v>0.7162072399490456</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.6768754162864432</v>
+        <v>0.6768754162864431</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6446312378490995</v>
+        <v>0.6446312378490993</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0.6171656544030198</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.5933516387160817</v>
+        <v>0.5933516387160813</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.5724800026430085</v>
@@ -4419,13 +4419,13 @@
         <v>0.5541992204938717</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5381521735211686</v>
+        <v>0.5381521735211688</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.5241056797248543</v>
+        <v>0.5241056797248544</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5116577227873375</v>
+        <v>0.5116577227873376</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>0.5006277313683627</v>
@@ -4434,10 +4434,10 @@
         <v>0.4908125161156869</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0.4820311420268309</v>
+        <v>0.4820311420268308</v>
       </c>
       <c r="R78" s="2" t="n">
-        <v>0.474084587425221</v>
+        <v>0.4740845874252208</v>
       </c>
       <c r="S78" s="1" t="inlineStr"/>
     </row>
@@ -4454,16 +4454,16 @@
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>423.4832578774369</v>
@@ -4478,7 +4478,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>570.9315691201923</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.9001179490256411</v>
+        <v>0.9001179490256412</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9152540141204015</v>
+        <v>0.9152540141204016</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>0.9244318040653919</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.9317173785273669</v>
+        <v>0.931717378527367</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0.937726382807626</v>
@@ -4543,7 +4543,7 @@
         <v>0.9564711798415051</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9587739854529909</v>
+        <v>0.9587739854529908</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0.9608011997304212</v>
@@ -4572,16 +4572,16 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>617.8311110563023</v>
+        <v>617.8311110563025</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>628.2203405174404</v>
+        <v>628.2203405174405</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>634.5198751116486</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>639.5206137030721</v>
+        <v>639.5206137030722</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>643.6451284900878</v>
@@ -4602,7 +4602,7 @@
         <v>656.5113520672343</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>658.0919726414946</v>
+        <v>658.0919726414945</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>659.4834303395994</v>
@@ -4634,7 +4634,7 @@
         <v>455.0748040551998</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>458.7438421848687</v>
+        <v>458.7438421848688</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>460.9384929530079</v>
@@ -4661,7 +4661,7 @@
         <v>467.6634924923767</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>467.9889608220808</v>
+        <v>467.9889608220807</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>468.2745682991455</v>
@@ -4690,22 +4690,22 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.5447468172074134</v>
+        <v>0.5447468172074129</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5225627094398959</v>
+        <v>0.5225627094398955</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0.5128242264736803</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.5058701247484856</v>
+        <v>0.5058701247484854</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0.500517867126743</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4963537393673502</v>
+        <v>0.4963537393673499</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.4931527461005401</v>
@@ -4714,13 +4714,13 @@
         <v>0.4908656433918407</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.4893667613005351</v>
+        <v>0.4893667613005354</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.4886103521768771</v>
+        <v>0.4886103521768774</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4885192069755876</v>
+        <v>0.4885192069755879</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>0.4889480192746724</v>
@@ -4729,10 +4729,10 @@
         <v>0.4898496347186731</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>0.4911141294015546</v>
+        <v>0.4911141294015545</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>0.4926388829310537</v>
+        <v>0.4926388829310535</v>
       </c>
       <c r="S83" s="1" t="inlineStr"/>
     </row>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -431,7 +431,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -439,8 +439,8 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
@@ -849,7 +849,7 @@
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="2" t="n">
-        <v>0.4537118711400233</v>
+        <v>0.4537118711400231</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -880,7 +880,7 @@
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="2" t="n">
-        <v>0.05503600366715335</v>
+        <v>0.05503600366715333</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -942,7 +942,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="2" t="n">
-        <v>0.05503600366715335</v>
+        <v>0.05503600366715333</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -973,7 +973,7 @@
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="2" t="n">
-        <v>0.3446443080405244</v>
+        <v>0.3446443080405253</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1004,7 +1004,7 @@
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="2" t="n">
-        <v>0.5062544510926422</v>
+        <v>0.5062544510926434</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1035,7 +1035,7 @@
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="2" t="n">
-        <v>0.7925571175792671</v>
+        <v>0.7925571175792675</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1066,7 +1066,7 @@
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="2" t="n">
-        <v>0.8596778720441987</v>
+        <v>0.8596778720441994</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1097,7 +1097,7 @@
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="2" t="n">
-        <v>0.7111184547506979</v>
+        <v>0.7111184547506971</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1128,7 +1128,7 @@
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="2" t="n">
-        <v>141.4703657841592</v>
+        <v>141.4703657841591</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1252,7 +1252,7 @@
       <c r="Q24" s="1" t="inlineStr"/>
       <c r="R24" s="1" t="inlineStr"/>
       <c r="S24" s="2" t="n">
-        <v>0.1680642932462094</v>
+        <v>0.168064293246209</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1681,49 +1681,49 @@
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16967.12604306353</v>
+        <v>16967.12604306373</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18630.78159247993</v>
+        <v>18630.78159248007</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20218.56077089675</v>
+        <v>20218.5607708968</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21743.63912220303</v>
+        <v>21743.63912220311</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23213.05010780867</v>
+        <v>23213.0501078087</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24632.76848581409</v>
+        <v>24632.76848581418</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26002.02390990612</v>
+        <v>26002.0239099061</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>27318.78381964874</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>28574.47174295066</v>
+        <v>28574.47174295057</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29758.48274205857</v>
+        <v>29758.48274205851</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>30856.11876136265</v>
+        <v>30856.11876136259</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31847.15753258981</v>
+        <v>31847.15753258983</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>32709.42570822141</v>
+        <v>32709.42570822144</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>33415.02270248363</v>
+        <v>33415.02270248366</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>33933.38931404923</v>
+        <v>33933.38931404932</v>
       </c>
       <c r="S32" s="1" t="inlineStr"/>
     </row>
@@ -1740,49 +1740,49 @@
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>16797.4547826329</v>
+        <v>16797.45478263309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18258.16596063033</v>
+        <v>18258.16596063047</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>19612.00394776985</v>
+        <v>19612.0039477699</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20873.89355731491</v>
+        <v>20873.89355731498</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>22052.39760241824</v>
+        <v>22052.39760241826</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23154.80237666525</v>
+        <v>23154.80237666533</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24441.90247531175</v>
+        <v>24441.90247531174</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>25679.65679046982</v>
+        <v>25679.65679046981</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>26860.00343837362</v>
+        <v>26860.00343837353</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27972.97377753505</v>
+        <v>27972.97377753499</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>29004.75163568088</v>
+        <v>29004.75163568083</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>29936.32808063442</v>
+        <v>29936.32808063443</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>30746.86016572812</v>
+        <v>30746.86016572815</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>31410.12134033461</v>
+        <v>31410.12134033464</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>31897.38595520627</v>
+        <v>31897.38595520635</v>
       </c>
       <c r="S33" s="1" t="inlineStr"/>
     </row>
@@ -1799,49 +1799,49 @@
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>13701.87693398587</v>
+        <v>13701.87693398603</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15183.18715242563</v>
+        <v>15183.18715242576</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16585.02366398539</v>
+        <v>16585.02366398544</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>17906.5231284628</v>
+        <v>17906.52312846286</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19142.33211474172</v>
+        <v>19142.33211474175</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20287.4065673813</v>
+        <v>20287.40656738138</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>21560.80915145568</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22748.1208072058</v>
+        <v>22748.12080720581</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23831.00891765527</v>
+        <v>23831.00891765521</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24789.99333265438</v>
+        <v>24789.99333265435</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>25602.74626396982</v>
+        <v>25602.7462639698</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>26243.62718943147</v>
+        <v>26243.62718943152</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>26686.8166302572</v>
+        <v>26686.81663025726</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>26904.66888708486</v>
+        <v>26904.66888708492</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>26870.38869889738</v>
+        <v>26870.38869889748</v>
       </c>
       <c r="S34" s="1" t="inlineStr"/>
     </row>
@@ -1858,49 +1858,49 @@
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>16.69727115569871</v>
+        <v>16.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.08373681547265</v>
+        <v>18.08373681547279</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19.35093521240866</v>
+        <v>19.35093521240871</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.5667342483578</v>
+        <v>20.56673424835787</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.65781275498965</v>
+        <v>21.65781275498967</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.64232024894005</v>
+        <v>22.64232024894013</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23.81327704394782</v>
+        <v>23.81327704394781</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>24.88456689222609</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>25.8983915489779</v>
+        <v>25.89839154897781</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.82431759468595</v>
+        <v>26.82431759468589</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>27.61009078020994</v>
+        <v>27.61009078020989</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>28.34277284468554</v>
+        <v>28.34277284468556</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>28.93863549455281</v>
+        <v>28.93863549455284</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>29.38971940023345</v>
+        <v>29.38971940023348</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>29.65175826002287</v>
+        <v>29.65175826002295</v>
       </c>
       <c r="S35" s="1" t="inlineStr"/>
     </row>
@@ -1917,16 +1917,16 @@
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>334.5400980960845</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>364.2636577736323</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>393.9358180901933</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>423.4832578774369</v>
@@ -1941,7 +1941,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>541.5492817938724</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>570.9315691201923</v>
@@ -1976,16 +1976,16 @@
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>334.5400980960845</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>364.2636577736323</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>393.9358180901933</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>423.4832578774369</v>
@@ -2000,7 +2000,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>541.5492817938724</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>570.9315691201923</v>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>1.175559285399185</v>
+        <v>1.175559285399187</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.177149157361193</v>
+        <v>1.177149157361195</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>1.177580116958397</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.177095915781243</v>
+        <v>1.177095915781244</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.175855347567405</v>
+        <v>1.175855347567406</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.173962116210551</v>
+        <v>1.173962116210552</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.173396175963183</v>
@@ -2059,10 +2059,10 @@
         <v>1.172215437821457</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.170376301404518</v>
+        <v>1.170376301404517</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.167847518639032</v>
+        <v>1.167847518639031</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>1.164588351389238</v>
@@ -2074,7 +2074,7 @@
         <v>1.155630506097777</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>1.149848870725616</v>
+        <v>1.149848870725617</v>
       </c>
       <c r="R38" s="2" t="n">
         <v>1.143155604508661</v>
@@ -2094,22 +2094,22 @@
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>117900.2252355229</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>265350.467214071</v>
+        <v>265350.4672140714</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>559906.720188837</v>
+        <v>559906.7201888376</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>706445.5229259072</v>
+        <v>706445.5229259076</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>852200.0936189099</v>
+        <v>852200.0936189106</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>998610.46481496</v>
@@ -2118,10 +2118,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1288927.093135039</v>
+        <v>1288927.093135038</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1432269.084259005</v>
+        <v>1432269.084259004</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2130,10 +2130,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1851080.725235522</v>
+        <v>1851080.725235523</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1985694.583576009</v>
+        <v>1985694.583576011</v>
       </c>
       <c r="R39" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2153,22 +2153,22 @@
       </c>
       <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>117900.2252355229</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>265350.467214071</v>
+        <v>265350.4672140714</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>559906.720188837</v>
+        <v>559906.7201888376</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>706445.5229259072</v>
+        <v>706445.5229259076</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>852200.0936189099</v>
+        <v>852200.0936189106</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>998610.46481496</v>
@@ -2177,10 +2177,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1288927.093135039</v>
+        <v>1288927.093135038</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1432269.084259005</v>
+        <v>1432269.084259004</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2189,10 +2189,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1851080.725235522</v>
+        <v>1851080.725235523</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1985694.583576009</v>
+        <v>1985694.583576011</v>
       </c>
       <c r="R40" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2271,10 +2271,10 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.5338237912141</v>
+        <v>319.5338237912142</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>334.7109771300941</v>
+        <v>334.7109771300942</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>349.222944744292</v>
@@ -2295,7 +2295,7 @@
         <v>413.3312413404398</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>424.8720601328998</v>
+        <v>424.8720601328997</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>435.9907411935118</v>
@@ -2389,49 +2389,49 @@
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>0.2675658145409686</v>
+        <v>0.2675658145409672</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2627510762416373</v>
+        <v>0.2627510762416364</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2591274840795847</v>
+        <v>0.2591274840795844</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.2565767994012265</v>
+        <v>0.256576799401226</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2550220951838037</v>
+        <v>0.2550220951838035</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.2543930169194235</v>
+        <v>0.254393016919423</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.2546621015587227</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2558078397057247</v>
+        <v>0.2558078397057248</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2578470068353892</v>
+        <v>0.2578470068353897</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2608045797416072</v>
+        <v>0.2608045797416076</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2647254322067377</v>
+        <v>0.2647254322067381</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.2696810959896802</v>
+        <v>0.2696810959896801</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.2757469847403647</v>
+        <v>0.2757469847403645</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.2830232632486964</v>
+        <v>0.2830232632486962</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>0.2916156103246137</v>
+        <v>0.2916156103246133</v>
       </c>
       <c r="S44" s="1" t="inlineStr"/>
     </row>
@@ -2448,13 +2448,13 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1.180296158977292</v>
+        <v>1.180296158977294</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.175262487903346</v>
+        <v>1.175262487903347</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.168251369555616</v>
+        <v>1.168251369555617</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>1.15925817796077</v>
@@ -2463,7 +2463,7 @@
         <v>1.148224245120433</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.13508172383252</v>
+        <v>1.135081723832521</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.119697021419855</v>
@@ -2472,10 +2472,10 @@
         <v>1.101922316939652</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.081544540058968</v>
+        <v>1.081544540058967</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.05833206210163</v>
+        <v>1.058332062101629</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>1.032020278583349</v>
@@ -2484,13 +2484,13 @@
         <v>1.0023075858643</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.9689068762009185</v>
+        <v>0.9689068762009189</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.9315321714560331</v>
+        <v>0.9315321714560333</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.8899613152251311</v>
+        <v>0.8899613152251319</v>
       </c>
       <c r="S45" s="1" t="inlineStr"/>
     </row>
@@ -2566,22 +2566,22 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.6934155588636791</v>
+        <v>0.6934155588636786</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6419546944869916</v>
+        <v>0.6419546944869913</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.5966106211168185</v>
+        <v>0.5966106211168183</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5561238216798055</v>
+        <v>0.5561238216798053</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0.5198537807125588</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4871134947236219</v>
+        <v>0.4871134947236217</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4573452836046674</v>
@@ -2590,13 +2590,13 @@
         <v>0.4302607947475137</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4054971202086972</v>
+        <v>0.4054971202086974</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.3828668774546138</v>
+        <v>0.382866877454614</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3622495702925324</v>
+        <v>0.3622495702925325</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0.3434267211217917</v>
@@ -2605,10 +2605,10 @@
         <v>0.3264013915200195</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0.3111320861419943</v>
+        <v>0.3111320861419942</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0.2976385445704194</v>
+        <v>0.2976385445704193</v>
       </c>
       <c r="S47" s="1" t="inlineStr"/>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.8876763917513484</v>
+        <v>0.8876763917513479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8476827557110533</v>
+        <v>0.8476827557110529</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.8078381023904093</v>
+        <v>0.807838102390409</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7687303178641439</v>
+        <v>0.7687303178641441</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.7310690251477326</v>
+        <v>0.7310690251477328</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.695043801549282</v>
+        <v>0.6950438015492818</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.6606666216532919</v>
@@ -2649,25 +2649,25 @@
         <v>0.6281613417983278</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.5974295303378842</v>
+        <v>0.5974295303378844</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5685574328276751</v>
+        <v>0.5685574328276755</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5416626339362808</v>
+        <v>0.5416626339362809</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>0.5165679427658935</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.4934870266617922</v>
+        <v>0.4934870266617923</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>0.4724845076896957</v>
+        <v>0.4724845076896956</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>0.4537118711400232</v>
+        <v>0.4537118711400231</v>
       </c>
       <c r="S48" s="1" t="inlineStr"/>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.3009117955899138</v>
+        <v>0.3009117955899137</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0.1472682986886746</v>
@@ -2693,10 +2693,10 @@
         <v>0.1040512028785386</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.08416531485429168</v>
+        <v>0.08416531485429166</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.07304667532585597</v>
+        <v>0.07304667532585596</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>0.06619932070733821</v>
@@ -2708,7 +2708,7 @@
         <v>0.05890202559086238</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.05707687219159214</v>
+        <v>0.05707687219159215</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>0.05602993268923052</v>
@@ -2720,13 +2720,13 @@
         <v>0.0556712005930268</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.05621043688048773</v>
+        <v>0.05621043688048771</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>0.05718010096659844</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>0.05857117009930016</v>
+        <v>0.05857117009930012</v>
       </c>
       <c r="S49" s="1" t="inlineStr"/>
     </row>
@@ -2861,22 +2861,22 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.652860938167221</v>
+        <v>0.6528609381672205</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.6040008906918648</v>
+        <v>0.6040008906918644</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.5608528404519377</v>
+        <v>0.5608528404519376</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.5224733005942057</v>
+        <v>0.5224733005942056</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0.4880639358485558</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4569203160469203</v>
+        <v>0.4569203160469202</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.4285352724020985</v>
@@ -2885,25 +2885,25 @@
         <v>0.4026243969644493</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.378924075111542</v>
+        <v>0.3789240751115422</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3572719824747075</v>
+        <v>0.3572719824747077</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3374139715597592</v>
+        <v>0.3374139715597593</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0.3192848027412507</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3028179399616255</v>
+        <v>0.3028179399616254</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>0.2879901483751847</v>
+        <v>0.2879901483751846</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>0.2747820638038409</v>
+        <v>0.2747820638038408</v>
       </c>
       <c r="S52" s="1" t="inlineStr"/>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.856644940865214</v>
+        <v>0.8566449408652137</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.814630580231293</v>
+        <v>0.8146305802312926</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.773466762197916</v>
+        <v>0.7734667621979159</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.733875954874381</v>
+        <v>0.7338759548743808</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0.6961191242501733</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.6601638683567803</v>
+        <v>0.6601638683567802</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6260427988521639</v>
@@ -2944,25 +2944,25 @@
         <v>0.5937907596548805</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.5634296976475786</v>
+        <v>0.5634296976475788</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.5350423151502401</v>
+        <v>0.5350423151502405</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5084161145598953</v>
+        <v>0.5084161145598954</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>0.4836795065578707</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>0.460865840601904</v>
+        <v>0.4608658406019039</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>0.4400685175575865</v>
+        <v>0.4400685175575864</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>0.4213432296968065</v>
+        <v>0.4213432296968064</v>
       </c>
       <c r="S53" s="1" t="inlineStr"/>
     </row>
@@ -2979,22 +2979,22 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2728264862976842</v>
+        <v>0.2728264862976837</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1338497572918129</v>
+        <v>0.1338497572918128</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0.09484023765812551</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.07693362720631673</v>
+        <v>0.07693362720631663</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.06697624254320884</v>
+        <v>0.0669762425432088</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.06091105339602899</v>
+        <v>0.06091105339602894</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.05699304098048162</v>
@@ -3003,10 +3003,10 @@
         <v>0.05449766392638357</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.05299351220560665</v>
+        <v>0.05299351220560669</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.05222397695379559</v>
+        <v>0.05222397695379562</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0.05206385535377919</v>
@@ -3018,10 +3018,10 @@
         <v>0.05326713372110947</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>0.05457087868506506</v>
+        <v>0.05457087868506504</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>0.05635161751966031</v>
+        <v>0.05635161751966029</v>
       </c>
       <c r="S54" s="1" t="inlineStr"/>
     </row>
@@ -3038,16 +3038,16 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5004644049712288</v>
+        <v>0.5004644049712301</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.7951571965663653</v>
+        <v>0.7951571965663656</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>0.8599102873979747</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.8880543221133665</v>
+        <v>0.8880543221133667</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0.9033251749764167</v>
@@ -3065,7 +3065,7 @@
         <v>0.9243435965300111</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9254864808911323</v>
+        <v>0.9254864808911322</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>0.9257241100343748</v>
@@ -3080,7 +3080,7 @@
         <v>0.921996524014703</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>0.9193396390285495</v>
+        <v>0.9193396390285498</v>
       </c>
       <c r="S55" s="1" t="inlineStr"/>
     </row>
@@ -3097,13 +3097,13 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7925571175792671</v>
+        <v>0.7925571175792675</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9071180477959626</v>
+        <v>0.9071180477959627</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9358895185677402</v>
+        <v>0.9358895185677403</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0.948685461697101</v>
@@ -3156,49 +3156,49 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2811863433358094</v>
+        <v>0.2811863433358084</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.341972806795301</v>
+        <v>0.3419728067953003</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.350941065593623</v>
+        <v>0.3509410655936228</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.350505751148655</v>
+        <v>0.3505057511486546</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.3468279629635576</v>
+        <v>0.3468279629635574</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.3417081181479371</v>
+        <v>0.3417081181479366</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3359234221056464</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.3297983277471503</v>
+        <v>0.3297983277471504</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.3235650470477318</v>
+        <v>0.3235650470477323</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.3173906374217697</v>
+        <v>0.31739063742177</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3114061941828089</v>
+        <v>0.3114061941828092</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.3057573784837126</v>
+        <v>0.3057573784837125</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>0.3005825024172694</v>
+        <v>0.3005825024172691</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>0.2960388638501387</v>
+        <v>0.2960388638501384</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>0.2922862607409261</v>
+        <v>0.2922862607409257</v>
       </c>
       <c r="S57" s="1" t="inlineStr"/>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.150578245989657</v>
+        <v>1.150578245989658</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1.058842137058633</v>
@@ -3224,13 +3224,13 @@
         <v>1.03259772936633</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.017231933919796</v>
+        <v>1.017231933919797</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.0052394018726</v>
+        <v>1.005239401872601</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.9944293535476192</v>
+        <v>0.9944293535476197</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.9838133341616834</v>
@@ -3239,25 +3239,25 @@
         <v>0.9729365229403433</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.9614252343707773</v>
+        <v>0.9614252343707766</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.9489575905895599</v>
+        <v>0.9489575905895593</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9352269846819273</v>
+        <v>0.9352269846819268</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.9198661432115164</v>
+        <v>0.9198661432115165</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>0.9024768235733479</v>
+        <v>0.9024768235733482</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>0.8825869545836458</v>
+        <v>0.8825869545836461</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>0.8596778720441987</v>
+        <v>0.8596778720441994</v>
       </c>
       <c r="S58" s="1" t="inlineStr"/>
     </row>
@@ -3274,22 +3274,22 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6612407210601751</v>
+        <v>0.6612407210601744</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6393366808686478</v>
+        <v>0.6393366808686474</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.6009807379947487</v>
+        <v>0.6009807379947486</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5629187482016864</v>
+        <v>0.5629187482016862</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.5272267598629744</v>
+        <v>0.5272267598629743</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.4940432659250182</v>
+        <v>0.4940432659250179</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4632008778470891</v>
@@ -3298,13 +3298,13 @@
         <v>0.434547983835321</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.4078868049211561</v>
+        <v>0.4078868049211564</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.3830869581536963</v>
+        <v>0.3830869581536965</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3598891790707873</v>
+        <v>0.3598891790707875</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>0.3382266797622753</v>
@@ -3313,10 +3313,10 @@
         <v>0.3180205486364964</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0.2992319827470268</v>
+        <v>0.2992319827470267</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0.2818236131273246</v>
+        <v>0.2818236131273244</v>
       </c>
       <c r="S59" s="1" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2707047831582413</v>
+        <v>0.2707047831582408</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.1289535490674907</v>
+        <v>0.1289535490674906</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.09035121456081506</v>
+        <v>0.09035121456081503</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.07279583956722319</v>
+        <v>0.07279583956722309</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.06308713031955175</v>
+        <v>0.0630871303195517</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.05720514952891342</v>
+        <v>0.0572051495289134</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3357,13 +3357,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.04971625102356633</v>
+        <v>0.04971625102356635</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04910680533129991</v>
+        <v>0.04910680533129995</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.04914211499311785</v>
+        <v>0.04914211499311783</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3372,10 +3372,10 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>0.05266952243484317</v>
+        <v>0.05266952243484315</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>0.05503600366715335</v>
+        <v>0.05503600366715333</v>
       </c>
       <c r="S60" s="1" t="inlineStr"/>
     </row>
@@ -3392,19 +3392,19 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.1289535490674907</v>
+        <v>0.1289535490674906</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.09035121456081506</v>
+        <v>0.09035121456081503</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.07279583956722319</v>
+        <v>0.07279583956722309</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.06308713031955175</v>
+        <v>0.0630871303195517</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.05720514952891342</v>
+        <v>0.0572051495289134</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3413,13 +3413,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.04971625102356633</v>
+        <v>0.04971625102356635</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.04910680533129991</v>
+        <v>0.04910680533129995</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.04914211499311785</v>
+        <v>0.04914211499311783</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3428,13 +3428,13 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>0.05266952243484317</v>
+        <v>0.05266952243484315</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>0.05503600366715335</v>
+        <v>0.05503600366715333</v>
       </c>
       <c r="R61" s="2" t="n">
-        <v>0.05740248489946354</v>
+        <v>0.05740248489946351</v>
       </c>
       <c r="S61" s="1" t="inlineStr"/>
     </row>
@@ -3451,16 +3451,16 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5062544510926422</v>
+        <v>0.5062544510926434</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.8035709709007143</v>
+        <v>0.8035709709007146</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8670515451401449</v>
+        <v>0.8670515451401452</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8944317807808951</v>
+        <v>0.8944317807808952</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>0.9092199502745679</v>
@@ -3510,13 +3510,13 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.7811324271604738</v>
+        <v>0.781132427160474</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.8434383830980787</v>
+        <v>0.8434383830980788</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.863169055628738</v>
+        <v>0.8631690556287381</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0.8752186331837397</v>
@@ -3569,49 +3569,49 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4947976924542974</v>
+        <v>0.4947976924542986</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.4779735242447278</v>
+        <v>0.4779735242447286</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.486558246995227</v>
+        <v>0.4865582469952273</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.4994124070984713</v>
+        <v>0.4994124070984718</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>0.5137734390610369</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5288702372127249</v>
+        <v>0.5288702372127254</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5443607442121167</v>
+        <v>0.5443607442121166</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0.5600965560548041</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.5759477597191393</v>
+        <v>0.5759477597191387</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5918081993459788</v>
+        <v>0.5918081993459784</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6075771359846212</v>
+        <v>0.6075771359846209</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.6231339534389797</v>
+        <v>0.6231339534389799</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.6383608968284005</v>
+        <v>0.6383608968284006</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>0.6531207208541023</v>
+        <v>0.6531207208541026</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>0.6672755281010991</v>
+        <v>0.6672755281010996</v>
       </c>
       <c r="S64" s="1" t="inlineStr"/>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.9130337357818012</v>
+        <v>0.9130337357818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8830355266498343</v>
+        <v>0.8830355266498334</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8530645253444218</v>
+        <v>0.8530645253444216</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.8230510799514995</v>
+        <v>0.8230510799514991</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.7929681334991679</v>
+        <v>0.7929681334991677</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7627977092904867</v>
+        <v>0.7627977092904863</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7325616461288711</v>
@@ -3652,25 +3652,25 @@
         <v>0.7022863254977531</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6720276223556494</v>
+        <v>0.6720276223556498</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6418422361217931</v>
+        <v>0.6418422361217935</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6117946368585556</v>
+        <v>0.611794636858556</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>0.5819584578441279</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>0.5523963652145252</v>
+        <v>0.552396365214525</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0.5231726932408488</v>
+        <v>0.5231726932408487</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.494337429249565</v>
+        <v>0.4943374292495647</v>
       </c>
       <c r="S65" s="1" t="inlineStr"/>
     </row>
@@ -3746,49 +3746,49 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.149900190948777</v>
+        <v>1.149900190948778</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.037406335378523</v>
+        <v>1.037406335378524</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1.008925798296564</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9938963560643226</v>
+        <v>0.9938963560643232</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0.9831646987246834</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.9741269377820945</v>
+        <v>0.9741269377820952</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9656506714457722</v>
+        <v>0.9656506714457721</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0.9572427390595025</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.9485264056880337</v>
+        <v>0.9485264056880329</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9392010422085484</v>
+        <v>0.9392010422085477</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.9290023750862318</v>
+        <v>0.9290023750862315</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.9176220242343971</v>
+        <v>0.9176220242343975</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>0.9047385458666746</v>
+        <v>0.9047385458666748</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>0.8899750486647007</v>
+        <v>0.8899750486647011</v>
       </c>
       <c r="R67" s="2" t="n">
-        <v>0.872925764302713</v>
+        <v>0.8729257643027138</v>
       </c>
       <c r="S67" s="1" t="inlineStr"/>
     </row>
@@ -3805,22 +3805,22 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9123908734224133</v>
+        <v>0.9123908734224122</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.9132006195531571</v>
+        <v>0.9132006195531562</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.8879673231596732</v>
+        <v>0.887967323159673</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8577821070040718</v>
+        <v>0.8577821070040713</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>0.8255539583207618</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.7921601127455445</v>
+        <v>0.792160112745544</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7580358219315676</v>
@@ -3829,25 +3829,25 @@
         <v>0.72342089195214</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.6885297165190221</v>
+        <v>0.6885297165190225</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.6535447189435523</v>
+        <v>0.6535447189435526</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6186306556226797</v>
+        <v>0.6186306556226798</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.583951057858041</v>
+        <v>0.5839510578580409</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.549645877449551</v>
+        <v>0.5496458774495508</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>0.5158449565439995</v>
+        <v>0.5158449565439994</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>0.4826515564353131</v>
+        <v>0.4826515564353129</v>
       </c>
       <c r="S68" s="1" t="inlineStr"/>
     </row>
@@ -3864,49 +3864,49 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2368664551669755</v>
+        <v>0.236866455166978</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1543708087286889</v>
+        <v>0.1543708087286905</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1558612729521425</v>
+        <v>0.1558612729521429</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1708452761128231</v>
+        <v>0.1708452761128242</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1901965652255154</v>
+        <v>0.1901965652255156</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.2113292284916077</v>
+        <v>0.211329228491609</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2330890253169011</v>
+        <v>0.233089025316901</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0.2549564135617495</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.2764987833323843</v>
+        <v>0.2764987833323831</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.2973588060867552</v>
+        <v>0.2973588060867542</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3172077382276762</v>
+        <v>0.3172077382276756</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3356635663902692</v>
+        <v>0.3356635663902696</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.3523421806521494</v>
+        <v>0.3523421806521498</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.3668023554238519</v>
+        <v>0.3668023554238524</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.3785883350531479</v>
+        <v>0.3785883350531491</v>
       </c>
       <c r="S69" s="1" t="inlineStr"/>
     </row>
@@ -3923,22 +3923,22 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.2381873725672434</v>
+        <v>0.2381873725672461</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1456415175054754</v>
+        <v>0.1456415175054772</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.1446304062066563</v>
+        <v>0.1446304062066568</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.1594498269157244</v>
+        <v>0.1594498269157253</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.1796854435518385</v>
+        <v>0.1796854435518387</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.2022692408020746</v>
+        <v>0.2022692408020758</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.2257775122301158</v>
@@ -3947,25 +3947,25 @@
         <v>0.2495156309882033</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.2728955178517553</v>
+        <v>0.2728955178517541</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.2954128716460076</v>
+        <v>0.2954128716460067</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3165963290592476</v>
+        <v>0.316596329059247</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.3359150853534754</v>
+        <v>0.3359150853534756</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.352830946123797</v>
+        <v>0.3528309461237974</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0.3667419980396462</v>
+        <v>0.3667419980396467</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0.3770263156088856</v>
+        <v>0.3770263156088866</v>
       </c>
       <c r="S70" s="1" t="inlineStr"/>
     </row>
@@ -3982,22 +3982,22 @@
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>251.7894146864383</v>
+        <v>251.7894146864385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.6625952542773</v>
+        <v>249.6625952542775</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>247.6528107706312</v>
+        <v>247.6528107706313</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>245.7731838000792</v>
+        <v>245.7731838000793</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>244.0304158041251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>242.4310417988147</v>
+        <v>242.4310417988148</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>240.972909827971</v>
@@ -4006,25 +4006,25 @@
         <v>239.6524840515102</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>238.4569611637399</v>
+        <v>238.4569611637397</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>237.3706330162412</v>
+        <v>237.3706330162411</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>236.3718770966747</v>
+        <v>236.3718770966746</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>235.4310839272837</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>234.5161748631907</v>
+        <v>234.5161748631908</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>233.5872660970408</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>232.6016263665795</v>
+        <v>232.6016263665796</v>
       </c>
       <c r="S71" s="1" t="inlineStr"/>
     </row>
@@ -4100,22 +4100,22 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>247.9005511003572</v>
+        <v>247.9005511003574</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>239.7224251109928</v>
+        <v>239.722425110993</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>236.3804261005702</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>234.0471923727897</v>
+        <v>234.0471923727898</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>232.2443952114634</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>230.844791132339</v>
+        <v>230.8447911323391</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>229.7932112410973</v>
@@ -4124,10 +4124,10 @@
         <v>229.0678517566361</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>228.6458226289367</v>
+        <v>228.6458226289366</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>228.5052237669686</v>
+        <v>228.5052237669685</v>
       </c>
       <c r="N73" s="2" t="n">
         <v>228.6215960141323</v>
@@ -4142,7 +4142,7 @@
         <v>230.1629008037089</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>230.9323888012639</v>
+        <v>230.932388801264</v>
       </c>
       <c r="S73" s="1" t="inlineStr"/>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>0.9198717705829681</v>
+        <v>0.9198717705829682</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>0.9316127880691234</v>
@@ -4168,7 +4168,7 @@
         <v>0.9411937231993717</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9489889140291672</v>
+        <v>0.9489889140291673</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0.9555931563290563</v>
@@ -4183,25 +4183,25 @@
         <v>0.9700508464641263</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.9735532872138979</v>
+        <v>0.9735532872138978</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>0.9765720654514889</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9792051916840199</v>
+        <v>0.9792051916840198</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>0.9814270687200961</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.98333723871931</v>
+        <v>0.9833372387193101</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>0.9849622306534793</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0.9863414798135991</v>
+        <v>0.9863414798135992</v>
       </c>
       <c r="S74" s="1" t="inlineStr"/>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>264.9230699278948</v>
+        <v>264.9230699278949</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>294.8147930348406</v>
@@ -4254,13 +4254,13 @@
         <v>589.8572714101675</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>618.9875214592723</v>
+        <v>618.9875214592724</v>
       </c>
       <c r="Q75" s="2" t="n">
         <v>648.0388565102273</v>
       </c>
       <c r="R75" s="2" t="n">
-        <v>677.0139991251235</v>
+        <v>677.0139991251236</v>
       </c>
       <c r="S75" s="1" t="inlineStr"/>
     </row>
@@ -4336,22 +4336,22 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.8448204141343573</v>
+        <v>0.8448204141343578</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7943214505742261</v>
+        <v>0.7943214505742267</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7511095390711755</v>
+        <v>0.7511095390711756</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7135754513445639</v>
+        <v>0.7135754513445642</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6807840523057971</v>
+        <v>0.6807840523057973</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.6518956097662678</v>
+        <v>0.651895609766268</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6262006800178096</v>
@@ -4360,25 +4360,25 @@
         <v>0.6032931870271456</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.5826698506248713</v>
+        <v>0.582669850624871</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5640185684375761</v>
+        <v>0.5640185684375758</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5470938594252943</v>
+        <v>0.5470938594252941</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.5314851030679412</v>
+        <v>0.5314851030679409</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>0.5170517482371181</v>
+        <v>0.5170517482371183</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>0.5035581698659796</v>
+        <v>0.5035581698659797</v>
       </c>
       <c r="R77" s="2" t="n">
-        <v>0.4908332230905135</v>
+        <v>0.4908332230905137</v>
       </c>
       <c r="S77" s="1" t="inlineStr"/>
     </row>
@@ -4395,22 +4395,22 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7758194364498243</v>
+        <v>0.7758194364498247</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7162072399490456</v>
+        <v>0.7162072399490459</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.6768754162864431</v>
+        <v>0.6768754162864432</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6446312378490993</v>
+        <v>0.6446312378490995</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0.6171656544030198</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.5933516387160813</v>
+        <v>0.5933516387160817</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.5724800026430085</v>
@@ -4419,13 +4419,13 @@
         <v>0.5541992204938717</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5381521735211688</v>
+        <v>0.5381521735211686</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.5241056797248544</v>
+        <v>0.5241056797248543</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5116577227873376</v>
+        <v>0.5116577227873375</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>0.5006277313683627</v>
@@ -4434,10 +4434,10 @@
         <v>0.4908125161156869</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0.4820311420268308</v>
+        <v>0.4820311420268309</v>
       </c>
       <c r="R78" s="2" t="n">
-        <v>0.4740845874252208</v>
+        <v>0.474084587425221</v>
       </c>
       <c r="S78" s="1" t="inlineStr"/>
     </row>
@@ -4454,16 +4454,16 @@
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>334.5400980960845</v>
+        <v>334.5400980960846</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>364.2636577736323</v>
+        <v>364.2636577736324</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>393.9358180901933</v>
+        <v>393.9358180901934</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>423.4832578774369</v>
@@ -4478,7 +4478,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>541.5492817938724</v>
+        <v>541.5492817938723</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>570.9315691201923</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.9001179490256412</v>
+        <v>0.9001179490256411</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9152540141204016</v>
+        <v>0.9152540141204015</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>0.9244318040653919</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.931717378527367</v>
+        <v>0.9317173785273669</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0.937726382807626</v>
@@ -4543,7 +4543,7 @@
         <v>0.9564711798415051</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9587739854529908</v>
+        <v>0.9587739854529909</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0.9608011997304212</v>
@@ -4572,16 +4572,16 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>617.8311110563025</v>
+        <v>617.8311110563023</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>628.2203405174405</v>
+        <v>628.2203405174404</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>634.5198751116486</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>639.5206137030722</v>
+        <v>639.5206137030721</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>643.6451284900878</v>
@@ -4602,7 +4602,7 @@
         <v>656.5113520672343</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>658.0919726414945</v>
+        <v>658.0919726414946</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>659.4834303395994</v>
@@ -4634,7 +4634,7 @@
         <v>455.0748040551998</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>458.7438421848688</v>
+        <v>458.7438421848687</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>460.9384929530079</v>
@@ -4661,7 +4661,7 @@
         <v>467.6634924923767</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>467.9889608220807</v>
+        <v>467.9889608220808</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>468.2745682991455</v>
@@ -4690,22 +4690,22 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.5447468172074129</v>
+        <v>0.5447468172074134</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5225627094398955</v>
+        <v>0.5225627094398959</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0.5128242264736803</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.5058701247484854</v>
+        <v>0.5058701247484856</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0.500517867126743</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4963537393673499</v>
+        <v>0.4963537393673502</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.4931527461005401</v>
@@ -4714,13 +4714,13 @@
         <v>0.4908656433918407</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.4893667613005354</v>
+        <v>0.4893667613005351</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.4886103521768774</v>
+        <v>0.4886103521768771</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4885192069755879</v>
+        <v>0.4885192069755876</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>0.4889480192746724</v>
@@ -4729,10 +4729,10 @@
         <v>0.4898496347186731</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>0.4911141294015545</v>
+        <v>0.4911141294015546</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>0.4926388829310535</v>
+        <v>0.4926388829310537</v>
       </c>
       <c r="S83" s="1" t="inlineStr"/>
     </row>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -973,7 +973,7 @@
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="2" t="n">
-        <v>0.3446443080405253</v>
+        <v>0.3559988181585447</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1004,7 +1004,7 @@
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="2" t="n">
-        <v>0.5062544510926434</v>
+        <v>0.5229333027467026</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1035,7 +1035,7 @@
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="2" t="n">
-        <v>0.7925571175792675</v>
+        <v>0.7979533943538226</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1252,7 +1252,7 @@
       <c r="Q24" s="1" t="inlineStr"/>
       <c r="R24" s="1" t="inlineStr"/>
       <c r="S24" s="2" t="n">
-        <v>0.168064293246209</v>
+        <v>0.1623870381871993</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1.180296158977294</v>
+        <v>1.241053280171341</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1.175262487903347</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.6934155588636786</v>
+        <v>0.6777265196059805</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0.6419546944869913</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.8876763917513479</v>
+        <v>0.8760708611733966</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>0.8476827557110529</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.3009117955899137</v>
+        <v>0.2979995060628132</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0.1472682986886746</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6528609381672205</v>
+        <v>0.6380894771611995</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>0.6040008906918644</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.8566449408652137</v>
+        <v>0.8444462060062202</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>0.8146305802312926</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2728264862976837</v>
+        <v>0.2705056205597923</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>0.1338497572918128</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5004644049712301</v>
+        <v>0.5067945619819988</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>0.7951571965663656</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7925571175792675</v>
+        <v>0.7979533943538226</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>0.9071180477959627</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2811863433358084</v>
+        <v>0.2824829975607913</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>0.3419728067953003</v>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.150578245989658</v>
+        <v>1.148861981379653</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1.058842137058633</v>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6612407210601744</v>
+        <v>0.6617491813593513</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>0.6393366808686474</v>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2707047831582408</v>
+        <v>0.2644565799050165</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>0.1289535490674906</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5062544510926434</v>
+        <v>0.5229333027467026</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>0.8035709709007146</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.781132427160474</v>
+        <v>0.7838305655477515</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>0.8434383830980788</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4947976924542986</v>
+        <v>0.49309447659793</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>0.4779735242447286</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.149900190948778</v>
+        <v>1.144182651182124</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>1.037406335378524</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9123908734224122</v>
+        <v>0.9140589290878374</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>0.9132006195531562</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.236866455166978</v>
+        <v>0.2311489154003236</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>0.1543708087286905</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.2381873725672461</v>
+        <v>0.2348030522918152</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>0.1456415175054772</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>247.9005511003574</v>
+        <v>247.581434039078</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>239.722425110993</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>0.9198717705829682</v>
+        <v>0.9234566717804606</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>0.9316127880691234</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>264.9230699278949</v>
+        <v>265.9555214727727</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>294.8147930348406</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>298.0389802067385</v>
+        <v>298.6191705006453</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>314.3092699735009</v>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.8448204141343578</v>
+        <v>0.8431790037602239</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>0.7943214505742267</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7758194364498247</v>
+        <v>0.7748207407327543</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>0.7162072399490459</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.9001179490256411</v>
+        <v>0.9003749355554335</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>0.9152540141204015</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>617.8311110563023</v>
+        <v>618.0075037983869</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>628.2203405174404</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>455.0748040551998</v>
+        <v>455.1397620691718</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>458.7438421848687</v>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.5447468172074134</v>
+        <v>0.5439679295729182</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>0.5225627094398959</v>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -431,7 +431,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -439,8 +439,8 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
@@ -849,7 +849,7 @@
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>0.4537118711400233</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -880,7 +880,7 @@
       <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -942,7 +942,7 @@
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -973,7 +973,7 @@
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="2" t="n">
-        <v>0.3559988181585447</v>
+        <v>0.3446443080405244</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1004,7 +1004,7 @@
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="2" t="n">
-        <v>0.5229333027467026</v>
+        <v>0.5062544510926422</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1035,7 +1035,7 @@
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="2" t="n">
-        <v>0.7979533943538226</v>
+        <v>0.7925571175792671</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1066,7 +1066,7 @@
       <c r="Q18" s="1" t="inlineStr"/>
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="2" t="n">
-        <v>0.8596778720441994</v>
+        <v>0.8596778720441987</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1097,7 +1097,7 @@
       <c r="Q19" s="1" t="inlineStr"/>
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="2" t="n">
-        <v>0.7111184547506971</v>
+        <v>0.7111184547506979</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1128,7 +1128,7 @@
       <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="2" t="n">
-        <v>141.4703657841591</v>
+        <v>141.4703657841592</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1252,7 +1252,7 @@
       <c r="Q24" s="1" t="inlineStr"/>
       <c r="R24" s="1" t="inlineStr"/>
       <c r="S24" s="2" t="n">
-        <v>0.1623870381871993</v>
+        <v>0.1680642932462094</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1681,49 +1681,49 @@
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16967.12604306373</v>
+        <v>16967.12604306353</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18630.78159248007</v>
+        <v>18630.78159247993</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20218.5607708968</v>
+        <v>20218.56077089675</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21743.63912220311</v>
+        <v>21743.63912220303</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23213.0501078087</v>
+        <v>23213.05010780867</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24632.76848581418</v>
+        <v>24632.76848581409</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26002.0239099061</v>
+        <v>26002.02390990612</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>27318.78381964874</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>28574.47174295057</v>
+        <v>28574.47174295066</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29758.48274205851</v>
+        <v>29758.48274205857</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>30856.11876136259</v>
+        <v>30856.11876136265</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31847.15753258983</v>
+        <v>31847.15753258981</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>32709.42570822144</v>
+        <v>32709.42570822141</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>33415.02270248366</v>
+        <v>33415.02270248363</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>33933.38931404932</v>
+        <v>33933.38931404923</v>
       </c>
       <c r="S32" s="1" t="inlineStr"/>
     </row>
@@ -1740,49 +1740,49 @@
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>16797.45478263309</v>
+        <v>16797.4547826329</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18258.16596063047</v>
+        <v>18258.16596063033</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>19612.0039477699</v>
+        <v>19612.00394776985</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20873.89355731498</v>
+        <v>20873.89355731491</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>22052.39760241826</v>
+        <v>22052.39760241824</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23154.80237666533</v>
+        <v>23154.80237666525</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24441.90247531174</v>
+        <v>24441.90247531175</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>25679.65679046981</v>
+        <v>25679.65679046982</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>26860.00343837353</v>
+        <v>26860.00343837362</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27972.97377753499</v>
+        <v>27972.97377753505</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>29004.75163568083</v>
+        <v>29004.75163568088</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>29936.32808063443</v>
+        <v>29936.32808063442</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>30746.86016572815</v>
+        <v>30746.86016572812</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>31410.12134033464</v>
+        <v>31410.12134033461</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>31897.38595520635</v>
+        <v>31897.38595520627</v>
       </c>
       <c r="S33" s="1" t="inlineStr"/>
     </row>
@@ -1799,49 +1799,49 @@
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>13701.87693398603</v>
+        <v>13701.87693398587</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15183.18715242576</v>
+        <v>15183.18715242563</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16585.02366398544</v>
+        <v>16585.02366398539</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>17906.52312846286</v>
+        <v>17906.5231284628</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19142.33211474175</v>
+        <v>19142.33211474172</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20287.40656738138</v>
+        <v>20287.4065673813</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>21560.80915145568</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22748.12080720581</v>
+        <v>22748.1208072058</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23831.00891765521</v>
+        <v>23831.00891765527</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24789.99333265435</v>
+        <v>24789.99333265438</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>25602.7462639698</v>
+        <v>25602.74626396982</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>26243.62718943152</v>
+        <v>26243.62718943147</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>26686.81663025726</v>
+        <v>26686.8166302572</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>26904.66888708492</v>
+        <v>26904.66888708486</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>26870.38869889748</v>
+        <v>26870.38869889738</v>
       </c>
       <c r="S34" s="1" t="inlineStr"/>
     </row>
@@ -1858,49 +1858,49 @@
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>16.6972711556989</v>
+        <v>16.69727115569871</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.08373681547279</v>
+        <v>18.08373681547265</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19.35093521240871</v>
+        <v>19.35093521240866</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.56673424835787</v>
+        <v>20.5667342483578</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.65781275498967</v>
+        <v>21.65781275498965</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.64232024894013</v>
+        <v>22.64232024894005</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23.81327704394781</v>
+        <v>23.81327704394782</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>24.88456689222609</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>25.89839154897781</v>
+        <v>25.8983915489779</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.82431759468589</v>
+        <v>26.82431759468595</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>27.61009078020989</v>
+        <v>27.61009078020994</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>28.34277284468556</v>
+        <v>28.34277284468554</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>28.93863549455284</v>
+        <v>28.93863549455281</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>29.38971940023348</v>
+        <v>29.38971940023345</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>29.65175826002295</v>
+        <v>29.65175826002287</v>
       </c>
       <c r="S35" s="1" t="inlineStr"/>
     </row>
@@ -1917,16 +1917,16 @@
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>423.4832578774369</v>
@@ -1941,7 +1941,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>570.9315691201923</v>
@@ -1976,16 +1976,16 @@
       </c>
       <c r="C37" s="1" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>423.4832578774369</v>
@@ -2000,7 +2000,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>570.9315691201923</v>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>1.175559285399187</v>
+        <v>1.175559285399185</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.177149157361195</v>
+        <v>1.177149157361193</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>1.177580116958397</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.177095915781244</v>
+        <v>1.177095915781243</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.175855347567406</v>
+        <v>1.175855347567405</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.173962116210552</v>
+        <v>1.173962116210551</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.173396175963183</v>
@@ -2059,10 +2059,10 @@
         <v>1.172215437821457</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.170376301404517</v>
+        <v>1.170376301404518</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.167847518639031</v>
+        <v>1.167847518639032</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>1.164588351389238</v>
@@ -2074,7 +2074,7 @@
         <v>1.155630506097777</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>1.149848870725617</v>
+        <v>1.149848870725616</v>
       </c>
       <c r="R38" s="2" t="n">
         <v>1.143155604508661</v>
@@ -2094,22 +2094,22 @@
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>117900.225235523</v>
+        <v>117900.2252355229</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>265350.4672140714</v>
+        <v>265350.467214071</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>559906.7201888376</v>
+        <v>559906.720188837</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>706445.5229259076</v>
+        <v>706445.5229259072</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>852200.0936189106</v>
+        <v>852200.0936189099</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>998610.46481496</v>
@@ -2118,10 +2118,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1288927.093135038</v>
+        <v>1288927.093135039</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1432269.084259004</v>
+        <v>1432269.084259005</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2130,10 +2130,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1851080.725235523</v>
+        <v>1851080.725235522</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1985694.583576011</v>
+        <v>1985694.583576009</v>
       </c>
       <c r="R39" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2153,22 +2153,22 @@
       </c>
       <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>117900.225235523</v>
+        <v>117900.2252355229</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>265350.4672140714</v>
+        <v>265350.467214071</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>412792.3261747835</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>559906.7201888376</v>
+        <v>559906.720188837</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>706445.5229259076</v>
+        <v>706445.5229259072</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>852200.0936189106</v>
+        <v>852200.0936189099</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>998610.46481496</v>
@@ -2177,10 +2177,10 @@
         <v>1144279.063503702</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1288927.093135038</v>
+        <v>1288927.093135039</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1432269.084259004</v>
+        <v>1432269.084259005</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>1573991.10153848</v>
@@ -2189,10 +2189,10 @@
         <v>1713714.468054943</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1851080.725235523</v>
+        <v>1851080.725235522</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1985694.583576011</v>
+        <v>1985694.583576009</v>
       </c>
       <c r="R40" s="2" t="n">
         <v>2117173.208233083</v>
@@ -2271,10 +2271,10 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.5338237912142</v>
+        <v>319.5338237912141</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>334.7109771300942</v>
+        <v>334.7109771300941</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>349.222944744292</v>
@@ -2295,7 +2295,7 @@
         <v>413.3312413404398</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>424.8720601328997</v>
+        <v>424.8720601328998</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>435.9907411935118</v>
@@ -2389,49 +2389,49 @@
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>0.2675658145409672</v>
+        <v>0.2675658145409686</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2627510762416364</v>
+        <v>0.2627510762416373</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2591274840795844</v>
+        <v>0.2591274840795847</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.256576799401226</v>
+        <v>0.2565767994012265</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2550220951838035</v>
+        <v>0.2550220951838037</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.254393016919423</v>
+        <v>0.2543930169194235</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.2546621015587227</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2558078397057248</v>
+        <v>0.2558078397057247</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2578470068353897</v>
+        <v>0.2578470068353892</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2608045797416076</v>
+        <v>0.2608045797416072</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2647254322067381</v>
+        <v>0.2647254322067377</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.2696810959896801</v>
+        <v>0.2696810959896802</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.2757469847403645</v>
+        <v>0.2757469847403647</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.2830232632486962</v>
+        <v>0.2830232632486964</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>0.2916156103246133</v>
+        <v>0.2916156103246137</v>
       </c>
       <c r="S44" s="1" t="inlineStr"/>
     </row>
@@ -2448,13 +2448,13 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1.241053280171341</v>
+        <v>1.180296158977292</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.175262487903347</v>
+        <v>1.175262487903346</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.168251369555617</v>
+        <v>1.168251369555616</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>1.15925817796077</v>
@@ -2463,7 +2463,7 @@
         <v>1.148224245120433</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.135081723832521</v>
+        <v>1.13508172383252</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.119697021419855</v>
@@ -2472,10 +2472,10 @@
         <v>1.101922316939652</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.081544540058967</v>
+        <v>1.081544540058968</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.058332062101629</v>
+        <v>1.05833206210163</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>1.032020278583349</v>
@@ -2484,13 +2484,13 @@
         <v>1.0023075858643</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.9689068762009189</v>
+        <v>0.9689068762009185</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.9315321714560333</v>
+        <v>0.9315321714560331</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.8899613152251319</v>
+        <v>0.8899613152251311</v>
       </c>
       <c r="S45" s="1" t="inlineStr"/>
     </row>
@@ -2566,22 +2566,22 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.6777265196059805</v>
+        <v>0.6934155588636791</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6419546944869913</v>
+        <v>0.6419546944869916</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.5966106211168183</v>
+        <v>0.5966106211168185</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5561238216798053</v>
+        <v>0.5561238216798055</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0.5198537807125588</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.4871134947236217</v>
+        <v>0.4871134947236219</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4573452836046674</v>
@@ -2590,13 +2590,13 @@
         <v>0.4302607947475137</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4054971202086974</v>
+        <v>0.4054971202086972</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.382866877454614</v>
+        <v>0.3828668774546138</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3622495702925325</v>
+        <v>0.3622495702925324</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>0.3434267211217917</v>
@@ -2605,10 +2605,10 @@
         <v>0.3264013915200195</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0.3111320861419942</v>
+        <v>0.3111320861419943</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0.2976385445704193</v>
+        <v>0.2976385445704194</v>
       </c>
       <c r="S47" s="1" t="inlineStr"/>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.8760708611733966</v>
+        <v>0.8876763917513484</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8476827557110529</v>
+        <v>0.8476827557110533</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.807838102390409</v>
+        <v>0.8078381023904093</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7687303178641441</v>
+        <v>0.7687303178641439</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.7310690251477328</v>
+        <v>0.7310690251477326</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.6950438015492818</v>
+        <v>0.695043801549282</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.6606666216532919</v>
@@ -2649,25 +2649,25 @@
         <v>0.6281613417983278</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.5974295303378844</v>
+        <v>0.5974295303378842</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5685574328276755</v>
+        <v>0.5685574328276751</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5416626339362809</v>
+        <v>0.5416626339362808</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>0.5165679427658935</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.4934870266617923</v>
+        <v>0.4934870266617922</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>0.4724845076896956</v>
+        <v>0.4724845076896957</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>0.4537118711400231</v>
+        <v>0.4537118711400232</v>
       </c>
       <c r="S48" s="1" t="inlineStr"/>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.2979995060628132</v>
+        <v>0.3009117955899138</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0.1472682986886746</v>
@@ -2693,10 +2693,10 @@
         <v>0.1040512028785386</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.08416531485429166</v>
+        <v>0.08416531485429168</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.07304667532585596</v>
+        <v>0.07304667532585597</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>0.06619932070733821</v>
@@ -2708,7 +2708,7 @@
         <v>0.05890202559086238</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.05707687219159215</v>
+        <v>0.05707687219159214</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>0.05602993268923052</v>
@@ -2720,13 +2720,13 @@
         <v>0.0556712005930268</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.05621043688048771</v>
+        <v>0.05621043688048773</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>0.05718010096659844</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>0.05857117009930012</v>
+        <v>0.05857117009930016</v>
       </c>
       <c r="S49" s="1" t="inlineStr"/>
     </row>
@@ -2861,22 +2861,22 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6380894771611995</v>
+        <v>0.652860938167221</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.6040008906918644</v>
+        <v>0.6040008906918648</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.5608528404519376</v>
+        <v>0.5608528404519377</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.5224733005942056</v>
+        <v>0.5224733005942057</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>0.4880639358485558</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4569203160469202</v>
+        <v>0.4569203160469203</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.4285352724020985</v>
@@ -2885,25 +2885,25 @@
         <v>0.4026243969644493</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.3789240751115422</v>
+        <v>0.378924075111542</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3572719824747077</v>
+        <v>0.3572719824747075</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3374139715597593</v>
+        <v>0.3374139715597592</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>0.3192848027412507</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3028179399616254</v>
+        <v>0.3028179399616255</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>0.2879901483751846</v>
+        <v>0.2879901483751847</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>0.2747820638038408</v>
+        <v>0.2747820638038409</v>
       </c>
       <c r="S52" s="1" t="inlineStr"/>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.8444462060062202</v>
+        <v>0.856644940865214</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.8146305802312926</v>
+        <v>0.814630580231293</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.7734667621979159</v>
+        <v>0.773466762197916</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.7338759548743808</v>
+        <v>0.733875954874381</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0.6961191242501733</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.6601638683567802</v>
+        <v>0.6601638683567803</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6260427988521639</v>
@@ -2944,25 +2944,25 @@
         <v>0.5937907596548805</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.5634296976475788</v>
+        <v>0.5634296976475786</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.5350423151502405</v>
+        <v>0.5350423151502401</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5084161145598954</v>
+        <v>0.5084161145598953</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>0.4836795065578707</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>0.4608658406019039</v>
+        <v>0.460865840601904</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>0.4400685175575864</v>
+        <v>0.4400685175575865</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>0.4213432296968064</v>
+        <v>0.4213432296968065</v>
       </c>
       <c r="S53" s="1" t="inlineStr"/>
     </row>
@@ -2979,22 +2979,22 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2705056205597923</v>
+        <v>0.2728264862976842</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1338497572918128</v>
+        <v>0.1338497572918129</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0.09484023765812551</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.07693362720631663</v>
+        <v>0.07693362720631673</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.0669762425432088</v>
+        <v>0.06697624254320884</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.06091105339602894</v>
+        <v>0.06091105339602899</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.05699304098048162</v>
@@ -3003,10 +3003,10 @@
         <v>0.05449766392638357</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.05299351220560669</v>
+        <v>0.05299351220560665</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.05222397695379562</v>
+        <v>0.05222397695379559</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0.05206385535377919</v>
@@ -3018,10 +3018,10 @@
         <v>0.05326713372110947</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>0.05457087868506504</v>
+        <v>0.05457087868506506</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>0.05635161751966029</v>
+        <v>0.05635161751966031</v>
       </c>
       <c r="S54" s="1" t="inlineStr"/>
     </row>
@@ -3038,16 +3038,16 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5067945619819988</v>
+        <v>0.5004644049712288</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.7951571965663656</v>
+        <v>0.7951571965663653</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>0.8599102873979747</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.8880543221133667</v>
+        <v>0.8880543221133665</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0.9033251749764167</v>
@@ -3065,7 +3065,7 @@
         <v>0.9243435965300111</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.9254864808911322</v>
+        <v>0.9254864808911323</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>0.9257241100343748</v>
@@ -3080,7 +3080,7 @@
         <v>0.921996524014703</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>0.9193396390285498</v>
+        <v>0.9193396390285495</v>
       </c>
       <c r="S55" s="1" t="inlineStr"/>
     </row>
@@ -3097,13 +3097,13 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7979533943538226</v>
+        <v>0.7925571175792671</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.9071180477959627</v>
+        <v>0.9071180477959626</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.9358895185677403</v>
+        <v>0.9358895185677402</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0.948685461697101</v>
@@ -3156,49 +3156,49 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2824829975607913</v>
+        <v>0.2811863433358094</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.3419728067953003</v>
+        <v>0.341972806795301</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.3509410655936228</v>
+        <v>0.350941065593623</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.3505057511486546</v>
+        <v>0.350505751148655</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.3468279629635574</v>
+        <v>0.3468279629635576</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.3417081181479366</v>
+        <v>0.3417081181479371</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3359234221056464</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.3297983277471504</v>
+        <v>0.3297983277471503</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.3235650470477323</v>
+        <v>0.3235650470477318</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.31739063742177</v>
+        <v>0.3173906374217697</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3114061941828092</v>
+        <v>0.3114061941828089</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.3057573784837125</v>
+        <v>0.3057573784837126</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>0.3005825024172691</v>
+        <v>0.3005825024172694</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>0.2960388638501384</v>
+        <v>0.2960388638501387</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>0.2922862607409257</v>
+        <v>0.2922862607409261</v>
       </c>
       <c r="S57" s="1" t="inlineStr"/>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.148861981379653</v>
+        <v>1.150578245989657</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1.058842137058633</v>
@@ -3224,13 +3224,13 @@
         <v>1.03259772936633</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.017231933919797</v>
+        <v>1.017231933919796</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.005239401872601</v>
+        <v>1.0052394018726</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.9944293535476197</v>
+        <v>0.9944293535476192</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.9838133341616834</v>
@@ -3239,25 +3239,25 @@
         <v>0.9729365229403433</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.9614252343707766</v>
+        <v>0.9614252343707773</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.9489575905895593</v>
+        <v>0.9489575905895599</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9352269846819268</v>
+        <v>0.9352269846819273</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.9198661432115165</v>
+        <v>0.9198661432115164</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>0.9024768235733482</v>
+        <v>0.9024768235733479</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>0.8825869545836461</v>
+        <v>0.8825869545836458</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>0.8596778720441994</v>
+        <v>0.8596778720441987</v>
       </c>
       <c r="S58" s="1" t="inlineStr"/>
     </row>
@@ -3274,22 +3274,22 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6617491813593513</v>
+        <v>0.6612407210601751</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6393366808686474</v>
+        <v>0.6393366808686478</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.6009807379947486</v>
+        <v>0.6009807379947487</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5629187482016862</v>
+        <v>0.5629187482016864</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.5272267598629743</v>
+        <v>0.5272267598629744</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.4940432659250179</v>
+        <v>0.4940432659250182</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4632008778470891</v>
@@ -3298,13 +3298,13 @@
         <v>0.434547983835321</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.4078868049211564</v>
+        <v>0.4078868049211561</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.3830869581536965</v>
+        <v>0.3830869581536963</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3598891790707875</v>
+        <v>0.3598891790707873</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>0.3382266797622753</v>
@@ -3313,10 +3313,10 @@
         <v>0.3180205486364964</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0.2992319827470267</v>
+        <v>0.2992319827470268</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0.2818236131273244</v>
+        <v>0.2818236131273246</v>
       </c>
       <c r="S59" s="1" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2644565799050165</v>
+        <v>0.2707047831582413</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.1289535490674906</v>
+        <v>0.1289535490674907</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.09035121456081503</v>
+        <v>0.09035121456081506</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.07279583956722309</v>
+        <v>0.07279583956722319</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.0630871303195517</v>
+        <v>0.06308713031955175</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.0572051495289134</v>
+        <v>0.05720514952891342</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3357,13 +3357,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.04971625102356635</v>
+        <v>0.04971625102356633</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04910680533129995</v>
+        <v>0.04910680533129991</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.04914211499311783</v>
+        <v>0.04914211499311785</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3372,10 +3372,10 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>0.05266952243484315</v>
+        <v>0.05266952243484317</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
       <c r="S60" s="1" t="inlineStr"/>
     </row>
@@ -3392,19 +3392,19 @@
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="2" t="n">
-        <v>0.1289535490674906</v>
+        <v>0.1289535490674907</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.09035121456081503</v>
+        <v>0.09035121456081506</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.07279583956722309</v>
+        <v>0.07279583956722319</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0630871303195517</v>
+        <v>0.06308713031955175</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.0572051495289134</v>
+        <v>0.05720514952891342</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>0.05343833731776829</v>
@@ -3413,13 +3413,13 @@
         <v>0.05108008787467855</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.04971625102356635</v>
+        <v>0.04971625102356633</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.04910680533129995</v>
+        <v>0.04910680533129991</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.04914211499311783</v>
+        <v>0.04914211499311785</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0.04975559312298664</v>
@@ -3428,13 +3428,13 @@
         <v>0.0509264267870588</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>0.05266952243484315</v>
+        <v>0.05266952243484317</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>0.05503600366715333</v>
+        <v>0.05503600366715335</v>
       </c>
       <c r="R61" s="2" t="n">
-        <v>0.05740248489946351</v>
+        <v>0.05740248489946354</v>
       </c>
       <c r="S61" s="1" t="inlineStr"/>
     </row>
@@ -3451,16 +3451,16 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5229333027467026</v>
+        <v>0.5062544510926422</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.8035709709007146</v>
+        <v>0.8035709709007143</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.8670515451401452</v>
+        <v>0.8670515451401449</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.8944317807808952</v>
+        <v>0.8944317807808951</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>0.9092199502745679</v>
@@ -3510,13 +3510,13 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.7838305655477515</v>
+        <v>0.7811324271604738</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.8434383830980788</v>
+        <v>0.8434383830980787</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.8631690556287381</v>
+        <v>0.863169055628738</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0.8752186331837397</v>
@@ -3569,49 +3569,49 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.49309447659793</v>
+        <v>0.4947976924542974</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.4779735242447286</v>
+        <v>0.4779735242447278</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.4865582469952273</v>
+        <v>0.486558246995227</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.4994124070984718</v>
+        <v>0.4994124070984713</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>0.5137734390610369</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5288702372127254</v>
+        <v>0.5288702372127249</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5443607442121166</v>
+        <v>0.5443607442121167</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0.5600965560548041</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.5759477597191387</v>
+        <v>0.5759477597191393</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.5918081993459784</v>
+        <v>0.5918081993459788</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6075771359846209</v>
+        <v>0.6075771359846212</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>0.6231339534389799</v>
+        <v>0.6231339534389797</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.6383608968284006</v>
+        <v>0.6383608968284005</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>0.6531207208541026</v>
+        <v>0.6531207208541023</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>0.6672755281010996</v>
+        <v>0.6672755281010991</v>
       </c>
       <c r="S64" s="1" t="inlineStr"/>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.9130337357818</v>
+        <v>0.9130337357818012</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8830355266498334</v>
+        <v>0.8830355266498343</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8530645253444216</v>
+        <v>0.8530645253444218</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.8230510799514991</v>
+        <v>0.8230510799514995</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.7929681334991677</v>
+        <v>0.7929681334991679</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7627977092904863</v>
+        <v>0.7627977092904867</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7325616461288711</v>
@@ -3652,25 +3652,25 @@
         <v>0.7022863254977531</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6720276223556498</v>
+        <v>0.6720276223556494</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6418422361217935</v>
+        <v>0.6418422361217931</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.611794636858556</v>
+        <v>0.6117946368585556</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>0.5819584578441279</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>0.552396365214525</v>
+        <v>0.5523963652145252</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0.5231726932408487</v>
+        <v>0.5231726932408488</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.4943374292495647</v>
+        <v>0.494337429249565</v>
       </c>
       <c r="S65" s="1" t="inlineStr"/>
     </row>
@@ -3746,49 +3746,49 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.144182651182124</v>
+        <v>1.149900190948777</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.037406335378524</v>
+        <v>1.037406335378523</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1.008925798296564</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.9938963560643232</v>
+        <v>0.9938963560643226</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0.9831646987246834</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0.9741269377820952</v>
+        <v>0.9741269377820945</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9656506714457721</v>
+        <v>0.9656506714457722</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0.9572427390595025</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.9485264056880329</v>
+        <v>0.9485264056880337</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9392010422085477</v>
+        <v>0.9392010422085484</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.9290023750862315</v>
+        <v>0.9290023750862318</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>0.9176220242343975</v>
+        <v>0.9176220242343971</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>0.9047385458666748</v>
+        <v>0.9047385458666746</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>0.8899750486647011</v>
+        <v>0.8899750486647007</v>
       </c>
       <c r="R67" s="2" t="n">
-        <v>0.8729257643027138</v>
+        <v>0.872925764302713</v>
       </c>
       <c r="S67" s="1" t="inlineStr"/>
     </row>
@@ -3805,22 +3805,22 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9140589290878374</v>
+        <v>0.9123908734224133</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.9132006195531562</v>
+        <v>0.9132006195531571</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.887967323159673</v>
+        <v>0.8879673231596732</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8577821070040713</v>
+        <v>0.8577821070040718</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>0.8255539583207618</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.792160112745544</v>
+        <v>0.7921601127455445</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7580358219315676</v>
@@ -3829,25 +3829,25 @@
         <v>0.72342089195214</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.6885297165190225</v>
+        <v>0.6885297165190221</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.6535447189435526</v>
+        <v>0.6535447189435523</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6186306556226798</v>
+        <v>0.6186306556226797</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>0.5839510578580409</v>
+        <v>0.583951057858041</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.5496458774495508</v>
+        <v>0.549645877449551</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>0.5158449565439994</v>
+        <v>0.5158449565439995</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>0.4826515564353129</v>
+        <v>0.4826515564353131</v>
       </c>
       <c r="S68" s="1" t="inlineStr"/>
     </row>
@@ -3864,49 +3864,49 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2311489154003236</v>
+        <v>0.2368664551669755</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1543708087286905</v>
+        <v>0.1543708087286889</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1558612729521429</v>
+        <v>0.1558612729521425</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.1708452761128242</v>
+        <v>0.1708452761128231</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1901965652255156</v>
+        <v>0.1901965652255154</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.211329228491609</v>
+        <v>0.2113292284916077</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.233089025316901</v>
+        <v>0.2330890253169011</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0.2549564135617495</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.2764987833323831</v>
+        <v>0.2764987833323843</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.2973588060867542</v>
+        <v>0.2973588060867552</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3172077382276756</v>
+        <v>0.3172077382276762</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3356635663902696</v>
+        <v>0.3356635663902692</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.3523421806521498</v>
+        <v>0.3523421806521494</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.3668023554238524</v>
+        <v>0.3668023554238519</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.3785883350531491</v>
+        <v>0.3785883350531479</v>
       </c>
       <c r="S69" s="1" t="inlineStr"/>
     </row>
@@ -3923,22 +3923,22 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.2348030522918152</v>
+        <v>0.2381873725672434</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1456415175054772</v>
+        <v>0.1456415175054754</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.1446304062066568</v>
+        <v>0.1446304062066563</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.1594498269157253</v>
+        <v>0.1594498269157244</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.1796854435518387</v>
+        <v>0.1796854435518385</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.2022692408020758</v>
+        <v>0.2022692408020746</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.2257775122301158</v>
@@ -3947,25 +3947,25 @@
         <v>0.2495156309882033</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.2728955178517541</v>
+        <v>0.2728955178517553</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.2954128716460067</v>
+        <v>0.2954128716460076</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.316596329059247</v>
+        <v>0.3165963290592476</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.3359150853534756</v>
+        <v>0.3359150853534754</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.3528309461237974</v>
+        <v>0.352830946123797</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0.3667419980396467</v>
+        <v>0.3667419980396462</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0.3770263156088866</v>
+        <v>0.3770263156088856</v>
       </c>
       <c r="S70" s="1" t="inlineStr"/>
     </row>
@@ -3982,22 +3982,22 @@
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>251.7894146864385</v>
+        <v>251.7894146864383</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.6625952542775</v>
+        <v>249.6625952542773</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>247.6528107706313</v>
+        <v>247.6528107706312</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>245.7731838000793</v>
+        <v>245.7731838000792</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>244.0304158041251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>242.4310417988148</v>
+        <v>242.4310417988147</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>240.972909827971</v>
@@ -4006,25 +4006,25 @@
         <v>239.6524840515102</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>238.4569611637397</v>
+        <v>238.4569611637399</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>237.3706330162411</v>
+        <v>237.3706330162412</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>236.3718770966746</v>
+        <v>236.3718770966747</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>235.4310839272837</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>234.5161748631908</v>
+        <v>234.5161748631907</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>233.5872660970408</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>232.6016263665796</v>
+        <v>232.6016263665795</v>
       </c>
       <c r="S71" s="1" t="inlineStr"/>
     </row>
@@ -4100,22 +4100,22 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>247.581434039078</v>
+        <v>247.9005511003572</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>239.722425110993</v>
+        <v>239.7224251109928</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>236.3804261005702</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>234.0471923727898</v>
+        <v>234.0471923727897</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>232.2443952114634</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>230.8447911323391</v>
+        <v>230.844791132339</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>229.7932112410973</v>
@@ -4124,10 +4124,10 @@
         <v>229.0678517566361</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>228.6458226289366</v>
+        <v>228.6458226289367</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>228.5052237669685</v>
+        <v>228.5052237669686</v>
       </c>
       <c r="N73" s="2" t="n">
         <v>228.6215960141323</v>
@@ -4142,7 +4142,7 @@
         <v>230.1629008037089</v>
       </c>
       <c r="R73" s="2" t="n">
-        <v>230.932388801264</v>
+        <v>230.9323888012639</v>
       </c>
       <c r="S73" s="1" t="inlineStr"/>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>0.9234566717804606</v>
+        <v>0.9198717705829681</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>0.9316127880691234</v>
@@ -4168,7 +4168,7 @@
         <v>0.9411937231993717</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9489889140291673</v>
+        <v>0.9489889140291672</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0.9555931563290563</v>
@@ -4183,25 +4183,25 @@
         <v>0.9700508464641263</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.9735532872138978</v>
+        <v>0.9735532872138979</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>0.9765720654514889</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9792051916840198</v>
+        <v>0.9792051916840199</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>0.9814270687200961</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.9833372387193101</v>
+        <v>0.98333723871931</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>0.9849622306534793</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0.9863414798135992</v>
+        <v>0.9863414798135991</v>
       </c>
       <c r="S74" s="1" t="inlineStr"/>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>265.9555214727727</v>
+        <v>264.9230699278948</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>294.8147930348406</v>
@@ -4254,13 +4254,13 @@
         <v>589.8572714101675</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>618.9875214592724</v>
+        <v>618.9875214592723</v>
       </c>
       <c r="Q75" s="2" t="n">
         <v>648.0388565102273</v>
       </c>
       <c r="R75" s="2" t="n">
-        <v>677.0139991251236</v>
+        <v>677.0139991251235</v>
       </c>
       <c r="S75" s="1" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="2" t="n">
-        <v>298.6191705006453</v>
+        <v>298.0389802067385</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>314.3092699735009</v>
@@ -4336,22 +4336,22 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.8431790037602239</v>
+        <v>0.8448204141343573</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.7943214505742267</v>
+        <v>0.7943214505742261</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7511095390711756</v>
+        <v>0.7511095390711755</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7135754513445642</v>
+        <v>0.7135754513445639</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.6807840523057973</v>
+        <v>0.6807840523057971</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.651895609766268</v>
+        <v>0.6518956097662678</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6262006800178096</v>
@@ -4360,25 +4360,25 @@
         <v>0.6032931870271456</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.582669850624871</v>
+        <v>0.5826698506248713</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5640185684375758</v>
+        <v>0.5640185684375761</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5470938594252941</v>
+        <v>0.5470938594252943</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.5314851030679409</v>
+        <v>0.5314851030679412</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>0.5170517482371183</v>
+        <v>0.5170517482371181</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>0.5035581698659797</v>
+        <v>0.5035581698659796</v>
       </c>
       <c r="R77" s="2" t="n">
-        <v>0.4908332230905137</v>
+        <v>0.4908332230905135</v>
       </c>
       <c r="S77" s="1" t="inlineStr"/>
     </row>
@@ -4395,22 +4395,22 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7748207407327543</v>
+        <v>0.7758194364498243</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7162072399490459</v>
+        <v>0.7162072399490456</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.6768754162864432</v>
+        <v>0.6768754162864431</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6446312378490995</v>
+        <v>0.6446312378490993</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0.6171656544030198</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.5933516387160817</v>
+        <v>0.5933516387160813</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.5724800026430085</v>
@@ -4419,13 +4419,13 @@
         <v>0.5541992204938717</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5381521735211686</v>
+        <v>0.5381521735211688</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.5241056797248543</v>
+        <v>0.5241056797248544</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5116577227873375</v>
+        <v>0.5116577227873376</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>0.5006277313683627</v>
@@ -4434,10 +4434,10 @@
         <v>0.4908125161156869</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0.4820311420268309</v>
+        <v>0.4820311420268308</v>
       </c>
       <c r="R78" s="2" t="n">
-        <v>0.474084587425221</v>
+        <v>0.4740845874252208</v>
       </c>
       <c r="S78" s="1" t="inlineStr"/>
     </row>
@@ -4454,16 +4454,16 @@
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>304.6972711556989</v>
+        <v>304.6972711556987</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>334.5400980960846</v>
+        <v>334.5400980960845</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>364.2636577736324</v>
+        <v>364.2636577736323</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>393.9358180901934</v>
+        <v>393.9358180901933</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>423.4832578774369</v>
@@ -4478,7 +4478,7 @@
         <v>512.0790958565088</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>541.5492817938723</v>
+        <v>541.5492817938724</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>570.9315691201923</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.9003749355554335</v>
+        <v>0.9001179490256412</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9152540141204015</v>
+        <v>0.9152540141204016</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>0.9244318040653919</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.9317173785273669</v>
+        <v>0.931717378527367</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>0.937726382807626</v>
@@ -4543,7 +4543,7 @@
         <v>0.9564711798415051</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9587739854529909</v>
+        <v>0.9587739854529908</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0.9608011997304212</v>
@@ -4572,16 +4572,16 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>618.0075037983869</v>
+        <v>617.8311110563025</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>628.2203405174404</v>
+        <v>628.2203405174405</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>634.5198751116486</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>639.5206137030721</v>
+        <v>639.5206137030722</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>643.6451284900878</v>
@@ -4602,7 +4602,7 @@
         <v>656.5113520672343</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>658.0919726414946</v>
+        <v>658.0919726414945</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>659.4834303395994</v>
@@ -4631,10 +4631,10 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>455.1397620691718</v>
+        <v>455.0748040551998</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>458.7438421848687</v>
+        <v>458.7438421848688</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>460.9384929530079</v>
@@ -4661,7 +4661,7 @@
         <v>467.6634924923767</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>467.9889608220808</v>
+        <v>467.9889608220807</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>468.2745682991455</v>
@@ -4690,22 +4690,22 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.5439679295729182</v>
+        <v>0.5447468172074129</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5225627094398959</v>
+        <v>0.5225627094398955</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0.5128242264736803</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.5058701247484856</v>
+        <v>0.5058701247484854</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0.500517867126743</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.4963537393673502</v>
+        <v>0.4963537393673499</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.4931527461005401</v>
@@ -4714,13 +4714,13 @@
         <v>0.4908656433918407</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.4893667613005351</v>
+        <v>0.4893667613005354</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.4886103521768771</v>
+        <v>0.4886103521768774</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4885192069755876</v>
+        <v>0.4885192069755879</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>0.4889480192746724</v>
@@ -4729,10 +4729,10 @@
         <v>0.4898496347186731</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>0.4911141294015546</v>
+        <v>0.4911141294015545</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>0.4926388829310537</v>
+        <v>0.4926388829310535</v>
       </c>
       <c r="S83" s="1" t="inlineStr"/>
     </row>

--- a/results/поступенчатый_расчет_ступеней.xlsx
+++ b/results/поступенчатый_расчет_ступеней.xlsx
@@ -444,17 +444,17 @@
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
     <col width="21" customWidth="1" min="25" max="25"/>
     <col width="21" customWidth="1" min="26" max="26"/>
     <col width="21" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
     <col width="21" customWidth="1" min="30" max="30"/>
-    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
     <col width="21" customWidth="1" min="32" max="32"/>
     <col width="21" customWidth="1" min="33" max="33"/>
     <col width="21" customWidth="1" min="34" max="34"/>
@@ -951,7 +951,7 @@
       <c r="AF8" s="1" t="inlineStr"/>
       <c r="AG8" s="1" t="inlineStr"/>
       <c r="AH8" s="2" t="n">
-        <v>466.9638497108409</v>
+        <v>466.963849710841</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1089,7 +1089,7 @@
       <c r="AF11" s="1" t="inlineStr"/>
       <c r="AG11" s="1" t="inlineStr"/>
       <c r="AH11" s="2" t="n">
-        <v>0.4726509790396709</v>
+        <v>0.4726509790396704</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1135,7 +1135,7 @@
       <c r="AF12" s="1" t="inlineStr"/>
       <c r="AG12" s="1" t="inlineStr"/>
       <c r="AH12" s="2" t="n">
-        <v>0.1451057510225273</v>
+        <v>0.145105751022527</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1227,7 +1227,7 @@
       <c r="AF14" s="1" t="inlineStr"/>
       <c r="AG14" s="1" t="inlineStr"/>
       <c r="AH14" s="2" t="n">
-        <v>0.1451057510225273</v>
+        <v>0.145105751022527</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1273,7 +1273,7 @@
       <c r="AF15" s="1" t="inlineStr"/>
       <c r="AG15" s="1" t="inlineStr"/>
       <c r="AH15" s="2" t="n">
-        <v>0.5279179420709107</v>
+        <v>0.527917942070911</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1319,7 +1319,7 @@
       <c r="AF16" s="1" t="inlineStr"/>
       <c r="AG16" s="1" t="inlineStr"/>
       <c r="AH16" s="2" t="n">
-        <v>0.7754685098517303</v>
+        <v>0.7754685098517308</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1365,7 +1365,7 @@
       <c r="AF17" s="1" t="inlineStr"/>
       <c r="AG17" s="1" t="inlineStr"/>
       <c r="AH17" s="2" t="n">
-        <v>0.8948048417872086</v>
+        <v>0.8948048417872089</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1411,7 +1411,7 @@
       <c r="AF18" s="1" t="inlineStr"/>
       <c r="AG18" s="1" t="inlineStr"/>
       <c r="AH18" s="2" t="n">
-        <v>0.9904415988404255</v>
+        <v>0.9904415988404269</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1457,7 +1457,7 @@
       <c r="AF19" s="1" t="inlineStr"/>
       <c r="AG19" s="1" t="inlineStr"/>
       <c r="AH19" s="2" t="n">
-        <v>0.5803547279544711</v>
+        <v>0.5803547279544696</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1503,7 +1503,7 @@
       <c r="AF20" s="1" t="inlineStr"/>
       <c r="AG20" s="1" t="inlineStr"/>
       <c r="AH20" s="2" t="n">
-        <v>128.8516869002362</v>
+        <v>128.8516869002361</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1549,7 +1549,7 @@
       <c r="AF21" s="1" t="inlineStr"/>
       <c r="AG21" s="1" t="inlineStr"/>
       <c r="AH21" s="2" t="n">
-        <v>0.821663992941369</v>
+        <v>0.8216639929413696</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -1595,7 +1595,7 @@
       <c r="AF22" s="1" t="inlineStr"/>
       <c r="AG22" s="1" t="inlineStr"/>
       <c r="AH22" s="2" t="n">
-        <v>0.5593665748081917</v>
+        <v>0.5593665748081921</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1641,7 +1641,7 @@
       <c r="AF23" s="1" t="inlineStr"/>
       <c r="AG23" s="1" t="inlineStr"/>
       <c r="AH23" s="2" t="n">
-        <v>0.06070315986237579</v>
+        <v>0.06070315986237562</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1687,7 +1687,7 @@
       <c r="AF24" s="1" t="inlineStr"/>
       <c r="AG24" s="1" t="inlineStr"/>
       <c r="AH24" s="2" t="n">
-        <v>0.07642747623101631</v>
+        <v>0.07642747623101614</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1898,49 +1898,49 @@
         <v>100292.8790575521</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>117900.2252355229</v>
+        <v>117900.225235523</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>139640.1520749114</v>
+        <v>139640.1520749118</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>166236.9660251446</v>
+        <v>166236.9660251453</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>198519.8102005615</v>
+        <v>198519.8102005624</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>237416.5737215993</v>
+        <v>237416.5737216003</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>283940.2419324598</v>
+        <v>283940.241932461</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>339784.6893019705</v>
+        <v>339784.6893019718</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>406353.0047389641</v>
+        <v>406353.0047389656</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>485117.8368060024</v>
+        <v>485117.8368060038</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>577545.6003012427</v>
+        <v>577545.6003012438</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>684992.8334751748</v>
+        <v>684992.8334751757</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>808604.3243026375</v>
+        <v>808604.324302639</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>949171.5006658965</v>
+        <v>949171.5006658983</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>1106962.677100719</v>
+        <v>1106962.677100721</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>1281540.58970547</v>
+        <v>1281540.589705474</v>
       </c>
       <c r="T28" s="1" t="inlineStr"/>
       <c r="U28" s="1" t="inlineStr"/>
@@ -1974,49 +1974,49 @@
         <v>288</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>322.8285183857189</v>
+        <v>322.8285183857192</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>342.2987237128249</v>
+        <v>342.2987237128252</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>362.9110546823131</v>
+        <v>362.9110546823135</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>384.6044413446236</v>
+        <v>384.6044413446241</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>407.3155434909061</v>
+        <v>407.3155434909066</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>431.3517658449545</v>
+        <v>431.351765844955</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>456.5274980662524</v>
+        <v>456.527498066253</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>482.6547776336109</v>
+        <v>482.6547776336114</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>509.8334607983726</v>
+        <v>509.833460798373</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>537.8853814797804</v>
+        <v>537.8853814797809</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>566.6820226940119</v>
+        <v>566.6820226940124</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>596.0579089275222</v>
+        <v>596.0579089275227</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>625.8550304374809</v>
+        <v>625.8550304374814</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>655.9273822945767</v>
+        <v>655.9273822945773</v>
       </c>
       <c r="T29" s="1" t="inlineStr"/>
       <c r="U29" s="1" t="inlineStr"/>
@@ -2195,49 +2195,49 @@
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>16967.12604306353</v>
+        <v>16967.12604306373</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18630.78159247993</v>
+        <v>18630.78159248007</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20218.56077089675</v>
+        <v>20218.5607708968</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21743.63912220303</v>
+        <v>21743.63912220311</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23213.05010780867</v>
+        <v>23213.0501078087</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24632.76848581409</v>
+        <v>24632.76848581418</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26002.02390990612</v>
+        <v>26002.0239099061</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>27318.78381964874</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>28574.47174295066</v>
+        <v>28574.47174295057</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29758.48274205857</v>
+        <v>29758.48274205851</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>30856.11876136265</v>
+        <v>30856.11876136259</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>31847.15753258981</v>
+        <v>31847.15753258983</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>32709.42570822141</v>
+        <v>32709.42570822144</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>33415.02270248363</v>
+        <v>33415.02270248366</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>33933.38931404923</v>
+        <v>33933.38931404932</v>
       </c>
       <c r="S32" s="1" t="inlineStr"/>
       <c r="T32" s="1" t="inlineStr"/>
@@ -2269,49 +2269,49 @@
       </c>
       <c r="C33" s="1" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>16797.4547826329</v>
+        <v>16797.45478263309</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18258.16596063033</v>
+        <v>18258.16596063047</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>19612.00394776985</v>
+        <v>19612.0039477699</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20873.89355731491</v>
+        <v>20873.89355731498</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>22052.39760241824</v>
+        <v>22052.39760241826</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23154.80237666525</v>
+        <v>23154.80237666533</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24441.90247531175</v>
+        <v>24441.90247531174</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>25679.65679046982</v>
+        <v>25679.65679046981</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>26860.00343837362</v>
+        <v>26860.00343837353</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27972.97377753505</v>
+        <v>27972.97377753499</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>29004.75163568088</v>
+        <v>29004.75163568083</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>29936.32808063442</v>
+        <v>29936.32808063443</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>30746.86016572812</v>
+        <v>30746.86016572815</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>31410.12134033461</v>
+        <v>31410.12134033464</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>31897.38595520627</v>
+        <v>31897.38595520635</v>
       </c>
       <c r="S33" s="1" t="inlineStr"/>
       <c r="T33" s="1" t="inlineStr"/>
@@ -2343,49 +2343,49 @@
       </c>
       <c r="C34" s="1" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>13701.87693398587</v>
+        <v>13701.87693398603</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15183.18715242563</v>
+        <v>15183.18715242576</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16585.02366398539</v>
+        <v>16585.02366398544</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>17906.5231284628</v>
+        <v>17906.52312846286</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19142.33211474172</v>
+        <v>19142.33211474175</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20287.4065673813</v>
+        <v>20287.40656738138</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>21560.80915145568</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22748.1208072058</v>
+        <v>22748.12080720581</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>23831.00891765527</v>
+        <v>23831.00891765521</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24789.99333265438</v>
+        <v>24789.99333265435</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>25602.74626396982</v>
+        <v>25602.7462639698</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>26243.62718943147</v>
+        <v>26243.62718943152</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>26686.8166302572</v>
+        <v>26686.81663025726</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>26904.66888708486</v>
+        <v>26904.66888708492</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>26870.38869889738</v>
+        <v>26870.38869889748</v>
       </c>
       <c r="S34" s="1" t="inlineStr"/>
       <c r="T34" s="1" t="inlineStr"/>
@@ -2417,49 +2417,49 @@
       </c>
       <c r="C35" s="1" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>16.69727115569871</v>
+        <v>16.6972711556989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>18.13124723002019</v>
+        <v>18.13124723002033</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19.47020532710597</v>
+        <v>19.47020532710601</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.61233096948821</v>
+        <v>20.61233096948828</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>21.69338666231059</v>
+        <v>21.6933866623106</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.71110214628245</v>
+        <v>22.71110214628252</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>24.03622235404839</v>
+        <v>24.03622235404838</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>25.17573222129796</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>26.12727956735856</v>
+        <v>26.12727956735847</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>27.17868316476164</v>
+        <v>27.17868316476157</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>28.05192068140789</v>
+        <v>28.05192068140784</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>28.7966412142315</v>
+        <v>28.79664121423152</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>29.37588623351027</v>
+        <v>29.3758862335103</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>29.79712150995868</v>
+        <v>29.79712150995869</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>30.0723518570958</v>
+        <v>30.07235185709587</v>
       </c>
       <c r="S35" s="1" t="inlineStr"/>
       <c r="T35" s="1" t="inlineStr"/>
@@ -2491,49 +2491,49 @@
       </c>
       <c r="C36" s="1" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>322.8285183857189</v>
+        <v>322.8285183857192</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>342.2987237128249</v>
+        <v>342.2987237128252</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>362.9110546823131</v>
+        <v>362.9110546823135</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>384.6044413446236</v>
+        <v>384.6044413446241</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>407.3155434909061</v>
+        <v>407.3155434909066</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>431.3517658449545</v>
+        <v>431.351765844955</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>456.5274980662524</v>
+        <v>456.527498066253</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>482.6547776336109</v>
+        <v>482.6547776336114</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>509.8334607983726</v>
+        <v>509.833460798373</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>537.8853814797804</v>
+        <v>537.8853814797809</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>566.6820226940119</v>
+        <v>566.6820226940124</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>596.0579089275222</v>
+        <v>596.0579089275227</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>625.8550304374809</v>
+        <v>625.8550304374814</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>655.9273822945767</v>
+        <v>655.9273822945773</v>
       </c>
       <c r="S36" s="1" t="inlineStr"/>
       <c r="T36" s="1" t="inlineStr"/>
@@ -2609,16 +2609,16 @@
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>1.175559285399185</v>
+        <v>1.175559285399187</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.184392581065557</v>
+        <v>1.184392581065558</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1.190466807397668</v>
+        <v>1.190466807397669</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.194197746429839</v>
+        <v>1.19419774642984</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>1.195933914513322</v>
@@ -2627,22 +2627,22 @@
         <v>1.195957963176637</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.196676761946249</v>
+        <v>1.196676761946248</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>1.195913228385148</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1.193833517036833</v>
+        <v>1.193833517036832</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.190526417465458</v>
+        <v>1.190526417465457</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.186041124922238</v>
+        <v>1.186041124922237</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>1.180456619086574</v>
+        <v>1.180456619086575</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>1.173839258755496</v>
@@ -2651,7 +2651,7 @@
         <v>1.166240954689562</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>1.157708941969023</v>
+        <v>1.157708941969024</v>
       </c>
       <c r="S38" s="1" t="inlineStr"/>
       <c r="T38" s="1" t="inlineStr"/>
@@ -2683,49 +2683,49 @@
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>117900.2252355229</v>
+        <v>117900.225235523</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>139640.1520749114</v>
+        <v>139640.1520749118</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>166236.9660251446</v>
+        <v>166236.9660251453</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>198519.8102005615</v>
+        <v>198519.8102005624</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>237416.5737215993</v>
+        <v>237416.5737216003</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>283940.2419324598</v>
+        <v>283940.241932461</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>339784.6893019705</v>
+        <v>339784.6893019718</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>406353.0047389641</v>
+        <v>406353.0047389656</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>485117.8368060024</v>
+        <v>485117.8368060038</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>577545.6003012427</v>
+        <v>577545.6003012438</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>684992.8334751748</v>
+        <v>684992.8334751757</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>808604.3243026375</v>
+        <v>808604.324302639</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>949171.5006658965</v>
+        <v>949171.5006658983</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1106962.677100719</v>
+        <v>1106962.677100721</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>1281540.58970547</v>
+        <v>1281540.589705474</v>
       </c>
       <c r="S39" s="1" t="inlineStr"/>
       <c r="T39" s="1" t="inlineStr"/>
@@ -2807,43 +2807,43 @@
         <v>319.603501788464</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>328.9675372967836</v>
+        <v>328.9675372967838</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>338.592166869569</v>
+        <v>338.5921668695692</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>348.5283165323537</v>
+        <v>348.5283165323539</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>358.7074454835424</v>
+        <v>358.7074454835426</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>369.2256907351672</v>
+        <v>369.2256907351675</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>379.8676268829587</v>
+        <v>379.8676268829589</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>390.5458915815844</v>
+        <v>390.5458915815846</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>401.5285631993603</v>
+        <v>401.5285631993605</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>412.525463795994</v>
+        <v>412.5254637959942</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>423.5380060530449</v>
+        <v>423.538006053045</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>434.4915407893902</v>
+        <v>434.4915407893904</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>445.3601216692393</v>
+        <v>445.3601216692394</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>456.1337985130332</v>
+        <v>456.1337985130334</v>
       </c>
       <c r="S41" s="1" t="inlineStr"/>
       <c r="T41" s="1" t="inlineStr"/>
@@ -2875,49 +2875,49 @@
       </c>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>319.629946112995</v>
+        <v>319.6299461129951</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>328.9752254240867</v>
+        <v>328.9752254240869</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>338.7425379783234</v>
+        <v>338.7425379783236</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>348.637714248565</v>
+        <v>348.6377142485653</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>358.7939549645347</v>
+        <v>358.7939549645349</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>369.1464832150569</v>
+        <v>369.1464832150572</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>379.9637892086837</v>
+        <v>379.963789208684</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>390.7958690278944</v>
+        <v>390.7958690278946</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>401.5659749087814</v>
+        <v>401.5659749087816</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>412.6789411929174</v>
+        <v>412.6789411929175</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>423.7224398001781</v>
+        <v>423.7224398001782</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>434.7276211997423</v>
+        <v>434.7276211997425</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>445.6109305287287</v>
+        <v>445.6109305287289</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>456.356218893945</v>
+        <v>456.3562188939453</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>466.9638497108409</v>
+        <v>466.963849710841</v>
       </c>
       <c r="S42" s="1" t="inlineStr"/>
       <c r="T42" s="1" t="inlineStr"/>
@@ -3023,49 +3023,49 @@
       </c>
       <c r="C44" s="1" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>0.2675658145409686</v>
+        <v>0.2675658145409672</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.2627510762416373</v>
+        <v>0.2627510762416364</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.2591274840795847</v>
+        <v>0.2591274840795844</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.2565767994012265</v>
+        <v>0.256576799401226</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.2550220951838037</v>
+        <v>0.2550220951838035</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.2543930169194235</v>
+        <v>0.254393016919423</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.2546621015587227</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.2558078397057247</v>
+        <v>0.2558078397057248</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.2578470068353892</v>
+        <v>0.2578470068353897</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.2608045797416072</v>
+        <v>0.2608045797416076</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2647254322067377</v>
+        <v>0.2647254322067381</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.2696810959896802</v>
+        <v>0.2696810959896801</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.2757469847403647</v>
+        <v>0.2757469847403645</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.2830232632486964</v>
+        <v>0.2830232632486962</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>0.2916156103246137</v>
+        <v>0.2916156103246133</v>
       </c>
       <c r="S44" s="1" t="inlineStr"/>
       <c r="T44" s="1" t="inlineStr"/>
@@ -3097,13 +3097,13 @@
       </c>
       <c r="C45" s="1" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>1.180296158977292</v>
+        <v>1.180296158977294</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1.175262487903346</v>
+        <v>1.175262487903347</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1.168251369555616</v>
+        <v>1.168251369555617</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>1.15925817796077</v>
@@ -3112,7 +3112,7 @@
         <v>1.148224245120433</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.13508172383252</v>
+        <v>1.135081723832521</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.119697021419855</v>
@@ -3121,10 +3121,10 @@
         <v>1.101922316939652</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.081544540058968</v>
+        <v>1.081544540058967</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.05833206210163</v>
+        <v>1.058332062101629</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>1.032020278583349</v>
@@ -3133,13 +3133,13 @@
         <v>1.0023075858643</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.9689068762009185</v>
+        <v>0.9689068762009189</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.9315321714560331</v>
+        <v>0.9315321714560333</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.8899613152251311</v>
+        <v>0.8899613152251319</v>
       </c>
       <c r="S45" s="1" t="inlineStr"/>
       <c r="T45" s="1" t="inlineStr"/>
@@ -3245,28 +3245,28 @@
       </c>
       <c r="C47" s="1" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>0.6934155588636791</v>
+        <v>0.6934155588636786</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6540821830258048</v>
+        <v>0.6540821830258043</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.6163656247447922</v>
+        <v>0.6163656247447916</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5807090801674251</v>
+        <v>0.5807090801674247</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.5469419177899001</v>
+        <v>0.5469419177899</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.5151000967419065</v>
+        <v>0.5151000967419059</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4849868200355705</v>
+        <v>0.4849868200355701</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.4568311988725236</v>
+        <v>0.4568311988725234</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0.4306488534763115</v>
@@ -3275,19 +3275,19 @@
         <v>0.406081111352707</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3834018709211738</v>
+        <v>0.3834018709211737</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0.3625645893983592</v>
+        <v>0.3625645893983591</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>0.3436040103689347</v>
+        <v>0.3436040103689345</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0.3265300858864763</v>
+        <v>0.3265300858864761</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0.3113594601711941</v>
+        <v>0.3113594601711937</v>
       </c>
       <c r="S47" s="1" t="inlineStr"/>
       <c r="T47" s="1" t="inlineStr"/>
@@ -3319,49 +3319,49 @@
       </c>
       <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>0.8876763917513484</v>
+        <v>0.8876763917513479</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.8575883429430604</v>
+        <v>0.8575883429430602</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.8256309230709437</v>
+        <v>0.8256309230709432</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.7928351150508233</v>
+        <v>0.792835115050823</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>0.7594460282445432</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.7259722051918993</v>
+        <v>0.7259722051918986</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6925025368812674</v>
+        <v>0.6925025368812668</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.6599140794268062</v>
+        <v>0.6599140794268059</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0.6285499206988452</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.5979933931802333</v>
+        <v>0.5979933931802336</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.5690608038601747</v>
+        <v>0.5690608038601745</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.5418524390379528</v>
+        <v>0.5418524390379525</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.5166152590801675</v>
+        <v>0.5166152590801671</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>0.4935020512702951</v>
+        <v>0.4935020512702948</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>0.4726509790396709</v>
+        <v>0.4726509790396704</v>
       </c>
       <c r="S48" s="1" t="inlineStr"/>
       <c r="T48" s="1" t="inlineStr"/>
@@ -3393,94 +3393,94 @@
       </c>
       <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>0.3009117955899138</v>
+        <v>0.3009117955899137</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.2648629250939623</v>
+        <v>0.2648629250939619</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.2730956874847147</v>
+        <v>0.2730956874847144</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.232177273821087</v>
+        <v>0.2321772738210864</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.2472564702336293</v>
+        <v>0.2472564702336288</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.2372396826699456</v>
+        <v>0.2372396826699451</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2235805246851127</v>
+        <v>0.2235805246851119</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.2016098886118487</v>
+        <v>0.201609888611848</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.2022386842964319</v>
+        <v>0.2022386842964311</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.2155627758643922</v>
+        <v>0.2155627758643918</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1832115428853446</v>
+        <v>0.183211542885344</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0.2075827569894816</v>
+        <v>0.2075827569894811</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>0.1664820183336858</v>
+        <v>0.1664820183336853</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>0.194258776042587</v>
+        <v>0.1942587760425863</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>0.1515651451617463</v>
+        <v>0.1515651451617459</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>0.1761324255823544</v>
+        <v>0.1761324255823537</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>0.1383445382292229</v>
+        <v>0.1383445382292226</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>0.1791411554826508</v>
+        <v>0.1791411554826503</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>0.1268426587043471</v>
+        <v>0.1268426587043468</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>0.193041918950649</v>
+        <v>0.1930419189506488</v>
       </c>
       <c r="X49" s="2" t="n">
-        <v>0.1168392170471884</v>
+        <v>0.1168392170471883</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>0.1655373817729619</v>
+        <v>0.1655373817729615</v>
       </c>
       <c r="Z49" s="2" t="n">
         <v>0.1082366211495665</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>0.1905493286517205</v>
+        <v>0.1905493286517199</v>
       </c>
       <c r="AB49" s="2" t="n">
-        <v>0.1009196617433606</v>
+        <v>0.1009196617433605</v>
       </c>
       <c r="AC49" s="2" t="n">
-        <v>0.1544420115480235</v>
+        <v>0.154442011548023</v>
       </c>
       <c r="AD49" s="2" t="n">
-        <v>0.09480342326792218</v>
+        <v>0.09480342326792209</v>
       </c>
       <c r="AE49" s="2" t="n">
-        <v>0.1838299604930433</v>
+        <v>0.1838299604930427</v>
       </c>
       <c r="AF49" s="2" t="n">
-        <v>0.08982417564428935</v>
+        <v>0.08982417564428928</v>
       </c>
       <c r="AG49" s="2" t="n">
-        <v>0.1451057510225273</v>
+        <v>0.145105751022527</v>
       </c>
       <c r="AH49" s="1" t="inlineStr"/>
     </row>
@@ -3645,31 +3645,31 @@
       </c>
       <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>0.6815640881547563</v>
+        <v>0.6815640881547557</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.642438871795643</v>
+        <v>0.6424388717956422</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.6051637032899576</v>
+        <v>0.6051637032899572</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.5701804384723499</v>
+        <v>0.5701804384723494</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.5371373050910845</v>
+        <v>0.5371373050910843</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.5060395290299008</v>
+        <v>0.5060395290299002</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4764647692665556</v>
+        <v>0.4764647692665553</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.4489409600353256</v>
+        <v>0.4489409600353254</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.4234377925643552</v>
+        <v>0.4234377925643551</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>0.3994552024495294</v>
@@ -3678,16 +3678,16 @@
         <v>0.377376350608807</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>0.3571179616943223</v>
+        <v>0.3571179616943221</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>0.3387153432306435</v>
+        <v>0.3387153432306432</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>0.3221674888138325</v>
+        <v>0.3221674888138323</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>0.3074837820224099</v>
+        <v>0.3074837820224096</v>
       </c>
       <c r="S52" s="1" t="inlineStr"/>
       <c r="T52" s="1" t="inlineStr"/>
@@ -3719,49 +3719,49 @@
       </c>
       <c r="C53" s="1" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>0.8789593194535794</v>
+        <v>0.8789593194535787</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.8480398486022682</v>
+        <v>0.8480398486022673</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.8155700186744087</v>
+        <v>0.8155700186744084</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.782636203732417</v>
+        <v>0.7826362037324166</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0.7493196190945572</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.7160894723034211</v>
+        <v>0.7160894723034205</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6827589393731028</v>
+        <v>0.6827589393731023</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.6505241801773038</v>
+        <v>0.6505241801773035</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.6196698573783065</v>
+        <v>0.6196698573783063</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.5895882985276618</v>
+        <v>0.589588298527662</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0.5612209018416938</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>0.5346100910596384</v>
+        <v>0.5346100910596382</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>0.5099932447711192</v>
+        <v>0.509993244771119</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>0.4874990159044001</v>
+        <v>0.4874990159043998</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>0.4672470827390187</v>
+        <v>0.4672470827390181</v>
       </c>
       <c r="S53" s="1" t="inlineStr"/>
       <c r="T53" s="1" t="inlineStr"/>
@@ -3793,49 +3793,49 @@
       </c>
       <c r="C54" s="1" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>0.2659001663083078</v>
+        <v>0.2659001663083074</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.2327768388130431</v>
+        <v>0.2327768388130427</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.2391326866004641</v>
+        <v>0.2391326866004636</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.2027980908073383</v>
+        <v>0.2027980908073377</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.2157135089863433</v>
+        <v>0.2157135089863429</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.2069581189015046</v>
+        <v>0.2069581189015043</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1950120220359981</v>
+        <v>0.1950120220359975</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.1759356260449672</v>
+        <v>0.1759356260449667</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.1766789063324201</v>
+        <v>0.1766789063324196</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.1887461596048379</v>
+        <v>0.1887461596048377</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1608824320227261</v>
+        <v>0.1608824320227256</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>0.1829405462744706</v>
+        <v>0.18294054627447</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>0.1473452085749868</v>
+        <v>0.1473452085749864</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>0.1727826874553519</v>
+        <v>0.1727826874553513</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>0.1355766574085735</v>
+        <v>0.1355766574085731</v>
       </c>
       <c r="S54" s="1" t="inlineStr"/>
       <c r="T54" s="1" t="inlineStr"/>
@@ -3867,49 +3867,49 @@
       </c>
       <c r="C55" s="1" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>0.5191274203591439</v>
+        <v>0.5191274203591448</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.6004106060513515</v>
+        <v>0.6004106060513525</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.5856889058926846</v>
+        <v>0.5856889058926859</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.6654723280821587</v>
+        <v>0.6654723280821601</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.6382561634668539</v>
+        <v>0.6382561634668547</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.6568291915418998</v>
+        <v>0.6568291915419006</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6813545791971686</v>
+        <v>0.6813545791971697</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.7187854947845653</v>
+        <v>0.7187854947845663</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.717363628734079</v>
+        <v>0.71736362873408</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.693871924399209</v>
+        <v>0.6938719243992092</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.7469994523764414</v>
+        <v>0.7469994523764423</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>0.7052715727899114</v>
+        <v>0.7052715727899125</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>0.7714913835044298</v>
+        <v>0.7714913835044306</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>0.7247859312576563</v>
+        <v>0.7247859312576574</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>0.7921683279402482</v>
+        <v>0.7921683279402488</v>
       </c>
       <c r="S55" s="1" t="inlineStr"/>
       <c r="T55" s="1" t="inlineStr"/>
@@ -3941,94 +3941,94 @@
       </c>
       <c r="C56" s="1" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>0.7967098840132271</v>
+        <v>0.7967098840132273</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.7976035632489641</v>
+        <v>0.7976035632489644</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.8247705425931964</v>
+        <v>0.8247705425931967</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.8252696768163554</v>
+        <v>0.8252696768163561</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.8194606441086021</v>
+        <v>0.8194606441086025</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.8210457168908978</v>
+        <v>0.8210457168908981</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.849368418132876</v>
+        <v>0.8493684181328766</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.8503286904884024</v>
+        <v>0.850328690488403</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.8388596218091044</v>
+        <v>0.8388596218091047</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.8389830269000562</v>
+        <v>0.8389830269000567</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.8459978093534243</v>
+        <v>0.8459978093534246</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>0.8454905441619814</v>
+        <v>0.8454905441619818</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>0.8556412982649185</v>
+        <v>0.8556412982649191</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>0.8562457162021042</v>
+        <v>0.8562457162021047</v>
       </c>
       <c r="R56" s="2" t="n">
-        <v>0.8708193232561771</v>
+        <v>0.8708193232561774</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>0.8706640915817581</v>
+        <v>0.8706640915817586</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>0.8702328929173286</v>
+        <v>0.8702328929173291</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>0.8682874081197905</v>
+        <v>0.868287408119791</v>
       </c>
       <c r="V56" s="2" t="n">
         <v>0.8606562169267883</v>
       </c>
       <c r="W56" s="2" t="n">
-        <v>0.8572212435630236</v>
+        <v>0.8572212435630239</v>
       </c>
       <c r="X56" s="2" t="n">
-        <v>0.8826120840580826</v>
+        <v>0.8826120840580829</v>
       </c>
       <c r="Y56" s="2" t="n">
-        <v>0.8789822673133694</v>
+        <v>0.8789822673133696</v>
       </c>
       <c r="Z56" s="2" t="n">
-        <v>0.8652768318248083</v>
+        <v>0.8652768318248087</v>
       </c>
       <c r="AA56" s="2" t="n">
-        <v>0.8592160399483763</v>
+        <v>0.8592160399483768</v>
       </c>
       <c r="AB56" s="2" t="n">
-        <v>0.8930842498951538</v>
+        <v>0.8930842498951542</v>
       </c>
       <c r="AC56" s="2" t="n">
-        <v>0.8876096916751938</v>
+        <v>0.8876096916751942</v>
       </c>
       <c r="AD56" s="2" t="n">
-        <v>0.8733025381129463</v>
+        <v>0.8733025381129468</v>
       </c>
       <c r="AE56" s="2" t="n">
-        <v>0.864570559988337</v>
+        <v>0.8645705599883374</v>
       </c>
       <c r="AF56" s="2" t="n">
-        <v>0.9020894245560273</v>
+        <v>0.9020894245560275</v>
       </c>
       <c r="AG56" s="2" t="n">
-        <v>0.8948048417872086</v>
+        <v>0.8948048417872089</v>
       </c>
       <c r="AH56" s="1" t="inlineStr"/>
     </row>
@@ -4045,49 +4045,49 @@
       </c>
       <c r="C57" s="1" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>0.2739314988170215</v>
+        <v>0.2739314988170207</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.2639258373816489</v>
+        <v>0.2639258373816488</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.2721134499656994</v>
+        <v>0.2721134499656992</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.2629741747287038</v>
+        <v>0.2629741747287041</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.2497905509103288</v>
+        <v>0.2497905509103286</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.2420184919558131</v>
+        <v>0.2420184919558135</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2535500919438118</v>
+        <v>0.2535500919438122</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.2463663176446679</v>
+        <v>0.2463663176446689</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.2306772554049352</v>
+        <v>0.2306772554049358</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.2238056430199334</v>
+        <v>0.2238056430199341</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2227026707430972</v>
+        <v>0.2227026707430973</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>0.2169025529658915</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>0.2200322159073712</v>
+        <v>0.2200322159073714</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>0.2172599586722597</v>
+        <v>0.2172599586722595</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>0.2249084255862191</v>
+        <v>0.2249084255862184</v>
       </c>
       <c r="S57" s="1" t="inlineStr"/>
       <c r="T57" s="1" t="inlineStr"/>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>1.164218001918405</v>
+        <v>1.164218001918406</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1.165574311355616</v>
@@ -4134,34 +4134,34 @@
         <v>1.146148191487569</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1.143500279041414</v>
+        <v>1.143500279041413</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.109859093426275</v>
+        <v>1.109859093426274</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.104603195853015</v>
+        <v>1.104603195853014</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1.113412408516754</v>
+        <v>1.113412408516752</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.107253505865092</v>
+        <v>1.10725350586509</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.089851050596934</v>
+        <v>1.089851050596933</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>1.079971800355373</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1.051477615092535</v>
+        <v>1.051477615092534</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>1.032634571544535</v>
+        <v>1.032634571544536</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>0.9904415988404255</v>
+        <v>0.9904415988404269</v>
       </c>
       <c r="S58" s="1" t="inlineStr"/>
       <c r="T58" s="1" t="inlineStr"/>
@@ -4193,49 +4193,49 @@
       </c>
       <c r="C59" s="1" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>0.6861940960968426</v>
+        <v>0.6861940960968421</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.6450785683954093</v>
+        <v>0.6450785683954089</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.6123766740454043</v>
+        <v>0.612376674045404</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.5749142809948463</v>
+        <v>0.574914280994846</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.5376403617043304</v>
+        <v>0.53764036170433</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.504081763429316</v>
+        <v>0.5040817634293158</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4787695282649448</v>
+        <v>0.4787695282649447</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.4483337348032017</v>
+        <v>0.4483337348032018</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.416582216268712</v>
+        <v>0.4165822162687121</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.3892127811341328</v>
+        <v>0.3892127811341329</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3653637975163816</v>
+        <v>0.3653637975163815</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.3412333199614154</v>
+        <v>0.3412333199614153</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>0.3215913875915704</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0.3011121830385978</v>
+        <v>0.3011121830385975</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0.2857091462281143</v>
+        <v>0.2857091462281139</v>
       </c>
       <c r="S59" s="1" t="inlineStr"/>
       <c r="T59" s="1" t="inlineStr"/>
@@ -4267,49 +4267,49 @@
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>0.2648629250939623</v>
+        <v>0.2648629250939619</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.232177273821087</v>
+        <v>0.2321772738210864</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.2372396826699456</v>
+        <v>0.2372396826699451</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.2016098886118487</v>
+        <v>0.201609888611848</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.2155627758643922</v>
+        <v>0.2155627758643918</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.2075827569894816</v>
+        <v>0.2075827569894811</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.194258776042587</v>
+        <v>0.1942587760425863</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.1761324255823544</v>
+        <v>0.1761324255823537</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.1791411554826508</v>
+        <v>0.1791411554826503</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.193041918950649</v>
+        <v>0.1930419189506488</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1655373817729619</v>
+        <v>0.1655373817729615</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>0.1905493286517205</v>
+        <v>0.1905493286517199</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>0.1544420115480235</v>
+        <v>0.154442011548023</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>0.1838299604930433</v>
+        <v>0.1838299604930427</v>
       </c>
       <c r="R60" s="2" t="n">
-        <v>0.1451057510225273</v>
+        <v>0.145105751022527</v>
       </c>
       <c r="S60" s="1" t="inlineStr"/>
       <c r="T60" s="1" t="inlineStr"/>
@@ -4385,49 +4385,49 @@
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="2" t="n">
-        <v>0.5218648179508643</v>
+        <v>0.5218648179508654</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.6017807565427327</v>
+        <v>0.6017807565427342</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.5901119711120733</v>
+        <v>0.5901119711120744</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.6679204771044548</v>
+        <v>0.6679204771044562</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.6385804873723916</v>
+        <v>0.6385804873723925</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.6555215637449671</v>
+        <v>0.6555215637449681</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6828714762156262</v>
+        <v>0.6828714762156276</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.7184092988956754</v>
+        <v>0.7184092988956766</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.7126331778683669</v>
+        <v>0.7126331778683679</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.6853149063251679</v>
+        <v>0.6853149063251682</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.7383899054718333</v>
+        <v>0.738389905471834</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>0.6902929860639897</v>
+        <v>0.6902929860639909</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>0.7587502418526567</v>
+        <v>0.7587502418526577</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>0.7035371393161082</v>
+        <v>0.7035371393161094</v>
       </c>
       <c r="R62" s="2" t="n">
-        <v>0.7754685098517303</v>
+        <v>0.7754685098517308</v>
       </c>
       <c r="S62" s="1" t="inlineStr"/>
       <c r="T62" s="1" t="inlineStr"/>
@@ -4459,49 +4459,49 @@
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="2" t="n">
-        <v>0.7832088103774537</v>
+        <v>0.7832088103774539</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.7886811408245795</v>
+        <v>0.7886811408245797</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.8076095676414661</v>
+        <v>0.8076095676414663</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.8135107407433668</v>
+        <v>0.8135107407433673</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.8165517185977313</v>
+        <v>0.8165517185977316</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.8235709467581545</v>
+        <v>0.8235709467581546</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8442276666399686</v>
+        <v>0.8442276666399688</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.8514595684023596</v>
+        <v>0.8514595684023598</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.852721210245589</v>
+        <v>0.8527212102455892</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.8600118548181679</v>
+        <v>0.8600118548181681</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.8709696855721069</v>
+        <v>0.870969685572107</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>0.8783771244285804</v>
+        <v>0.8783771244285805</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>0.8913137603780317</v>
+        <v>0.891313760378032</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>0.8996674036439352</v>
+        <v>0.8996674036439354</v>
       </c>
       <c r="R63" s="2" t="n">
-        <v>0.9151862426021149</v>
+        <v>0.9151862426021151</v>
       </c>
       <c r="S63" s="1" t="inlineStr"/>
       <c r="T63" s="1" t="inlineStr"/>
@@ -4533,49 +4533,49 @@
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="2" t="n">
-        <v>0.4934859227055411</v>
+        <v>0.4934859227055423</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.5111586870597318</v>
+        <v>0.5111586870597326</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.5200310142359447</v>
+        <v>0.5200310142359449</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.5372947429511727</v>
+        <v>0.5372947429511731</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.5566306390224987</v>
+        <v>0.5566306390224985</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0.5734561135951178</v>
+        <v>0.5734561135951184</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5808660783659977</v>
+        <v>0.5808660783659974</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.597575231761914</v>
+        <v>0.5975752317619138</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.6186312241541631</v>
+        <v>0.6186312241541623</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.6354019849594422</v>
+        <v>0.6354019849594417</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.6493139478162154</v>
+        <v>0.649313947816215</v>
       </c>
       <c r="O64" s="2" t="n">
         <v>0.6656035643657155</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.6773033557616863</v>
+        <v>0.6773033557616862</v>
       </c>
       <c r="Q64" s="2" t="n">
         <v>0.6919233475730167</v>
       </c>
       <c r="R64" s="2" t="n">
-        <v>0.7003182082608708</v>
+        <v>0.700318208260871</v>
       </c>
       <c r="S64" s="1" t="inlineStr"/>
       <c r="T64" s="1" t="inlineStr"/>
@@ -4607,22 +4607,22 @@
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="2" t="n">
-        <v>0.9130337357818012</v>
+        <v>0.9130337357818</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.8830355266498343</v>
+        <v>0.8830355266498334</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.8530645253444218</v>
+        <v>0.8530645253444216</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.8230510799514995</v>
+        <v>0.8230510799514991</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.7929681334991679</v>
+        <v>0.7929681334991677</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0.7627977092904867</v>
+        <v>0.7627977092904863</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7325616461288711</v>
@@ -4631,25 +4631,25 @@
         <v>0.7022863254977531</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.6720276223556494</v>
+        <v>0.6720276223556498</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6418422361217931</v>
+        <v>0.6418422361217935</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6117946368585556</v>
+        <v>0.611794636858556</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>0.5819584578441279</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>0.5523963652145252</v>
+        <v>0.552396365214525</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0.5231726932408488</v>
+        <v>0.5231726932408487</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.494337429249565</v>
+        <v>0.4943374292495647</v>
       </c>
       <c r="S65" s="1" t="inlineStr"/>
       <c r="T65" s="1" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
       </c>
       <c r="C67" s="1" t="inlineStr"/>
       <c r="D67" s="2" t="n">
-        <v>1.147520773572786</v>
+        <v>1.147520773572787</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1.151290553099862</v>
+        <v>1.151290553099863</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>1.124785841940117</v>
@@ -4773,25 +4773,25 @@
         <v>1.136306121063523</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.10054037319311</v>
+        <v>1.100540373193109</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.098769043512219</v>
+        <v>1.098769043512218</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1.114139267470737</v>
+        <v>1.114139267470735</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.112809546850304</v>
+        <v>1.112809546850303</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.099369441780514</v>
+        <v>1.099369441780513</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>1.096048112145915</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>1.072319242131117</v>
+        <v>1.072319242131116</v>
       </c>
       <c r="Q67" s="2" t="n">
         <v>1.061872941002132</v>
@@ -4829,49 +4829,49 @@
       </c>
       <c r="C68" s="1" t="inlineStr"/>
       <c r="D68" s="2" t="n">
-        <v>0.9162832529809215</v>
+        <v>0.9162832529809204</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.8831215817976051</v>
+        <v>0.8831215817976044</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.8578684810318051</v>
+        <v>0.8578684810318049</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8241335857655185</v>
+        <v>0.8241335857655183</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.7882290147990376</v>
+        <v>0.7882290147990377</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0.7544006623721049</v>
+        <v>0.7544006623721045</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7283796035685758</v>
+        <v>0.7283796035685761</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.6940733226829661</v>
+        <v>0.6940733226829662</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.6563128317182521</v>
+        <v>0.6563128317182526</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.6221138840720148</v>
+        <v>0.6221138840720153</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.5900743963413215</v>
+        <v>0.5900743963413219</v>
       </c>
       <c r="O68" s="2" t="n">
         <v>0.5564262703673644</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.5259476469710294</v>
+        <v>0.5259476469710295</v>
       </c>
       <c r="Q68" s="2" t="n">
         <v>0.4936758332529367</v>
       </c>
       <c r="R68" s="2" t="n">
-        <v>0.4651883754407929</v>
+        <v>0.4651883754407928</v>
       </c>
       <c r="S68" s="1" t="inlineStr"/>
       <c r="T68" s="1" t="inlineStr"/>
@@ -4903,49 +4903,49 @@
       </c>
       <c r="C69" s="1" t="inlineStr"/>
       <c r="D69" s="2" t="n">
-        <v>0.2344870377909849</v>
+        <v>0.2344870377909872</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.2682550264500275</v>
+        <v>0.2682550264500293</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.2717213165956951</v>
+        <v>0.2717213165956953</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.3037042944369724</v>
+        <v>0.3037042944369727</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.3431314051008222</v>
+        <v>0.343131405100822</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.3735084117730358</v>
+        <v>0.3735084117730372</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.367978727064239</v>
+        <v>0.3679787270642381</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.396482718014466</v>
+        <v>0.3964827180144653</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.4421116451150875</v>
+        <v>0.4421116451150853</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.4709673107285107</v>
+        <v>0.4709673107285091</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4875748049219588</v>
+        <v>0.4875748049219574</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.5140896543017872</v>
+        <v>0.514089654301787</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.5199228769165916</v>
+        <v>0.5199228769165911</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.5387002477612836</v>
+        <v>0.5387002477612832</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.5277913915153327</v>
+        <v>0.5277913915153333</v>
       </c>
       <c r="S69" s="1" t="inlineStr"/>
       <c r="T69" s="1" t="inlineStr"/>
@@ -4977,49 +4977,49 @@
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="2" t="n">
-        <v>0.247934748937483</v>
+        <v>0.2479347489374852</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.2824527295580105</v>
+        <v>0.2824527295580115</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.2835617236326664</v>
+        <v>0.2835617236326669</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.3166492002702097</v>
+        <v>0.3166492002702095</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.357919176688531</v>
+        <v>0.3579191766885313</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0.3890996166693088</v>
+        <v>0.3890996166693086</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3814794898576991</v>
+        <v>0.3814794898576981</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.4105298731700493</v>
+        <v>0.4105298731700476</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.4570995767985016</v>
+        <v>0.4570995767984999</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.4851396217930768</v>
+        <v>0.485139621793075</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.4997766542556121</v>
+        <v>0.4997766542556116</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>0.523545529988009</v>
+        <v>0.5235455299880087</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.5255299681215058</v>
+        <v>0.525529968121505</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0.5389587382915986</v>
+        <v>0.538958738291599</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0.5252532233996325</v>
+        <v>0.5252532233996341</v>
       </c>
       <c r="S70" s="1" t="inlineStr"/>
       <c r="T70" s="1" t="inlineStr"/>
@@ -5051,22 +5051,22 @@
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="2" t="n">
-        <v>251.7894146864383</v>
+        <v>251.7894146864385</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>249.6625952542773</v>
+        <v>249.6625952542775</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>247.6528107706312</v>
+        <v>247.6528107706313</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>245.7731838000792</v>
+        <v>245.7731838000793</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>244.0304158041251</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>242.4310417988147</v>
+        <v>242.4310417988148</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>240.972909827971</v>
@@ -5075,25 +5075,25 @@
         <v>239.6524840515102</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>238.4569611637399</v>
+        <v>238.4569611637397</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>237.3706330162412</v>
+        <v>237.3706330162411</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>236.3718770966747</v>
+        <v>236.3718770966746</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>235.4310839272837</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>234.5161748631907</v>
+        <v>234.5161748631908</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>233.5872660970408</v>
       </c>
       <c r="R71" s="2" t="n">
-        <v>232.6016263665795</v>
+        <v>232.6016263665796</v>
       </c>
       <c r="S71" s="1" t="inlineStr"/>
       <c r="T71" s="1" t="inlineStr"/>
@@ -5199,13 +5199,13 @@
       </c>
       <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="2" t="n">
-        <v>248.4956004763466</v>
+        <v>248.4956004763468</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>246.863997661203</v>
+        <v>246.8639976612031</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>243.7343471363886</v>
+        <v>243.7343471363887</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>242.5038477902846</v>
@@ -5214,28 +5214,28 @@
         <v>241.9994310516497</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>241.246708242752</v>
+        <v>241.2467082427522</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>238.610012010142</v>
+        <v>238.6100120101419</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>238.3225257302129</v>
+        <v>238.3225257302128</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>239.370306822362</v>
+        <v>239.3703068223618</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>239.6874045980132</v>
+        <v>239.687404598013</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>239.5552403641066</v>
+        <v>239.5552403641065</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>240.2877167927296</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>240.0725358203821</v>
+        <v>240.072535820382</v>
       </c>
       <c r="Q73" s="2" t="n">
         <v>240.868569262042</v>
@@ -5273,22 +5273,22 @@
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="2" t="n">
-        <v>0.9198717705829681</v>
+        <v>0.9198717705829682</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.9287869370332283</v>
+        <v>0.9287869370332285</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.9367836265928445</v>
+        <v>0.9367836265928446</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9442352943136306</v>
+        <v>0.9442352943136307</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0.9507507177926868</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.9564671714526909</v>
+        <v>0.956467171452691</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.9612908243219992</v>
@@ -5300,7 +5300,7 @@
         <v>0.9698642552393725</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.9732402756794528</v>
+        <v>0.9732402756794529</v>
       </c>
       <c r="N74" s="2" t="n">
         <v>0.9762728760788605</v>
@@ -5315,7 +5315,7 @@
         <v>0.9831711164100618</v>
       </c>
       <c r="R74" s="2" t="n">
-        <v>0.98480792147758</v>
+        <v>0.9848079214775801</v>
       </c>
       <c r="S74" s="1" t="inlineStr"/>
       <c r="T74" s="1" t="inlineStr"/>
@@ -5347,49 +5347,49 @@
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="2" t="n">
-        <v>264.9230699278948</v>
+        <v>264.9230699278949</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>282.9988451990845</v>
+        <v>282.9988451990847</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>302.4204702209685</v>
+        <v>302.4204702209689</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>323.2105361281593</v>
+        <v>323.2105361281597</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>345.0379457341102</v>
+        <v>345.0379457341106</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>367.8615221410345</v>
+        <v>367.861522141035</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>391.5486945615362</v>
+        <v>391.5486945615368</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>416.5899773284209</v>
+        <v>416.5899773284214</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>442.76970190832</v>
+        <v>442.7697019083205</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>469.7390688421405</v>
+        <v>469.7390688421411</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>497.7365790948662</v>
+        <v>497.7365790948666</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>526.5439243217386</v>
+        <v>526.543924321739</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>556.0347271729115</v>
+        <v>556.034727172912</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>586.026919765319</v>
+        <v>586.0269197653195</v>
       </c>
       <c r="R75" s="2" t="n">
-        <v>616.3469916714231</v>
+        <v>616.3469916714238</v>
       </c>
       <c r="S75" s="1" t="inlineStr"/>
       <c r="T75" s="1" t="inlineStr"/>
@@ -5424,46 +5424,46 @@
         <v>298.0389802067385</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>308.0133770756283</v>
+        <v>308.0133770756284</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>318.3997289340273</v>
+        <v>318.3997289340275</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>329.016002642554</v>
+        <v>329.0160026425542</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>339.8375777278104</v>
+        <v>339.8375777278106</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>350.8127955112437</v>
+        <v>350.8127955112439</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>362.008951914945</v>
+        <v>362.0089519149453</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>373.3110988604274</v>
+        <v>373.3110988604276</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>384.6161801202268</v>
+        <v>384.616180120227</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>396.1197363242031</v>
+        <v>396.1197363242033</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>407.6020625368918</v>
+        <v>407.6020625368919</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>419.0490109911946</v>
+        <v>419.0490109911948</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>430.3903903559673</v>
+        <v>430.3903903559675</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>441.596764391697</v>
+        <v>441.5967643916971</v>
       </c>
       <c r="R76" s="2" t="n">
-        <v>452.6557279350682</v>
+        <v>452.6557279350684</v>
       </c>
       <c r="S76" s="1" t="inlineStr"/>
       <c r="T76" s="1" t="inlineStr"/>
@@ -5495,46 +5495,46 @@
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="2" t="n">
-        <v>0.8448204141343573</v>
+        <v>0.8448204141343578</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.8105576375436974</v>
+        <v>0.8105576375436977</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.7778047161024598</v>
+        <v>0.7778047161024594</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7469946197938871</v>
+        <v>0.746994619793887</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.7180795526961379</v>
+        <v>0.7180795526961377</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0.6910553004359976</v>
+        <v>0.6910553004359974</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6656545606214408</v>
+        <v>0.6656545606214403</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.6419645298065751</v>
+        <v>0.6419645298065748</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.6199868166991852</v>
+        <v>0.6199868166991845</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.5992396016894395</v>
+        <v>0.5992396016894388</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5799084421347372</v>
+        <v>0.5799084421347368</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>0.5618223113578253</v>
+        <v>0.561822311357825</v>
       </c>
       <c r="P77" s="2" t="n">
         <v>0.5448917543656749</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>0.5289605471154415</v>
+        <v>0.5289605471154414</v>
       </c>
       <c r="R77" s="2" t="n">
         <v>0.5138598983993092</v>
@@ -5569,46 +5569,46 @@
       </c>
       <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="2" t="n">
-        <v>0.7774478064345662</v>
+        <v>0.7774478064345668</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.7504030047945618</v>
+        <v>0.7504030047945619</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.7195268376715814</v>
+        <v>0.7195268376715812</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.6955754867569743</v>
+        <v>0.6955754867569741</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.6744802349737758</v>
+        <v>0.6744802349737755</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.6535256848219975</v>
+        <v>0.6535256848219972</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6279809255168065</v>
+        <v>0.6279809255168058</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.6098389072613297</v>
+        <v>0.6098389072613294</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.5960921038609824</v>
+        <v>0.5960921038609815</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.5808084219300281</v>
+        <v>0.5808084219300275</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5653588714279039</v>
+        <v>0.5653588714279034</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0.5527316532811835</v>
+        <v>0.5527316532811832</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>0.5387492078247046</v>
+        <v>0.5387492078247043</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>0.5278082324501393</v>
+        <v>0.527808232450139</v>
       </c>
       <c r="R78" s="2" t="n">
         <v>0.5144008896950421</v>
@@ -5643,49 +5643,49 @@
       </c>
       <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="2" t="n">
-        <v>304.6972711556987</v>
+        <v>304.6972711556989</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>322.8285183857189</v>
+        <v>322.8285183857192</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>342.2987237128249</v>
+        <v>342.2987237128252</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>362.9110546823131</v>
+        <v>362.9110546823135</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>384.6044413446236</v>
+        <v>384.6044413446241</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>407.3155434909061</v>
+        <v>407.3155434909066</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>431.3517658449545</v>
+        <v>431.351765844955</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>456.5274980662524</v>
+        <v>456.527498066253</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>482.6547776336109</v>
+        <v>482.6547776336114</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>509.8334607983726</v>
+        <v>509.833460798373</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>537.8853814797804</v>
+        <v>537.8853814797809</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>566.6820226940119</v>
+        <v>566.6820226940124</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>596.0579089275222</v>
+        <v>596.0579089275227</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>625.8550304374809</v>
+        <v>625.8550304374814</v>
       </c>
       <c r="R79" s="2" t="n">
-        <v>655.9273822945767</v>
+        <v>655.9273822945773</v>
       </c>
       <c r="S79" s="1" t="inlineStr"/>
       <c r="T79" s="1" t="inlineStr"/>
@@ -5717,46 +5717,46 @@
       </c>
       <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="2" t="n">
-        <v>0.8992741671325648</v>
+        <v>0.8992741671325647</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.9062688045613386</v>
+        <v>0.9062688045613385</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.9138516918449189</v>
+        <v>0.913851691844919</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>0.9199924968338543</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.9251044624590486</v>
+        <v>0.9251044624590488</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.9299256714249228</v>
+        <v>0.9299256714249229</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9350996624977284</v>
+        <v>0.9350996624977286</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0.9390145624566704</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.942261954794899</v>
+        <v>0.9422619547948993</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0.9452578478540937</v>
+        <v>0.9452578478540938</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.9484076790553084</v>
+        <v>0.9484076790553085</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0.9509953810907157</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>0.9538090691880814</v>
+        <v>0.9538090691880815</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>0.9560295185590798</v>
+        <v>0.9560295185590799</v>
       </c>
       <c r="R80" s="2" t="n">
         <v>0.9585335852388071</v>
@@ -5791,49 +5791,49 @@
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="2" t="n">
-        <v>274.0063847461062</v>
+        <v>274.0063847461063</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>292.5694154357336</v>
+        <v>292.5694154357338</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>312.8102677813214</v>
+        <v>312.8102677813218</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>333.8754473257886</v>
+        <v>333.875447325789</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>355.7992849694808</v>
+        <v>355.7992849694812</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>378.7731802625881</v>
+        <v>378.7731802625887</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>403.3568906594161</v>
+        <v>403.3568906594167</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>428.6859688461204</v>
+        <v>428.6859688461209</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>454.7872342641435</v>
+        <v>454.7872342641442</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>481.9240799182741</v>
+        <v>481.9240799182746</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>510.1346262470178</v>
+        <v>510.1346262470183</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>538.9119861291495</v>
+        <v>538.9119861291499</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>568.5254392963542</v>
+        <v>568.5254392963546</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>598.335883436923</v>
+        <v>598.3358834369237</v>
       </c>
       <c r="R81" s="2" t="n">
-        <v>628.7284254071262</v>
+        <v>628.7284254071268</v>
       </c>
       <c r="S81" s="1" t="inlineStr"/>
       <c r="T81" s="1" t="inlineStr"/>
@@ -5865,49 +5865,49 @@
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="2" t="n">
-        <v>303.1052931312994</v>
+        <v>303.1052931312995</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>313.1783334378803</v>
+        <v>313.1783334378804</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>323.822929373662</v>
+        <v>323.8229293736622</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>334.4001844138083</v>
+        <v>334.4001844138085</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>345.0964607708531</v>
+        <v>345.0964607708532</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>355.9777500844307</v>
+        <v>355.9777500844309</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>367.4270789690838</v>
+        <v>367.4270789690841</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>378.6919977527857</v>
+        <v>378.6919977527859</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>389.8008085136061</v>
+        <v>389.8008085136064</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>401.2245082665477</v>
+        <v>401.2245082665479</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>412.647287964106</v>
+        <v>412.6472879641062</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>423.9419943671659</v>
+        <v>423.9419943671661</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>435.1976674825116</v>
+        <v>435.1976674825117</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>446.2103339824699</v>
+        <v>446.2103339824702</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>457.1796890076138</v>
+        <v>457.1796890076141</v>
       </c>
       <c r="S82" s="1" t="inlineStr"/>
       <c r="T82" s="1" t="inlineStr"/>
@@ -5939,49 +5939,49 @@
       </c>
       <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="2" t="n">
-        <v>0.8198325997847323</v>
+        <v>0.8198325997847329</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.7882537560989005</v>
+        <v>0.7882537560989007</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.7526778527012258</v>
+        <v>0.7526778527012253</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.7251905324615333</v>
+        <v>0.725190532461533</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.7012515587992059</v>
+        <v>0.7012515587992055</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.6777016490090553</v>
+        <v>0.6777016490090552</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6494078027118388</v>
+        <v>0.6494078027118381</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.6293307678653206</v>
+        <v>0.6293307678653201</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.6140836591261372</v>
+        <v>0.6140836591261362</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.5973897398081683</v>
+        <v>0.5973897398081676</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.5805326906327426</v>
+        <v>0.580532690632742</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>0.5667938538417646</v>
+        <v>0.5667938538417644</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>0.551640217212399</v>
+        <v>0.5516402172123986</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>0.5398094820267092</v>
+        <v>0.5398094820267089</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>0.5254096485959114</v>
+        <v>0.5254096485959113</v>
       </c>
       <c r="S83" s="1" t="inlineStr"/>
       <c r="T83" s="1" t="inlineStr"/>
